--- a/Results/Phase 2/Hydrogen/hydrogen climate change results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen climate change results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.906527426681871</v>
+        <v>4.90652742668187</v>
       </c>
       <c r="C2" t="n">
-        <v>4.796154230079236</v>
+        <v>4.796154230079231</v>
       </c>
       <c r="D2" t="n">
-        <v>4.844712523659499</v>
+        <v>4.844712523659493</v>
       </c>
       <c r="E2" t="n">
-        <v>3.716199518160816</v>
+        <v>3.716199518160813</v>
       </c>
       <c r="F2" t="n">
-        <v>4.83272707167562</v>
+        <v>4.832727071675615</v>
       </c>
       <c r="G2" t="n">
-        <v>4.973872608839958</v>
+        <v>4.973872608839954</v>
       </c>
       <c r="H2" t="n">
-        <v>4.906527426681871</v>
+        <v>4.90652742668187</v>
       </c>
       <c r="I2" t="n">
-        <v>4.906527426681871</v>
+        <v>4.90652742668187</v>
       </c>
       <c r="J2" t="n">
-        <v>4.901666310329686</v>
+        <v>4.901666310329683</v>
       </c>
       <c r="K2" t="n">
-        <v>4.906527426681871</v>
+        <v>4.90652742668187</v>
       </c>
       <c r="L2" t="n">
-        <v>4.906527426681871</v>
+        <v>4.90652742668187</v>
       </c>
       <c r="M2" t="n">
-        <v>4.994486088844432</v>
+        <v>4.994486088844427</v>
       </c>
       <c r="N2" t="n">
-        <v>4.898350621990192</v>
+        <v>4.89835062199019</v>
       </c>
       <c r="O2" t="n">
-        <v>4.906527426681871</v>
+        <v>4.90652742668187</v>
       </c>
       <c r="P2" t="n">
-        <v>4.906527426681871</v>
+        <v>4.90652742668187</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.906527426681871</v>
+        <v>4.90652742668187</v>
       </c>
       <c r="R2" t="n">
-        <v>4.906527426681871</v>
+        <v>4.90652742668187</v>
       </c>
       <c r="S2" t="n">
-        <v>4.906527426681871</v>
+        <v>4.90652742668187</v>
       </c>
       <c r="T2" t="n">
-        <v>4.906527426681871</v>
+        <v>4.90652742668187</v>
       </c>
       <c r="U2" t="n">
-        <v>4.906527426681871</v>
+        <v>4.90652742668187</v>
       </c>
       <c r="V2" t="n">
-        <v>5.013294685465062</v>
+        <v>5.013294685465056</v>
       </c>
       <c r="W2" t="n">
-        <v>4.906527426681871</v>
+        <v>4.90652742668187</v>
       </c>
       <c r="X2" t="n">
-        <v>4.906527426681871</v>
+        <v>4.90652742668187</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.906527426681871</v>
+        <v>4.90652742668187</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.865608053533249</v>
+        <v>4.865608053533244</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.906527426681871</v>
+        <v>4.90652742668187</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.906527426681871</v>
+        <v>4.90652742668187</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="C3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="D3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="E3" t="n">
-        <v>9.991362973240959</v>
+        <v>9.991362973240955</v>
       </c>
       <c r="F3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="G3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="H3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="I3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="J3" t="n">
         <v>11.09346538391463</v>
       </c>
       <c r="K3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="L3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="M3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="N3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="O3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="P3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="R3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="S3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="T3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="U3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="V3" t="n">
         <v>11.29315919205548</v>
       </c>
       <c r="W3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="X3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="Y3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.09832705726582</v>
+        <v>11.09832705726581</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35.64858144896244</v>
+        <v>35.64858144896245</v>
       </c>
       <c r="C4" t="n">
         <v>13.26281589895902</v>
       </c>
       <c r="D4" t="n">
-        <v>28.20228037517964</v>
+        <v>28.2022803751796</v>
       </c>
       <c r="E4" t="n">
-        <v>15.64071360141841</v>
+        <v>15.64071360141836</v>
       </c>
       <c r="F4" t="n">
-        <v>25.05122706785686</v>
+        <v>25.05122706785677</v>
       </c>
       <c r="G4" t="n">
-        <v>61.60240182419113</v>
+        <v>61.60240182419103</v>
       </c>
       <c r="H4" t="n">
         <v>44.56022682068973</v>
       </c>
       <c r="I4" t="n">
-        <v>27.45771814973002</v>
+        <v>27.45771814972995</v>
       </c>
       <c r="J4" t="n">
-        <v>43.95591031957332</v>
+        <v>43.9559103195733</v>
       </c>
       <c r="K4" t="n">
-        <v>40.63043561969166</v>
+        <v>40.63043561969168</v>
       </c>
       <c r="L4" t="n">
-        <v>51.28330339976598</v>
+        <v>51.28330339976605</v>
       </c>
       <c r="M4" t="n">
-        <v>74.46065440360745</v>
+        <v>74.46065440360735</v>
       </c>
       <c r="N4" t="n">
-        <v>52.5531596936182</v>
+        <v>52.55315969361815</v>
       </c>
       <c r="O4" t="n">
-        <v>32.21355188555157</v>
+        <v>32.21355188555147</v>
       </c>
       <c r="P4" t="n">
-        <v>36.29031060528008</v>
+        <v>36.29031060528004</v>
       </c>
       <c r="Q4" t="n">
-        <v>31.49474197351817</v>
+        <v>31.49474197351809</v>
       </c>
       <c r="R4" t="n">
-        <v>28.11392378688745</v>
+        <v>28.11392378688747</v>
       </c>
       <c r="S4" t="n">
-        <v>45.89194878741063</v>
+        <v>45.89194878741057</v>
       </c>
       <c r="T4" t="n">
-        <v>37.68852179860561</v>
+        <v>37.68852179860558</v>
       </c>
       <c r="U4" t="n">
-        <v>52.55315969361821</v>
+        <v>52.55315969361811</v>
       </c>
       <c r="V4" t="n">
-        <v>19.07434274692771</v>
+        <v>19.07434274692763</v>
       </c>
       <c r="W4" t="n">
-        <v>46.37222733650852</v>
+        <v>46.37222733650856</v>
       </c>
       <c r="X4" t="n">
-        <v>35.83455192870408</v>
+        <v>35.83455192870407</v>
       </c>
       <c r="Y4" t="n">
-        <v>34.29131224559002</v>
+        <v>34.29131224558991</v>
       </c>
       <c r="Z4" t="n">
-        <v>31.5732307961941</v>
+        <v>31.57323079619402</v>
       </c>
       <c r="AA4" t="n">
-        <v>44.75596210398425</v>
+        <v>44.7559621039842</v>
       </c>
       <c r="AB4" t="n">
-        <v>64.47222305572984</v>
+        <v>64.47222305572973</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.099423472865108</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="C5" t="n">
-        <v>1.099423472865109</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="D5" t="n">
-        <v>1.099423472865109</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="E5" t="n">
-        <v>1.099423472865109</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="F5" t="n">
-        <v>1.099423472865108</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="G5" t="n">
-        <v>1.099423472865109</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="H5" t="n">
-        <v>1.099423472865109</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="I5" t="n">
-        <v>1.099423472865109</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="J5" t="n">
-        <v>1.096954611192572</v>
+        <v>1.096954611192564</v>
       </c>
       <c r="K5" t="n">
-        <v>1.099423472865109</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="L5" t="n">
-        <v>1.099423472865109</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="M5" t="n">
-        <v>1.099423472865109</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="N5" t="n">
-        <v>1.099423472865108</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="O5" t="n">
-        <v>1.099423472865108</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="P5" t="n">
-        <v>1.099423472865108</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.099423472865108</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="R5" t="n">
-        <v>1.099423472865109</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="S5" t="n">
-        <v>1.099423472865109</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="T5" t="n">
-        <v>1.099423472865109</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="U5" t="n">
-        <v>1.076131529755453</v>
+        <v>1.076131529755445</v>
       </c>
       <c r="V5" t="n">
-        <v>1.083273421500143</v>
+        <v>1.083273421500137</v>
       </c>
       <c r="W5" t="n">
-        <v>1.099423472865108</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="X5" t="n">
-        <v>1.099423472865108</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.076131529755453</v>
+        <v>1.076131529755445</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.099423472865109</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.099423472865109</v>
+        <v>1.099423472865101</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.099423472865108</v>
+        <v>1.099423472865101</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.236945480228245</v>
+        <v>1.80338597411646</v>
       </c>
       <c r="C6" t="n">
-        <v>1.803385974116466</v>
+        <v>1.80338597411646</v>
       </c>
       <c r="D6" t="n">
-        <v>1.236945480228245</v>
+        <v>1.236945480228251</v>
       </c>
       <c r="E6" t="n">
-        <v>1.803385974116466</v>
+        <v>1.236945480228251</v>
       </c>
       <c r="F6" t="n">
-        <v>1.236945480228245</v>
+        <v>1.80338597411646</v>
       </c>
       <c r="G6" t="n">
-        <v>1.236945480228245</v>
+        <v>1.80338597411646</v>
       </c>
       <c r="H6" t="n">
-        <v>1.803385974116466</v>
+        <v>1.80338597411646</v>
       </c>
       <c r="I6" t="n">
-        <v>1.803385974116466</v>
+        <v>1.236945480228251</v>
       </c>
       <c r="J6" t="n">
-        <v>1.234476618555682</v>
+        <v>1.800917112443921</v>
       </c>
       <c r="K6" t="n">
-        <v>1.236945480228245</v>
+        <v>1.236945480228251</v>
       </c>
       <c r="L6" t="n">
-        <v>1.803385974116466</v>
+        <v>1.236945480228251</v>
       </c>
       <c r="M6" t="n">
-        <v>1.236945480228245</v>
+        <v>1.236945480228251</v>
       </c>
       <c r="N6" t="n">
-        <v>1.242561530203871</v>
+        <v>1.242561530203865</v>
       </c>
       <c r="O6" t="n">
-        <v>1.833584786202271</v>
+        <v>1.833584786202265</v>
       </c>
       <c r="P6" t="n">
-        <v>1.833589921211383</v>
+        <v>1.833589921211379</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.236945480228245</v>
+        <v>1.236945480228251</v>
       </c>
       <c r="R6" t="n">
-        <v>1.803385974116466</v>
+        <v>1.236945480228251</v>
       </c>
       <c r="S6" t="n">
-        <v>1.803385974116466</v>
+        <v>1.80338597411646</v>
       </c>
       <c r="T6" t="n">
-        <v>1.236945480228245</v>
+        <v>1.236945480228251</v>
       </c>
       <c r="U6" t="n">
-        <v>1.236945480228245</v>
+        <v>1.236945480228251</v>
       </c>
       <c r="V6" t="n">
-        <v>1.7872359227515</v>
+        <v>1.787235922751493</v>
       </c>
       <c r="W6" t="n">
-        <v>1.26602507571781</v>
+        <v>1.833587987831327</v>
       </c>
       <c r="X6" t="n">
-        <v>1.803385974116466</v>
+        <v>1.80338597411646</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.254372053902141</v>
+        <v>1.254372053902166</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.236945480228245</v>
+        <v>1.236945480228251</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.803385974116466</v>
+        <v>1.236945480228251</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.251095167860214</v>
+        <v>1.251095167860211</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
       <c r="C7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
       <c r="D7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
       <c r="E7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
       <c r="F7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
       <c r="G7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
       <c r="H7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
       <c r="I7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
       <c r="J7" t="n">
-        <v>1.746710065732872</v>
+        <v>1.746710065732869</v>
       </c>
       <c r="K7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
       <c r="L7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
       <c r="M7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
       <c r="N7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
       <c r="O7" t="n">
-        <v>1.746999967044207</v>
+        <v>1.746999967044203</v>
       </c>
       <c r="P7" t="n">
-        <v>1.746999967044207</v>
+        <v>1.746999967044203</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
       <c r="R7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
       <c r="S7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
       <c r="T7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
       <c r="U7" t="n">
-        <v>1.747800494933857</v>
+        <v>1.747800494933856</v>
       </c>
       <c r="V7" t="n">
-        <v>1.733028876040447</v>
+        <v>1.733028876040443</v>
       </c>
       <c r="W7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
       <c r="X7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.749178927405409</v>
+        <v>1.749178927405406</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.05400135168943</v>
+        <v>2.054001351689421</v>
       </c>
       <c r="C8" t="n">
-        <v>2.816966684319893</v>
+        <v>2.816966684319879</v>
       </c>
       <c r="D8" t="n">
-        <v>2.816966684319893</v>
+        <v>2.816966684319879</v>
       </c>
       <c r="E8" t="n">
-        <v>2.816966684319893</v>
+        <v>2.410710150881402</v>
       </c>
       <c r="F8" t="n">
-        <v>2.172862433479522</v>
+        <v>2.172862433479511</v>
       </c>
       <c r="G8" t="n">
-        <v>2.816966684319893</v>
+        <v>2.975172516255868</v>
       </c>
       <c r="H8" t="n">
-        <v>2.816966684319893</v>
+        <v>2.816966684319879</v>
       </c>
       <c r="I8" t="n">
-        <v>2.816966684319893</v>
+        <v>2.816966684319879</v>
       </c>
       <c r="J8" t="n">
-        <v>2.814497822647357</v>
+        <v>2.814497822647341</v>
       </c>
       <c r="K8" t="n">
-        <v>2.816966684319893</v>
+        <v>2.816966684319879</v>
       </c>
       <c r="L8" t="n">
-        <v>2.816966684319893</v>
+        <v>2.816966684319879</v>
       </c>
       <c r="M8" t="n">
-        <v>2.816966684319893</v>
+        <v>2.816966684319944</v>
       </c>
       <c r="N8" t="n">
-        <v>2.225540910060874</v>
+        <v>2.225540910060865</v>
       </c>
       <c r="O8" t="n">
-        <v>2.388069847788316</v>
+        <v>2.388069847788309</v>
       </c>
       <c r="P8" t="n">
-        <v>2.348230077933848</v>
+        <v>2.348230077933838</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.90406125015001</v>
+        <v>1.904061250150007</v>
       </c>
       <c r="R8" t="n">
-        <v>2.816966684319893</v>
+        <v>2.816966684319879</v>
       </c>
       <c r="S8" t="n">
-        <v>2.816966684319893</v>
+        <v>2.816966684319879</v>
       </c>
       <c r="T8" t="n">
-        <v>2.816966684319893</v>
+        <v>2.816966684319879</v>
       </c>
       <c r="U8" t="n">
-        <v>2.348060081251712</v>
+        <v>2.445193877760012</v>
       </c>
       <c r="V8" t="n">
-        <v>2.800816632954921</v>
+        <v>2.592970974498643</v>
       </c>
       <c r="W8" t="n">
-        <v>2.817116628282915</v>
+        <v>2.817116628282903</v>
       </c>
       <c r="X8" t="n">
-        <v>1.973988538561574</v>
+        <v>1.973988538561566</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.576627054051876</v>
+        <v>3.576627054051859</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.816966684319893</v>
+        <v>2.039828878977807</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.816966684319893</v>
+        <v>2.816966684319879</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.613947771831938</v>
+        <v>3.613947771831924</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.783284679130603</v>
+        <v>3.7832846791306</v>
       </c>
       <c r="C9" t="n">
-        <v>4.593610006209936</v>
+        <v>4.593610006209929</v>
       </c>
       <c r="D9" t="n">
-        <v>4.593610006209936</v>
+        <v>4.593610006209929</v>
       </c>
       <c r="E9" t="n">
-        <v>4.593610006209936</v>
+        <v>4.406590326944283</v>
       </c>
       <c r="F9" t="n">
-        <v>4.593610006209936</v>
+        <v>2.725588797194693</v>
       </c>
       <c r="G9" t="n">
-        <v>4.593610006209936</v>
+        <v>4.593610137472151</v>
       </c>
       <c r="H9" t="n">
-        <v>4.593610006209936</v>
+        <v>4.593610006209929</v>
       </c>
       <c r="I9" t="n">
-        <v>4.593610006209936</v>
+        <v>4.593610006209929</v>
       </c>
       <c r="J9" t="n">
-        <v>4.591141144537395</v>
+        <v>4.59114114453739</v>
       </c>
       <c r="K9" t="n">
-        <v>4.593610006209936</v>
+        <v>4.593610006209929</v>
       </c>
       <c r="L9" t="n">
-        <v>4.593610006209936</v>
+        <v>4.593610006209929</v>
       </c>
       <c r="M9" t="n">
-        <v>4.593610006209936</v>
+        <v>4.593610006209929</v>
       </c>
       <c r="N9" t="n">
-        <v>4.593610006209936</v>
+        <v>4.593610006209929</v>
       </c>
       <c r="O9" t="n">
-        <v>4.862150933335935</v>
+        <v>4.862150933335928</v>
       </c>
       <c r="P9" t="n">
-        <v>4.92055394905218</v>
+        <v>4.920553949052175</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.593610137472154</v>
+        <v>4.593610137472151</v>
       </c>
       <c r="R9" t="n">
-        <v>4.593610006209936</v>
+        <v>4.593610006209929</v>
       </c>
       <c r="S9" t="n">
-        <v>4.593610006209936</v>
+        <v>4.593610006209929</v>
       </c>
       <c r="T9" t="n">
-        <v>4.593610006209936</v>
+        <v>4.593610006209929</v>
       </c>
       <c r="U9" t="n">
-        <v>4.593610006209936</v>
+        <v>4.593610006209929</v>
       </c>
       <c r="V9" t="n">
-        <v>4.57745995484497</v>
+        <v>5.512557045732454</v>
       </c>
       <c r="W9" t="n">
-        <v>4.593610006209936</v>
+        <v>4.593610006209929</v>
       </c>
       <c r="X9" t="n">
-        <v>4.593610006209936</v>
+        <v>4.593610006209929</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.593610006209936</v>
+        <v>4.593610006209929</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.593610006209936</v>
+        <v>4.105055943043429</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.593610006209936</v>
+        <v>4.593610006209929</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.593610006209936</v>
+        <v>4.593610006209929</v>
       </c>
     </row>
     <row r="10">
@@ -1293,19 +1293,19 @@
         <v>10.33468106463018</v>
       </c>
       <c r="C10" t="n">
-        <v>10.86050757046758</v>
+        <v>10.86050757046757</v>
       </c>
       <c r="D10" t="n">
         <v>10.5763522843661</v>
       </c>
       <c r="E10" t="n">
-        <v>9.693863064367456</v>
+        <v>9.69386306436745</v>
       </c>
       <c r="F10" t="n">
-        <v>10.64876645156914</v>
+        <v>10.64876645156913</v>
       </c>
       <c r="G10" t="n">
-        <v>9.800498568534111</v>
+        <v>9.800498568534106</v>
       </c>
       <c r="H10" t="n">
         <v>10.29840155284059</v>
@@ -1323,16 +1323,16 @@
         <v>10.07046701698014</v>
       </c>
       <c r="M10" t="n">
-        <v>9.704362478869243</v>
+        <v>9.704362478869236</v>
       </c>
       <c r="N10" t="n">
-        <v>10.25862413684042</v>
+        <v>10.25862413684041</v>
       </c>
       <c r="O10" t="n">
         <v>10.39330777006104</v>
       </c>
       <c r="P10" t="n">
-        <v>10.33399132481073</v>
+        <v>10.33399132481072</v>
       </c>
       <c r="Q10" t="n">
         <v>10.49908746944818</v>
@@ -1341,7 +1341,7 @@
         <v>10.59193134350871</v>
       </c>
       <c r="S10" t="n">
-        <v>10.14080262157552</v>
+        <v>10.14080262157551</v>
       </c>
       <c r="T10" t="n">
         <v>10.39678123692269</v>
@@ -1362,13 +1362,13 @@
         <v>10.42515505814729</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.44458677501172</v>
+        <v>10.44458677501171</v>
       </c>
       <c r="AA10" t="n">
         <v>10.21878703881363</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.933852611751478</v>
+        <v>9.933852611751474</v>
       </c>
     </row>
     <row r="11">
@@ -1378,85 +1378,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.559066066437276</v>
+        <v>4.559066066437274</v>
       </c>
       <c r="C11" t="n">
-        <v>4.687945605700302</v>
+        <v>4.687945605700297</v>
       </c>
       <c r="D11" t="n">
-        <v>4.607212338555228</v>
+        <v>4.607212338555223</v>
       </c>
       <c r="E11" t="n">
-        <v>3.580836111547415</v>
+        <v>3.580836111547412</v>
       </c>
       <c r="F11" t="n">
-        <v>4.628175563418989</v>
+        <v>4.628175563418983</v>
       </c>
       <c r="G11" t="n">
-        <v>4.383356510533039</v>
+        <v>4.383356510533035</v>
       </c>
       <c r="H11" t="n">
-        <v>4.542558772957067</v>
+        <v>4.542558772957069</v>
       </c>
       <c r="I11" t="n">
-        <v>4.678471016327386</v>
+        <v>4.678471016327383</v>
       </c>
       <c r="J11" t="n">
-        <v>4.495175991793104</v>
+        <v>4.495175991793101</v>
       </c>
       <c r="K11" t="n">
-        <v>4.557043738758868</v>
+        <v>4.557043738758864</v>
       </c>
       <c r="L11" t="n">
-        <v>4.438847832756295</v>
+        <v>4.438847832756291</v>
       </c>
       <c r="M11" t="n">
-        <v>4.360227763372458</v>
+        <v>4.360227763372455</v>
       </c>
       <c r="N11" t="n">
         <v>4.516283117222202</v>
       </c>
       <c r="O11" t="n">
-        <v>4.585741404240541</v>
+        <v>4.585741404240539</v>
       </c>
       <c r="P11" t="n">
-        <v>4.558752232621353</v>
+        <v>4.558752232621348</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.633871504561588</v>
+        <v>4.633871504561591</v>
       </c>
       <c r="R11" t="n">
         <v>4.676115763135002</v>
       </c>
       <c r="S11" t="n">
-        <v>4.470850756993463</v>
+        <v>4.470850756993462</v>
       </c>
       <c r="T11" t="n">
-        <v>4.587321842731871</v>
+        <v>4.587321842731873</v>
       </c>
       <c r="U11" t="n">
-        <v>4.416880365390351</v>
+        <v>4.416880365390348</v>
       </c>
       <c r="V11" t="n">
-        <v>4.83452524605238</v>
+        <v>4.834525246052373</v>
       </c>
       <c r="W11" t="n">
-        <v>4.488397620220867</v>
+        <v>4.488397620220866</v>
       </c>
       <c r="X11" t="n">
-        <v>4.597714044367494</v>
+        <v>4.59771404436749</v>
       </c>
       <c r="Y11" t="n">
         <v>4.60023202181107</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.568154141760965</v>
+        <v>4.568154141760961</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.506333915358399</v>
+        <v>4.506333915358396</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.376687843012975</v>
+        <v>4.376687843012974</v>
       </c>
     </row>
   </sheetData>
@@ -1625,7 +1625,7 @@
         <v>4.535336752766672</v>
       </c>
       <c r="C2" t="n">
-        <v>4.532061876688453</v>
+        <v>4.532061876688454</v>
       </c>
       <c r="D2" t="n">
         <v>4.550592253934298</v>
@@ -1634,16 +1634,16 @@
         <v>3.534825804951144</v>
       </c>
       <c r="F2" t="n">
-        <v>4.492350811808903</v>
+        <v>4.492350811808904</v>
       </c>
       <c r="G2" t="n">
-        <v>4.568626839601899</v>
+        <v>4.568626839601898</v>
       </c>
       <c r="H2" t="n">
-        <v>4.563713395927696</v>
+        <v>4.563713395927697</v>
       </c>
       <c r="I2" t="n">
-        <v>4.539989820815474</v>
+        <v>4.539989820815473</v>
       </c>
       <c r="J2" t="n">
         <v>4.554400991006646</v>
@@ -1652,40 +1652,40 @@
         <v>4.53806484888571</v>
       </c>
       <c r="L2" t="n">
-        <v>4.446456988453598</v>
+        <v>4.446456988453597</v>
       </c>
       <c r="M2" t="n">
         <v>4.535374848222512</v>
       </c>
       <c r="N2" t="n">
-        <v>4.539947988746332</v>
+        <v>4.53994798874633</v>
       </c>
       <c r="O2" t="n">
-        <v>4.509650502296424</v>
+        <v>4.509650502296425</v>
       </c>
       <c r="P2" t="n">
-        <v>4.535408668272786</v>
+        <v>4.535408668272785</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.548346813349934</v>
+        <v>4.548346813349933</v>
       </c>
       <c r="R2" t="n">
         <v>4.400975877814668</v>
       </c>
       <c r="S2" t="n">
-        <v>4.502035816429025</v>
+        <v>4.502035816429026</v>
       </c>
       <c r="T2" t="n">
-        <v>4.512572892119044</v>
+        <v>4.512572892119043</v>
       </c>
       <c r="U2" t="n">
-        <v>4.566432643408248</v>
+        <v>4.566432643408252</v>
       </c>
       <c r="V2" t="n">
-        <v>4.787356131417861</v>
+        <v>4.78735613141786</v>
       </c>
       <c r="W2" t="n">
-        <v>4.667802560672976</v>
+        <v>4.667802560672975</v>
       </c>
       <c r="X2" t="n">
         <v>4.719449657521984</v>
@@ -1697,10 +1697,10 @@
         <v>4.572039411195877</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.681418412736188</v>
+        <v>4.681418412736189</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.554684065577127</v>
+        <v>4.554684065577125</v>
       </c>
     </row>
     <row r="3">
@@ -1710,28 +1710,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.88674791809097</v>
+        <v>10.88674791809098</v>
       </c>
       <c r="C3" t="n">
         <v>10.88638992112017</v>
       </c>
       <c r="D3" t="n">
-        <v>10.88674791809097</v>
+        <v>10.88674791809098</v>
       </c>
       <c r="E3" t="n">
         <v>9.864286190293246</v>
       </c>
       <c r="F3" t="n">
-        <v>10.88650879917407</v>
+        <v>10.88650879917408</v>
       </c>
       <c r="G3" t="n">
         <v>10.88663389895443</v>
       </c>
       <c r="H3" t="n">
-        <v>10.88674791809097</v>
+        <v>10.88674791809098</v>
       </c>
       <c r="I3" t="n">
-        <v>10.88674791809097</v>
+        <v>10.88674791809098</v>
       </c>
       <c r="J3" t="n">
         <v>10.88714854883766</v>
@@ -1740,16 +1740,16 @@
         <v>10.88661140239395</v>
       </c>
       <c r="L3" t="n">
-        <v>10.88674791809097</v>
+        <v>10.88674791809098</v>
       </c>
       <c r="M3" t="n">
         <v>10.88612823217016</v>
       </c>
       <c r="N3" t="n">
-        <v>10.88674791809097</v>
+        <v>10.88674791809098</v>
       </c>
       <c r="O3" t="n">
-        <v>10.88643312810008</v>
+        <v>10.88643312810009</v>
       </c>
       <c r="P3" t="n">
         <v>10.88615535296781</v>
@@ -1758,10 +1758,10 @@
         <v>10.88674442144246</v>
       </c>
       <c r="R3" t="n">
-        <v>10.88751682118027</v>
+        <v>10.88751682118028</v>
       </c>
       <c r="S3" t="n">
-        <v>10.88674791809097</v>
+        <v>10.88674791809098</v>
       </c>
       <c r="T3" t="n">
         <v>10.88629459385082</v>
@@ -1773,7 +1773,7 @@
         <v>11.09701665255782</v>
       </c>
       <c r="W3" t="n">
-        <v>10.88674791809097</v>
+        <v>10.88674791809098</v>
       </c>
       <c r="X3" t="n">
         <v>10.88784793657165</v>
@@ -1785,7 +1785,7 @@
         <v>10.88671632918549</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.88674791809097</v>
+        <v>10.88674791809098</v>
       </c>
       <c r="AB3" t="n">
         <v>10.89039246547957</v>
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.729512467511648</v>
+        <v>-1.729512467511654</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.546423260579719</v>
+        <v>-2.546423260579721</v>
       </c>
       <c r="D4" t="n">
-        <v>1.888279004435816</v>
+        <v>1.888279004435819</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3214349707755026</v>
+        <v>-0.3214349707755</v>
       </c>
       <c r="F4" t="n">
-        <v>-12.84861585506631</v>
+        <v>-12.84861585506628</v>
       </c>
       <c r="G4" t="n">
-        <v>5.781940760768197</v>
+        <v>5.781940760768176</v>
       </c>
       <c r="H4" t="n">
-        <v>5.492936726795142</v>
+        <v>5.492936726795134</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8219332719237333</v>
+        <v>-0.8219332719237258</v>
       </c>
       <c r="J4" t="n">
-        <v>2.489078595546379</v>
+        <v>2.48907859554638</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.9685232082967419</v>
+        <v>-0.9685232082967383</v>
       </c>
       <c r="L4" t="n">
-        <v>-21.81083237579195</v>
+        <v>-21.8108323757919</v>
       </c>
       <c r="M4" t="n">
         <v>-1.758154960647495</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8662871315488294</v>
+        <v>-0.8662871315488181</v>
       </c>
       <c r="O4" t="n">
-        <v>-7.272586698530286</v>
+        <v>-7.27258669853027</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.537128777843237</v>
+        <v>-1.537128777843233</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.296502049776514</v>
+        <v>1.296502049776517</v>
       </c>
       <c r="R4" t="n">
-        <v>-38.18564921905833</v>
+        <v>-38.18564921905828</v>
       </c>
       <c r="S4" t="n">
-        <v>-9.16150897877367</v>
+        <v>-9.161508978773648</v>
       </c>
       <c r="T4" t="n">
-        <v>-7.936911855910402</v>
+        <v>-7.936911855910406</v>
       </c>
       <c r="U4" t="n">
-        <v>5.089165690674753</v>
+        <v>5.08916569067475</v>
       </c>
       <c r="V4" t="n">
-        <v>8.437014375325358</v>
+        <v>8.437014375325361</v>
       </c>
       <c r="W4" t="n">
-        <v>31.34477583137783</v>
+        <v>31.3447758313778</v>
       </c>
       <c r="X4" t="n">
-        <v>42.77804017586854</v>
+        <v>42.77804017586843</v>
       </c>
       <c r="Y4" t="n">
-        <v>25.97232525401918</v>
+        <v>25.97232525401919</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.338513120615542</v>
+        <v>6.338513120615545</v>
       </c>
       <c r="AA4" t="n">
-        <v>35.27356099667382</v>
+        <v>35.27356099667386</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.182202414656119</v>
+        <v>2.182202414656127</v>
       </c>
     </row>
     <row r="5">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6280187405740036</v>
+        <v>0.6280187405740046</v>
       </c>
       <c r="C5" t="n">
-        <v>0.628018740574004</v>
+        <v>0.6280187405740058</v>
       </c>
       <c r="D5" t="n">
-        <v>0.628018740574004</v>
+        <v>0.6280187405740058</v>
       </c>
       <c r="E5" t="n">
-        <v>0.628018740574004</v>
+        <v>0.6280187405740058</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6280187405740035</v>
+        <v>0.6280187405740046</v>
       </c>
       <c r="G5" t="n">
-        <v>0.628018740574004</v>
+        <v>0.6280187405740058</v>
       </c>
       <c r="H5" t="n">
-        <v>0.628018740574004</v>
+        <v>0.6280187405740058</v>
       </c>
       <c r="I5" t="n">
-        <v>0.628018740574004</v>
+        <v>0.6280187405740058</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6266573918931629</v>
+        <v>0.6266573918931626</v>
       </c>
       <c r="K5" t="n">
-        <v>0.628018740574004</v>
+        <v>0.6280187405740058</v>
       </c>
       <c r="L5" t="n">
-        <v>0.628018740574004</v>
+        <v>0.6280187405740058</v>
       </c>
       <c r="M5" t="n">
-        <v>0.628018740574004</v>
+        <v>0.6280187405740058</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8662871315488294</v>
+        <v>-0.8662871315488181</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6280187405740035</v>
+        <v>0.6280187405740046</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6280187405740035</v>
+        <v>0.6280187405740046</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6280187405740035</v>
+        <v>0.6280187405740046</v>
       </c>
       <c r="R5" t="n">
-        <v>0.628018740574004</v>
+        <v>0.6280187405740058</v>
       </c>
       <c r="S5" t="n">
-        <v>0.628018740574004</v>
+        <v>0.6280187405740058</v>
       </c>
       <c r="T5" t="n">
-        <v>0.628018740574004</v>
+        <v>0.6280187405740058</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5986915818039045</v>
+        <v>0.598691581803902</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6189316302155381</v>
+        <v>0.6189316302155383</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6280187405740043</v>
+        <v>0.6280187405740058</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6280187405740035</v>
+        <v>0.6280187405740046</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5986915818039045</v>
+        <v>0.5986915818039019</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.628018740574004</v>
+        <v>0.6280187405740058</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.628018740574004</v>
+        <v>0.6280187405740058</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6280187405740035</v>
+        <v>0.6280187405740046</v>
       </c>
     </row>
     <row r="6">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9275012892162922</v>
+        <v>0.6887218716723296</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9275012892162922</v>
+        <v>0.6887218716723296</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9275012892162922</v>
+        <v>0.9275012892162965</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9275012892162922</v>
+        <v>0.6887218716723296</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9275012892162922</v>
+        <v>0.6887218716723296</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6887218716723259</v>
+        <v>0.9275012892162965</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6887218716723259</v>
+        <v>0.9275012892162965</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6887218716723259</v>
+        <v>0.9275012892162965</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6873605229914839</v>
+        <v>0.926139940535451</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9275012892162922</v>
+        <v>0.6887218716723296</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6887218716723259</v>
+        <v>0.9275012892162965</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6887218716723259</v>
+        <v>0.9275012892162965</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8662871315488294</v>
+        <v>-0.8662871315488181</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9616944554471776</v>
+        <v>0.9616944554471774</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6779533851465708</v>
+        <v>0.9612765951381341</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9275012892162922</v>
+        <v>0.9275012892162965</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6887218716723259</v>
+        <v>0.9275012892162965</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6887218716723259</v>
+        <v>0.9275012892162965</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9275012892162922</v>
+        <v>0.6887218716723296</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6887218716723259</v>
+        <v>0.9275012892162965</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6796347613138618</v>
+        <v>0.9184141788578276</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7095792621152179</v>
+        <v>0.7095792621152182</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6887218716723259</v>
+        <v>0.6887218716723296</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.700445919499964</v>
+        <v>0.7004459194999568</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.9275012892162922</v>
+        <v>0.6887218716723296</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6887218716723259</v>
+        <v>0.6887218716723296</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6897867276969692</v>
+        <v>0.6897867276969738</v>
       </c>
     </row>
     <row r="7">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9909626061908966</v>
+        <v>0.9909626061908973</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9909626061908966</v>
+        <v>0.9909626061908973</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9909626061908966</v>
+        <v>0.9909626061908973</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9909626061908966</v>
+        <v>0.9909626061908973</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9909626061908966</v>
+        <v>0.9909626061908973</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9909626061908966</v>
+        <v>0.9909626061908973</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9909626061908966</v>
+        <v>0.9909626061908973</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9909626061908966</v>
+        <v>0.9909626061908973</v>
       </c>
       <c r="J7" t="n">
-        <v>0.989601257510057</v>
+        <v>0.9896012575100567</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9909626061908966</v>
+        <v>0.9909626061908973</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9909626061908966</v>
+        <v>0.9909626061908973</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9909626061908966</v>
+        <v>0.9909626061908973</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8662871315488294</v>
+        <v>-0.8662871315488181</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9890718352717573</v>
+        <v>0.9890718352717588</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9890718352717573</v>
+        <v>0.9890718352717588</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9909626061908966</v>
+        <v>0.9909626061908973</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9909626061908966</v>
+        <v>0.9909626061908973</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9909626061908966</v>
+        <v>0.9909626061908973</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9909626061908966</v>
+        <v>0.9909626061908973</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9811629210782545</v>
+        <v>0.9811629210782572</v>
       </c>
       <c r="V7" t="n">
         <v>0.9818754958324321</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9909626061908966</v>
+        <v>0.9909626061908973</v>
       </c>
       <c r="X7" t="n">
-        <v>0.9909626061908966</v>
+        <v>0.9909626061908973</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.9909626061908966</v>
+        <v>0.9909626061908973</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.9909626061908966</v>
+        <v>0.9909626061908973</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.9909626061908966</v>
+        <v>0.9909626061908973</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9909626061908966</v>
+        <v>0.9909626061908973</v>
       </c>
     </row>
     <row r="8">
@@ -2150,85 +2150,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.091411298767955</v>
+        <v>1.091411298767957</v>
       </c>
       <c r="C8" t="n">
-        <v>1.47566510256978</v>
+        <v>1.47566510256979</v>
       </c>
       <c r="D8" t="n">
-        <v>1.47566510256978</v>
+        <v>1.47566510256979</v>
       </c>
       <c r="E8" t="n">
-        <v>1.47566510256978</v>
+        <v>1.271061286896487</v>
       </c>
       <c r="F8" t="n">
-        <v>1.151273550487997</v>
+        <v>1.151273550488001</v>
       </c>
       <c r="G8" t="n">
-        <v>1.47566510256978</v>
+        <v>1.555342631936042</v>
       </c>
       <c r="H8" t="n">
-        <v>1.47566510256978</v>
+        <v>1.47566510256979</v>
       </c>
       <c r="I8" t="n">
-        <v>1.47566510256978</v>
+        <v>1.47566510256979</v>
       </c>
       <c r="J8" t="n">
-        <v>1.474303753888943</v>
+        <v>1.474303753888949</v>
       </c>
       <c r="K8" t="n">
-        <v>1.47566510256978</v>
+        <v>1.47566510256979</v>
       </c>
       <c r="L8" t="n">
-        <v>1.47566510256978</v>
+        <v>1.47566510256979</v>
       </c>
       <c r="M8" t="n">
-        <v>1.47566510256978</v>
+        <v>1.475665102569171</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8662871315488294</v>
+        <v>-0.8662871315488181</v>
       </c>
       <c r="O8" t="n">
-        <v>1.25965890429349</v>
+        <v>1.259658904293491</v>
       </c>
       <c r="P8" t="n">
         <v>1.239594318858517</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.015896656256469</v>
+        <v>1.015896656256474</v>
       </c>
       <c r="R8" t="n">
-        <v>1.47566510256978</v>
+        <v>1.47566510256979</v>
       </c>
       <c r="S8" t="n">
-        <v>1.47566510256978</v>
+        <v>1.47566510256979</v>
       </c>
       <c r="T8" t="n">
-        <v>1.47566510256978</v>
+        <v>1.47566510256979</v>
       </c>
       <c r="U8" t="n">
-        <v>1.23346007553615</v>
+        <v>1.281986734940747</v>
       </c>
       <c r="V8" t="n">
-        <v>1.466577992211321</v>
+        <v>1.354795289515117</v>
       </c>
       <c r="W8" t="n">
-        <v>1.475740619078785</v>
+        <v>1.475740619078788</v>
       </c>
       <c r="X8" t="n">
-        <v>1.051114280670135</v>
+        <v>1.051114280670139</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.847234610921518</v>
+        <v>1.84723461092152</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.47566510256978</v>
+        <v>1.08427358711846</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.47566510256978</v>
+        <v>1.47566510256979</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.877050331072359</v>
+        <v>1.877050331072362</v>
       </c>
     </row>
     <row r="9">
@@ -2238,85 +2238,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.350812726871132</v>
+        <v>1.350812726871127</v>
       </c>
       <c r="C9" t="n">
-        <v>1.589799163637287</v>
+        <v>1.589799163637284</v>
       </c>
       <c r="D9" t="n">
-        <v>1.589799163637287</v>
+        <v>1.589799163637284</v>
       </c>
       <c r="E9" t="n">
-        <v>1.589799163637287</v>
+        <v>1.534642207333558</v>
       </c>
       <c r="F9" t="n">
-        <v>1.589799163637287</v>
+        <v>1.038869966292015</v>
       </c>
       <c r="G9" t="n">
-        <v>1.589799163637287</v>
+        <v>1.589799343685713</v>
       </c>
       <c r="H9" t="n">
-        <v>1.589799163637287</v>
+        <v>1.589799163637284</v>
       </c>
       <c r="I9" t="n">
-        <v>1.589799163637287</v>
+        <v>1.589799163637284</v>
       </c>
       <c r="J9" t="n">
-        <v>1.588437814956448</v>
+        <v>1.58843781495644</v>
       </c>
       <c r="K9" t="n">
-        <v>1.589799163637287</v>
+        <v>1.589799163637284</v>
       </c>
       <c r="L9" t="n">
-        <v>1.589799163637287</v>
+        <v>1.589799163637284</v>
       </c>
       <c r="M9" t="n">
-        <v>1.589799163637287</v>
+        <v>1.589799163637284</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8662871315488294</v>
+        <v>-0.8662871315488181</v>
       </c>
       <c r="O9" t="n">
-        <v>1.668999195571845</v>
+        <v>1.668999195571836</v>
       </c>
       <c r="P9" t="n">
-        <v>1.686223804516426</v>
+        <v>1.686223804516421</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.589799343685707</v>
+        <v>1.589799343685713</v>
       </c>
       <c r="R9" t="n">
-        <v>1.589799163637287</v>
+        <v>1.589799163637284</v>
       </c>
       <c r="S9" t="n">
-        <v>1.589799163637287</v>
+        <v>1.589799163637284</v>
       </c>
       <c r="T9" t="n">
-        <v>1.589799163637287</v>
+        <v>1.589799163637284</v>
       </c>
       <c r="U9" t="n">
-        <v>1.589799163637287</v>
+        <v>1.589799163637284</v>
       </c>
       <c r="V9" t="n">
-        <v>1.580712053278827</v>
+        <v>1.856497515392121</v>
       </c>
       <c r="W9" t="n">
-        <v>1.589799163637287</v>
+        <v>1.589799163637284</v>
       </c>
       <c r="X9" t="n">
-        <v>1.589799163637287</v>
+        <v>1.589799163637284</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.589799163637287</v>
+        <v>1.589799163637284</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.589799163637287</v>
+        <v>1.445711665265663</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.589799163637287</v>
+        <v>1.589799163637284</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.589799163637287</v>
+        <v>1.589799163637284</v>
       </c>
     </row>
     <row r="10">
@@ -2329,7 +2329,7 @@
         <v>10.9483650092835</v>
       </c>
       <c r="C10" t="n">
-        <v>10.96442546535979</v>
+        <v>10.96442546535978</v>
       </c>
       <c r="D10" t="n">
         <v>10.85806787451015</v>
@@ -2344,7 +2344,7 @@
         <v>10.74965928673729</v>
       </c>
       <c r="H10" t="n">
-        <v>10.78192742750734</v>
+        <v>10.78192742750735</v>
       </c>
       <c r="I10" t="n">
         <v>10.92011080222048</v>
@@ -2392,7 +2392,7 @@
         <v>10.1660721865437</v>
       </c>
       <c r="X10" t="n">
-        <v>9.874994101148765</v>
+        <v>9.874994101148763</v>
       </c>
       <c r="Y10" t="n">
         <v>10.30305308866424</v>
@@ -2401,7 +2401,7 @@
         <v>10.72998589546532</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.08636349403479</v>
+        <v>10.0863634940348</v>
       </c>
       <c r="AB10" t="n">
         <v>10.85726024448849</v>
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.563372725621292</v>
+        <v>4.56337272562129</v>
       </c>
       <c r="C11" t="n">
         <v>4.567568298002003</v>
       </c>
       <c r="D11" t="n">
-        <v>4.537542742707146</v>
+        <v>4.537542742707148</v>
       </c>
       <c r="E11" t="n">
         <v>3.546570546399337</v>
@@ -2429,19 +2429,19 @@
         <v>4.63325453151647</v>
       </c>
       <c r="G11" t="n">
-        <v>4.506302954530912</v>
+        <v>4.506302954530913</v>
       </c>
       <c r="H11" t="n">
-        <v>4.516019738669064</v>
+        <v>4.516019738669063</v>
       </c>
       <c r="I11" t="n">
-        <v>4.5551700394156</v>
+        <v>4.555170039415598</v>
       </c>
       <c r="J11" t="n">
-        <v>4.531811533699258</v>
+        <v>4.531811533699257</v>
       </c>
       <c r="K11" t="n">
-        <v>4.558098734688485</v>
+        <v>4.558098734688483</v>
       </c>
       <c r="L11" t="n">
         <v>4.713397341462612</v>
@@ -2453,19 +2453,19 @@
         <v>4.555330905563522</v>
       </c>
       <c r="O11" t="n">
-        <v>4.606542729026818</v>
+        <v>4.606542729026819</v>
       </c>
       <c r="P11" t="n">
-        <v>4.561835690887805</v>
+        <v>4.561835690887804</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.541254344958711</v>
+        <v>4.541254344958713</v>
       </c>
       <c r="R11" t="n">
-        <v>4.787030131738572</v>
+        <v>4.787030131738574</v>
       </c>
       <c r="S11" t="n">
-        <v>4.61985004419285</v>
+        <v>4.619850044192851</v>
       </c>
       <c r="T11" t="n">
         <v>4.599693209518907</v>
@@ -2474,25 +2474,25 @@
         <v>4.513240630606678</v>
       </c>
       <c r="V11" t="n">
-        <v>4.693666422053812</v>
+        <v>4.693666422053811</v>
       </c>
       <c r="W11" t="n">
-        <v>4.339892806161683</v>
+        <v>4.339892806161682</v>
       </c>
       <c r="X11" t="n">
         <v>4.258597934630917</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.378420445579598</v>
+        <v>4.3784204455796</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.500726564382943</v>
+        <v>4.500726564382946</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.317240949116809</v>
+        <v>4.31724094911681</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.539608799440066</v>
+        <v>4.539608799440063</v>
       </c>
     </row>
   </sheetData>
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.875299218905514</v>
+        <v>4.875299218905512</v>
       </c>
       <c r="C2" t="n">
-        <v>4.758865158305923</v>
+        <v>4.758865158305919</v>
       </c>
       <c r="D2" t="n">
-        <v>4.818995404861573</v>
+        <v>4.818995404861572</v>
       </c>
       <c r="E2" t="n">
-        <v>3.703978825963543</v>
+        <v>3.703978825963544</v>
       </c>
       <c r="F2" t="n">
-        <v>4.787620713901735</v>
+        <v>4.787620713901733</v>
       </c>
       <c r="G2" t="n">
         <v>4.941052530891759</v>
       </c>
       <c r="H2" t="n">
-        <v>4.875299218905514</v>
+        <v>4.875299218905512</v>
       </c>
       <c r="I2" t="n">
-        <v>4.875299218905514</v>
+        <v>4.875299218905512</v>
       </c>
       <c r="J2" t="n">
         <v>4.869935921560193</v>
       </c>
       <c r="K2" t="n">
-        <v>4.875230612656312</v>
+        <v>4.875230612656309</v>
       </c>
       <c r="L2" t="n">
-        <v>4.875299218905514</v>
+        <v>4.875299218905512</v>
       </c>
       <c r="M2" t="n">
-        <v>4.951450960054722</v>
+        <v>4.951450960054721</v>
       </c>
       <c r="N2" t="n">
-        <v>4.846732865588871</v>
+        <v>4.846732865588869</v>
       </c>
       <c r="O2" t="n">
-        <v>4.875074039365703</v>
+        <v>4.875074039365701</v>
       </c>
       <c r="P2" t="n">
-        <v>4.875242855464123</v>
+        <v>4.875242855464121</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.875296023602798</v>
+        <v>4.875296023602797</v>
       </c>
       <c r="R2" t="n">
-        <v>4.875286536126355</v>
+        <v>4.875286536126353</v>
       </c>
       <c r="S2" t="n">
-        <v>4.875299218905514</v>
+        <v>4.875299218905512</v>
       </c>
       <c r="T2" t="n">
-        <v>4.875201270392333</v>
+        <v>4.875201270392331</v>
       </c>
       <c r="U2" t="n">
-        <v>4.875520377764142</v>
+        <v>4.875520377764141</v>
       </c>
       <c r="V2" t="n">
         <v>4.956404027896357</v>
       </c>
       <c r="W2" t="n">
-        <v>4.875299218905514</v>
+        <v>4.875299218905512</v>
       </c>
       <c r="X2" t="n">
-        <v>4.875482915154727</v>
+        <v>4.875482915154726</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.874782183822445</v>
+        <v>4.874782183822443</v>
       </c>
       <c r="Z2" t="n">
         <v>4.818869778203921</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.875299218905514</v>
+        <v>4.875299218905512</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.878629698928064</v>
+        <v>4.878629698928061</v>
       </c>
     </row>
     <row r="3">
@@ -2746,16 +2746,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.0697947461836</v>
+        <v>11.06979474618359</v>
       </c>
       <c r="C3" t="n">
         <v>11.06945252594566</v>
       </c>
       <c r="D3" t="n">
-        <v>11.0697947461836</v>
+        <v>11.06979474618359</v>
       </c>
       <c r="E3" t="n">
-        <v>9.980049189598867</v>
+        <v>9.980049189598866</v>
       </c>
       <c r="F3" t="n">
         <v>11.06966710100908</v>
@@ -2764,10 +2764,10 @@
         <v>11.06975550294358</v>
       </c>
       <c r="H3" t="n">
-        <v>11.0697947461836</v>
+        <v>11.06979474618359</v>
       </c>
       <c r="I3" t="n">
-        <v>11.0697947461836</v>
+        <v>11.06979474618359</v>
       </c>
       <c r="J3" t="n">
         <v>11.064430834508</v>
@@ -2776,16 +2776,16 @@
         <v>11.06971967023784</v>
       </c>
       <c r="L3" t="n">
-        <v>11.0697947461836</v>
+        <v>11.06979474618359</v>
       </c>
       <c r="M3" t="n">
         <v>11.06970635624242</v>
       </c>
       <c r="N3" t="n">
-        <v>11.0697947461836</v>
+        <v>11.06979474618359</v>
       </c>
       <c r="O3" t="n">
-        <v>11.06954833186754</v>
+        <v>11.06954833186753</v>
       </c>
       <c r="P3" t="n">
         <v>11.0697330674302</v>
@@ -2797,7 +2797,7 @@
         <v>11.06978086731337</v>
       </c>
       <c r="S3" t="n">
-        <v>11.0697947461836</v>
+        <v>11.06979474618359</v>
       </c>
       <c r="T3" t="n">
         <v>11.06968756086527</v>
@@ -2809,7 +2809,7 @@
         <v>11.25702024677416</v>
       </c>
       <c r="W3" t="n">
-        <v>11.0697947461836</v>
+        <v>11.06979474618359</v>
       </c>
       <c r="X3" t="n">
         <v>11.06999576511609</v>
@@ -2821,7 +2821,7 @@
         <v>11.06977565291818</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.0697947461836</v>
+        <v>11.06979474618359</v>
       </c>
       <c r="AB3" t="n">
         <v>11.07343929357219</v>
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27.34516797412099</v>
+        <v>27.34516797412088</v>
       </c>
       <c r="C4" t="n">
-        <v>9.806808892601971</v>
+        <v>9.806808892601959</v>
       </c>
       <c r="D4" t="n">
-        <v>27.1395972158416</v>
+        <v>27.13959721584157</v>
       </c>
       <c r="E4" t="n">
         <v>14.37596362818166</v>
       </c>
       <c r="F4" t="n">
-        <v>18.22431835264861</v>
+        <v>18.22431835264863</v>
       </c>
       <c r="G4" t="n">
-        <v>55.93714307448611</v>
+        <v>55.93714307448602</v>
       </c>
       <c r="H4" t="n">
-        <v>32.41790923743753</v>
+        <v>32.41790923743766</v>
       </c>
       <c r="I4" t="n">
-        <v>18.95824058734322</v>
+        <v>18.95824058734323</v>
       </c>
       <c r="J4" t="n">
-        <v>40.16948653835529</v>
+        <v>40.16948653835527</v>
       </c>
       <c r="K4" t="n">
-        <v>31.12508810270533</v>
+        <v>31.12508810270537</v>
       </c>
       <c r="L4" t="n">
-        <v>43.43431888345172</v>
+        <v>43.43431888345175</v>
       </c>
       <c r="M4" t="n">
-        <v>65.11745556650376</v>
+        <v>65.11745556650385</v>
       </c>
       <c r="N4" t="n">
-        <v>42.05659380065983</v>
+        <v>42.05659380065975</v>
       </c>
       <c r="O4" t="n">
         <v>25.32422682475563</v>
       </c>
       <c r="P4" t="n">
-        <v>38.44394748830242</v>
+        <v>38.44394748830246</v>
       </c>
       <c r="Q4" t="n">
-        <v>24.32130283644488</v>
+        <v>24.32130283644492</v>
       </c>
       <c r="R4" t="n">
-        <v>23.27561378138319</v>
+        <v>23.27561378138324</v>
       </c>
       <c r="S4" t="n">
-        <v>41.00033746384101</v>
+        <v>41.00033746384116</v>
       </c>
       <c r="T4" t="n">
-        <v>27.1657699209135</v>
+        <v>27.16576992091349</v>
       </c>
       <c r="U4" t="n">
-        <v>42.05659380065983</v>
+        <v>42.05659380065975</v>
       </c>
       <c r="V4" t="n">
-        <v>12.14229851945611</v>
+        <v>12.1422985194561</v>
       </c>
       <c r="W4" t="n">
-        <v>45.48282814997562</v>
+        <v>45.4828281499756</v>
       </c>
       <c r="X4" t="n">
-        <v>35.66303420116073</v>
+        <v>35.66303420116074</v>
       </c>
       <c r="Y4" t="n">
         <v>30.29092425622808</v>
       </c>
       <c r="Z4" t="n">
-        <v>24.59862912465315</v>
+        <v>24.5986291246531</v>
       </c>
       <c r="AA4" t="n">
-        <v>33.1757577551645</v>
+        <v>33.17575775516453</v>
       </c>
       <c r="AB4" t="n">
-        <v>59.2383500007203</v>
+        <v>59.2383500007202</v>
       </c>
     </row>
     <row r="5">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580941</v>
       </c>
       <c r="C5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580943</v>
       </c>
       <c r="D5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580943</v>
       </c>
       <c r="E5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580943</v>
       </c>
       <c r="F5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580941</v>
       </c>
       <c r="G5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580943</v>
       </c>
       <c r="H5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580943</v>
       </c>
       <c r="I5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580943</v>
       </c>
       <c r="J5" t="n">
-        <v>1.050804892285098</v>
+        <v>1.050804892285094</v>
       </c>
       <c r="K5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580943</v>
       </c>
       <c r="L5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580943</v>
       </c>
       <c r="M5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580943</v>
       </c>
       <c r="N5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580941</v>
       </c>
       <c r="O5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580941</v>
       </c>
       <c r="P5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580941</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580941</v>
       </c>
       <c r="R5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580943</v>
       </c>
       <c r="S5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580943</v>
       </c>
       <c r="T5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580943</v>
       </c>
       <c r="U5" t="n">
-        <v>1.02932688842754</v>
+        <v>1.029326888427534</v>
       </c>
       <c r="V5" t="n">
-        <v>1.036543007433563</v>
+        <v>1.036543007433554</v>
       </c>
       <c r="W5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580941</v>
       </c>
       <c r="X5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580941</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.02932688842754</v>
+        <v>1.029326888427534</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580943</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580943</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.053380836580948</v>
+        <v>1.053380836580941</v>
       </c>
     </row>
     <row r="6">
@@ -3010,85 +3010,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.677803350597295</v>
+        <v>1.168152525356228</v>
       </c>
       <c r="C6" t="n">
-        <v>1.677803350597295</v>
+        <v>1.677803350597294</v>
       </c>
       <c r="D6" t="n">
-        <v>1.16815252535623</v>
+        <v>1.677803350597294</v>
       </c>
       <c r="E6" t="n">
-        <v>1.16815252535623</v>
+        <v>1.168152525356228</v>
       </c>
       <c r="F6" t="n">
-        <v>1.677803350597295</v>
+        <v>1.168152525356228</v>
       </c>
       <c r="G6" t="n">
-        <v>1.677803350597295</v>
+        <v>1.168152525356228</v>
       </c>
       <c r="H6" t="n">
-        <v>1.16815252535623</v>
+        <v>1.677803350597294</v>
       </c>
       <c r="I6" t="n">
-        <v>1.16815252535623</v>
+        <v>1.168152525356228</v>
       </c>
       <c r="J6" t="n">
-        <v>1.675227406301445</v>
+        <v>1.675227406301438</v>
       </c>
       <c r="K6" t="n">
-        <v>1.16815252535623</v>
+        <v>1.677803350597294</v>
       </c>
       <c r="L6" t="n">
-        <v>1.16815252535623</v>
+        <v>1.168152525356228</v>
       </c>
       <c r="M6" t="n">
-        <v>1.16815252535623</v>
+        <v>1.168152525356228</v>
       </c>
       <c r="N6" t="n">
-        <v>1.17155821426404</v>
+        <v>1.171558214264125</v>
       </c>
       <c r="O6" t="n">
-        <v>1.704502135394486</v>
+        <v>1.70450213539449</v>
       </c>
       <c r="P6" t="n">
-        <v>1.704450970332718</v>
+        <v>1.704450970332721</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.16815252535623</v>
+        <v>1.677803350597294</v>
       </c>
       <c r="R6" t="n">
-        <v>1.16815252535623</v>
+        <v>1.677803350597294</v>
       </c>
       <c r="S6" t="n">
-        <v>1.16815252535623</v>
+        <v>1.677803350597294</v>
       </c>
       <c r="T6" t="n">
-        <v>1.677803350597295</v>
+        <v>1.168152525356228</v>
       </c>
       <c r="U6" t="n">
-        <v>1.677803350597295</v>
+        <v>1.168152525356228</v>
       </c>
       <c r="V6" t="n">
-        <v>1.660965521449909</v>
+        <v>1.660965521449906</v>
       </c>
       <c r="W6" t="n">
-        <v>1.704521526831644</v>
+        <v>1.704521526831646</v>
       </c>
       <c r="X6" t="n">
-        <v>1.16815252535623</v>
+        <v>1.677803350597294</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18109669582453</v>
+        <v>1.181096695824504</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.16815252535623</v>
+        <v>1.677803350597294</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.677803350597295</v>
+        <v>1.168152525356228</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.181126489764534</v>
+        <v>1.181126489764538</v>
       </c>
     </row>
     <row r="7">
@@ -3122,7 +3122,7 @@
         <v>1.632044151203653</v>
       </c>
       <c r="J7" t="n">
-        <v>1.629468206907803</v>
+        <v>1.629468206907804</v>
       </c>
       <c r="K7" t="n">
         <v>1.632044151203653</v>
@@ -3137,10 +3137,10 @@
         <v>1.632044151203653</v>
       </c>
       <c r="O7" t="n">
-        <v>1.630006301315224</v>
+        <v>1.63000630131522</v>
       </c>
       <c r="P7" t="n">
-        <v>1.630006301315224</v>
+        <v>1.63000630131522</v>
       </c>
       <c r="Q7" t="n">
         <v>1.632044151203653</v>
@@ -3158,7 +3158,7 @@
         <v>1.630475617567823</v>
       </c>
       <c r="V7" t="n">
-        <v>1.615206322056267</v>
+        <v>1.615206322056263</v>
       </c>
       <c r="W7" t="n">
         <v>1.632044151203653</v>
@@ -3186,85 +3186,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.901103461797944</v>
+        <v>1.901103461797941</v>
       </c>
       <c r="C8" t="n">
-        <v>2.580470472433688</v>
+        <v>2.580470472433691</v>
       </c>
       <c r="D8" t="n">
-        <v>2.580470472433688</v>
+        <v>2.580470472433691</v>
       </c>
       <c r="E8" t="n">
-        <v>2.580470472433688</v>
+        <v>2.218727579451757</v>
       </c>
       <c r="F8" t="n">
-        <v>2.006940902061089</v>
+        <v>2.006940902061085</v>
       </c>
       <c r="G8" t="n">
-        <v>2.580470472433688</v>
+        <v>2.721341647711016</v>
       </c>
       <c r="H8" t="n">
-        <v>2.580470472433688</v>
+        <v>2.580470472433691</v>
       </c>
       <c r="I8" t="n">
-        <v>2.580470472433688</v>
+        <v>2.580470472433691</v>
       </c>
       <c r="J8" t="n">
-        <v>2.577894528137837</v>
+        <v>2.577894528137831</v>
       </c>
       <c r="K8" t="n">
-        <v>2.580470472433688</v>
+        <v>2.580470472433691</v>
       </c>
       <c r="L8" t="n">
-        <v>2.580470472433688</v>
+        <v>2.580470472433691</v>
       </c>
       <c r="M8" t="n">
-        <v>2.580470472433688</v>
+        <v>2.580470472433653</v>
       </c>
       <c r="N8" t="n">
-        <v>2.053847383425341</v>
+        <v>2.053847383425333</v>
       </c>
       <c r="O8" t="n">
-        <v>2.198567980596473</v>
+        <v>2.198567980596463</v>
       </c>
       <c r="P8" t="n">
-        <v>2.163093465319556</v>
+        <v>2.16309346531955</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.767592338558357</v>
+        <v>1.767592338558351</v>
       </c>
       <c r="R8" t="n">
-        <v>2.580470472433688</v>
+        <v>2.580470472433691</v>
       </c>
       <c r="S8" t="n">
-        <v>2.580470472433688</v>
+        <v>2.580470472433691</v>
       </c>
       <c r="T8" t="n">
-        <v>2.580470472433688</v>
+        <v>2.580470472433691</v>
       </c>
       <c r="U8" t="n">
-        <v>2.162764904303655</v>
+        <v>2.249244210202909</v>
       </c>
       <c r="V8" t="n">
-        <v>2.563632643286301</v>
+        <v>2.378352555259123</v>
       </c>
       <c r="W8" t="n">
-        <v>2.580603986974261</v>
+        <v>2.580603986974264</v>
       </c>
       <c r="X8" t="n">
-        <v>1.829857674672687</v>
+        <v>1.829857674672689</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.256571827118945</v>
+        <v>3.256571827118946</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.580470472433688</v>
+        <v>1.888483870833847</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.580470472433688</v>
+        <v>2.580470472433691</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.290126122283248</v>
+        <v>3.290126122283238</v>
       </c>
     </row>
     <row r="9">
@@ -3274,85 +3274,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.229074795561497</v>
+        <v>3.229074795561495</v>
       </c>
       <c r="C9" t="n">
-        <v>3.892028821734655</v>
+        <v>3.892028821734654</v>
       </c>
       <c r="D9" t="n">
-        <v>3.892028821734655</v>
+        <v>3.892028821734654</v>
       </c>
       <c r="E9" t="n">
-        <v>3.892028821734655</v>
+        <v>3.739021810432407</v>
       </c>
       <c r="F9" t="n">
-        <v>3.892028821734655</v>
+        <v>2.363738728855891</v>
       </c>
       <c r="G9" t="n">
-        <v>3.892028821734655</v>
+        <v>3.892028917675752</v>
       </c>
       <c r="H9" t="n">
-        <v>3.892028821734655</v>
+        <v>3.892028821734654</v>
       </c>
       <c r="I9" t="n">
-        <v>3.892028821734655</v>
+        <v>3.892028821734654</v>
       </c>
       <c r="J9" t="n">
-        <v>3.889452877438809</v>
+        <v>3.889452877438803</v>
       </c>
       <c r="K9" t="n">
-        <v>3.892028821734655</v>
+        <v>3.892028821734654</v>
       </c>
       <c r="L9" t="n">
-        <v>3.892028821734655</v>
+        <v>3.892028821734654</v>
       </c>
       <c r="M9" t="n">
-        <v>3.892028821734655</v>
+        <v>3.892028821734654</v>
       </c>
       <c r="N9" t="n">
-        <v>3.892028821734655</v>
+        <v>3.892028821734654</v>
       </c>
       <c r="O9" t="n">
-        <v>4.111731045680112</v>
+        <v>4.111731045680108</v>
       </c>
       <c r="P9" t="n">
-        <v>4.159512489067342</v>
+        <v>4.159512489067345</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.892028917675753</v>
+        <v>3.892028917675752</v>
       </c>
       <c r="R9" t="n">
-        <v>3.892028821734655</v>
+        <v>3.892028821734654</v>
       </c>
       <c r="S9" t="n">
-        <v>3.892028821734655</v>
+        <v>3.892028821734654</v>
       </c>
       <c r="T9" t="n">
-        <v>3.892028821734655</v>
+        <v>3.892028821734654</v>
       </c>
       <c r="U9" t="n">
-        <v>3.892028821734655</v>
+        <v>3.892028821734654</v>
       </c>
       <c r="V9" t="n">
-        <v>3.875190992587271</v>
+        <v>4.64022481349277</v>
       </c>
       <c r="W9" t="n">
-        <v>3.892028821734655</v>
+        <v>3.892028821734654</v>
       </c>
       <c r="X9" t="n">
-        <v>3.892028821734655</v>
+        <v>3.892028821734654</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.892028821734655</v>
+        <v>3.892028821734654</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.892028821734655</v>
+        <v>3.492326534221556</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.892028821734655</v>
+        <v>3.892028821734654</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.892028821734655</v>
+        <v>3.892028821734654</v>
       </c>
     </row>
     <row r="10">
@@ -3368,7 +3368,7 @@
         <v>10.88278611318529</v>
       </c>
       <c r="D10" t="n">
-        <v>10.53296252733812</v>
+        <v>10.53296252733811</v>
       </c>
       <c r="E10" t="n">
         <v>9.687982427827068</v>
@@ -3395,7 +3395,7 @@
         <v>10.14216389944622</v>
       </c>
       <c r="M10" t="n">
-        <v>9.761525177373958</v>
+        <v>9.761525177373956</v>
       </c>
       <c r="N10" t="n">
         <v>10.36752721149578</v>
@@ -3419,10 +3419,10 @@
         <v>10.53164595926842</v>
       </c>
       <c r="U10" t="n">
-        <v>10.15144547954129</v>
+        <v>10.15144547954128</v>
       </c>
       <c r="V10" t="n">
-        <v>10.98961879896754</v>
+        <v>10.98961879896755</v>
       </c>
       <c r="W10" t="n">
         <v>10.10615828925491</v>
@@ -3450,85 +3450,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.590904854345299</v>
+        <v>4.590904854345298</v>
       </c>
       <c r="C11" t="n">
-        <v>4.673931345629391</v>
+        <v>4.67393134562939</v>
       </c>
       <c r="D11" t="n">
-        <v>4.574735034504108</v>
+        <v>4.574735034504105</v>
       </c>
       <c r="E11" t="n">
-        <v>3.571087518595831</v>
+        <v>3.57108751859583</v>
       </c>
       <c r="F11" t="n">
-        <v>4.627456571802048</v>
+        <v>4.627456571802046</v>
       </c>
       <c r="G11" t="n">
-        <v>4.362793598772519</v>
+        <v>4.362793598772513</v>
       </c>
       <c r="H11" t="n">
-        <v>4.593410741343266</v>
+        <v>4.593410741343265</v>
       </c>
       <c r="I11" t="n">
-        <v>4.709749695285086</v>
+        <v>4.709749695285084</v>
       </c>
       <c r="J11" t="n">
-        <v>4.471625342259953</v>
+        <v>4.47162534225995</v>
       </c>
       <c r="K11" t="n">
-        <v>4.570469603914019</v>
+        <v>4.57046960391402</v>
       </c>
       <c r="L11" t="n">
-        <v>4.453224227455899</v>
+        <v>4.453224227455897</v>
       </c>
       <c r="M11" t="n">
         <v>4.356224354743508</v>
       </c>
       <c r="N11" t="n">
-        <v>4.52719889931207</v>
+        <v>4.527198899312068</v>
       </c>
       <c r="O11" t="n">
-        <v>4.605250914771898</v>
+        <v>4.605250914771895</v>
       </c>
       <c r="P11" t="n">
-        <v>4.479288484092477</v>
+        <v>4.479288484092472</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.650992408341211</v>
+        <v>4.650992408341208</v>
       </c>
       <c r="R11" t="n">
-        <v>4.672751200645235</v>
+        <v>4.672751200645233</v>
       </c>
       <c r="S11" t="n">
-        <v>4.455816949684674</v>
+        <v>4.455816949684673</v>
       </c>
       <c r="T11" t="n">
-        <v>4.630390627028915</v>
+        <v>4.630390627028911</v>
       </c>
       <c r="U11" t="n">
         <v>4.457558417568476</v>
       </c>
       <c r="V11" t="n">
-        <v>4.834735516986497</v>
+        <v>4.834735516986498</v>
       </c>
       <c r="W11" t="n">
-        <v>4.436841560075782</v>
+        <v>4.436841560075781</v>
       </c>
       <c r="X11" t="n">
         <v>4.544955862129195</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.58323778839108</v>
+        <v>4.583237788391078</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.571349383055835</v>
+        <v>4.571349383055836</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.557869722757691</v>
+        <v>4.557869722757689</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.359204867078597</v>
+        <v>4.359204867078596</v>
       </c>
     </row>
   </sheetData>
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.851526995138777</v>
+        <v>4.851526995138784</v>
       </c>
       <c r="C2" t="n">
-        <v>4.750705634976036</v>
+        <v>4.750705634976039</v>
       </c>
       <c r="D2" t="n">
-        <v>4.815434056748282</v>
+        <v>4.815434056748284</v>
       </c>
       <c r="E2" t="n">
-        <v>3.697405691557715</v>
+        <v>3.697405691557716</v>
       </c>
       <c r="F2" t="n">
-        <v>4.756691469405327</v>
+        <v>4.756691469405329</v>
       </c>
       <c r="G2" t="n">
-        <v>4.914236906382364</v>
+        <v>4.914236906382365</v>
       </c>
       <c r="H2" t="n">
-        <v>4.851526995138777</v>
+        <v>4.851526995138784</v>
       </c>
       <c r="I2" t="n">
-        <v>4.851526995138777</v>
+        <v>4.851526995138784</v>
       </c>
       <c r="J2" t="n">
-        <v>4.847183925656845</v>
+        <v>4.847183925656844</v>
       </c>
       <c r="K2" t="n">
-        <v>4.851429682055727</v>
+        <v>4.851429682055732</v>
       </c>
       <c r="L2" t="n">
-        <v>4.851526995138777</v>
+        <v>4.851526995138784</v>
       </c>
       <c r="M2" t="n">
-        <v>4.909659770208878</v>
+        <v>4.909659770208882</v>
       </c>
       <c r="N2" t="n">
-        <v>4.803396327620989</v>
+        <v>4.80339632762099</v>
       </c>
       <c r="O2" t="n">
-        <v>4.851275538764041</v>
+        <v>4.851275538764046</v>
       </c>
       <c r="P2" t="n">
-        <v>4.851498560909968</v>
+        <v>4.851498560909974</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.851523799836062</v>
+        <v>4.851523799836068</v>
       </c>
       <c r="R2" t="n">
-        <v>4.851891496489532</v>
+        <v>4.851891496489538</v>
       </c>
       <c r="S2" t="n">
-        <v>4.851526995138777</v>
+        <v>4.851526995138784</v>
       </c>
       <c r="T2" t="n">
-        <v>4.851238537411424</v>
+        <v>4.85123853741143</v>
       </c>
       <c r="U2" t="n">
-        <v>4.851872749085677</v>
+        <v>4.851872749085683</v>
       </c>
       <c r="V2" t="n">
         <v>4.961652464916135</v>
       </c>
       <c r="W2" t="n">
-        <v>4.851526995138777</v>
+        <v>4.851526995138784</v>
       </c>
       <c r="X2" t="n">
-        <v>4.853719656097176</v>
+        <v>4.853719656097182</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.850905540117211</v>
+        <v>4.850905540117216</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.804046199756204</v>
+        <v>4.804046199756206</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.851526995138777</v>
+        <v>4.851526995138784</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.854857475161326</v>
+        <v>4.854857475161332</v>
       </c>
     </row>
     <row r="3">
@@ -3791,7 +3791,7 @@
         <v>11.05262669488094</v>
       </c>
       <c r="E3" t="n">
-        <v>9.971778436935161</v>
+        <v>9.971778436935164</v>
       </c>
       <c r="F3" t="n">
         <v>11.05244653633846</v>
@@ -3873,79 +3873,79 @@
         <v>20.90809940370497</v>
       </c>
       <c r="C4" t="n">
-        <v>11.10770092787546</v>
+        <v>11.10770092787547</v>
       </c>
       <c r="D4" t="n">
-        <v>28.59449909572442</v>
+        <v>28.59449909572453</v>
       </c>
       <c r="E4" t="n">
-        <v>13.87233226735821</v>
+        <v>13.87233226735825</v>
       </c>
       <c r="F4" t="n">
-        <v>13.1471057176654</v>
+        <v>13.14710571766537</v>
       </c>
       <c r="G4" t="n">
-        <v>48.96696071618879</v>
+        <v>48.96696071618884</v>
       </c>
       <c r="H4" t="n">
-        <v>26.22542219932589</v>
+        <v>26.22542219932587</v>
       </c>
       <c r="I4" t="n">
-        <v>17.43373773523479</v>
+        <v>17.43373773523481</v>
       </c>
       <c r="J4" t="n">
         <v>35.42552503631593</v>
       </c>
       <c r="K4" t="n">
-        <v>23.13329353212897</v>
+        <v>23.133293532129</v>
       </c>
       <c r="L4" t="n">
-        <v>35.21522801253214</v>
+        <v>35.21522801253215</v>
       </c>
       <c r="M4" t="n">
-        <v>54.22471430360542</v>
+        <v>54.22471430360545</v>
       </c>
       <c r="N4" t="n">
-        <v>31.3878743665945</v>
+        <v>31.38787436659468</v>
       </c>
       <c r="O4" t="n">
-        <v>19.20638947292941</v>
+        <v>19.20638947292946</v>
       </c>
       <c r="P4" t="n">
-        <v>35.32841739444651</v>
+        <v>35.32841739444678</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.03548430337264</v>
+        <v>12.03548430337267</v>
       </c>
       <c r="R4" t="n">
         <v>18.60748279150798</v>
       </c>
       <c r="S4" t="n">
-        <v>35.31153645864631</v>
+        <v>35.31153645864633</v>
       </c>
       <c r="T4" t="n">
-        <v>22.95352258153093</v>
+        <v>22.95352258153102</v>
       </c>
       <c r="U4" t="n">
-        <v>31.3878743665945</v>
+        <v>31.38787436659468</v>
       </c>
       <c r="V4" t="n">
-        <v>15.00974438300852</v>
+        <v>15.00974438300856</v>
       </c>
       <c r="W4" t="n">
-        <v>38.58880801301648</v>
+        <v>38.58880801301638</v>
       </c>
       <c r="X4" t="n">
-        <v>40.9328340142518</v>
+        <v>40.93283401425192</v>
       </c>
       <c r="Y4" t="n">
-        <v>38.70857092495921</v>
+        <v>38.70857092495927</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.06771611132159</v>
+        <v>22.06771611132158</v>
       </c>
       <c r="AA4" t="n">
-        <v>29.88645066629426</v>
+        <v>29.88645066629427</v>
       </c>
       <c r="AB4" t="n">
         <v>52.56350964305046</v>
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.001833535606516</v>
+        <v>1.001833535606512</v>
       </c>
       <c r="C5" t="n">
-        <v>1.001833535606514</v>
+        <v>1.001833535606513</v>
       </c>
       <c r="D5" t="n">
-        <v>1.001833535606514</v>
+        <v>1.001833535606513</v>
       </c>
       <c r="E5" t="n">
-        <v>1.001833535606514</v>
+        <v>1.001833535606513</v>
       </c>
       <c r="F5" t="n">
-        <v>1.001833535606516</v>
+        <v>1.001833535606512</v>
       </c>
       <c r="G5" t="n">
-        <v>1.001833535606514</v>
+        <v>1.001833535606513</v>
       </c>
       <c r="H5" t="n">
-        <v>1.001833535606514</v>
+        <v>1.001833535606513</v>
       </c>
       <c r="I5" t="n">
-        <v>1.001833535606514</v>
+        <v>1.001833535606513</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9994606618822383</v>
+        <v>0.9994606618822376</v>
       </c>
       <c r="K5" t="n">
-        <v>1.001833535606514</v>
+        <v>1.001833535606513</v>
       </c>
       <c r="L5" t="n">
-        <v>1.001833535606514</v>
+        <v>1.001833535606513</v>
       </c>
       <c r="M5" t="n">
-        <v>1.001833535606514</v>
+        <v>1.001833535606513</v>
       </c>
       <c r="N5" t="n">
-        <v>1.001833535606516</v>
+        <v>1.001833535606512</v>
       </c>
       <c r="O5" t="n">
-        <v>1.001833535606516</v>
+        <v>1.001833535606512</v>
       </c>
       <c r="P5" t="n">
-        <v>1.001833535606516</v>
+        <v>1.001833535606512</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.001833535606516</v>
+        <v>1.001833535606512</v>
       </c>
       <c r="R5" t="n">
-        <v>1.001833535606514</v>
+        <v>1.001833535606513</v>
       </c>
       <c r="S5" t="n">
-        <v>1.001833535606514</v>
+        <v>1.001833535606513</v>
       </c>
       <c r="T5" t="n">
-        <v>1.001833535606514</v>
+        <v>1.001833535606513</v>
       </c>
       <c r="U5" t="n">
         <v>0.9834232527450657</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9862912714987655</v>
+        <v>0.9862912714987656</v>
       </c>
       <c r="W5" t="n">
-        <v>1.001833535606516</v>
+        <v>1.001833535606513</v>
       </c>
       <c r="X5" t="n">
-        <v>1.001833535606516</v>
+        <v>1.001833535606512</v>
       </c>
       <c r="Y5" t="n">
         <v>0.9834232527450657</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.001833535606514</v>
+        <v>1.001833535606513</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.001833535606514</v>
+        <v>1.001833535606513</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.001833535606516</v>
+        <v>1.001833535606512</v>
       </c>
     </row>
     <row r="6">
@@ -4046,85 +4046,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.577575286028855</v>
+        <v>1.118732680761106</v>
       </c>
       <c r="C6" t="n">
-        <v>1.118732680761107</v>
+        <v>1.118732680761106</v>
       </c>
       <c r="D6" t="n">
-        <v>1.577575286028855</v>
+        <v>1.577575286028859</v>
       </c>
       <c r="E6" t="n">
-        <v>1.118732680761107</v>
+        <v>1.118732680761106</v>
       </c>
       <c r="F6" t="n">
-        <v>1.118732680761107</v>
+        <v>1.577575286028859</v>
       </c>
       <c r="G6" t="n">
-        <v>1.577575286028855</v>
+        <v>1.118732680761106</v>
       </c>
       <c r="H6" t="n">
-        <v>1.118732680761107</v>
+        <v>1.118732680761106</v>
       </c>
       <c r="I6" t="n">
-        <v>1.577575286028855</v>
+        <v>1.118732680761106</v>
       </c>
       <c r="J6" t="n">
-        <v>1.575202412304576</v>
+        <v>1.575202412304584</v>
       </c>
       <c r="K6" t="n">
-        <v>1.118732680761107</v>
+        <v>1.577575286028859</v>
       </c>
       <c r="L6" t="n">
-        <v>1.577575286028855</v>
+        <v>1.118732680761106</v>
       </c>
       <c r="M6" t="n">
-        <v>1.577575286028855</v>
+        <v>1.577575286028859</v>
       </c>
       <c r="N6" t="n">
         <v>1.12177072188881</v>
       </c>
       <c r="O6" t="n">
-        <v>1.601547295488025</v>
+        <v>1.121770721888811</v>
       </c>
       <c r="P6" t="n">
         <v>1.601440121373086</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.577575286028855</v>
+        <v>1.577575286028859</v>
       </c>
       <c r="R6" t="n">
-        <v>1.577575286028855</v>
+        <v>1.577575286028859</v>
       </c>
       <c r="S6" t="n">
-        <v>1.118732680761107</v>
+        <v>1.118732680761106</v>
       </c>
       <c r="T6" t="n">
-        <v>1.118732680761107</v>
+        <v>1.118732680761106</v>
       </c>
       <c r="U6" t="n">
-        <v>1.577575286028855</v>
+        <v>1.118732680761106</v>
       </c>
       <c r="V6" t="n">
-        <v>1.562033021921103</v>
+        <v>1.562033021921113</v>
       </c>
       <c r="W6" t="n">
-        <v>1.60156511104691</v>
+        <v>1.142269331763233</v>
       </c>
       <c r="X6" t="n">
-        <v>1.118732680761107</v>
+        <v>1.118732680761106</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.131462674740275</v>
+        <v>1.131462674740273</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.577575286028855</v>
+        <v>1.118732680761106</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.118732680761107</v>
+        <v>1.577575286028859</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.129843935992688</v>
+        <v>1.129843935992689</v>
       </c>
     </row>
     <row r="7">
@@ -4134,43 +4134,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
       <c r="C7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
       <c r="D7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
       <c r="E7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
       <c r="F7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
       <c r="G7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
       <c r="H7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
       <c r="I7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
       <c r="J7" t="n">
-        <v>1.509574755762331</v>
+        <v>1.509574755762332</v>
       </c>
       <c r="K7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
       <c r="L7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
       <c r="M7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
       <c r="N7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
       <c r="O7" t="n">
         <v>1.510050226531974</v>
@@ -4179,40 +4179,40 @@
         <v>1.510050226531974</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
       <c r="R7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
       <c r="S7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
       <c r="T7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
       <c r="U7" t="n">
-        <v>1.50854448811569</v>
+        <v>1.508544488115689</v>
       </c>
       <c r="V7" t="n">
-        <v>1.496405365378853</v>
+        <v>1.496405365378858</v>
       </c>
       <c r="W7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
       <c r="X7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.511947629486606</v>
+        <v>1.511947629486607</v>
       </c>
     </row>
     <row r="8">
@@ -4222,85 +4222,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.744412810498202</v>
+        <v>1.744412810498204</v>
       </c>
       <c r="C8" t="n">
-        <v>2.340357772453611</v>
+        <v>2.340357772453614</v>
       </c>
       <c r="D8" t="n">
-        <v>2.340357772453611</v>
+        <v>2.340357772453614</v>
       </c>
       <c r="E8" t="n">
-        <v>2.340357772453611</v>
+        <v>2.023034659589714</v>
       </c>
       <c r="F8" t="n">
         <v>1.837254070557501</v>
       </c>
       <c r="G8" t="n">
-        <v>2.340357772453611</v>
+        <v>2.463930842495894</v>
       </c>
       <c r="H8" t="n">
-        <v>2.340357772453611</v>
+        <v>2.340357772453614</v>
       </c>
       <c r="I8" t="n">
-        <v>2.340357772453611</v>
+        <v>2.340357772453614</v>
       </c>
       <c r="J8" t="n">
-        <v>2.337984898729336</v>
+        <v>2.337984898729337</v>
       </c>
       <c r="K8" t="n">
-        <v>2.340357772453611</v>
+        <v>2.340357772453614</v>
       </c>
       <c r="L8" t="n">
-        <v>2.340357772453611</v>
+        <v>2.340357772453614</v>
       </c>
       <c r="M8" t="n">
-        <v>2.340357772453611</v>
+        <v>2.340357772453542</v>
       </c>
       <c r="N8" t="n">
-        <v>1.878400727389531</v>
+        <v>1.878400727389532</v>
       </c>
       <c r="O8" t="n">
         <v>2.00535053422048</v>
       </c>
       <c r="P8" t="n">
-        <v>1.974232069055563</v>
+        <v>1.974232069055568</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.627296023829945</v>
+        <v>1.627296023829942</v>
       </c>
       <c r="R8" t="n">
-        <v>2.340357772453611</v>
+        <v>2.340357772453614</v>
       </c>
       <c r="S8" t="n">
-        <v>2.340357772453611</v>
+        <v>2.340357772453614</v>
       </c>
       <c r="T8" t="n">
-        <v>2.340357772453611</v>
+        <v>2.340357772453614</v>
       </c>
       <c r="U8" t="n">
-        <v>1.972548560535976</v>
+        <v>2.048318079904004</v>
       </c>
       <c r="V8" t="n">
-        <v>2.324815508345857</v>
+        <v>2.160647696266029</v>
       </c>
       <c r="W8" t="n">
-        <v>2.340474892214354</v>
+        <v>2.340474892214357</v>
       </c>
       <c r="X8" t="n">
-        <v>1.681915563446727</v>
+        <v>1.68191556344673</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.930896039370176</v>
+        <v>2.930896039370182</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.340357772453611</v>
+        <v>1.733342826915589</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.340357772453611</v>
+        <v>2.340357772453614</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.962872116854932</v>
+        <v>2.96287211685494</v>
       </c>
     </row>
     <row r="9">
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.847056874728183</v>
+        <v>2.847056874728187</v>
       </c>
       <c r="C9" t="n">
-        <v>3.411385734993318</v>
+        <v>3.411385734993314</v>
       </c>
       <c r="D9" t="n">
-        <v>3.411385734993318</v>
+        <v>3.411385734993314</v>
       </c>
       <c r="E9" t="n">
-        <v>3.411385734993318</v>
+        <v>3.281141026739198</v>
       </c>
       <c r="F9" t="n">
-        <v>3.411385734993318</v>
+        <v>2.110453537976545</v>
       </c>
       <c r="G9" t="n">
-        <v>3.411385734993318</v>
+        <v>3.411385853088848</v>
       </c>
       <c r="H9" t="n">
-        <v>3.411385734993318</v>
+        <v>3.411385734993314</v>
       </c>
       <c r="I9" t="n">
-        <v>3.411385734993318</v>
+        <v>3.411385734993314</v>
       </c>
       <c r="J9" t="n">
-        <v>3.40901286126904</v>
+        <v>3.409012861269042</v>
       </c>
       <c r="K9" t="n">
-        <v>3.411385734993318</v>
+        <v>3.411385734993314</v>
       </c>
       <c r="L9" t="n">
-        <v>3.411385734993318</v>
+        <v>3.411385734993314</v>
       </c>
       <c r="M9" t="n">
-        <v>3.411385734993318</v>
+        <v>3.411385734993314</v>
       </c>
       <c r="N9" t="n">
-        <v>3.411385734993318</v>
+        <v>3.411385734993314</v>
       </c>
       <c r="O9" t="n">
-        <v>3.598403737591878</v>
+        <v>3.598403737591881</v>
       </c>
       <c r="P9" t="n">
-        <v>3.639076918784751</v>
+        <v>3.63907691878475</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.411385853088846</v>
+        <v>3.411385853088848</v>
       </c>
       <c r="R9" t="n">
-        <v>3.411385734993318</v>
+        <v>3.411385734993314</v>
       </c>
       <c r="S9" t="n">
-        <v>3.411385734993318</v>
+        <v>3.411385734993314</v>
       </c>
       <c r="T9" t="n">
-        <v>3.411385734993318</v>
+        <v>3.411385734993314</v>
       </c>
       <c r="U9" t="n">
-        <v>3.411385734993318</v>
+        <v>3.411385734993314</v>
       </c>
       <c r="V9" t="n">
-        <v>3.395843470885574</v>
+        <v>4.047066185607572</v>
       </c>
       <c r="W9" t="n">
-        <v>3.411385734993318</v>
+        <v>3.411385734993314</v>
       </c>
       <c r="X9" t="n">
-        <v>3.411385734993318</v>
+        <v>3.411385734993314</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.411385734993318</v>
+        <v>3.411385734993314</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.411385734993318</v>
+        <v>3.071145661228107</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.411385734993318</v>
+        <v>3.411385734993314</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.411385734993318</v>
+        <v>3.411385734993314</v>
       </c>
     </row>
     <row r="10">
@@ -4398,22 +4398,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10.55376346448124</v>
+        <v>10.55376346448125</v>
       </c>
       <c r="C10" t="n">
-        <v>10.81391912503647</v>
+        <v>10.81391912503648</v>
       </c>
       <c r="D10" t="n">
         <v>10.43733059710119</v>
       </c>
       <c r="E10" t="n">
-        <v>9.67012272409314</v>
+        <v>9.670122724093138</v>
       </c>
       <c r="F10" t="n">
-        <v>10.78160519365079</v>
+        <v>10.7816051936508</v>
       </c>
       <c r="G10" t="n">
-        <v>9.840095551002918</v>
+        <v>9.84009555100292</v>
       </c>
       <c r="H10" t="n">
         <v>10.52172625765304</v>
@@ -4422,7 +4422,7 @@
         <v>10.69295857960971</v>
       </c>
       <c r="J10" t="n">
-        <v>10.21363275522016</v>
+        <v>10.21363275522015</v>
       </c>
       <c r="K10" t="n">
         <v>10.49865447585437</v>
@@ -4431,13 +4431,13 @@
         <v>10.2447908458708</v>
       </c>
       <c r="M10" t="n">
-        <v>9.88831940732244</v>
+        <v>9.888319407322442</v>
       </c>
       <c r="N10" t="n">
         <v>10.50553347297242</v>
       </c>
       <c r="O10" t="n">
-        <v>10.57076342584161</v>
+        <v>10.57076342584162</v>
       </c>
       <c r="P10" t="n">
         <v>10.18417264583742</v>
@@ -4476,7 +4476,7 @@
         <v>10.38140054476275</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.974820399307735</v>
+        <v>9.97482039930774</v>
       </c>
     </row>
     <row r="11">
@@ -4486,61 +4486,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.624542635524131</v>
+        <v>4.624542635524135</v>
       </c>
       <c r="C11" t="n">
-        <v>4.642256459343362</v>
+        <v>4.642256459343367</v>
       </c>
       <c r="D11" t="n">
-        <v>4.535472371426179</v>
+        <v>4.535472371426182</v>
       </c>
       <c r="E11" t="n">
-        <v>3.560151380894877</v>
+        <v>3.560151380894879</v>
       </c>
       <c r="F11" t="n">
-        <v>4.633457795362289</v>
+        <v>4.633457795362291</v>
       </c>
       <c r="G11" t="n">
-        <v>4.362564916979479</v>
+        <v>4.362564916979481</v>
       </c>
       <c r="H11" t="n">
-        <v>4.609965604320778</v>
+        <v>4.60996560432078</v>
       </c>
       <c r="I11" t="n">
-        <v>4.687876856496094</v>
+        <v>4.687876856496097</v>
       </c>
       <c r="J11" t="n">
-        <v>4.467415346160646</v>
+        <v>4.467415346160647</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5994190102476</v>
+        <v>4.599419010247605</v>
       </c>
       <c r="L11" t="n">
         <v>4.483959109419068</v>
       </c>
       <c r="M11" t="n">
-        <v>4.380005028178239</v>
+        <v>4.380005028178241</v>
       </c>
       <c r="N11" t="n">
-        <v>4.55446716816996</v>
+        <v>4.554467168169961</v>
       </c>
       <c r="O11" t="n">
-        <v>4.632151418571995</v>
+        <v>4.632151418571996</v>
       </c>
       <c r="P11" t="n">
         <v>4.456363358718678</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.735090291089682</v>
+        <v>4.735090291089685</v>
       </c>
       <c r="R11" t="n">
-        <v>4.679736407179083</v>
+        <v>4.679736407179086</v>
       </c>
       <c r="S11" t="n">
-        <v>4.46133692198909</v>
+        <v>4.461336921989095</v>
       </c>
       <c r="T11" t="n">
-        <v>4.630937444611171</v>
+        <v>4.630937444611172</v>
       </c>
       <c r="U11" t="n">
         <v>4.515409229346095</v>
@@ -4549,22 +4549,22 @@
         <v>4.79374281876004</v>
       </c>
       <c r="W11" t="n">
-        <v>4.453649053266775</v>
+        <v>4.453649053266779</v>
       </c>
       <c r="X11" t="n">
-        <v>4.442384353634829</v>
+        <v>4.44238435363483</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.448449559129877</v>
+        <v>4.448449559129874</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.550725892920449</v>
+        <v>4.55072589292045</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.54611695776418</v>
+        <v>4.546116957764185</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.362793895234363</v>
+        <v>4.362793895234366</v>
       </c>
     </row>
   </sheetData>
@@ -4733,13 +4733,13 @@
         <v>4.820906631468678</v>
       </c>
       <c r="C2" t="n">
-        <v>4.741008848950675</v>
+        <v>4.741008848950676</v>
       </c>
       <c r="D2" t="n">
         <v>4.766144357539615</v>
       </c>
       <c r="E2" t="n">
-        <v>3.667172880496831</v>
+        <v>3.66717288049683</v>
       </c>
       <c r="F2" t="n">
         <v>4.747921604464699</v>
@@ -4754,7 +4754,7 @@
         <v>4.820906631468678</v>
       </c>
       <c r="J2" t="n">
-        <v>4.818931402332491</v>
+        <v>4.818931402332492</v>
       </c>
       <c r="K2" t="n">
         <v>4.820781880034988</v>
@@ -4766,7 +4766,7 @@
         <v>4.863537987591811</v>
       </c>
       <c r="N2" t="n">
-        <v>4.774046787369466</v>
+        <v>4.774046787369463</v>
       </c>
       <c r="O2" t="n">
         <v>4.820618968434169</v>
@@ -4790,7 +4790,7 @@
         <v>4.821889641773672</v>
       </c>
       <c r="V2" t="n">
-        <v>4.990282655322639</v>
+        <v>4.990282655322638</v>
       </c>
       <c r="W2" t="n">
         <v>4.820906631468678</v>
@@ -4827,7 +4827,7 @@
         <v>11.03576123989268</v>
       </c>
       <c r="E3" t="n">
-        <v>9.956322540656021</v>
+        <v>9.95632254065602</v>
       </c>
       <c r="F3" t="n">
         <v>11.03552212097578</v>
@@ -4842,7 +4842,7 @@
         <v>11.03576123989268</v>
       </c>
       <c r="J3" t="n">
-        <v>11.03378578466143</v>
+        <v>11.03378578466144</v>
       </c>
       <c r="K3" t="n">
         <v>11.03562472419565</v>
@@ -4906,85 +4906,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.13832652169289</v>
+        <v>18.13832652169291</v>
       </c>
       <c r="C4" t="n">
-        <v>12.67223879113319</v>
+        <v>12.6722387911332</v>
       </c>
       <c r="D4" t="n">
-        <v>19.20880434053713</v>
+        <v>19.20880434053712</v>
       </c>
       <c r="E4" t="n">
-        <v>9.561726979129002</v>
+        <v>9.561726979129011</v>
       </c>
       <c r="F4" t="n">
-        <v>15.03762673351973</v>
+        <v>15.03762673351971</v>
       </c>
       <c r="G4" t="n">
-        <v>40.68581623570714</v>
+        <v>40.6858162357072</v>
       </c>
       <c r="H4" t="n">
-        <v>23.64809693121171</v>
+        <v>23.64809693121174</v>
       </c>
       <c r="I4" t="n">
-        <v>18.04476596213342</v>
+        <v>18.04476596213343</v>
       </c>
       <c r="J4" t="n">
-        <v>31.2243557128871</v>
+        <v>31.22435571288714</v>
       </c>
       <c r="K4" t="n">
-        <v>26.8382215612704</v>
+        <v>26.83822156127049</v>
       </c>
       <c r="L4" t="n">
-        <v>29.09241672323542</v>
+        <v>29.09241672323543</v>
       </c>
       <c r="M4" t="n">
-        <v>44.44157792901066</v>
+        <v>44.44157792901068</v>
       </c>
       <c r="N4" t="n">
-        <v>32.0966648774059</v>
+        <v>32.09666487740581</v>
       </c>
       <c r="O4" t="n">
-        <v>15.72616256548588</v>
+        <v>15.72616256548584</v>
       </c>
       <c r="P4" t="n">
-        <v>31.94149066268117</v>
+        <v>31.94149066268118</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.92059224495154</v>
+        <v>14.92059224495157</v>
       </c>
       <c r="R4" t="n">
-        <v>16.98609326753477</v>
+        <v>16.98609326753479</v>
       </c>
       <c r="S4" t="n">
-        <v>31.44374025298862</v>
+        <v>31.44374025298865</v>
       </c>
       <c r="T4" t="n">
-        <v>20.68538245742371</v>
+        <v>20.68538245742369</v>
       </c>
       <c r="U4" t="n">
-        <v>32.09666487740586</v>
+        <v>32.09666487740581</v>
       </c>
       <c r="V4" t="n">
-        <v>22.32912935857089</v>
+        <v>22.32912935857088</v>
       </c>
       <c r="W4" t="n">
         <v>38.38823880723512</v>
       </c>
       <c r="X4" t="n">
-        <v>41.18331029155202</v>
+        <v>41.1833102915522</v>
       </c>
       <c r="Y4" t="n">
-        <v>56.89445011421222</v>
+        <v>56.89445011421228</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.71411892704774</v>
+        <v>18.71411892704775</v>
       </c>
       <c r="AA4" t="n">
-        <v>31.86070200223419</v>
+        <v>31.86070200223425</v>
       </c>
       <c r="AB4" t="n">
-        <v>47.0076241509534</v>
+        <v>47.00762415095343</v>
       </c>
     </row>
     <row r="5">
@@ -4994,7 +4994,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9534638500257411</v>
+        <v>0.9534638500257413</v>
       </c>
       <c r="C5" t="n">
         <v>0.9534638500257412</v>
@@ -5006,7 +5006,7 @@
         <v>0.9534638500257412</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9534638500257411</v>
+        <v>0.9534638500257413</v>
       </c>
       <c r="G5" t="n">
         <v>0.9534638500257412</v>
@@ -5018,7 +5018,7 @@
         <v>0.9534638500257412</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9515658912830161</v>
+        <v>0.9515658912830166</v>
       </c>
       <c r="K5" t="n">
         <v>0.9534638500257412</v>
@@ -5030,16 +5030,16 @@
         <v>0.9534638500257412</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9534638500257411</v>
+        <v>0.9534638500257413</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9534638500257411</v>
+        <v>0.9534638500257413</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9534638500257411</v>
+        <v>0.9534638500257413</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9534638500257411</v>
+        <v>0.9534638500257413</v>
       </c>
       <c r="R5" t="n">
         <v>0.9534638500257412</v>
@@ -5051,19 +5051,19 @@
         <v>0.9534638500257412</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9433955009380113</v>
+        <v>0.9433955009380123</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9409587552837103</v>
+        <v>0.9409587552837105</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9534638500257411</v>
+        <v>0.9534638500257413</v>
       </c>
       <c r="X5" t="n">
-        <v>0.9534638500257411</v>
+        <v>0.9534638500257413</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.9433955009380113</v>
+        <v>0.9433955009380123</v>
       </c>
       <c r="Z5" t="n">
         <v>0.9534638500257412</v>
@@ -5072,7 +5072,7 @@
         <v>0.9534638500257412</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9534638500257411</v>
+        <v>0.9534638500257413</v>
       </c>
     </row>
     <row r="6">
@@ -5082,85 +5082,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.089294258630795</v>
+        <v>1.519536863224299</v>
       </c>
       <c r="C6" t="n">
-        <v>1.089294258630795</v>
+        <v>1.089294258630796</v>
       </c>
       <c r="D6" t="n">
-        <v>1.089294258630795</v>
+        <v>1.089294258630796</v>
       </c>
       <c r="E6" t="n">
-        <v>1.089294258630795</v>
+        <v>1.519536863224299</v>
       </c>
       <c r="F6" t="n">
-        <v>1.089294258630795</v>
+        <v>1.089294258630796</v>
       </c>
       <c r="G6" t="n">
-        <v>1.089294258630795</v>
+        <v>1.519536863224299</v>
       </c>
       <c r="H6" t="n">
-        <v>1.519536863224298</v>
+        <v>1.089294258630796</v>
       </c>
       <c r="I6" t="n">
-        <v>1.089294258630795</v>
+        <v>1.089294258630796</v>
       </c>
       <c r="J6" t="n">
-        <v>1.087396299888069</v>
+        <v>1.517638904481575</v>
       </c>
       <c r="K6" t="n">
-        <v>1.519536863224298</v>
+        <v>1.519536863224299</v>
       </c>
       <c r="L6" t="n">
-        <v>1.089294258630795</v>
+        <v>1.519536863224299</v>
       </c>
       <c r="M6" t="n">
-        <v>1.089294258630795</v>
+        <v>1.089294258630796</v>
       </c>
       <c r="N6" t="n">
-        <v>1.095046908125935</v>
+        <v>1.095046908125892</v>
       </c>
       <c r="O6" t="n">
-        <v>1.095046908125934</v>
+        <v>1.544557240530011</v>
       </c>
       <c r="P6" t="n">
-        <v>1.544423491041113</v>
+        <v>1.076721508457709</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.519536863224298</v>
+        <v>1.519536863224299</v>
       </c>
       <c r="R6" t="n">
-        <v>1.519536863224298</v>
+        <v>1.519536863224299</v>
       </c>
       <c r="S6" t="n">
-        <v>1.519536863224298</v>
+        <v>1.519536863224299</v>
       </c>
       <c r="T6" t="n">
-        <v>1.089294258630795</v>
+        <v>1.519536863224299</v>
       </c>
       <c r="U6" t="n">
-        <v>1.519536863224298</v>
+        <v>1.089294258630796</v>
       </c>
       <c r="V6" t="n">
-        <v>1.507031768482268</v>
+        <v>1.076789163888763</v>
       </c>
       <c r="W6" t="n">
-        <v>1.544577398310538</v>
+        <v>1.544577398310536</v>
       </c>
       <c r="X6" t="n">
-        <v>1.089294258630795</v>
+        <v>1.089294258630796</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.107289785622543</v>
+        <v>1.10728978562242</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.519536863224298</v>
+        <v>1.519536863224299</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.519536863224298</v>
+        <v>1.519536863224299</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.100216120855742</v>
+        <v>1.100216120855741</v>
       </c>
     </row>
     <row r="7">
@@ -5230,7 +5230,7 @@
         <v>1.439520358852758</v>
       </c>
       <c r="V7" t="n">
-        <v>1.433572636828107</v>
+        <v>1.433572636828106</v>
       </c>
       <c r="W7" t="n">
         <v>1.446077731570137</v>
@@ -5267,13 +5267,13 @@
         <v>2.229668659690807</v>
       </c>
       <c r="E8" t="n">
-        <v>2.229668659690807</v>
+        <v>1.927010989721683</v>
       </c>
       <c r="F8" t="n">
         <v>1.749816458583555</v>
       </c>
       <c r="G8" t="n">
-        <v>2.229668659690807</v>
+        <v>2.347530661964445</v>
       </c>
       <c r="H8" t="n">
         <v>2.229668659690807</v>
@@ -5282,7 +5282,7 @@
         <v>2.229668659690807</v>
       </c>
       <c r="J8" t="n">
-        <v>2.227770700948081</v>
+        <v>2.22777070094808</v>
       </c>
       <c r="K8" t="n">
         <v>2.229668659690807</v>
@@ -5291,19 +5291,19 @@
         <v>2.229668659690807</v>
       </c>
       <c r="M8" t="n">
-        <v>2.229668659690807</v>
+        <v>2.229668659690645</v>
       </c>
       <c r="N8" t="n">
-        <v>1.78906147660699</v>
+        <v>1.789061476606989</v>
       </c>
       <c r="O8" t="n">
-        <v>1.910144155995344</v>
+        <v>1.910144155995345</v>
       </c>
       <c r="P8" t="n">
         <v>1.880463865535117</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.549561858029059</v>
+        <v>1.54956185802906</v>
       </c>
       <c r="R8" t="n">
         <v>2.229668659690807</v>
@@ -5315,28 +5315,28 @@
         <v>2.229668659690807</v>
       </c>
       <c r="U8" t="n">
-        <v>1.876511092348334</v>
+        <v>1.948626327898088</v>
       </c>
       <c r="V8" t="n">
-        <v>2.217163564948776</v>
+        <v>2.057825987877072</v>
       </c>
       <c r="W8" t="n">
-        <v>2.229780366622154</v>
+        <v>2.22978036662215</v>
       </c>
       <c r="X8" t="n">
-        <v>1.60165709447278</v>
+        <v>1.601657094472779</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.788638484422186</v>
+        <v>2.788638484422185</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.229668659690807</v>
+        <v>1.650707589393137</v>
       </c>
       <c r="AA8" t="n">
         <v>2.229668659690807</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.823412806775155</v>
+        <v>2.823412806775153</v>
       </c>
     </row>
     <row r="9">
@@ -5346,85 +5346,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.624458167825826</v>
+        <v>2.624458167825823</v>
       </c>
       <c r="C9" t="n">
-        <v>3.138233098629348</v>
+        <v>3.138233098629344</v>
       </c>
       <c r="D9" t="n">
-        <v>3.138233098629348</v>
+        <v>3.138233098629344</v>
       </c>
       <c r="E9" t="n">
-        <v>3.138233098629348</v>
+        <v>3.019655986530042</v>
       </c>
       <c r="F9" t="n">
-        <v>3.138233098629348</v>
+        <v>1.953841582111087</v>
       </c>
       <c r="G9" t="n">
-        <v>3.138233098629348</v>
+        <v>3.138233158795908</v>
       </c>
       <c r="H9" t="n">
-        <v>3.138233098629348</v>
+        <v>3.138233098629344</v>
       </c>
       <c r="I9" t="n">
-        <v>3.138233098629348</v>
+        <v>3.138233098629344</v>
       </c>
       <c r="J9" t="n">
-        <v>3.136335139886621</v>
+        <v>3.136335139886617</v>
       </c>
       <c r="K9" t="n">
-        <v>3.138233098629348</v>
+        <v>3.138233098629344</v>
       </c>
       <c r="L9" t="n">
-        <v>3.138233098629348</v>
+        <v>3.138233098629344</v>
       </c>
       <c r="M9" t="n">
-        <v>3.138233098629348</v>
+        <v>3.138233098629344</v>
       </c>
       <c r="N9" t="n">
-        <v>3.138233098629348</v>
+        <v>3.138233098629344</v>
       </c>
       <c r="O9" t="n">
-        <v>3.308497518072506</v>
+        <v>3.308497518072505</v>
       </c>
       <c r="P9" t="n">
         <v>3.345527094970704</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.138233158795911</v>
+        <v>3.138233158795908</v>
       </c>
       <c r="R9" t="n">
-        <v>3.138233098629348</v>
+        <v>3.138233098629344</v>
       </c>
       <c r="S9" t="n">
-        <v>3.138233098629348</v>
+        <v>3.138233098629344</v>
       </c>
       <c r="T9" t="n">
-        <v>3.138233098629348</v>
+        <v>3.138233098629344</v>
       </c>
       <c r="U9" t="n">
-        <v>3.138233098629348</v>
+        <v>3.138233098629344</v>
       </c>
       <c r="V9" t="n">
-        <v>3.125728003887315</v>
+        <v>3.71861269104941</v>
       </c>
       <c r="W9" t="n">
-        <v>3.138233098629348</v>
+        <v>3.138233098629344</v>
       </c>
       <c r="X9" t="n">
-        <v>3.138233098629348</v>
+        <v>3.138233098629344</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.138233098629348</v>
+        <v>3.138233098629344</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.138233098629348</v>
+        <v>2.828472525895724</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.138233098629348</v>
+        <v>3.138233098629344</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.138233098629348</v>
+        <v>3.138233098629344</v>
       </c>
     </row>
     <row r="10">
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10.59101485795524</v>
+        <v>10.59101485795523</v>
       </c>
       <c r="C10" t="n">
         <v>10.75638335894703</v>
@@ -5449,13 +5449,13 @@
         <v>10.71852983209153</v>
       </c>
       <c r="G10" t="n">
-        <v>9.994987998525554</v>
+        <v>9.994987998525552</v>
       </c>
       <c r="H10" t="n">
         <v>10.5597572942702</v>
       </c>
       <c r="I10" t="n">
-        <v>10.65501514853269</v>
+        <v>10.65501514853268</v>
       </c>
       <c r="J10" t="n">
         <v>10.28249841781726</v>
@@ -5464,7 +5464,7 @@
         <v>10.38760029021212</v>
       </c>
       <c r="L10" t="n">
-        <v>10.34404839882844</v>
+        <v>10.34404839882843</v>
       </c>
       <c r="M10" t="n">
         <v>10.04111671441101</v>
@@ -5479,7 +5479,7 @@
         <v>10.22233832570227</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.70321092892705</v>
+        <v>10.70321092892704</v>
       </c>
       <c r="R10" t="n">
         <v>10.69204602347905</v>
@@ -5503,13 +5503,13 @@
         <v>10.09594630563472</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.749157660109088</v>
+        <v>9.749157660109086</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.53940571153314</v>
+        <v>10.53940571153313</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.32181331060395</v>
+        <v>10.32181331060394</v>
       </c>
       <c r="AB10" t="n">
         <v>10.0589388518389</v>
@@ -5522,37 +5522,37 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.618545610364517</v>
+        <v>4.618545610364516</v>
       </c>
       <c r="C11" t="n">
         <v>4.614053912558506</v>
       </c>
       <c r="D11" t="n">
-        <v>4.573217773945818</v>
+        <v>4.573217773945816</v>
       </c>
       <c r="E11" t="n">
         <v>3.570232872509551</v>
       </c>
       <c r="F11" t="n">
-        <v>4.603689102827878</v>
+        <v>4.603689102827879</v>
       </c>
       <c r="G11" t="n">
-        <v>4.39516960365038</v>
+        <v>4.395169603650378</v>
       </c>
       <c r="H11" t="n">
-        <v>4.60432331927588</v>
+        <v>4.604323319275879</v>
       </c>
       <c r="I11" t="n">
-        <v>4.647665946534082</v>
+        <v>4.647665946534081</v>
       </c>
       <c r="J11" t="n">
-        <v>4.477093256207611</v>
+        <v>4.47709325620761</v>
       </c>
       <c r="K11" t="n">
         <v>4.525928697441144</v>
       </c>
       <c r="L11" t="n">
-        <v>4.506175084426416</v>
+        <v>4.506175084426415</v>
       </c>
       <c r="M11" t="n">
         <v>4.411253517822414</v>
@@ -5561,34 +5561,34 @@
         <v>4.559151705728891</v>
       </c>
       <c r="O11" t="n">
-        <v>4.643428836502431</v>
+        <v>4.643428836502428</v>
       </c>
       <c r="P11" t="n">
-        <v>4.450524731411829</v>
+        <v>4.450524731411828</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.669593575887858</v>
+        <v>4.669593575887857</v>
       </c>
       <c r="R11" t="n">
-        <v>4.66486790239093</v>
+        <v>4.664867902390928</v>
       </c>
       <c r="S11" t="n">
-        <v>4.469239972796164</v>
+        <v>4.469239972796163</v>
       </c>
       <c r="T11" t="n">
-        <v>4.622749540960114</v>
+        <v>4.622749540960113</v>
       </c>
       <c r="U11" t="n">
-        <v>4.463977090094915</v>
+        <v>4.463977090094913</v>
       </c>
       <c r="V11" t="n">
         <v>4.730486290598659</v>
       </c>
       <c r="W11" t="n">
-        <v>4.425374070389164</v>
+        <v>4.425374070389163</v>
       </c>
       <c r="X11" t="n">
-        <v>4.393792554206777</v>
+        <v>4.393792554206774</v>
       </c>
       <c r="Y11" t="n">
         <v>4.234950449840012</v>
@@ -5597,7 +5597,7 @@
         <v>4.551416887710485</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.496058048425254</v>
+        <v>4.496058048425253</v>
       </c>
       <c r="AB11" t="n">
         <v>4.378121531302217</v>
@@ -5766,85 +5766,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.619519148346622</v>
+        <v>4.61951914834662</v>
       </c>
       <c r="C2" t="n">
-        <v>4.587880209950175</v>
+        <v>4.587880209950171</v>
       </c>
       <c r="D2" t="n">
-        <v>4.61689244726087</v>
+        <v>4.616892447260867</v>
       </c>
       <c r="E2" t="n">
-        <v>3.565470478494606</v>
+        <v>3.565470478494602</v>
       </c>
       <c r="F2" t="n">
         <v>4.578439927948483</v>
       </c>
       <c r="G2" t="n">
-        <v>4.640396392668876</v>
+        <v>4.640396392668874</v>
       </c>
       <c r="H2" t="n">
-        <v>4.619519148346622</v>
+        <v>4.61951914834662</v>
       </c>
       <c r="I2" t="n">
-        <v>4.619519148346622</v>
+        <v>4.61951914834662</v>
       </c>
       <c r="J2" t="n">
-        <v>4.617994774977133</v>
+        <v>4.617994774977132</v>
       </c>
       <c r="K2" t="n">
-        <v>4.619450542097418</v>
+        <v>4.619450542097416</v>
       </c>
       <c r="L2" t="n">
-        <v>4.619519148346622</v>
+        <v>4.61951914834662</v>
       </c>
       <c r="M2" t="n">
-        <v>4.644475598866682</v>
+        <v>4.644475598866681</v>
       </c>
       <c r="N2" t="n">
-        <v>4.60482359387953</v>
+        <v>4.604823593879529</v>
       </c>
       <c r="O2" t="n">
-        <v>4.61929396880681</v>
+        <v>4.619293968806808</v>
       </c>
       <c r="P2" t="n">
-        <v>4.619462784905229</v>
+        <v>4.619462784905228</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.619515953043907</v>
+        <v>4.619515953043904</v>
       </c>
       <c r="R2" t="n">
-        <v>4.619506465567463</v>
+        <v>4.61950646556746</v>
       </c>
       <c r="S2" t="n">
-        <v>4.619519148346622</v>
+        <v>4.61951914834662</v>
       </c>
       <c r="T2" t="n">
-        <v>4.61942119983344</v>
+        <v>4.619421199833439</v>
       </c>
       <c r="U2" t="n">
-        <v>4.61974030720525</v>
+        <v>4.619740307205247</v>
       </c>
       <c r="V2" t="n">
-        <v>4.783224562504627</v>
+        <v>4.783224562504617</v>
       </c>
       <c r="W2" t="n">
-        <v>4.619519148346622</v>
+        <v>4.61951914834662</v>
       </c>
       <c r="X2" t="n">
-        <v>4.619702844595835</v>
+        <v>4.619702844595833</v>
       </c>
       <c r="Y2" t="n">
         <v>4.619002113263551</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.59613613396695</v>
+        <v>4.596136133966946</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.619519148346622</v>
+        <v>4.61951914834662</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.62284962836917</v>
+        <v>4.622849628369169</v>
       </c>
     </row>
     <row r="3">
@@ -5863,10 +5863,10 @@
         <v>10.9200004594639</v>
       </c>
       <c r="E3" t="n">
-        <v>9.889923468628993</v>
+        <v>9.889923468628991</v>
       </c>
       <c r="F3" t="n">
-        <v>10.91987281428939</v>
+        <v>10.91987281428938</v>
       </c>
       <c r="G3" t="n">
         <v>10.91996121622388</v>
@@ -5881,7 +5881,7 @@
         <v>10.91847591246967</v>
       </c>
       <c r="K3" t="n">
-        <v>10.91992538351815</v>
+        <v>10.91992538351814</v>
       </c>
       <c r="L3" t="n">
         <v>10.9200004594639</v>
@@ -5893,16 +5893,16 @@
         <v>10.9200004594639</v>
       </c>
       <c r="O3" t="n">
-        <v>10.91975404514784</v>
+        <v>10.91975404514783</v>
       </c>
       <c r="P3" t="n">
-        <v>10.91993878071051</v>
+        <v>10.9199387807105</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.91999696281539</v>
+        <v>10.91999696281538</v>
       </c>
       <c r="R3" t="n">
-        <v>10.91998658059368</v>
+        <v>10.91998658059367</v>
       </c>
       <c r="S3" t="n">
         <v>10.9200004594639</v>
@@ -5914,7 +5914,7 @@
         <v>10.92024247374234</v>
       </c>
       <c r="V3" t="n">
-        <v>11.11259782491094</v>
+        <v>11.11259782491093</v>
       </c>
       <c r="W3" t="n">
         <v>10.9200004594639</v>
@@ -5942,85 +5942,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.468084226303501</v>
+        <v>4.468084226303496</v>
       </c>
       <c r="C4" t="n">
-        <v>3.253731659069881</v>
+        <v>3.253731659069876</v>
       </c>
       <c r="D4" t="n">
         <v>11.32820893527336</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8768717470550722</v>
+        <v>0.8768717470550758</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6357162404198657</v>
+        <v>0.6357162404198764</v>
       </c>
       <c r="G4" t="n">
-        <v>15.01856662304566</v>
+        <v>15.0185666230457</v>
       </c>
       <c r="H4" t="n">
-        <v>6.368720533204867</v>
+        <v>6.368720533204845</v>
       </c>
       <c r="I4" t="n">
-        <v>5.087879575924985</v>
+        <v>5.087879575924971</v>
       </c>
       <c r="J4" t="n">
         <v>10.72723587848439</v>
       </c>
       <c r="K4" t="n">
-        <v>10.93694431903627</v>
+        <v>10.93694431903625</v>
       </c>
       <c r="L4" t="n">
-        <v>1.915107101271865</v>
+        <v>1.91510710127184</v>
       </c>
       <c r="M4" t="n">
-        <v>17.61201739474446</v>
+        <v>17.61201739474447</v>
       </c>
       <c r="N4" t="n">
-        <v>19.41245949212378</v>
+        <v>19.41245949212376</v>
       </c>
       <c r="O4" t="n">
-        <v>3.140756198550287</v>
+        <v>3.140756198550177</v>
       </c>
       <c r="P4" t="n">
-        <v>5.506921205776362</v>
+        <v>5.506921205776282</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.566732952863648</v>
+        <v>4.566732952863651</v>
       </c>
       <c r="R4" t="n">
-        <v>-14.06243241323422</v>
+        <v>-14.06243241323423</v>
       </c>
       <c r="S4" t="n">
-        <v>7.277232774768617</v>
+        <v>7.277232774768631</v>
       </c>
       <c r="T4" t="n">
-        <v>3.531880137667378</v>
+        <v>3.531880137667363</v>
       </c>
       <c r="U4" t="n">
-        <v>19.41245949212378</v>
+        <v>19.41245949212376</v>
       </c>
       <c r="V4" t="n">
-        <v>4.356995283284133</v>
+        <v>4.356995283284132</v>
       </c>
       <c r="W4" t="n">
-        <v>37.91678990167201</v>
+        <v>37.91678990167205</v>
       </c>
       <c r="X4" t="n">
-        <v>18.84728898265841</v>
+        <v>18.84728898265839</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.754767280369961</v>
+        <v>8.754767280369819</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.888789224955975</v>
+        <v>4.888789224955968</v>
       </c>
       <c r="AA4" t="n">
-        <v>19.26813982745758</v>
+        <v>19.26813982745762</v>
       </c>
       <c r="AB4" t="n">
-        <v>15.52011224514896</v>
+        <v>15.52011224514899</v>
       </c>
     </row>
     <row r="5">
@@ -6030,85 +6030,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6939818125590161</v>
+        <v>0.6939818125590173</v>
       </c>
       <c r="C5" t="n">
+        <v>0.693981812559017</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.693981812559017</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.693981812559017</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.6939818125590173</v>
       </c>
-      <c r="D5" t="n">
+      <c r="G5" t="n">
+        <v>0.693981812559017</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.693981812559017</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.693981812559017</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.6922004664807537</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.693981812559017</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.693981812559017</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.693981812559017</v>
+      </c>
+      <c r="N5" t="n">
         <v>0.6939818125590173</v>
       </c>
-      <c r="E5" t="n">
+      <c r="O5" t="n">
         <v>0.6939818125590173</v>
       </c>
-      <c r="F5" t="n">
-        <v>0.6939818125590161</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="P5" t="n">
         <v>0.6939818125590173</v>
       </c>
-      <c r="H5" t="n">
+      <c r="Q5" t="n">
         <v>0.6939818125590173</v>
       </c>
-      <c r="I5" t="n">
+      <c r="R5" t="n">
+        <v>0.693981812559017</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.693981812559017</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.693981812559017</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.6828521633274327</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.6822193930336476</v>
+      </c>
+      <c r="W5" t="n">
         <v>0.6939818125590173</v>
       </c>
-      <c r="J5" t="n">
-        <v>0.6922004664807541</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="X5" t="n">
         <v>0.6939818125590173</v>
       </c>
-      <c r="L5" t="n">
+      <c r="Y5" t="n">
+        <v>0.6828521633274327</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.693981812559017</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.693981812559017</v>
+      </c>
+      <c r="AB5" t="n">
         <v>0.6939818125590173</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.6939818125590173</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.6939818125590161</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.6939818125590161</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.6939818125590161</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.6939818125590161</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.6939818125590173</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.6939818125590173</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.6939818125590173</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.6828521633274313</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.6822193930336465</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0.6939818125590161</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.6939818125590161</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.6828521633274313</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.6939818125590173</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.6939818125590173</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.6939818125590161</v>
       </c>
     </row>
     <row r="6">
@@ -6118,85 +6118,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7650027075084959</v>
+        <v>0.7650027075084991</v>
       </c>
       <c r="C6" t="n">
-        <v>1.079721891897813</v>
+        <v>1.079721891897814</v>
       </c>
       <c r="D6" t="n">
-        <v>1.079721891897813</v>
+        <v>0.7650027075084991</v>
       </c>
       <c r="E6" t="n">
-        <v>1.079721891897813</v>
+        <v>0.7650027075084991</v>
       </c>
       <c r="F6" t="n">
-        <v>1.079721891897813</v>
+        <v>1.079721891897814</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7650027075084959</v>
+        <v>1.079721891897814</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7650027075084959</v>
+        <v>0.7650027075084991</v>
       </c>
       <c r="I6" t="n">
-        <v>1.079721891897813</v>
+        <v>0.7650027075084991</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7632213614302593</v>
+        <v>0.7632213614302348</v>
       </c>
       <c r="K6" t="n">
-        <v>1.079721891897813</v>
+        <v>0.7650027075084991</v>
       </c>
       <c r="L6" t="n">
-        <v>1.079721891897813</v>
+        <v>0.7650027075084991</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7650027075084959</v>
+        <v>1.079721891897814</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7673012700721386</v>
+        <v>0.7673012700721236</v>
       </c>
       <c r="O6" t="n">
-        <v>1.109704502808165</v>
+        <v>1.10970450280817</v>
       </c>
       <c r="P6" t="n">
-        <v>1.109600649485839</v>
+        <v>0.753433751406695</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.079721891897813</v>
+        <v>1.079721891897814</v>
       </c>
       <c r="R6" t="n">
-        <v>1.079721891897813</v>
+        <v>0.7650027075084991</v>
       </c>
       <c r="S6" t="n">
-        <v>1.079721891897813</v>
+        <v>0.7650027075084991</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7650027075084959</v>
+        <v>1.079721891897814</v>
       </c>
       <c r="U6" t="n">
-        <v>1.079721891897813</v>
+        <v>0.7650027075084991</v>
       </c>
       <c r="V6" t="n">
-        <v>0.753240287983165</v>
+        <v>1.067959472372443</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7892694170976987</v>
+        <v>0.7892694170976529</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7650027075084959</v>
+        <v>0.7650027075084991</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.7764367294775605</v>
+        <v>0.7764367294777104</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.7650027075084959</v>
+        <v>1.079721891897814</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.7650027075084959</v>
+        <v>1.079721891897814</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7695819907156093</v>
+        <v>0.7695819907156106</v>
       </c>
     </row>
     <row r="7">
@@ -6206,61 +6206,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
       <c r="C7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
       <c r="D7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
       <c r="E7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
       <c r="F7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
       <c r="G7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
       <c r="H7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
       <c r="I7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
       <c r="J7" t="n">
-        <v>1.122141325809143</v>
+        <v>1.122141325809144</v>
       </c>
       <c r="K7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
       <c r="L7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
       <c r="M7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
       <c r="N7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
       <c r="O7" t="n">
-        <v>1.121892007746253</v>
+        <v>1.121892007746254</v>
       </c>
       <c r="P7" t="n">
-        <v>1.121892007746253</v>
+        <v>1.121892007746254</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
       <c r="R7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
       <c r="S7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
       <c r="T7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
       <c r="U7" t="n">
         <v>1.116653207581304</v>
@@ -6269,22 +6269,22 @@
         <v>1.112160252362038</v>
       </c>
       <c r="W7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
       <c r="X7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.123922671887406</v>
+        <v>1.123922671887407</v>
       </c>
     </row>
     <row r="8">
@@ -6294,85 +6294,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.272076080159217</v>
+        <v>1.272076080159215</v>
       </c>
       <c r="C8" t="n">
-        <v>1.748268787688051</v>
+        <v>1.748268787688048</v>
       </c>
       <c r="D8" t="n">
-        <v>1.748268787688051</v>
+        <v>1.748268787688048</v>
       </c>
       <c r="E8" t="n">
-        <v>1.748268787688051</v>
+        <v>1.494710217822739</v>
       </c>
       <c r="F8" t="n">
-        <v>1.346261338554673</v>
+        <v>1.346261338554669</v>
       </c>
       <c r="G8" t="n">
-        <v>1.748268787688051</v>
+        <v>1.847010447659893</v>
       </c>
       <c r="H8" t="n">
-        <v>1.748268787688051</v>
+        <v>1.748268787688048</v>
       </c>
       <c r="I8" t="n">
-        <v>1.748268787688051</v>
+        <v>1.748268787688048</v>
       </c>
       <c r="J8" t="n">
-        <v>1.746487441609779</v>
+        <v>1.746487441609786</v>
       </c>
       <c r="K8" t="n">
-        <v>1.748268787688051</v>
+        <v>1.748268787688048</v>
       </c>
       <c r="L8" t="n">
-        <v>1.748268787688051</v>
+        <v>1.748268787688048</v>
       </c>
       <c r="M8" t="n">
-        <v>1.748268787688051</v>
+        <v>1.748268787687325</v>
       </c>
       <c r="N8" t="n">
-        <v>1.379139773924827</v>
+        <v>1.379139773924825</v>
       </c>
       <c r="O8" t="n">
-        <v>1.480579631762605</v>
+        <v>1.480579631762604</v>
       </c>
       <c r="P8" t="n">
-        <v>1.455714271501296</v>
+        <v>1.455714271501297</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.178493344683514</v>
+        <v>1.178493344683511</v>
       </c>
       <c r="R8" t="n">
-        <v>1.748268787688051</v>
+        <v>1.748268787688048</v>
       </c>
       <c r="S8" t="n">
-        <v>1.748268787688051</v>
+        <v>1.748268787688048</v>
       </c>
       <c r="T8" t="n">
-        <v>1.748268787688051</v>
+        <v>1.748268787688048</v>
       </c>
       <c r="U8" t="n">
-        <v>1.451432363529573</v>
+        <v>1.511785541014306</v>
       </c>
       <c r="V8" t="n">
-        <v>1.736506368162676</v>
+        <v>1.60187772411948</v>
       </c>
       <c r="W8" t="n">
-        <v>1.748362372734431</v>
+        <v>1.748362372734426</v>
       </c>
       <c r="X8" t="n">
-        <v>1.222137352253183</v>
+        <v>1.222137352253181</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.214790979086493</v>
+        <v>2.214790979086498</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.748268787688051</v>
+        <v>1.263230556176574</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.748268787688051</v>
+        <v>1.748268787688048</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.245691888858776</v>
+        <v>2.245691888858778</v>
       </c>
     </row>
     <row r="9">
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.088414965267484</v>
+        <v>2.088414965267486</v>
       </c>
       <c r="C9" t="n">
         <v>2.521442199404285</v>
@@ -6391,13 +6391,13 @@
         <v>2.521442199404285</v>
       </c>
       <c r="E9" t="n">
-        <v>2.521442199404285</v>
+        <v>2.42150127906756</v>
       </c>
       <c r="F9" t="n">
-        <v>2.521442199404285</v>
+        <v>1.523196242043493</v>
       </c>
       <c r="G9" t="n">
-        <v>2.521442199404285</v>
+        <v>2.521442198125222</v>
       </c>
       <c r="H9" t="n">
         <v>2.521442199404285</v>
@@ -6406,7 +6406,7 @@
         <v>2.521442199404285</v>
       </c>
       <c r="J9" t="n">
-        <v>2.519660853326021</v>
+        <v>2.519660853326022</v>
       </c>
       <c r="K9" t="n">
         <v>2.521442199404285</v>
@@ -6421,13 +6421,13 @@
         <v>2.521442199404285</v>
       </c>
       <c r="O9" t="n">
-        <v>2.664946856093501</v>
+        <v>2.6649468560935</v>
       </c>
       <c r="P9" t="n">
-        <v>2.696156657076308</v>
+        <v>2.696156657076307</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.521442198125225</v>
+        <v>2.521442198125222</v>
       </c>
       <c r="R9" t="n">
         <v>2.521442199404285</v>
@@ -6442,7 +6442,7 @@
         <v>2.521442199404285</v>
       </c>
       <c r="V9" t="n">
-        <v>2.509679779878922</v>
+        <v>3.009383582084805</v>
       </c>
       <c r="W9" t="n">
         <v>2.521442199404285</v>
@@ -6454,7 +6454,7 @@
         <v>2.521442199404285</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.521442199404285</v>
+        <v>2.260365282995956</v>
       </c>
       <c r="AA9" t="n">
         <v>2.521442199404285</v>
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10.83012206085491</v>
+        <v>10.8301220608549</v>
       </c>
       <c r="C10" t="n">
-        <v>10.86553478736972</v>
+        <v>10.86553478736971</v>
       </c>
       <c r="D10" t="n">
-        <v>10.69783230972817</v>
+        <v>10.69783230972816</v>
       </c>
       <c r="E10" t="n">
         <v>9.886810544763238</v>
@@ -6494,7 +6494,7 @@
         <v>10.8299150188716</v>
       </c>
       <c r="J10" t="n">
-        <v>10.67850042172362</v>
+        <v>10.67850042172361</v>
       </c>
       <c r="K10" t="n">
         <v>10.68537608075413</v>
@@ -6558,46 +6558,46 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.578624190554069</v>
+        <v>4.578624190554067</v>
       </c>
       <c r="C11" t="n">
-        <v>4.563253866874374</v>
+        <v>4.563253866874373</v>
       </c>
       <c r="D11" t="n">
-        <v>4.515805231123229</v>
+        <v>4.515805231123225</v>
       </c>
       <c r="E11" t="n">
-        <v>3.564054088215387</v>
+        <v>3.564054088215385</v>
       </c>
       <c r="F11" t="n">
-        <v>4.579521882791743</v>
+        <v>4.579521882791742</v>
       </c>
       <c r="G11" t="n">
-        <v>4.474094811592645</v>
+        <v>4.474094811592646</v>
       </c>
       <c r="H11" t="n">
-        <v>4.568510620220575</v>
+        <v>4.568510620220573</v>
       </c>
       <c r="I11" t="n">
-        <v>4.578529985791867</v>
+        <v>4.578529985791863</v>
       </c>
       <c r="J11" t="n">
-        <v>4.508805161931165</v>
+        <v>4.508805161931168</v>
       </c>
       <c r="K11" t="n">
-        <v>4.512729861875514</v>
+        <v>4.512729861875513</v>
       </c>
       <c r="L11" t="n">
-        <v>4.607638652024847</v>
+        <v>4.607638652024846</v>
       </c>
       <c r="M11" t="n">
         <v>4.470323448338149</v>
       </c>
       <c r="N11" t="n">
-        <v>4.535609085782671</v>
+        <v>4.535609085782669</v>
       </c>
       <c r="O11" t="n">
-        <v>4.592599866501719</v>
+        <v>4.592599866501721</v>
       </c>
       <c r="P11" t="n">
         <v>4.56800928261511</v>
@@ -6612,22 +6612,22 @@
         <v>4.540997013638004</v>
       </c>
       <c r="T11" t="n">
-        <v>4.592129702258544</v>
+        <v>4.592129702258545</v>
       </c>
       <c r="U11" t="n">
-        <v>4.423486093731466</v>
+        <v>4.423486093731465</v>
       </c>
       <c r="V11" t="n">
-        <v>4.743350372183208</v>
+        <v>4.743350372183198</v>
       </c>
       <c r="W11" t="n">
-        <v>4.252035690781284</v>
+        <v>4.252035690781279</v>
       </c>
       <c r="X11" t="n">
-        <v>4.444458407620553</v>
+        <v>4.444458407620551</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.538609411065248</v>
+        <v>4.538609411065247</v>
       </c>
       <c r="Z11" t="n">
         <v>4.549651423329506</v>
@@ -6636,7 +6636,7 @@
         <v>4.435743463581732</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.485112353834314</v>
+        <v>4.485112353834311</v>
       </c>
     </row>
   </sheetData>
@@ -6802,85 +6802,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.530727865960084</v>
+        <v>4.530727865960079</v>
       </c>
       <c r="C2" t="n">
-        <v>4.519117192718737</v>
+        <v>4.519117192718741</v>
       </c>
       <c r="D2" t="n">
-        <v>4.53188071126587</v>
+        <v>4.531880711265877</v>
       </c>
       <c r="E2" t="n">
-        <v>3.437610942403197</v>
+        <v>3.437610942403193</v>
       </c>
       <c r="F2" t="n">
         <v>4.462662133012868</v>
       </c>
       <c r="G2" t="n">
-        <v>4.557511105837368</v>
+        <v>4.557511105837374</v>
       </c>
       <c r="H2" t="n">
-        <v>4.530727865960084</v>
+        <v>4.530727865960079</v>
       </c>
       <c r="I2" t="n">
-        <v>4.530727865960084</v>
+        <v>4.530727865960079</v>
       </c>
       <c r="J2" t="n">
-        <v>4.530217729033085</v>
+        <v>4.530217729033088</v>
       </c>
       <c r="K2" t="n">
-        <v>4.530630552877033</v>
+        <v>4.53063055287703</v>
       </c>
       <c r="L2" t="n">
-        <v>4.530727865960084</v>
+        <v>4.530727865960079</v>
       </c>
       <c r="M2" t="n">
-        <v>4.515925533032179</v>
+        <v>4.515925533032185</v>
       </c>
       <c r="N2" t="n">
-        <v>4.545680962054595</v>
+        <v>4.545680962054599</v>
       </c>
       <c r="O2" t="n">
-        <v>4.530476409585346</v>
+        <v>4.530476409585343</v>
       </c>
       <c r="P2" t="n">
-        <v>4.530699431731274</v>
+        <v>4.53069943173127</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.530724670657368</v>
+        <v>4.530724670657364</v>
       </c>
       <c r="R2" t="n">
-        <v>4.531092367310839</v>
+        <v>4.531092367310835</v>
       </c>
       <c r="S2" t="n">
-        <v>4.530727865960084</v>
+        <v>4.530727865960079</v>
       </c>
       <c r="T2" t="n">
-        <v>4.530439408232731</v>
+        <v>4.530439408232726</v>
       </c>
       <c r="U2" t="n">
-        <v>4.531073619906984</v>
+        <v>4.531073619906979</v>
       </c>
       <c r="V2" t="n">
-        <v>4.726391636302243</v>
+        <v>4.726391636302242</v>
       </c>
       <c r="W2" t="n">
-        <v>4.530727865960084</v>
+        <v>4.530727865960079</v>
       </c>
       <c r="X2" t="n">
-        <v>4.532920526918484</v>
+        <v>4.532920526918479</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.530106410938517</v>
+        <v>4.530106410938513</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.523632976184213</v>
+        <v>4.523632976184215</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.530727865960084</v>
+        <v>4.530727865960079</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.534058345982633</v>
+        <v>4.534058345982628</v>
       </c>
     </row>
     <row r="3">
@@ -6899,7 +6899,7 @@
         <v>10.85926559782818</v>
       </c>
       <c r="E3" t="n">
-        <v>9.828261076375629</v>
+        <v>9.828261076375634</v>
       </c>
       <c r="F3" t="n">
         <v>10.85908543928571</v>
@@ -6932,10 +6932,10 @@
         <v>10.85899042870497</v>
       </c>
       <c r="P3" t="n">
-        <v>10.85923448217282</v>
+        <v>10.85923448217281</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.85926210117967</v>
+        <v>10.85926210117966</v>
       </c>
       <c r="R3" t="n">
         <v>10.8596644720485</v>
@@ -6956,7 +6956,7 @@
         <v>10.85926559782818</v>
       </c>
       <c r="X3" t="n">
-        <v>10.8616650288966</v>
+        <v>10.86166502889659</v>
       </c>
       <c r="Y3" t="n">
         <v>10.85858553868945</v>
@@ -6978,85 +6978,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-7.981242241041533</v>
+        <v>-7.981242241041536</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8017919876608768</v>
+        <v>0.8017919876608786</v>
       </c>
       <c r="D4" t="n">
-        <v>3.829795484023814</v>
+        <v>3.829795484023828</v>
       </c>
       <c r="E4" t="n">
-        <v>-15.900374620167</v>
+        <v>-15.90037462016702</v>
       </c>
       <c r="F4" t="n">
-        <v>-13.40743786234498</v>
+        <v>-13.40743786234503</v>
       </c>
       <c r="G4" t="n">
-        <v>8.748978363506986</v>
+        <v>8.748978363506991</v>
       </c>
       <c r="H4" t="n">
-        <v>1.663453883860829</v>
+        <v>1.663453883860852</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.23629148968528</v>
+        <v>-2.236291489685257</v>
       </c>
       <c r="J4" t="n">
-        <v>3.199210304941358</v>
+        <v>3.199210304941352</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.358313381519498</v>
+        <v>-1.35831338151949</v>
       </c>
       <c r="L4" t="n">
-        <v>-12.92668899248491</v>
+        <v>-12.92668899248495</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1805206437855207</v>
+        <v>0.1805206437855369</v>
       </c>
       <c r="N4" t="n">
-        <v>2.444584099018763</v>
+        <v>2.444584099018754</v>
       </c>
       <c r="O4" t="n">
-        <v>0.468071583075565</v>
+        <v>0.4680715830755919</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.920393972915369</v>
+        <v>-7.920393972915289</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.526072492361801</v>
+        <v>1.526072492361807</v>
       </c>
       <c r="R4" t="n">
-        <v>-35.0565735261595</v>
+        <v>-35.05657352615949</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.532415682248098</v>
+        <v>-2.532415682248104</v>
       </c>
       <c r="T4" t="n">
-        <v>-4.899941167017689</v>
+        <v>-4.899941167017666</v>
       </c>
       <c r="U4" t="n">
-        <v>2.444584099018762</v>
+        <v>2.444584099018746</v>
       </c>
       <c r="V4" t="n">
-        <v>3.815534130382452</v>
+        <v>3.815534130382445</v>
       </c>
       <c r="W4" t="n">
-        <v>17.53434312045468</v>
+        <v>17.53434312045469</v>
       </c>
       <c r="X4" t="n">
-        <v>37.56565969512543</v>
+        <v>37.56565969512545</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.92376164846739</v>
+        <v>12.92376164846737</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.697775041585584</v>
+        <v>1.697775041585604</v>
       </c>
       <c r="AA4" t="n">
-        <v>28.86876075089569</v>
+        <v>28.86876075089562</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.7428361831281644</v>
+        <v>0.7428361831281645</v>
       </c>
     </row>
     <row r="5">
@@ -7066,85 +7066,85 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>0.5716709993826884</v>
+      </c>
+      <c r="C5" t="n">
         <v>0.5716709993826873</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.5716709993826918</v>
-      </c>
       <c r="D5" t="n">
-        <v>0.5716709993826918</v>
+        <v>0.5716709993826873</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5716709993826918</v>
+        <v>0.5716709993826873</v>
       </c>
       <c r="F5" t="n">
+        <v>0.5716709993826884</v>
+      </c>
+      <c r="G5" t="n">
         <v>0.5716709993826873</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.5716709993826918</v>
-      </c>
       <c r="H5" t="n">
-        <v>0.5716709993826918</v>
+        <v>0.5716709993826873</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5716709993826918</v>
+        <v>0.5716709993826873</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5700921772395124</v>
+        <v>0.5700921772395187</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5716709993826918</v>
+        <v>0.5716709993826873</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5716709993826918</v>
+        <v>0.5716709993826873</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5716709993826918</v>
+        <v>0.5716709993826873</v>
       </c>
       <c r="N5" t="n">
+        <v>0.5716709993826884</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.5716709993826884</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.5716709993826884</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5716709993826884</v>
+      </c>
+      <c r="R5" t="n">
         <v>0.5716709993826873</v>
       </c>
-      <c r="O5" t="n">
+      <c r="S5" t="n">
         <v>0.5716709993826873</v>
       </c>
-      <c r="P5" t="n">
+      <c r="T5" t="n">
         <v>0.5716709993826873</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="U5" t="n">
+        <v>0.5651112627971271</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.5611855468180291</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.5716709993826884</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.5716709993826884</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.5651112627971269</v>
+      </c>
+      <c r="Z5" t="n">
         <v>0.5716709993826873</v>
       </c>
-      <c r="R5" t="n">
-        <v>0.5716709993826918</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.5716709993826918</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.5716709993826918</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.565111262797113</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.5611855468180281</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="AA5" t="n">
         <v>0.5716709993826873</v>
       </c>
-      <c r="X5" t="n">
-        <v>0.5716709993826873</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.565111262797113</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.5716709993826918</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.5716709993826918</v>
-      </c>
       <c r="AB5" t="n">
-        <v>0.5716709993826873</v>
+        <v>0.5716709993826884</v>
       </c>
     </row>
     <row r="6">
@@ -7154,85 +7154,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6096470110912029</v>
+        <v>0.6096470110912009</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8600917026147576</v>
+        <v>0.6096470110912009</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6096470110912029</v>
+        <v>0.6096470110912009</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8600917026147576</v>
+        <v>0.8600917026147611</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8600917026147576</v>
+        <v>0.8600917026147611</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8600917026147576</v>
+        <v>0.6096470110912009</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8600917026147576</v>
+        <v>0.6096470110912009</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6096470110912029</v>
+        <v>0.6096470110912009</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8585128804715813</v>
+        <v>0.6080681889480208</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6096470110912029</v>
+        <v>0.6096470110912009</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8600917026147576</v>
+        <v>0.8600917026147611</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6096470110912029</v>
+        <v>0.8600917026147611</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6154524020393316</v>
+        <v>0.6154524020393257</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6154524020393316</v>
+        <v>0.6154524020393699</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8854711295363974</v>
+        <v>0.6052611157175329</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8600917026147576</v>
+        <v>0.6096470110912009</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8600917026147576</v>
+        <v>0.8600917026147611</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8600917026147576</v>
+        <v>0.6096470110912009</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8600917026147576</v>
+        <v>0.8600917026147611</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6096470110912029</v>
+        <v>0.6096470110912009</v>
       </c>
       <c r="V6" t="n">
-        <v>0.599161558526538</v>
+        <v>0.849606250050097</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6299662031017924</v>
+        <v>0.6299662031018174</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6096470110912029</v>
+        <v>0.6096470110912009</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6227258074140775</v>
+        <v>0.6227258074140526</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.8600917026147576</v>
+        <v>0.8600917026147611</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6096470110912029</v>
+        <v>0.8600917026147611</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6151963456984774</v>
+        <v>0.6151963456984957</v>
       </c>
     </row>
     <row r="7">
@@ -7242,85 +7242,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015132</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015132</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015132</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015132</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015132</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015132</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015132</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015132</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9208536683583224</v>
+        <v>0.9208536683583234</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015132</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015132</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015132</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015131</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9205421301980014</v>
+        <v>0.9205421301979981</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9205421301980015</v>
+        <v>0.9205421301979979</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015132</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015132</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015132</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015132</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9116939049631188</v>
+        <v>0.911693904963125</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9119470379368405</v>
+        <v>0.9119470379368403</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015132</v>
       </c>
       <c r="X7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015132</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015132</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015132</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015132</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9224324905015049</v>
+        <v>0.9224324905015132</v>
       </c>
     </row>
     <row r="8">
@@ -7330,85 +7330,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.010886313245076</v>
+        <v>1.01088631324508</v>
       </c>
       <c r="C8" t="n">
-        <v>1.375517978295317</v>
+        <v>1.375517978295322</v>
       </c>
       <c r="D8" t="n">
-        <v>1.375517978295317</v>
+        <v>1.375517978295322</v>
       </c>
       <c r="E8" t="n">
-        <v>1.375517978295317</v>
+        <v>1.181362372671722</v>
       </c>
       <c r="F8" t="n">
-        <v>1.067691665085105</v>
+        <v>1.067691665085121</v>
       </c>
       <c r="G8" t="n">
-        <v>1.375517978295317</v>
+        <v>1.451126729370255</v>
       </c>
       <c r="H8" t="n">
-        <v>1.375517978295317</v>
+        <v>1.375517978295322</v>
       </c>
       <c r="I8" t="n">
-        <v>1.375517978295317</v>
+        <v>1.375517978295322</v>
       </c>
       <c r="J8" t="n">
-        <v>1.373939156152136</v>
+        <v>1.373939156152135</v>
       </c>
       <c r="K8" t="n">
-        <v>1.375517978295317</v>
+        <v>1.375517978295322</v>
       </c>
       <c r="L8" t="n">
-        <v>1.375517978295317</v>
+        <v>1.375517978295322</v>
       </c>
       <c r="M8" t="n">
-        <v>1.375517978295317</v>
+        <v>1.375517978293541</v>
       </c>
       <c r="N8" t="n">
-        <v>1.09286743625599</v>
+        <v>1.092867436255991</v>
       </c>
       <c r="O8" t="n">
-        <v>1.170542259273956</v>
+        <v>1.170542259273958</v>
       </c>
       <c r="P8" t="n">
-        <v>1.151502283281154</v>
+        <v>1.151502283281156</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9392278688269107</v>
+        <v>0.9392278688269198</v>
       </c>
       <c r="R8" t="n">
-        <v>1.375517978295317</v>
+        <v>1.375517978295322</v>
       </c>
       <c r="S8" t="n">
-        <v>1.375517978295317</v>
+        <v>1.375517978295322</v>
       </c>
       <c r="T8" t="n">
-        <v>1.375517978295317</v>
+        <v>1.375517978295322</v>
       </c>
       <c r="U8" t="n">
-        <v>1.144703865863699</v>
+        <v>1.190688971749055</v>
       </c>
       <c r="V8" t="n">
-        <v>1.365032525730653</v>
+        <v>1.257809949647253</v>
       </c>
       <c r="W8" t="n">
-        <v>1.375589638576595</v>
+        <v>1.375589638576601</v>
       </c>
       <c r="X8" t="n">
-        <v>0.9726470852859821</v>
+        <v>0.9726470852859886</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.726332342062555</v>
+        <v>1.726332342062562</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.375517978295317</v>
+        <v>1.004113092887321</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.375517978295317</v>
+        <v>1.375517978295322</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.756406242178081</v>
+        <v>1.756406242178087</v>
       </c>
     </row>
     <row r="9">
@@ -7418,85 +7418,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.638036975402609</v>
+        <v>1.638036975402613</v>
       </c>
       <c r="C9" t="n">
-        <v>1.970185837335641</v>
+        <v>1.970185837335638</v>
       </c>
       <c r="D9" t="n">
-        <v>1.970185837335641</v>
+        <v>1.970185837335638</v>
       </c>
       <c r="E9" t="n">
-        <v>1.970185837335641</v>
+        <v>1.893527286222662</v>
       </c>
       <c r="F9" t="n">
-        <v>1.970185837335641</v>
+        <v>1.204491971315514</v>
       </c>
       <c r="G9" t="n">
-        <v>1.970185837335641</v>
+        <v>1.970185904171792</v>
       </c>
       <c r="H9" t="n">
-        <v>1.970185837335641</v>
+        <v>1.970185837335638</v>
       </c>
       <c r="I9" t="n">
-        <v>1.970185837335641</v>
+        <v>1.970185837335638</v>
       </c>
       <c r="J9" t="n">
-        <v>1.96860701519246</v>
+        <v>1.968607015192468</v>
       </c>
       <c r="K9" t="n">
-        <v>1.970185837335641</v>
+        <v>1.970185837335638</v>
       </c>
       <c r="L9" t="n">
-        <v>1.970185837335641</v>
+        <v>1.970185837335638</v>
       </c>
       <c r="M9" t="n">
-        <v>1.970185837335641</v>
+        <v>1.970185837335638</v>
       </c>
       <c r="N9" t="n">
-        <v>1.970185837335641</v>
+        <v>1.970185837335638</v>
       </c>
       <c r="O9" t="n">
-        <v>2.080259624253981</v>
+        <v>2.080259624253983</v>
       </c>
       <c r="P9" t="n">
-        <v>2.104198769824862</v>
+        <v>2.104198769824852</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.970185904171793</v>
+        <v>1.970185904171792</v>
       </c>
       <c r="R9" t="n">
-        <v>1.970185837335641</v>
+        <v>1.970185837335638</v>
       </c>
       <c r="S9" t="n">
-        <v>1.970185837335641</v>
+        <v>1.970185837335638</v>
       </c>
       <c r="T9" t="n">
-        <v>1.970185837335641</v>
+        <v>1.970185837335638</v>
       </c>
       <c r="U9" t="n">
-        <v>1.970185837335641</v>
+        <v>1.970185837335638</v>
       </c>
       <c r="V9" t="n">
-        <v>1.959700384770974</v>
+        <v>2.342993115258481</v>
       </c>
       <c r="W9" t="n">
-        <v>1.970185837335641</v>
+        <v>1.970185837335638</v>
       </c>
       <c r="X9" t="n">
-        <v>1.970185837335641</v>
+        <v>1.970185837335638</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.970185837335641</v>
+        <v>1.970185837335638</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.970185837335641</v>
+        <v>1.769929635959115</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.970185837335641</v>
+        <v>1.970185837335638</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.970185837335641</v>
+        <v>1.970185837335638</v>
       </c>
     </row>
     <row r="10">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11.07746819563277</v>
+        <v>11.07746819563278</v>
       </c>
       <c r="C10" t="n">
         <v>10.8554271395707</v>
       </c>
       <c r="D10" t="n">
-        <v>10.78295250570558</v>
+        <v>10.78295250570559</v>
       </c>
       <c r="E10" t="n">
         <v>10.22024846444031</v>
@@ -7521,7 +7521,7 @@
         <v>11.18566059090553</v>
       </c>
       <c r="G10" t="n">
-        <v>10.6289205374584</v>
+        <v>10.62892053745841</v>
       </c>
       <c r="H10" t="n">
         <v>10.83662354216173</v>
@@ -7545,13 +7545,13 @@
         <v>10.70144893609369</v>
       </c>
       <c r="O10" t="n">
-        <v>10.86399533592355</v>
+        <v>10.86399533592356</v>
       </c>
       <c r="P10" t="n">
         <v>11.07861986123407</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.83659405753749</v>
+        <v>10.8365940575375</v>
       </c>
       <c r="R10" t="n">
         <v>11.65399342319107</v>
@@ -7563,16 +7563,16 @@
         <v>10.99364994953189</v>
       </c>
       <c r="U10" t="n">
-        <v>10.81124622301223</v>
+        <v>10.81124622301224</v>
       </c>
       <c r="V10" t="n">
         <v>10.97004952315285</v>
       </c>
       <c r="W10" t="n">
-        <v>10.4384297090689</v>
+        <v>10.43842970906891</v>
       </c>
       <c r="X10" t="n">
-        <v>9.963573513397622</v>
+        <v>9.963573513397618</v>
       </c>
       <c r="Y10" t="n">
         <v>10.57107873663402</v>
@@ -7594,22 +7594,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.630010743331594</v>
+        <v>4.630010743331595</v>
       </c>
       <c r="C11" t="n">
-        <v>4.517534211341586</v>
+        <v>4.517534211341598</v>
       </c>
       <c r="D11" t="n">
-        <v>4.497158011154689</v>
+        <v>4.497158011154694</v>
       </c>
       <c r="E11" t="n">
-        <v>3.615966453162313</v>
+        <v>3.615966453162312</v>
       </c>
       <c r="F11" t="n">
-        <v>4.611254867733141</v>
+        <v>4.611254867733148</v>
       </c>
       <c r="G11" t="n">
-        <v>4.452736914472061</v>
+        <v>4.452736914472054</v>
       </c>
       <c r="H11" t="n">
         <v>4.520425658475898</v>
@@ -7618,34 +7618,34 @@
         <v>4.560506397343777</v>
       </c>
       <c r="J11" t="n">
-        <v>4.49805067204214</v>
+        <v>4.498050672042138</v>
       </c>
       <c r="K11" t="n">
-        <v>4.554891210967158</v>
+        <v>4.55489121096716</v>
       </c>
       <c r="L11" t="n">
-        <v>4.719015316844347</v>
+        <v>4.719015316844351</v>
       </c>
       <c r="M11" t="n">
-        <v>4.523118180573783</v>
+        <v>4.523118180573789</v>
       </c>
       <c r="N11" t="n">
-        <v>4.473873878033539</v>
+        <v>4.473873878033546</v>
       </c>
       <c r="O11" t="n">
-        <v>4.532753658319495</v>
+        <v>4.532753658319491</v>
       </c>
       <c r="P11" t="n">
-        <v>4.630520478343863</v>
+        <v>4.630520478343858</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.52041063856141</v>
+        <v>4.520410638561406</v>
       </c>
       <c r="R11" t="n">
-        <v>4.892514571456871</v>
+        <v>4.892514571456874</v>
       </c>
       <c r="S11" t="n">
-        <v>4.572338409470548</v>
+        <v>4.572338409470546</v>
       </c>
       <c r="T11" t="n">
         <v>4.591728342719954</v>
@@ -7654,22 +7654,22 @@
         <v>4.509052496913959</v>
       </c>
       <c r="V11" t="n">
-        <v>4.687499547643377</v>
+        <v>4.687499547643375</v>
       </c>
       <c r="W11" t="n">
-        <v>4.33924619545021</v>
+        <v>4.339246195450211</v>
       </c>
       <c r="X11" t="n">
-        <v>4.124286025318606</v>
+        <v>4.124286025318604</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.399289899773482</v>
+        <v>4.399289899773486</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.510622548298727</v>
+        <v>4.510622548298731</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.2300678341035</v>
+        <v>4.230067834103496</v>
       </c>
       <c r="AB11" t="n">
         <v>4.533100413750095</v>
@@ -7838,43 +7838,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.482396127661094</v>
+        <v>4.482396127661093</v>
       </c>
       <c r="C2" t="n">
         <v>4.454949507843003</v>
       </c>
       <c r="D2" t="n">
-        <v>4.468368807704689</v>
+        <v>4.468368807704687</v>
       </c>
       <c r="E2" t="n">
-        <v>3.406870103380095</v>
+        <v>3.406870103380093</v>
       </c>
       <c r="F2" t="n">
-        <v>4.430336034336212</v>
+        <v>4.430336034336213</v>
       </c>
       <c r="G2" t="n">
         <v>4.50733355007837</v>
       </c>
       <c r="H2" t="n">
-        <v>4.482396127661094</v>
+        <v>4.482396127661093</v>
       </c>
       <c r="I2" t="n">
-        <v>4.482396127661094</v>
+        <v>4.482396127661093</v>
       </c>
       <c r="J2" t="n">
         <v>4.482679926093283</v>
       </c>
       <c r="K2" t="n">
-        <v>4.482271376227405</v>
+        <v>4.482271376227404</v>
       </c>
       <c r="L2" t="n">
-        <v>4.482396127661094</v>
+        <v>4.482396127661093</v>
       </c>
       <c r="M2" t="n">
-        <v>4.481240092089695</v>
+        <v>4.481240092089693</v>
       </c>
       <c r="N2" t="n">
-        <v>4.509818058613869</v>
+        <v>4.509818058613868</v>
       </c>
       <c r="O2" t="n">
         <v>4.482108464626584</v>
@@ -7883,40 +7883,40 @@
         <v>4.481854626766466</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.482392932358378</v>
+        <v>4.482392932358377</v>
       </c>
       <c r="R2" t="n">
         <v>4.48309877076293</v>
       </c>
       <c r="S2" t="n">
-        <v>4.482396127661094</v>
+        <v>4.482396127661093</v>
       </c>
       <c r="T2" t="n">
-        <v>4.481981868489846</v>
+        <v>4.481981868489845</v>
       </c>
       <c r="U2" t="n">
-        <v>4.483379137966088</v>
+        <v>4.483379137966087</v>
       </c>
       <c r="V2" t="n">
-        <v>4.68976894398785</v>
+        <v>4.689768943987845</v>
       </c>
       <c r="W2" t="n">
-        <v>4.482396127661094</v>
+        <v>4.482396127661093</v>
       </c>
       <c r="X2" t="n">
-        <v>4.483401352413312</v>
+        <v>4.483401352413311</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.481305778872859</v>
+        <v>4.481305778872858</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.458146126412309</v>
+        <v>4.458146126412307</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.482396127661094</v>
+        <v>4.482396127661093</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.485726607683643</v>
+        <v>4.485726607683642</v>
       </c>
     </row>
     <row r="3">
@@ -7929,7 +7929,7 @@
         <v>10.8177241962162</v>
       </c>
       <c r="C3" t="n">
-        <v>10.81736619924539</v>
+        <v>10.8173661992454</v>
       </c>
       <c r="D3" t="n">
         <v>10.8177241962162</v>
@@ -7941,7 +7941,7 @@
         <v>10.8174850772993</v>
       </c>
       <c r="G3" t="n">
-        <v>10.81761017707965</v>
+        <v>10.81761017707966</v>
       </c>
       <c r="H3" t="n">
         <v>10.8177241962162</v>
@@ -7953,7 +7953,7 @@
         <v>10.8180080286728</v>
       </c>
       <c r="K3" t="n">
-        <v>10.81758768051917</v>
+        <v>10.81758768051918</v>
       </c>
       <c r="L3" t="n">
         <v>10.8177241962162</v>
@@ -7968,7 +7968,7 @@
         <v>10.81740940622531</v>
       </c>
       <c r="P3" t="n">
-        <v>10.81713163109303</v>
+        <v>10.81713163109304</v>
       </c>
       <c r="Q3" t="n">
         <v>10.81772069956769</v>
@@ -7980,31 +7980,31 @@
         <v>10.8177241962162</v>
       </c>
       <c r="T3" t="n">
-        <v>10.81727087197604</v>
+        <v>10.81727087197605</v>
       </c>
       <c r="U3" t="n">
         <v>10.81879990519945</v>
       </c>
       <c r="V3" t="n">
-        <v>11.01281629398895</v>
+        <v>11.01281629398896</v>
       </c>
       <c r="W3" t="n">
         <v>10.8177241962162</v>
       </c>
       <c r="X3" t="n">
-        <v>10.81882421469687</v>
+        <v>10.81882421469688</v>
       </c>
       <c r="Y3" t="n">
         <v>10.81653102627988</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.81769260731071</v>
+        <v>10.81769260731072</v>
       </c>
       <c r="AA3" t="n">
         <v>10.8177241962162</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.82136874360479</v>
+        <v>10.8213687436048</v>
       </c>
     </row>
     <row r="4">
@@ -8014,52 +8014,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-15.36798139666253</v>
+        <v>-15.36798139666254</v>
       </c>
       <c r="C4" t="n">
-        <v>-4.937662782260441</v>
+        <v>-4.937662782260452</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.739330584306355</v>
+        <v>-1.739330584306362</v>
       </c>
       <c r="E4" t="n">
         <v>-17.16094758940961</v>
       </c>
       <c r="F4" t="n">
-        <v>-11.59686724194225</v>
+        <v>-11.59686724194227</v>
       </c>
       <c r="G4" t="n">
-        <v>7.156088666951247</v>
+        <v>7.156088666951237</v>
       </c>
       <c r="H4" t="n">
-        <v>3.432900002017432</v>
+        <v>3.432900002017426</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9041759332044474</v>
+        <v>0.9041759332044395</v>
       </c>
       <c r="J4" t="n">
-        <v>1.691303050132061</v>
+        <v>1.691303050132057</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2900805673408182</v>
+        <v>-0.2900805673408273</v>
       </c>
       <c r="L4" t="n">
-        <v>-17.59390369618718</v>
+        <v>-17.59390369618719</v>
       </c>
       <c r="M4" t="n">
-        <v>1.624813465727043</v>
+        <v>1.624813465727035</v>
       </c>
       <c r="N4" t="n">
-        <v>2.54262158529793</v>
+        <v>2.542621585297923</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.514311690777435</v>
+        <v>-5.51431169077745</v>
       </c>
       <c r="P4" t="n">
-        <v>-10.13418573092021</v>
+        <v>-10.1341857309202</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.872292151417346</v>
+        <v>1.872292151417343</v>
       </c>
       <c r="R4" t="n">
         <v>-34.41767929840226</v>
@@ -8068,31 +8068,31 @@
         <v>-6.524423709543298</v>
       </c>
       <c r="T4" t="n">
-        <v>-3.155363360966144</v>
+        <v>-3.155363360966148</v>
       </c>
       <c r="U4" t="n">
-        <v>2.542621585297928</v>
+        <v>2.542621585297923</v>
       </c>
       <c r="V4" t="n">
-        <v>5.091433221828578</v>
+        <v>5.091433221828584</v>
       </c>
       <c r="W4" t="n">
-        <v>15.63853973165523</v>
+        <v>15.63853973165522</v>
       </c>
       <c r="X4" t="n">
-        <v>48.23208012538655</v>
+        <v>48.23208012538658</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.423429823758971</v>
+        <v>9.423429823758978</v>
       </c>
       <c r="Z4" t="n">
-        <v>-3.596815330181898</v>
+        <v>-3.596815330181903</v>
       </c>
       <c r="AA4" t="n">
-        <v>33.33514035073731</v>
+        <v>33.33514035073728</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.902914348996298</v>
+        <v>1.902914348996299</v>
       </c>
     </row>
     <row r="5">
@@ -8102,85 +8102,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5283448011297596</v>
+        <v>0.5283448011297635</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5283448011297596</v>
+        <v>0.528344801129764</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5283448011297596</v>
+        <v>0.528344801129764</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5283448011297596</v>
+        <v>0.528344801129764</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5283448011297597</v>
+        <v>0.5283448011297635</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5283448011297596</v>
+        <v>0.528344801129764</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5283448011297596</v>
+        <v>0.528344801129764</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5283448011297596</v>
+        <v>0.528344801129764</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5269065470265287</v>
+        <v>0.5269065470265261</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5283448011297596</v>
+        <v>0.528344801129764</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5283448011297596</v>
+        <v>0.528344801129764</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5283448011297596</v>
+        <v>0.528344801129764</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5283448011297597</v>
+        <v>0.5283448011297635</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5283448011297597</v>
+        <v>0.5283448011297635</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5283448011297597</v>
+        <v>0.5283448011297635</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5283448011297597</v>
+        <v>0.5283448011297635</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5283448011297596</v>
+        <v>0.528344801129764</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5283448011297596</v>
+        <v>0.528344801129764</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5283448011297596</v>
+        <v>0.528344801129764</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5235257060084518</v>
+        <v>0.5235257060084555</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5187475549260034</v>
+        <v>0.518747554926005</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5283448011297597</v>
+        <v>0.5283448011297635</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5283448011297597</v>
+        <v>0.5283448011297635</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5235257060084518</v>
+        <v>0.5235257060084555</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.5283448011297596</v>
+        <v>0.528344801129764</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.5283448011297596</v>
+        <v>0.528344801129764</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.5283448011297597</v>
+        <v>0.5283448011297635</v>
       </c>
     </row>
     <row r="6">
@@ -8190,85 +8190,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7795487789774794</v>
+        <v>0.7795487789774763</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7795487789774794</v>
+        <v>0.7795487789774763</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7795487789774794</v>
+        <v>0.7795487789774763</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7795487789774794</v>
+        <v>0.7795487789774763</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5563612984573714</v>
+        <v>0.7795487789774763</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5563612984573714</v>
+        <v>0.7795487789774763</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5563612984573714</v>
+        <v>0.5563612984573717</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7795487789774794</v>
+        <v>0.5563612984573717</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7781105248742487</v>
+        <v>0.5549230443541395</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5563612984573714</v>
+        <v>0.7795487789774763</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7795487789774794</v>
+        <v>0.7795487789774763</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7795487789774794</v>
+        <v>0.7795487789774763</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5628928616575424</v>
+        <v>0.562892861657553</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5628928616575687</v>
+        <v>0.8040422159282877</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8039866124538111</v>
+        <v>0.803986612453813</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7795487789774794</v>
+        <v>0.7795487789774763</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7795487789774794</v>
+        <v>0.5563612984573717</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5563612984573714</v>
+        <v>0.5563612984573717</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7795487789774794</v>
+        <v>0.7795487789774763</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7795487789774794</v>
+        <v>0.7795487789774763</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5467640522536144</v>
+        <v>0.5467640522536137</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8041728085830004</v>
+        <v>0.8041728085829991</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7795487789774794</v>
+        <v>0.5563612984573717</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5696921759024147</v>
+        <v>0.5696921759024129</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.7795487789774794</v>
+        <v>0.5563612984573717</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.7795487789774794</v>
+        <v>0.5563612984573717</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.5631293950296801</v>
+        <v>0.5631293950296791</v>
       </c>
     </row>
     <row r="7">
@@ -8278,85 +8278,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.860820449253511</v>
+        <v>0.8608204492535099</v>
       </c>
       <c r="C7" t="n">
-        <v>0.860820449253511</v>
+        <v>0.8608204492535099</v>
       </c>
       <c r="D7" t="n">
-        <v>0.860820449253511</v>
+        <v>0.8608204492535099</v>
       </c>
       <c r="E7" t="n">
-        <v>0.860820449253511</v>
+        <v>0.8608204492535099</v>
       </c>
       <c r="F7" t="n">
-        <v>0.860820449253511</v>
+        <v>0.8608204492535099</v>
       </c>
       <c r="G7" t="n">
-        <v>0.860820449253511</v>
+        <v>0.8608204492535099</v>
       </c>
       <c r="H7" t="n">
-        <v>0.860820449253511</v>
+        <v>0.8608204492535099</v>
       </c>
       <c r="I7" t="n">
-        <v>0.860820449253511</v>
+        <v>0.8608204492535099</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8593821951502797</v>
+        <v>0.8593821951502781</v>
       </c>
       <c r="K7" t="n">
-        <v>0.860820449253511</v>
+        <v>0.8608204492535099</v>
       </c>
       <c r="L7" t="n">
-        <v>0.860820449253511</v>
+        <v>0.8608204492535099</v>
       </c>
       <c r="M7" t="n">
-        <v>0.860820449253511</v>
+        <v>0.8608204492535099</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8608204492535111</v>
+        <v>0.8608204492535099</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8589312529899807</v>
+        <v>0.8589312529899802</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8589312529899807</v>
+        <v>0.8589312529899799</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.860820449253511</v>
+        <v>0.8608204492535099</v>
       </c>
       <c r="R7" t="n">
-        <v>0.860820449253511</v>
+        <v>0.8608204492535099</v>
       </c>
       <c r="S7" t="n">
-        <v>0.860820449253511</v>
+        <v>0.8608204492535099</v>
       </c>
       <c r="T7" t="n">
-        <v>0.860820449253511</v>
+        <v>0.8608204492535099</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8479245685404903</v>
+        <v>0.8479245685404901</v>
       </c>
       <c r="V7" t="n">
-        <v>0.851223203049754</v>
+        <v>0.8512232030497539</v>
       </c>
       <c r="W7" t="n">
-        <v>0.860820449253511</v>
+        <v>0.8608204492535099</v>
       </c>
       <c r="X7" t="n">
-        <v>0.860820449253511</v>
+        <v>0.8608204492535099</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.860820449253511</v>
+        <v>0.8608204492535099</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.860820449253511</v>
+        <v>0.8608204492535099</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.860820449253511</v>
+        <v>0.8608204492535099</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.860820449253511</v>
+        <v>0.8608204492535099</v>
       </c>
     </row>
     <row r="8">
@@ -8366,85 +8366,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9298843974188646</v>
+        <v>0.9298843974188642</v>
       </c>
       <c r="C8" t="n">
-        <v>1.260145329923736</v>
+        <v>1.260145329923735</v>
       </c>
       <c r="D8" t="n">
-        <v>1.260145329923736</v>
+        <v>1.260145329923735</v>
       </c>
       <c r="E8" t="n">
-        <v>1.260145329923736</v>
+        <v>1.084291125466821</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9813351908486235</v>
+        <v>0.9813351908486261</v>
       </c>
       <c r="G8" t="n">
-        <v>1.260145329923736</v>
+        <v>1.328627085716521</v>
       </c>
       <c r="H8" t="n">
-        <v>1.260145329923736</v>
+        <v>1.260145329923735</v>
       </c>
       <c r="I8" t="n">
-        <v>1.260145329923736</v>
+        <v>1.260145329923735</v>
       </c>
       <c r="J8" t="n">
-        <v>1.258707075820505</v>
+        <v>1.2587070758205</v>
       </c>
       <c r="K8" t="n">
-        <v>1.260145329923736</v>
+        <v>1.260145329923735</v>
       </c>
       <c r="L8" t="n">
-        <v>1.260145329923736</v>
+        <v>1.260145329923735</v>
       </c>
       <c r="M8" t="n">
-        <v>1.260145329923736</v>
+        <v>1.260145329921307</v>
       </c>
       <c r="N8" t="n">
-        <v>1.004137855754541</v>
+        <v>1.004137855754546</v>
       </c>
       <c r="O8" t="n">
-        <v>1.074490932485338</v>
+        <v>1.074490932485342</v>
       </c>
       <c r="P8" t="n">
-        <v>1.057245693414809</v>
+        <v>1.057245693414804</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8649805863644102</v>
+        <v>0.8649805863644067</v>
       </c>
       <c r="R8" t="n">
-        <v>1.260145329923736</v>
+        <v>1.260145329923735</v>
       </c>
       <c r="S8" t="n">
-        <v>1.260145329923736</v>
+        <v>1.260145329923735</v>
       </c>
       <c r="T8" t="n">
-        <v>1.260145329923736</v>
+        <v>1.260145329923735</v>
       </c>
       <c r="U8" t="n">
-        <v>1.048910486009663</v>
+        <v>1.090419466403432</v>
       </c>
       <c r="V8" t="n">
-        <v>1.25054808371998</v>
+        <v>1.150874549704638</v>
       </c>
       <c r="W8" t="n">
-        <v>1.260210235566886</v>
+        <v>1.260210235566881</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8952496570102866</v>
+        <v>0.8952496570102852</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.573924063168591</v>
+        <v>1.573924063168581</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.260145329923736</v>
+        <v>0.9237496310452071</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.260145329923736</v>
+        <v>1.260145329923735</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.605130489816374</v>
+        <v>1.605130489816371</v>
       </c>
     </row>
     <row r="9">
@@ -8457,43 +8457,43 @@
         <v>1.480487865711021</v>
       </c>
       <c r="C9" t="n">
-        <v>1.776507389696121</v>
+        <v>1.776507389696122</v>
       </c>
       <c r="D9" t="n">
-        <v>1.776507389696121</v>
+        <v>1.776507389696122</v>
       </c>
       <c r="E9" t="n">
-        <v>1.776507389696121</v>
+        <v>1.70818721879378</v>
       </c>
       <c r="F9" t="n">
-        <v>1.776507389696121</v>
+        <v>1.094101718048361</v>
       </c>
       <c r="G9" t="n">
-        <v>1.776507389696121</v>
+        <v>1.776507295822199</v>
       </c>
       <c r="H9" t="n">
-        <v>1.776507389696121</v>
+        <v>1.776507389696122</v>
       </c>
       <c r="I9" t="n">
-        <v>1.776507389696121</v>
+        <v>1.776507389696122</v>
       </c>
       <c r="J9" t="n">
-        <v>1.77506913559289</v>
+        <v>1.775069135592889</v>
       </c>
       <c r="K9" t="n">
-        <v>1.776507389696121</v>
+        <v>1.776507389696122</v>
       </c>
       <c r="L9" t="n">
-        <v>1.776507389696121</v>
+        <v>1.776507389696122</v>
       </c>
       <c r="M9" t="n">
-        <v>1.776507389696121</v>
+        <v>1.776507389696122</v>
       </c>
       <c r="N9" t="n">
-        <v>1.776507389696121</v>
+        <v>1.776507389696122</v>
       </c>
       <c r="O9" t="n">
-        <v>1.874607747356651</v>
+        <v>1.874607747356652</v>
       </c>
       <c r="P9" t="n">
         <v>1.895942912445096</v>
@@ -8502,37 +8502,37 @@
         <v>1.776507295822199</v>
       </c>
       <c r="R9" t="n">
-        <v>1.776507389696121</v>
+        <v>1.776507389696122</v>
       </c>
       <c r="S9" t="n">
-        <v>1.776507389696121</v>
+        <v>1.776507389696122</v>
       </c>
       <c r="T9" t="n">
-        <v>1.776507389696121</v>
+        <v>1.776507389696122</v>
       </c>
       <c r="U9" t="n">
-        <v>1.776507389696121</v>
+        <v>1.776507389696122</v>
       </c>
       <c r="V9" t="n">
-        <v>1.766910143492362</v>
+        <v>2.108510232960088</v>
       </c>
       <c r="W9" t="n">
-        <v>1.776507389696121</v>
+        <v>1.776507389696122</v>
       </c>
       <c r="X9" t="n">
-        <v>1.776507389696121</v>
+        <v>1.776507389696122</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.776507389696121</v>
+        <v>1.776507389696122</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.776507389696121</v>
+        <v>1.598033902539918</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.776507389696121</v>
+        <v>1.776507389696122</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.776507389696121</v>
+        <v>1.776507389696122</v>
       </c>
     </row>
     <row r="10">
@@ -8545,7 +8545,7 @@
         <v>11.22758970738231</v>
       </c>
       <c r="C10" t="n">
-        <v>10.94930062133318</v>
+        <v>10.94930062133319</v>
       </c>
       <c r="D10" t="n">
         <v>10.87281892485981</v>
@@ -8566,10 +8566,10 @@
         <v>10.81036876700543</v>
       </c>
       <c r="J10" t="n">
-        <v>10.79050591699847</v>
+        <v>10.79050591699846</v>
       </c>
       <c r="K10" t="n">
-        <v>10.84008290249772</v>
+        <v>10.84008290249773</v>
       </c>
       <c r="L10" t="n">
         <v>11.32653483252879</v>
@@ -8581,7 +8581,7 @@
         <v>10.62923127388733</v>
       </c>
       <c r="O10" t="n">
-        <v>10.98141189180147</v>
+        <v>10.98141189180146</v>
       </c>
       <c r="P10" t="n">
         <v>11.1016780147959</v>
@@ -8593,13 +8593,13 @@
         <v>11.58709973930891</v>
       </c>
       <c r="S10" t="n">
-        <v>11.0066934275155</v>
+        <v>11.00669342751551</v>
       </c>
       <c r="T10" t="n">
         <v>10.90402358180738</v>
       </c>
       <c r="U10" t="n">
-        <v>10.76760914909818</v>
+        <v>10.76760914909819</v>
       </c>
       <c r="V10" t="n">
         <v>10.89433440960339</v>
@@ -8614,7 +8614,7 @@
         <v>10.61248169862707</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.93415355302662</v>
+        <v>10.93415355302663</v>
       </c>
       <c r="AA10" t="n">
         <v>10.05499665538963</v>
@@ -8630,22 +8630,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.668886241405558</v>
+        <v>4.668886241405557</v>
       </c>
       <c r="C11" t="n">
-        <v>4.514980090343005</v>
+        <v>4.514980090343004</v>
       </c>
       <c r="D11" t="n">
-        <v>4.493437084814016</v>
+        <v>4.493437084814014</v>
       </c>
       <c r="E11" t="n">
-        <v>3.612485261199115</v>
+        <v>3.612485261199114</v>
       </c>
       <c r="F11" t="n">
-        <v>4.555574378074412</v>
+        <v>4.55557437807441</v>
       </c>
       <c r="G11" t="n">
-        <v>4.427077882795939</v>
+        <v>4.42707788279594</v>
       </c>
       <c r="H11" t="n">
         <v>4.45410535514372</v>
@@ -8654,61 +8654,61 @@
         <v>4.479049383929826</v>
       </c>
       <c r="J11" t="n">
-        <v>4.470166377637432</v>
+        <v>4.470166377637435</v>
       </c>
       <c r="K11" t="n">
-        <v>4.492506773915665</v>
+        <v>4.492506773915661</v>
       </c>
       <c r="L11" t="n">
-        <v>4.713906588666609</v>
+        <v>4.713906588666608</v>
       </c>
       <c r="M11" t="n">
-        <v>4.470536749994414</v>
+        <v>4.470536749994413</v>
       </c>
       <c r="N11" t="n">
         <v>4.424053178262929</v>
       </c>
       <c r="O11" t="n">
-        <v>4.556730118208645</v>
+        <v>4.556730118208642</v>
       </c>
       <c r="P11" t="n">
-        <v>4.611324138146791</v>
+        <v>4.61132413814679</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.468013671570297</v>
+        <v>4.468013671570296</v>
       </c>
       <c r="R11" t="n">
-        <v>4.832817241368512</v>
+        <v>4.83281724136851</v>
       </c>
       <c r="S11" t="n">
-        <v>4.568377730111487</v>
+        <v>4.568377730111486</v>
       </c>
       <c r="T11" t="n">
-        <v>4.521454627927588</v>
+        <v>4.521454627927587</v>
       </c>
       <c r="U11" t="n">
-        <v>4.460087180804752</v>
+        <v>4.46008718080475</v>
       </c>
       <c r="V11" t="n">
-        <v>4.635859309013056</v>
+        <v>4.635859309013051</v>
       </c>
       <c r="W11" t="n">
-        <v>4.315359581334119</v>
+        <v>4.315359581334117</v>
       </c>
       <c r="X11" t="n">
         <v>3.947791846529144</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.388462684524207</v>
+        <v>4.388462684524206</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.51113622785206</v>
+        <v>4.511136227852059</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.135352665916552</v>
+        <v>4.13535266591655</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.472542732347582</v>
+        <v>4.472542732347581</v>
       </c>
     </row>
   </sheetData>
@@ -8874,82 +8874,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.802622907760665</v>
+        <v>4.802622907760664</v>
       </c>
       <c r="C2" t="n">
-        <v>4.696463527969195</v>
+        <v>4.696463527969193</v>
       </c>
       <c r="D2" t="n">
-        <v>4.750214721473995</v>
+        <v>4.750214721473994</v>
       </c>
       <c r="E2" t="n">
-        <v>3.648641691644717</v>
+        <v>3.648641691644716</v>
       </c>
       <c r="F2" t="n">
-        <v>4.702071492527077</v>
+        <v>4.702071492527076</v>
       </c>
       <c r="G2" t="n">
-        <v>4.882571329243798</v>
+        <v>4.882571329243795</v>
       </c>
       <c r="H2" t="n">
-        <v>4.802622907760665</v>
+        <v>4.802622907760664</v>
       </c>
       <c r="I2" t="n">
-        <v>4.802622907760665</v>
+        <v>4.802622907760664</v>
       </c>
       <c r="J2" t="n">
-        <v>4.797903102610973</v>
+        <v>4.797903102610972</v>
       </c>
       <c r="K2" t="n">
-        <v>4.802554301511462</v>
+        <v>4.802554301511461</v>
       </c>
       <c r="L2" t="n">
-        <v>4.802622907760665</v>
+        <v>4.802622907760664</v>
       </c>
       <c r="M2" t="n">
-        <v>4.887201034758186</v>
+        <v>4.887201034758182</v>
       </c>
       <c r="N2" t="n">
-        <v>4.764494147753008</v>
+        <v>4.764494147753007</v>
       </c>
       <c r="O2" t="n">
-        <v>4.802397728220854</v>
+        <v>4.802397728220853</v>
       </c>
       <c r="P2" t="n">
-        <v>4.802566544319274</v>
+        <v>4.802566544319273</v>
       </c>
       <c r="Q2" t="n">
         <v>4.802619712457949</v>
       </c>
       <c r="R2" t="n">
-        <v>4.802610224981506</v>
+        <v>4.802610224981505</v>
       </c>
       <c r="S2" t="n">
-        <v>4.802622907760665</v>
+        <v>4.802622907760664</v>
       </c>
       <c r="T2" t="n">
-        <v>4.802524959247484</v>
+        <v>4.802524959247483</v>
       </c>
       <c r="U2" t="n">
-        <v>4.802844066619293</v>
+        <v>4.802844066619292</v>
       </c>
       <c r="V2" t="n">
-        <v>4.901405623887569</v>
+        <v>4.901405623887568</v>
       </c>
       <c r="W2" t="n">
-        <v>4.802622907760665</v>
+        <v>4.802622907760664</v>
       </c>
       <c r="X2" t="n">
-        <v>4.802806604009878</v>
+        <v>4.802806604009877</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.802105872677596</v>
+        <v>4.802105872677595</v>
       </c>
       <c r="Z2" t="n">
         <v>4.739449035965053</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.802622907760665</v>
+        <v>4.802622907760664</v>
       </c>
       <c r="AB2" t="n">
         <v>4.805953387783213</v>
@@ -9053,82 +9053,82 @@
         <v>16.44161488924768</v>
       </c>
       <c r="C4" t="n">
-        <v>5.329447851946175</v>
+        <v>5.329447851946177</v>
       </c>
       <c r="D4" t="n">
-        <v>20.66502993168336</v>
+        <v>20.66502993168335</v>
       </c>
       <c r="E4" t="n">
-        <v>7.671745639605863</v>
+        <v>7.671745639605873</v>
       </c>
       <c r="F4" t="n">
-        <v>6.952981500245295</v>
+        <v>6.952981500245267</v>
       </c>
       <c r="G4" t="n">
-        <v>50.33959186315604</v>
+        <v>50.33959186315606</v>
       </c>
       <c r="H4" t="n">
-        <v>27.04195522697775</v>
+        <v>27.04195522697771</v>
       </c>
       <c r="I4" t="n">
-        <v>8.789921418228273</v>
+        <v>8.7899214182283</v>
       </c>
       <c r="J4" t="n">
         <v>31.7425048214785</v>
       </c>
       <c r="K4" t="n">
-        <v>16.73520544699933</v>
+        <v>16.73520544699931</v>
       </c>
       <c r="L4" t="n">
-        <v>32.81805649332279</v>
+        <v>32.81805649332277</v>
       </c>
       <c r="M4" t="n">
-        <v>55.05329657479096</v>
+        <v>55.05329657479097</v>
       </c>
       <c r="N4" t="n">
-        <v>33.46232947711196</v>
+        <v>33.46232947711216</v>
       </c>
       <c r="O4" t="n">
-        <v>15.53944987948164</v>
+        <v>15.53944987948167</v>
       </c>
       <c r="P4" t="n">
-        <v>24.83942108016868</v>
+        <v>24.83942108016853</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.6881296911867</v>
+        <v>12.68812969118667</v>
       </c>
       <c r="R4" t="n">
-        <v>1.796776396528932</v>
+        <v>1.796776396528904</v>
       </c>
       <c r="S4" t="n">
-        <v>22.60948761973674</v>
+        <v>22.60948761973666</v>
       </c>
       <c r="T4" t="n">
-        <v>11.85622709074984</v>
+        <v>11.85622709074983</v>
       </c>
       <c r="U4" t="n">
-        <v>33.46232947711196</v>
+        <v>33.46232947711214</v>
       </c>
       <c r="V4" t="n">
-        <v>10.47642904537294</v>
+        <v>10.47642904537292</v>
       </c>
       <c r="W4" t="n">
-        <v>38.78506654904658</v>
+        <v>38.78506654904656</v>
       </c>
       <c r="X4" t="n">
-        <v>31.75389551711967</v>
+        <v>31.75389551711972</v>
       </c>
       <c r="Y4" t="n">
-        <v>28.69186402232851</v>
+        <v>28.69186402232837</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.63887231060139</v>
+        <v>15.63887231060141</v>
       </c>
       <c r="AA4" t="n">
-        <v>29.78236011022715</v>
+        <v>29.78236011022708</v>
       </c>
       <c r="AB4" t="n">
-        <v>51.52732693956908</v>
+        <v>51.52732693956899</v>
       </c>
     </row>
     <row r="5">
@@ -9138,85 +9138,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.955364259955459</v>
+        <v>0.9553642599554601</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9553642599554591</v>
+        <v>0.9553642599554597</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9553642599554591</v>
+        <v>0.9553642599554597</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9553642599554591</v>
+        <v>0.9553642599554597</v>
       </c>
       <c r="F5" t="n">
-        <v>0.955364259955459</v>
+        <v>0.9553642599554601</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9553642599554591</v>
+        <v>0.9553642599554597</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9553642599554591</v>
+        <v>0.9553642599554597</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9553642599554591</v>
+        <v>0.9553642599554597</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9529228012589912</v>
+        <v>0.952922801258992</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9553642599554591</v>
+        <v>0.9553642599554597</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9553642599554591</v>
+        <v>0.9553642599554597</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9553642599554591</v>
+        <v>0.9553642599554597</v>
       </c>
       <c r="N5" t="n">
-        <v>0.955364259955459</v>
+        <v>0.9553642599554601</v>
       </c>
       <c r="O5" t="n">
-        <v>0.955364259955459</v>
+        <v>0.9553642599554601</v>
       </c>
       <c r="P5" t="n">
-        <v>0.955364259955459</v>
+        <v>0.9553642599554601</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.955364259955459</v>
+        <v>0.9553642599554601</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9553642599554591</v>
+        <v>0.9553642599554597</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9553642599554591</v>
+        <v>0.9553642599554597</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9553642599554591</v>
+        <v>0.9553642599554597</v>
       </c>
       <c r="U5" t="n">
         <v>0.9330814370925539</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9393801574028151</v>
+        <v>0.9393801574028154</v>
       </c>
       <c r="W5" t="n">
-        <v>0.955364259955459</v>
+        <v>0.9553642599554601</v>
       </c>
       <c r="X5" t="n">
-        <v>0.955364259955459</v>
+        <v>0.9553642599554601</v>
       </c>
       <c r="Y5" t="n">
         <v>0.9330814370925539</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.9553642599554591</v>
+        <v>0.9553642599554597</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.9553642599554591</v>
+        <v>0.9553642599554597</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.955364259955459</v>
+        <v>0.9553642599554601</v>
       </c>
     </row>
     <row r="6">
@@ -9226,82 +9226,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.528695364805943</v>
+        <v>1.528695364805941</v>
       </c>
       <c r="C6" t="n">
-        <v>1.052084973748756</v>
+        <v>1.052084973748757</v>
       </c>
       <c r="D6" t="n">
-        <v>1.528695364805943</v>
+        <v>1.528695364805941</v>
       </c>
       <c r="E6" t="n">
-        <v>1.528695364805943</v>
+        <v>1.528695364805941</v>
       </c>
       <c r="F6" t="n">
-        <v>1.528695364805943</v>
+        <v>1.528695364805941</v>
       </c>
       <c r="G6" t="n">
-        <v>1.052084973748756</v>
+        <v>1.052084973748757</v>
       </c>
       <c r="H6" t="n">
-        <v>1.528695364805943</v>
+        <v>1.528695364805941</v>
       </c>
       <c r="I6" t="n">
-        <v>1.052084973748756</v>
+        <v>1.052084973748757</v>
       </c>
       <c r="J6" t="n">
-        <v>1.526253906109474</v>
+        <v>1.04964351505229</v>
       </c>
       <c r="K6" t="n">
-        <v>1.052084973748756</v>
+        <v>1.052084973748757</v>
       </c>
       <c r="L6" t="n">
-        <v>1.052084973748756</v>
+        <v>1.528695364805941</v>
       </c>
       <c r="M6" t="n">
-        <v>1.528695364805943</v>
+        <v>1.528695364805941</v>
       </c>
       <c r="N6" t="n">
-        <v>1.055961924913821</v>
+        <v>1.055961924913863</v>
       </c>
       <c r="O6" t="n">
-        <v>1.055961924913795</v>
+        <v>1.055961924913863</v>
       </c>
       <c r="P6" t="n">
-        <v>1.555972335978141</v>
+        <v>1.555972335978139</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.052084973748756</v>
+        <v>1.528695364805941</v>
       </c>
       <c r="R6" t="n">
-        <v>1.528695364805943</v>
+        <v>1.528695364805941</v>
       </c>
       <c r="S6" t="n">
-        <v>1.528695364805943</v>
+        <v>1.528695364805941</v>
       </c>
       <c r="T6" t="n">
-        <v>1.528695364805943</v>
+        <v>1.052084973748757</v>
       </c>
       <c r="U6" t="n">
-        <v>1.528695364805943</v>
+        <v>1.528695364805941</v>
       </c>
       <c r="V6" t="n">
-        <v>1.036100871196112</v>
+        <v>1.512711262253296</v>
       </c>
       <c r="W6" t="n">
-        <v>1.077434298957359</v>
+        <v>1.077434298957379</v>
       </c>
       <c r="X6" t="n">
-        <v>1.528695364805943</v>
+        <v>1.052084973748757</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.064778537612795</v>
+        <v>1.064778537612862</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.052084973748756</v>
+        <v>1.052084973748757</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.528695364805943</v>
+        <v>1.528695364805941</v>
       </c>
       <c r="AB6" t="n">
         <v>1.065043014885764</v>
@@ -9338,7 +9338,7 @@
         <v>1.486871243584424</v>
       </c>
       <c r="J7" t="n">
-        <v>1.484429784887955</v>
+        <v>1.484429784887956</v>
       </c>
       <c r="K7" t="n">
         <v>1.486871243584424</v>
@@ -9353,10 +9353,10 @@
         <v>1.486871243584424</v>
       </c>
       <c r="O7" t="n">
-        <v>1.48483494987856</v>
+        <v>1.484834949878559</v>
       </c>
       <c r="P7" t="n">
-        <v>1.48483494987856</v>
+        <v>1.484834949878559</v>
       </c>
       <c r="Q7" t="n">
         <v>1.486871243584424</v>
@@ -9374,7 +9374,7 @@
         <v>1.484059496229804</v>
       </c>
       <c r="V7" t="n">
-        <v>1.470887141031779</v>
+        <v>1.47088714103178</v>
       </c>
       <c r="W7" t="n">
         <v>1.486871243584424</v>
@@ -9405,82 +9405,82 @@
         <v>1.717603651503905</v>
       </c>
       <c r="C8" t="n">
-        <v>2.334001094816549</v>
+        <v>2.33400109481655</v>
       </c>
       <c r="D8" t="n">
-        <v>2.334001094816549</v>
+        <v>2.33400109481655</v>
       </c>
       <c r="E8" t="n">
-        <v>2.334001094816549</v>
+        <v>2.005787638942555</v>
       </c>
       <c r="F8" t="n">
         <v>1.813631169120211</v>
       </c>
       <c r="G8" t="n">
-        <v>2.334001094816549</v>
+        <v>2.461815120098497</v>
       </c>
       <c r="H8" t="n">
-        <v>2.334001094816549</v>
+        <v>2.33400109481655</v>
       </c>
       <c r="I8" t="n">
-        <v>2.334001094816549</v>
+        <v>2.33400109481655</v>
       </c>
       <c r="J8" t="n">
-        <v>2.331559636120078</v>
+        <v>2.331559636120081</v>
       </c>
       <c r="K8" t="n">
-        <v>2.334001094816549</v>
+        <v>2.33400109481655</v>
       </c>
       <c r="L8" t="n">
-        <v>2.334001094816549</v>
+        <v>2.33400109481655</v>
       </c>
       <c r="M8" t="n">
-        <v>2.334001094816549</v>
+        <v>2.334001094816159</v>
       </c>
       <c r="N8" t="n">
-        <v>1.856189955065623</v>
+        <v>1.856189955065625</v>
       </c>
       <c r="O8" t="n">
-        <v>1.98749660475992</v>
+        <v>1.987496604759921</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95531017213486</v>
+        <v>1.955310172134859</v>
       </c>
       <c r="Q8" t="n">
         <v>1.59646748544998</v>
       </c>
       <c r="R8" t="n">
-        <v>2.334001094816549</v>
+        <v>2.33400109481655</v>
       </c>
       <c r="S8" t="n">
-        <v>2.334001094816549</v>
+        <v>2.33400109481655</v>
       </c>
       <c r="T8" t="n">
-        <v>2.334001094816549</v>
+        <v>2.33400109481655</v>
       </c>
       <c r="U8" t="n">
-        <v>1.954137912225271</v>
+        <v>2.032544771841513</v>
       </c>
       <c r="V8" t="n">
-        <v>2.318016992263906</v>
+        <v>2.148883437964241</v>
       </c>
       <c r="W8" t="n">
-        <v>2.334122234044817</v>
+        <v>2.334122234044814</v>
       </c>
       <c r="X8" t="n">
         <v>1.652961535603859</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.94584297893628</v>
+        <v>2.945842978936283</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.334001094816549</v>
+        <v>1.706153752580039</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.334001094816549</v>
+        <v>2.33400109481655</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.977879766179234</v>
+        <v>2.977879766179229</v>
       </c>
     </row>
     <row r="9">
@@ -9493,82 +9493,82 @@
         <v>2.974423198176688</v>
       </c>
       <c r="C9" t="n">
-        <v>3.590292273878081</v>
+        <v>3.590292273878083</v>
       </c>
       <c r="D9" t="n">
-        <v>3.590292273878081</v>
+        <v>3.590292273878083</v>
       </c>
       <c r="E9" t="n">
-        <v>3.590292273878081</v>
+        <v>3.448152149676144</v>
       </c>
       <c r="F9" t="n">
-        <v>3.590292273878081</v>
+        <v>2.170546058747064</v>
       </c>
       <c r="G9" t="n">
-        <v>3.590292273878081</v>
+        <v>3.590292204177115</v>
       </c>
       <c r="H9" t="n">
-        <v>3.590292273878081</v>
+        <v>3.590292273878083</v>
       </c>
       <c r="I9" t="n">
-        <v>3.590292273878081</v>
+        <v>3.590292273878083</v>
       </c>
       <c r="J9" t="n">
-        <v>3.587850815181611</v>
+        <v>3.587850815181613</v>
       </c>
       <c r="K9" t="n">
-        <v>3.590292273878081</v>
+        <v>3.590292273878083</v>
       </c>
       <c r="L9" t="n">
-        <v>3.590292273878081</v>
+        <v>3.590292273878083</v>
       </c>
       <c r="M9" t="n">
-        <v>3.590292273878081</v>
+        <v>3.590292273878083</v>
       </c>
       <c r="N9" t="n">
-        <v>3.590292273878081</v>
+        <v>3.590292273878083</v>
       </c>
       <c r="O9" t="n">
-        <v>3.794390386354022</v>
+        <v>3.794390386354025</v>
       </c>
       <c r="P9" t="n">
-        <v>3.838778239242425</v>
+        <v>3.838778239242429</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.590292204177113</v>
+        <v>3.590292204177115</v>
       </c>
       <c r="R9" t="n">
-        <v>3.590292273878081</v>
+        <v>3.590292273878083</v>
       </c>
       <c r="S9" t="n">
-        <v>3.590292273878081</v>
+        <v>3.590292273878083</v>
       </c>
       <c r="T9" t="n">
-        <v>3.590292273878081</v>
+        <v>3.590292273878083</v>
       </c>
       <c r="U9" t="n">
-        <v>3.590292273878081</v>
+        <v>3.590292273878083</v>
       </c>
       <c r="V9" t="n">
-        <v>3.574308171325435</v>
+        <v>4.285006899662524</v>
       </c>
       <c r="W9" t="n">
-        <v>3.590292273878081</v>
+        <v>3.590292273878083</v>
       </c>
       <c r="X9" t="n">
-        <v>3.590292273878081</v>
+        <v>3.590292273878083</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.590292273878081</v>
+        <v>3.590292273878083</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.590292273878081</v>
+        <v>3.21897795876766</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.590292273878081</v>
+        <v>3.590292273878083</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.590292273878081</v>
+        <v>3.590292273878083</v>
       </c>
     </row>
     <row r="10">
@@ -9587,7 +9587,7 @@
         <v>10.61725468570428</v>
       </c>
       <c r="E10" t="n">
-        <v>9.801984787677437</v>
+        <v>9.801984787677439</v>
       </c>
       <c r="F10" t="n">
         <v>10.89905528177081</v>
@@ -9611,7 +9611,7 @@
         <v>10.2986956151449</v>
       </c>
       <c r="M10" t="n">
-        <v>9.818881048092203</v>
+        <v>9.818881048092205</v>
       </c>
       <c r="N10" t="n">
         <v>10.5315388583099</v>
@@ -9626,16 +9626,16 @@
         <v>10.76829764078865</v>
       </c>
       <c r="R10" t="n">
-        <v>11.00596502267695</v>
+        <v>11.00596502267694</v>
       </c>
       <c r="S10" t="n">
         <v>10.488647872853</v>
       </c>
       <c r="T10" t="n">
-        <v>10.79804609799686</v>
+        <v>10.79804609799685</v>
       </c>
       <c r="U10" t="n">
-        <v>10.28971085945999</v>
+        <v>10.28971085945998</v>
       </c>
       <c r="V10" t="n">
         <v>10.97735863255828</v>
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.63418514164939</v>
+        <v>4.634185141649389</v>
       </c>
       <c r="C11" t="n">
-        <v>4.654271048002614</v>
+        <v>4.654271048002613</v>
       </c>
       <c r="D11" t="n">
         <v>4.56564758670801</v>
@@ -9678,73 +9678,73 @@
         <v>3.581758880138355</v>
       </c>
       <c r="F11" t="n">
-        <v>4.645782605977765</v>
+        <v>4.645782605977764</v>
       </c>
       <c r="G11" t="n">
-        <v>4.337041877840424</v>
+        <v>4.337041877840423</v>
       </c>
       <c r="H11" t="n">
         <v>4.567800524748773</v>
       </c>
       <c r="I11" t="n">
-        <v>4.729465374127952</v>
+        <v>4.72946537412795</v>
       </c>
       <c r="J11" t="n">
         <v>4.470253281959859</v>
       </c>
       <c r="K11" t="n">
-        <v>4.637485006806529</v>
+        <v>4.637485006806528</v>
       </c>
       <c r="L11" t="n">
-        <v>4.473110380702643</v>
+        <v>4.473110380702644</v>
       </c>
       <c r="M11" t="n">
-        <v>4.339411568317802</v>
+        <v>4.339411568317801</v>
       </c>
       <c r="N11" t="n">
-        <v>4.540926038362446</v>
+        <v>4.540926038362445</v>
       </c>
       <c r="O11" t="n">
-        <v>4.639461439284653</v>
+        <v>4.639461439284651</v>
       </c>
       <c r="P11" t="n">
-        <v>4.549301655510989</v>
+        <v>4.549301655510991</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.686779194586911</v>
+        <v>4.68677919458691</v>
       </c>
       <c r="R11" t="n">
-        <v>4.794913847214615</v>
+        <v>4.794913847214613</v>
       </c>
       <c r="S11" t="n">
-        <v>4.559539263301758</v>
+        <v>4.559539263301756</v>
       </c>
       <c r="T11" t="n">
-        <v>4.700267262884085</v>
+        <v>4.700267262884084</v>
       </c>
       <c r="U11" t="n">
-        <v>4.469133329823969</v>
+        <v>4.469133329823968</v>
       </c>
       <c r="V11" t="n">
         <v>4.796609196553669</v>
       </c>
       <c r="W11" t="n">
-        <v>4.429140629905078</v>
+        <v>4.429140629905077</v>
       </c>
       <c r="X11" t="n">
-        <v>4.508384130958852</v>
+        <v>4.508384130958851</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.524587357601857</v>
+        <v>4.524587357601855</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.581258345312625</v>
+        <v>4.581258345312623</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.517345693215416</v>
+        <v>4.517345693215418</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.352648994589215</v>
+        <v>4.352648994589214</v>
       </c>
     </row>
   </sheetData>
@@ -9910,85 +9910,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.656483484489963</v>
+        <v>4.656483484489966</v>
       </c>
       <c r="C2" t="n">
-        <v>4.592791227203782</v>
+        <v>4.592791227203786</v>
       </c>
       <c r="D2" t="n">
-        <v>4.614971297807634</v>
+        <v>4.614971297807632</v>
       </c>
       <c r="E2" t="n">
-        <v>3.560619711903163</v>
+        <v>3.560619711903165</v>
       </c>
       <c r="F2" t="n">
-        <v>4.545466983291202</v>
+        <v>4.545466983291203</v>
       </c>
       <c r="G2" t="n">
         <v>4.769504482555539</v>
       </c>
       <c r="H2" t="n">
-        <v>4.656483484489963</v>
+        <v>4.656483484489966</v>
       </c>
       <c r="I2" t="n">
-        <v>4.656483484489963</v>
+        <v>4.656483484489966</v>
       </c>
       <c r="J2" t="n">
-        <v>4.652973740550482</v>
+        <v>4.65297374055048</v>
       </c>
       <c r="K2" t="n">
-        <v>4.656386171406912</v>
+        <v>4.656386171406916</v>
       </c>
       <c r="L2" t="n">
-        <v>4.656483484489963</v>
+        <v>4.656483484489966</v>
       </c>
       <c r="M2" t="n">
-        <v>4.603746521992398</v>
+        <v>4.603746521992401</v>
       </c>
       <c r="N2" t="n">
-        <v>4.608554632046331</v>
+        <v>4.608554632046327</v>
       </c>
       <c r="O2" t="n">
-        <v>4.656232028115225</v>
+        <v>4.656232028115229</v>
       </c>
       <c r="P2" t="n">
-        <v>4.656455050261153</v>
+        <v>4.656455050261156</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.656480289187247</v>
+        <v>4.65648028918725</v>
       </c>
       <c r="R2" t="n">
-        <v>4.656847985840717</v>
+        <v>4.656847985840721</v>
       </c>
       <c r="S2" t="n">
-        <v>4.656483484489963</v>
+        <v>4.656483484489966</v>
       </c>
       <c r="T2" t="n">
-        <v>4.656195026762608</v>
+        <v>4.656195026762612</v>
       </c>
       <c r="U2" t="n">
-        <v>4.656829238436862</v>
+        <v>4.656829238436866</v>
       </c>
       <c r="V2" t="n">
-        <v>4.813886021466473</v>
+        <v>4.813886021466472</v>
       </c>
       <c r="W2" t="n">
-        <v>4.656483484489963</v>
+        <v>4.656483484489966</v>
       </c>
       <c r="X2" t="n">
-        <v>4.658676145448362</v>
+        <v>4.658676145448365</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.655862029468396</v>
+        <v>4.655862029468399</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.622773102090944</v>
+        <v>4.622773102090947</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.656483484489963</v>
+        <v>4.656483484489966</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.659813964512511</v>
+        <v>4.659813964512514</v>
       </c>
     </row>
     <row r="3">
@@ -10086,31 +10086,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.514685092258907</v>
+        <v>-1.514685092258912</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.2688449422277</v>
+        <v>-1.268844942227708</v>
       </c>
       <c r="D4" t="n">
         <v>4.147276599609181</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.070812996270813</v>
+        <v>-2.07081299627083</v>
       </c>
       <c r="F4" t="n">
-        <v>-13.46710548229608</v>
+        <v>-13.4671054822961</v>
       </c>
       <c r="G4" t="n">
-        <v>37.34890583006216</v>
+        <v>37.34890583006197</v>
       </c>
       <c r="H4" t="n">
-        <v>16.81908697047171</v>
+        <v>16.81908697047154</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.197539818993306</v>
+        <v>-3.197539818993313</v>
       </c>
       <c r="J4" t="n">
-        <v>12.89822709264837</v>
+        <v>12.89822709264833</v>
       </c>
       <c r="K4" t="n">
         <v>0.1928277769156406</v>
@@ -10119,52 +10119,52 @@
         <v>-17.15663855116025</v>
       </c>
       <c r="M4" t="n">
-        <v>1.431996147863847</v>
+        <v>1.431996147863842</v>
       </c>
       <c r="N4" t="n">
-        <v>6.118280360914313</v>
+        <v>6.118280360914252</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.298233512726983</v>
+        <v>-3.298233512726922</v>
       </c>
       <c r="P4" t="n">
-        <v>9.106923690721137</v>
+        <v>9.106923690721159</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8556653116440724</v>
+        <v>0.8556653116440938</v>
       </c>
       <c r="R4" t="n">
         <v>-31.25367278709211</v>
       </c>
       <c r="S4" t="n">
-        <v>-8.612057248427348</v>
+        <v>-8.612057248427341</v>
       </c>
       <c r="T4" t="n">
-        <v>-9.512962360118017</v>
+        <v>-9.512962360118035</v>
       </c>
       <c r="U4" t="n">
-        <v>6.118280360914314</v>
+        <v>6.118280360914254</v>
       </c>
       <c r="V4" t="n">
-        <v>6.609770422302336</v>
+        <v>6.609770422302325</v>
       </c>
       <c r="W4" t="n">
-        <v>24.28495624183227</v>
+        <v>24.28495624183224</v>
       </c>
       <c r="X4" t="n">
-        <v>34.58528320499052</v>
+        <v>34.5852832049904</v>
       </c>
       <c r="Y4" t="n">
-        <v>45.73436339970792</v>
+        <v>45.73436339970785</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.454825443568503</v>
+        <v>5.454825443568496</v>
       </c>
       <c r="AA4" t="n">
-        <v>14.1416247584752</v>
+        <v>14.14162475847523</v>
       </c>
       <c r="AB4" t="n">
-        <v>28.92964986823604</v>
+        <v>28.92964986823598</v>
       </c>
     </row>
     <row r="5">
@@ -10174,85 +10174,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.731105895200417</v>
+        <v>0.7311058952004075</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7311058952004134</v>
+        <v>0.7311058952004073</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7311058952004134</v>
+        <v>0.7311058952004073</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7311058952004134</v>
+        <v>0.7311058952004073</v>
       </c>
       <c r="F5" t="n">
-        <v>0.731105895200417</v>
+        <v>0.7311058952004075</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7311058952004134</v>
+        <v>0.7311058952004073</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7311058952004134</v>
+        <v>0.7311058952004073</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7311058952004134</v>
+        <v>0.7311058952004073</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7289134691399723</v>
+        <v>0.7289134691399711</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7311058952004134</v>
+        <v>0.7311058952004073</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7311058952004134</v>
+        <v>0.7311058952004073</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7311058952004134</v>
+        <v>0.7311058952004073</v>
       </c>
       <c r="N5" t="n">
-        <v>0.731105895200417</v>
+        <v>0.7311058952004077</v>
       </c>
       <c r="O5" t="n">
-        <v>0.731105895200417</v>
+        <v>0.7311058952004075</v>
       </c>
       <c r="P5" t="n">
-        <v>0.731105895200417</v>
+        <v>0.7311058952004075</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.731105895200417</v>
+        <v>0.7311058952004075</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7311058952004134</v>
+        <v>0.7311058952004073</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7311058952004134</v>
+        <v>0.7311058952004073</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7311058952004134</v>
+        <v>0.7311058952004073</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7158920622650345</v>
+        <v>0.7158920622650297</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7167027576777172</v>
+        <v>0.7167027576777154</v>
       </c>
       <c r="W5" t="n">
-        <v>0.731105895200417</v>
+        <v>0.7311058952004075</v>
       </c>
       <c r="X5" t="n">
-        <v>0.731105895200417</v>
+        <v>0.7311058952004075</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.7158920622650345</v>
+        <v>0.7158920622650297</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.7311058952004134</v>
+        <v>0.7311058952004073</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.7311058952004134</v>
+        <v>0.7311058952004073</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.731105895200417</v>
+        <v>0.7311058952004075</v>
       </c>
     </row>
     <row r="6">
@@ -10262,85 +10262,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.165506932460301</v>
+        <v>0.790187102931289</v>
       </c>
       <c r="C6" t="n">
-        <v>1.165506932460301</v>
+        <v>1.165506932460305</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7901871029312861</v>
+        <v>0.790187102931289</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7901871029312861</v>
+        <v>1.165506932460305</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7901871029312861</v>
+        <v>1.165506932460305</v>
       </c>
       <c r="G6" t="n">
-        <v>1.165506932460301</v>
+        <v>0.790187102931289</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7901871029312861</v>
+        <v>1.165506932460305</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7901871029312861</v>
+        <v>1.165506932460305</v>
       </c>
       <c r="J6" t="n">
-        <v>1.163314506399868</v>
+        <v>0.7879946768708517</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7901871029312861</v>
+        <v>1.165506932460305</v>
       </c>
       <c r="L6" t="n">
-        <v>1.165506932460301</v>
+        <v>0.790187102931289</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7901871029312861</v>
+        <v>1.165506932460305</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7937212458045688</v>
+        <v>0.7937212458045204</v>
       </c>
       <c r="O6" t="n">
-        <v>1.192059178952193</v>
+        <v>0.7937212458044768</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7807155305114626</v>
+        <v>0.7807155305113801</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7901871029312861</v>
+        <v>1.165506932460305</v>
       </c>
       <c r="R6" t="n">
-        <v>1.165506932460301</v>
+        <v>1.165506932460305</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7901871029312861</v>
+        <v>0.790187102931289</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7901871029312861</v>
+        <v>0.790187102931289</v>
       </c>
       <c r="U6" t="n">
-        <v>1.165506932460301</v>
+        <v>0.790187102931289</v>
       </c>
       <c r="V6" t="n">
         <v>1.151103794937615</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8102220032735244</v>
+        <v>0.8102220032735161</v>
       </c>
       <c r="X6" t="n">
-        <v>1.165506932460301</v>
+        <v>0.790187102931289</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.800513779915608</v>
+        <v>0.8005137799159118</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.7901871029312861</v>
+        <v>0.790187102931289</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.165506932460301</v>
+        <v>1.165506932460305</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7998023092365663</v>
+        <v>0.7998023092365606</v>
       </c>
     </row>
     <row r="7">
@@ -10350,43 +10350,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
       <c r="C7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
       <c r="D7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
       <c r="E7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
       <c r="F7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
       <c r="G7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
       <c r="H7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
       <c r="I7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
       <c r="J7" t="n">
-        <v>1.142757792692925</v>
+        <v>1.142757792692929</v>
       </c>
       <c r="K7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
       <c r="L7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
       <c r="M7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
       <c r="N7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
       <c r="O7" t="n">
         <v>1.143055570125297</v>
@@ -10395,40 +10395,40 @@
         <v>1.143055570125297</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
       <c r="R7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
       <c r="S7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
       <c r="T7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
       <c r="U7" t="n">
-        <v>1.138608975899877</v>
+        <v>1.138608975899875</v>
       </c>
       <c r="V7" t="n">
         <v>1.130547081230673</v>
       </c>
       <c r="W7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
       <c r="X7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.144950218753376</v>
+        <v>1.144950218753364</v>
       </c>
     </row>
     <row r="8">
@@ -10438,85 +10438,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.292426628703831</v>
+        <v>1.29242662870383</v>
       </c>
       <c r="C8" t="n">
-        <v>1.755361189206038</v>
+        <v>1.755361189206035</v>
       </c>
       <c r="D8" t="n">
-        <v>1.755361189206038</v>
+        <v>1.755361189206035</v>
       </c>
       <c r="E8" t="n">
-        <v>1.755361189206038</v>
+        <v>1.508862191543612</v>
       </c>
       <c r="F8" t="n">
-        <v>1.364546422747235</v>
+        <v>1.364546422747238</v>
       </c>
       <c r="G8" t="n">
-        <v>1.755361189206038</v>
+        <v>1.851353686025647</v>
       </c>
       <c r="H8" t="n">
-        <v>1.755361189206038</v>
+        <v>1.755361189206035</v>
       </c>
       <c r="I8" t="n">
-        <v>1.755361189206038</v>
+        <v>1.755361189206035</v>
       </c>
       <c r="J8" t="n">
-        <v>1.753168763145598</v>
+        <v>1.753168763145599</v>
       </c>
       <c r="K8" t="n">
-        <v>1.755361189206038</v>
+        <v>1.755361189206035</v>
       </c>
       <c r="L8" t="n">
-        <v>1.755361189206038</v>
+        <v>1.755361189206035</v>
       </c>
       <c r="M8" t="n">
-        <v>1.755361189206038</v>
+        <v>1.755361189205463</v>
       </c>
       <c r="N8" t="n">
-        <v>1.396509457434039</v>
+        <v>1.396509457434049</v>
       </c>
       <c r="O8" t="n">
-        <v>1.495125028947054</v>
+        <v>1.495125028947051</v>
       </c>
       <c r="P8" t="n">
-        <v>1.470951969507037</v>
+        <v>1.470951969507045</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.201449421722455</v>
+        <v>1.201449421722456</v>
       </c>
       <c r="R8" t="n">
-        <v>1.755361189206038</v>
+        <v>1.755361189206035</v>
       </c>
       <c r="S8" t="n">
-        <v>1.755361189206038</v>
+        <v>1.755361189206035</v>
       </c>
       <c r="T8" t="n">
-        <v>1.755361189206038</v>
+        <v>1.755361189206035</v>
       </c>
       <c r="U8" t="n">
-        <v>1.467259619311087</v>
+        <v>1.525963007303397</v>
       </c>
       <c r="V8" t="n">
-        <v>1.740958051683344</v>
+        <v>1.610630217162065</v>
       </c>
       <c r="W8" t="n">
-        <v>1.755452168655882</v>
+        <v>1.755452168655879</v>
       </c>
       <c r="X8" t="n">
-        <v>1.243878293778026</v>
+        <v>1.243878293778027</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.209751379772786</v>
+        <v>2.209751379772788</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.755361189206038</v>
+        <v>1.283827381611502</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.755361189206038</v>
+        <v>1.755361189206035</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.238935047182611</v>
+        <v>2.238935047182615</v>
       </c>
     </row>
     <row r="9">
@@ -10526,85 +10526,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.224326035139192</v>
+        <v>2.224326035139195</v>
       </c>
       <c r="C9" t="n">
-        <v>2.683541114809072</v>
+        <v>2.683541114809068</v>
       </c>
       <c r="D9" t="n">
-        <v>2.683541114809072</v>
+        <v>2.683541114809068</v>
       </c>
       <c r="E9" t="n">
-        <v>2.683541114809072</v>
+        <v>2.577556413956228</v>
       </c>
       <c r="F9" t="n">
-        <v>2.683541114809072</v>
+        <v>1.624924572373828</v>
       </c>
       <c r="G9" t="n">
-        <v>2.683541114809072</v>
+        <v>2.683541461181099</v>
       </c>
       <c r="H9" t="n">
-        <v>2.683541114809072</v>
+        <v>2.683541114809068</v>
       </c>
       <c r="I9" t="n">
-        <v>2.683541114809072</v>
+        <v>2.683541114809068</v>
       </c>
       <c r="J9" t="n">
-        <v>2.68134868874864</v>
+        <v>2.681348688748633</v>
       </c>
       <c r="K9" t="n">
-        <v>2.683541114809072</v>
+        <v>2.683541114809068</v>
       </c>
       <c r="L9" t="n">
-        <v>2.683541114809072</v>
+        <v>2.683541114809068</v>
       </c>
       <c r="M9" t="n">
-        <v>2.683541114809072</v>
+        <v>2.683541114809068</v>
       </c>
       <c r="N9" t="n">
-        <v>2.683541114809072</v>
+        <v>2.683541114809068</v>
       </c>
       <c r="O9" t="n">
-        <v>2.835724852080096</v>
+        <v>2.835724852080093</v>
       </c>
       <c r="P9" t="n">
-        <v>2.868822128573366</v>
+        <v>2.868822128573361</v>
       </c>
       <c r="Q9" t="n">
         <v>2.683541461181099</v>
       </c>
       <c r="R9" t="n">
-        <v>2.683541114809072</v>
+        <v>2.683541114809068</v>
       </c>
       <c r="S9" t="n">
-        <v>2.683541114809072</v>
+        <v>2.683541114809068</v>
       </c>
       <c r="T9" t="n">
-        <v>2.683541114809072</v>
+        <v>2.683541114809068</v>
       </c>
       <c r="U9" t="n">
-        <v>2.683541114809072</v>
+        <v>2.683541114809068</v>
       </c>
       <c r="V9" t="n">
-        <v>2.669137977286377</v>
+        <v>3.199062682847112</v>
       </c>
       <c r="W9" t="n">
-        <v>2.683541114809072</v>
+        <v>2.683541114809068</v>
       </c>
       <c r="X9" t="n">
-        <v>2.683541114809072</v>
+        <v>2.683541114809068</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.683541114809072</v>
+        <v>2.683541114809068</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.683541114809072</v>
+        <v>2.406675394306776</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.683541114809072</v>
+        <v>2.683541114809068</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.683541114809072</v>
+        <v>2.683541114809068</v>
       </c>
     </row>
     <row r="10">
@@ -10623,13 +10623,13 @@
         <v>10.86559900021603</v>
       </c>
       <c r="E10" t="n">
-        <v>9.963440213533776</v>
+        <v>9.963440213533774</v>
       </c>
       <c r="F10" t="n">
         <v>11.26997762860876</v>
       </c>
       <c r="G10" t="n">
-        <v>9.94511286693826</v>
+        <v>9.94511286693827</v>
       </c>
       <c r="H10" t="n">
         <v>10.60399592676858</v>
@@ -10653,10 +10653,10 @@
         <v>10.90301332845561</v>
       </c>
       <c r="O10" t="n">
-        <v>11.05365703735035</v>
+        <v>11.05365703735036</v>
       </c>
       <c r="P10" t="n">
-        <v>10.72809394633524</v>
+        <v>10.72809394633523</v>
       </c>
       <c r="Q10" t="n">
         <v>10.94205511128342</v>
@@ -10683,7 +10683,7 @@
         <v>10.15479093606792</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.881963339952504</v>
+        <v>9.881963339952499</v>
       </c>
       <c r="Z10" t="n">
         <v>10.81789525587451</v>
@@ -10692,7 +10692,7 @@
         <v>10.63083733473391</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.3357646799901</v>
+        <v>10.33576467999009</v>
       </c>
     </row>
     <row r="11">
@@ -10708,79 +10708,79 @@
         <v>4.615883276112369</v>
       </c>
       <c r="D11" t="n">
-        <v>4.579798109125042</v>
+        <v>4.579798109125039</v>
       </c>
       <c r="E11" t="n">
-        <v>3.590973867926822</v>
+        <v>3.590973867926823</v>
       </c>
       <c r="F11" t="n">
-        <v>4.694369331916488</v>
+        <v>4.694369331916484</v>
       </c>
       <c r="G11" t="n">
-        <v>4.315540714985404</v>
+        <v>4.315540714985403</v>
       </c>
       <c r="H11" t="n">
-        <v>4.502280063709253</v>
+        <v>4.502280063709254</v>
       </c>
       <c r="I11" t="n">
-        <v>4.695979086194553</v>
+        <v>4.695979086194548</v>
       </c>
       <c r="J11" t="n">
-        <v>4.505014507966624</v>
+        <v>4.505014507966621</v>
       </c>
       <c r="K11" t="n">
-        <v>4.665021572203093</v>
+        <v>4.665021572203085</v>
       </c>
       <c r="L11" t="n">
         <v>4.871039253238858</v>
       </c>
       <c r="M11" t="n">
-        <v>4.597930846230974</v>
+        <v>4.59793084623097</v>
       </c>
       <c r="N11" t="n">
-        <v>4.590405081945139</v>
+        <v>4.590405081945137</v>
       </c>
       <c r="O11" t="n">
-        <v>4.706751048462128</v>
+        <v>4.706751048462127</v>
       </c>
       <c r="P11" t="n">
-        <v>4.558730781582546</v>
+        <v>4.558730781582542</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.656096465677703</v>
+        <v>4.656096465677707</v>
       </c>
       <c r="R11" t="n">
-        <v>4.971466731898519</v>
+        <v>4.971466731898518</v>
       </c>
       <c r="S11" t="n">
-        <v>4.771972985016641</v>
+        <v>4.771972985016643</v>
       </c>
       <c r="T11" t="n">
-        <v>4.761159168856476</v>
+        <v>4.761159168856475</v>
       </c>
       <c r="U11" t="n">
-        <v>4.594729838910961</v>
+        <v>4.594729838910963</v>
       </c>
       <c r="V11" t="n">
-        <v>4.743445838513205</v>
+        <v>4.743445838513207</v>
       </c>
       <c r="W11" t="n">
-        <v>4.407050934117647</v>
+        <v>4.407050934117646</v>
       </c>
       <c r="X11" t="n">
         <v>4.29899127358482</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.173440909780383</v>
+        <v>4.173440909780384</v>
       </c>
       <c r="Z11" t="n">
         <v>4.565909165364698</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.51449298987197</v>
+        <v>4.514492989871973</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.381906190969031</v>
+        <v>4.381906190969032</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Hydrogen/hydrogen climate change results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen climate change results.xlsx
@@ -886,7 +886,7 @@
         <v>0.7381287869732229</v>
       </c>
       <c r="N5" t="n">
-        <v>43.06464988705973</v>
+        <v>0.7381287869732217</v>
       </c>
       <c r="O5" t="n">
         <v>0.7381287869732217</v>
@@ -974,7 +974,7 @@
         <v>1.418049302866048</v>
       </c>
       <c r="N6" t="n">
-        <v>43.06464988705973</v>
+        <v>0.8885412381492358</v>
       </c>
       <c r="O6" t="n">
         <v>0.8885400775376213</v>
@@ -1062,7 +1062,7 @@
         <v>1.365930429388484</v>
       </c>
       <c r="N7" t="n">
-        <v>43.06464988705973</v>
+        <v>1.365930429388484</v>
       </c>
       <c r="O7" t="n">
         <v>1.36375172584861</v>
@@ -1150,7 +1150,7 @@
         <v>2.401355566189243</v>
       </c>
       <c r="N8" t="n">
-        <v>43.06464988705973</v>
+        <v>1.829915337813292</v>
       </c>
       <c r="O8" t="n">
         <v>1.986952074014027</v>
@@ -1238,7 +1238,7 @@
         <v>4.065838789179348</v>
       </c>
       <c r="N9" t="n">
-        <v>43.06464988705973</v>
+        <v>4.065838789179348</v>
       </c>
       <c r="O9" t="n">
         <v>4.321562927179746</v>
@@ -1822,7 +1822,7 @@
         <v>-0.2409488766220327</v>
       </c>
       <c r="J4" t="n">
-        <v>2.367416902071644</v>
+        <v>2.367416902071643</v>
       </c>
       <c r="K4" t="n">
         <v>-0.3044938174415819</v>
@@ -1922,7 +1922,7 @@
         <v>0.5210722587716079</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9085121421246969</v>
+        <v>0.5210722587716102</v>
       </c>
       <c r="O5" t="n">
         <v>0.5210722587716102</v>
@@ -2010,7 +2010,7 @@
         <v>0.5720520548065877</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9085121421246969</v>
+        <v>0.5737948146882463</v>
       </c>
       <c r="O6" t="n">
         <v>0.8231298444895622</v>
@@ -2098,7 +2098,7 @@
         <v>0.8810785700339088</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9085121421246969</v>
+        <v>0.8810785700339088</v>
       </c>
       <c r="O7" t="n">
         <v>0.8791855951143774</v>
@@ -2186,7 +2186,7 @@
         <v>1.323653176773191</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9085121421246969</v>
+        <v>1.046332506612949</v>
       </c>
       <c r="O8" t="n">
         <v>1.12254263471107</v>
@@ -2274,7 +2274,7 @@
         <v>1.851687542116518</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9085121421246969</v>
+        <v>1.851687542116518</v>
       </c>
       <c r="O9" t="n">
         <v>1.955706922416583</v>
@@ -2958,7 +2958,7 @@
         <v>0.6834499854914111</v>
       </c>
       <c r="N5" t="n">
-        <v>34.19134557475276</v>
+        <v>0.68344998549141</v>
       </c>
       <c r="O5" t="n">
         <v>0.68344998549141</v>
@@ -3046,7 +3046,7 @@
         <v>1.278519409120054</v>
       </c>
       <c r="N6" t="n">
-        <v>34.19134557475276</v>
+        <v>0.8048201807124722</v>
       </c>
       <c r="O6" t="n">
         <v>0.8055169269232063</v>
@@ -3134,7 +3134,7 @@
         <v>1.241692111566006</v>
       </c>
       <c r="N7" t="n">
-        <v>34.19134557475276</v>
+        <v>1.241692111566006</v>
       </c>
       <c r="O7" t="n">
         <v>1.239654297931014</v>
@@ -3222,7 +3222,7 @@
         <v>2.154318509494807</v>
       </c>
       <c r="N8" t="n">
-        <v>34.19134557475276</v>
+        <v>1.648761702792441</v>
       </c>
       <c r="O8" t="n">
         <v>1.787693102711081</v>
@@ -3310,7 +3310,7 @@
         <v>3.362336521983579</v>
       </c>
       <c r="N9" t="n">
-        <v>34.19134557475276</v>
+        <v>3.362336521983579</v>
       </c>
       <c r="O9" t="n">
         <v>3.569583190345405</v>
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.777426709685599</v>
+        <v>4.777426709685604</v>
       </c>
       <c r="C2" t="n">
-        <v>4.726687797651637</v>
+        <v>4.72668779765164</v>
       </c>
       <c r="D2" t="n">
-        <v>4.814525398108811</v>
+        <v>4.814525398108812</v>
       </c>
       <c r="E2" t="n">
         <v>3.677151750319296</v>
       </c>
       <c r="F2" t="n">
-        <v>4.736082392121607</v>
+        <v>4.73608239212161</v>
       </c>
       <c r="G2" t="n">
-        <v>4.857661355673679</v>
+        <v>4.857661355673681</v>
       </c>
       <c r="H2" t="n">
-        <v>4.778949962583519</v>
+        <v>4.77894996258352</v>
       </c>
       <c r="I2" t="n">
-        <v>4.751706606650505</v>
+        <v>4.751706606650508</v>
       </c>
       <c r="J2" t="n">
-        <v>4.812882770376468</v>
+        <v>4.812882770376472</v>
       </c>
       <c r="K2" t="n">
-        <v>4.778984842009819</v>
+        <v>4.778984842009821</v>
       </c>
       <c r="L2" t="n">
         <v>4.839533421997777</v>
       </c>
       <c r="M2" t="n">
-        <v>4.870806226993524</v>
+        <v>4.870806226993528</v>
       </c>
       <c r="N2" t="n">
-        <v>4.77950149245364</v>
+        <v>4.779501492453641</v>
       </c>
       <c r="O2" t="n">
-        <v>4.770339120006957</v>
+        <v>4.770339120006962</v>
       </c>
       <c r="P2" t="n">
-        <v>4.817129835755637</v>
+        <v>4.817129835755638</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.730661725328165</v>
+        <v>4.730661725328167</v>
       </c>
       <c r="R2" t="n">
         <v>4.763635095563828</v>
       </c>
       <c r="S2" t="n">
-        <v>4.824078383745117</v>
+        <v>4.824078383745121</v>
       </c>
       <c r="T2" t="n">
-        <v>4.768961095552165</v>
+        <v>4.768961095552169</v>
       </c>
       <c r="U2" t="n">
-        <v>4.816575228343513</v>
+        <v>4.816575228343516</v>
       </c>
       <c r="V2" t="n">
-        <v>4.934584704089098</v>
+        <v>4.934584704089099</v>
       </c>
       <c r="W2" t="n">
-        <v>4.837344685611854</v>
+        <v>4.837344685611857</v>
       </c>
       <c r="X2" t="n">
-        <v>4.844851483368811</v>
+        <v>4.844851483368814</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.823517068557815</v>
+        <v>4.823517068557819</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.778403620824059</v>
+        <v>4.778403620824061</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.802024290092212</v>
+        <v>4.802024290092215</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.886510081211504</v>
+        <v>4.886510081211505</v>
       </c>
     </row>
     <row r="3">
@@ -3791,7 +3791,7 @@
         <v>11.02951508850462</v>
       </c>
       <c r="E3" t="n">
-        <v>9.955409516589969</v>
+        <v>9.95540951658997</v>
       </c>
       <c r="F3" t="n">
         <v>11.02933492996215</v>
@@ -3870,85 +3870,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.03766546582386</v>
+        <v>22.03766546582391</v>
       </c>
       <c r="C4" t="n">
-        <v>10.5193638544737</v>
+        <v>10.51936385447369</v>
       </c>
       <c r="D4" t="n">
         <v>34.05623627805077</v>
       </c>
       <c r="E4" t="n">
-        <v>12.5538459998978</v>
+        <v>12.55384599989777</v>
       </c>
       <c r="F4" t="n">
-        <v>13.43103952136797</v>
+        <v>13.43103952136798</v>
       </c>
       <c r="G4" t="n">
-        <v>40.74268777083589</v>
+        <v>40.74268777083593</v>
       </c>
       <c r="H4" t="n">
-        <v>25.97373766485653</v>
+        <v>25.97373766485652</v>
       </c>
       <c r="I4" t="n">
-        <v>17.84412835158932</v>
+        <v>17.84412835158928</v>
       </c>
       <c r="J4" t="n">
-        <v>32.17607648051514</v>
+        <v>32.17607648051512</v>
       </c>
       <c r="K4" t="n">
-        <v>22.15980292897401</v>
+        <v>22.15980292897402</v>
       </c>
       <c r="L4" t="n">
-        <v>38.75884452312437</v>
+        <v>38.75884452312408</v>
       </c>
       <c r="M4" t="n">
-        <v>49.66104221600438</v>
+        <v>49.66104221600433</v>
       </c>
       <c r="N4" t="n">
-        <v>24.46190297069545</v>
+        <v>24.46190297069543</v>
       </c>
       <c r="O4" t="n">
-        <v>19.38990354868092</v>
+        <v>19.38990354868098</v>
       </c>
       <c r="P4" t="n">
-        <v>31.24446064838019</v>
+        <v>31.24446064838018</v>
       </c>
       <c r="Q4" t="n">
         <v>11.62266485047813</v>
       </c>
       <c r="R4" t="n">
-        <v>21.26523126689966</v>
+        <v>21.26523126689965</v>
       </c>
       <c r="S4" t="n">
-        <v>33.10175339045634</v>
+        <v>33.10175339045629</v>
       </c>
       <c r="T4" t="n">
-        <v>22.39100553210473</v>
+        <v>22.39100553210476</v>
       </c>
       <c r="U4" t="n">
-        <v>31.99295706622204</v>
+        <v>31.99295706622227</v>
       </c>
       <c r="V4" t="n">
-        <v>15.1989444554294</v>
+        <v>15.19894445542946</v>
       </c>
       <c r="W4" t="n">
-        <v>38.70750313555603</v>
+        <v>38.70750313555601</v>
       </c>
       <c r="X4" t="n">
-        <v>40.87581830248157</v>
+        <v>40.87581830248168</v>
       </c>
       <c r="Y4" t="n">
-        <v>35.01888599505952</v>
+        <v>35.01888599505959</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.13883205707949</v>
+        <v>21.13883205707946</v>
       </c>
       <c r="AA4" t="n">
-        <v>29.75640163008458</v>
+        <v>29.75640163008457</v>
       </c>
       <c r="AB4" t="n">
-        <v>55.33011314621479</v>
+        <v>55.33011314621477</v>
       </c>
     </row>
     <row r="5">
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6555237587110461</v>
+        <v>0.6555237587110441</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6555237587110462</v>
+        <v>0.6555237587110474</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6555237587110462</v>
+        <v>0.6555237587110474</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6555237587110462</v>
+        <v>0.6555237587110474</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6555237587110452</v>
+        <v>0.6555237587110446</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6555237587110462</v>
+        <v>0.6555237587110474</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6555237587110462</v>
+        <v>0.6555237587110474</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6555237587110462</v>
+        <v>0.6555237587110474</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6533374861063742</v>
+        <v>0.6533374861063772</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6555237587110462</v>
+        <v>0.6555237587110474</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6555237587110463</v>
+        <v>0.655523758711047</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6555237587110462</v>
+        <v>0.6555237587110474</v>
       </c>
       <c r="N5" t="n">
-        <v>24.46190297069545</v>
+        <v>0.6555237587110446</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6555237587110452</v>
+        <v>0.6555237587110446</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6555237587110452</v>
+        <v>0.6555237587110446</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6555237587110452</v>
+        <v>0.6555237587110446</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6555237587110462</v>
+        <v>0.6555237587110474</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6555237587110462</v>
+        <v>0.6555237587110474</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6555237587110462</v>
+        <v>0.6555237587110474</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6373525243404145</v>
+        <v>0.6373525243404167</v>
       </c>
       <c r="V5" t="n">
         <v>0.6411650762974168</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6555237587110452</v>
+        <v>0.6555237587110446</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6555237587110461</v>
+        <v>0.6555237587110441</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6373525243404145</v>
+        <v>0.6373525243404167</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.6555237587110462</v>
+        <v>0.6555237587110474</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.6555237587110462</v>
+        <v>0.6555237587110474</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6555237587110452</v>
+        <v>0.6555237587110446</v>
       </c>
     </row>
     <row r="6">
@@ -4046,85 +4046,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.194490424479504</v>
+        <v>1.194490424479515</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7711398423916992</v>
+        <v>0.7711398423917016</v>
       </c>
       <c r="D6" t="n">
-        <v>1.194490424479504</v>
+        <v>1.194490424479514</v>
       </c>
       <c r="E6" t="n">
-        <v>1.194490424479504</v>
+        <v>1.194490424479514</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7711398423916992</v>
+        <v>0.7711398423917016</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7711398423916992</v>
+        <v>0.7711398423917016</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7711398423916992</v>
+        <v>0.7711398423917016</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7711398423916992</v>
+        <v>0.7711398423917016</v>
       </c>
       <c r="J6" t="n">
-        <v>1.192304151874833</v>
+        <v>1.192304151874839</v>
       </c>
       <c r="K6" t="n">
-        <v>1.194490424479504</v>
+        <v>1.194490424479514</v>
       </c>
       <c r="L6" t="n">
-        <v>1.194490424479504</v>
+        <v>1.194490424479515</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7711398423916992</v>
+        <v>0.7711398423917016</v>
       </c>
       <c r="N6" t="n">
-        <v>24.46190297069545</v>
+        <v>0.7741378292059697</v>
       </c>
       <c r="O6" t="n">
-        <v>1.217247270408066</v>
+        <v>1.217247270408061</v>
       </c>
       <c r="P6" t="n">
         <v>1.217016841763707</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.194490424479504</v>
+        <v>1.194490424479514</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7711398423916992</v>
+        <v>0.7711398423917016</v>
       </c>
       <c r="S6" t="n">
-        <v>1.194490424479504</v>
+        <v>1.194490424479514</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7711398423916992</v>
+        <v>0.7711398423917016</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7711398423916992</v>
+        <v>0.7711398423917016</v>
       </c>
       <c r="V6" t="n">
         <v>1.180131742065881</v>
       </c>
       <c r="W6" t="n">
-        <v>1.217330400305535</v>
+        <v>1.217330400305533</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7711398423916992</v>
+        <v>0.7711398423917016</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.7850133732029565</v>
+        <v>0.7850133732029885</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.194490424479504</v>
+        <v>1.194490424479514</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.194490424479504</v>
+        <v>1.194490424479514</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7839088193085108</v>
+        <v>0.7839088193085124</v>
       </c>
     </row>
     <row r="7">
@@ -4134,85 +4134,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.151534829448269</v>
+        <v>1.15153482944827</v>
       </c>
       <c r="C7" t="n">
-        <v>1.151534829448267</v>
+        <v>1.151534829448271</v>
       </c>
       <c r="D7" t="n">
-        <v>1.151534829448267</v>
+        <v>1.151534829448271</v>
       </c>
       <c r="E7" t="n">
-        <v>1.151534829448267</v>
+        <v>1.151534829448271</v>
       </c>
       <c r="F7" t="n">
-        <v>1.151534829448267</v>
+        <v>1.151534829448271</v>
       </c>
       <c r="G7" t="n">
-        <v>1.151534829448267</v>
+        <v>1.151534829448271</v>
       </c>
       <c r="H7" t="n">
-        <v>1.151534829448267</v>
+        <v>1.151534829448271</v>
       </c>
       <c r="I7" t="n">
-        <v>1.151534829448267</v>
+        <v>1.151534829448271</v>
       </c>
       <c r="J7" t="n">
-        <v>1.149348556843595</v>
+        <v>1.149348556843598</v>
       </c>
       <c r="K7" t="n">
-        <v>1.151534829448267</v>
+        <v>1.151534829448271</v>
       </c>
       <c r="L7" t="n">
-        <v>1.151534829448269</v>
+        <v>1.15153482944827</v>
       </c>
       <c r="M7" t="n">
-        <v>1.151534829448267</v>
+        <v>1.151534829448271</v>
       </c>
       <c r="N7" t="n">
-        <v>24.46190297069545</v>
+        <v>1.151534829448271</v>
       </c>
       <c r="O7" t="n">
-        <v>1.149637646705132</v>
+        <v>1.149637646705136</v>
       </c>
       <c r="P7" t="n">
-        <v>1.149637646705132</v>
+        <v>1.149637646705136</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.151534829448267</v>
+        <v>1.151534829448271</v>
       </c>
       <c r="R7" t="n">
-        <v>1.151534829448267</v>
+        <v>1.151534829448271</v>
       </c>
       <c r="S7" t="n">
-        <v>1.151534829448267</v>
+        <v>1.151534829448271</v>
       </c>
       <c r="T7" t="n">
-        <v>1.151534829448267</v>
+        <v>1.151534829448271</v>
       </c>
       <c r="U7" t="n">
-        <v>1.149186101429512</v>
+        <v>1.14918610142951</v>
       </c>
       <c r="V7" t="n">
-        <v>1.137176147034638</v>
+        <v>1.137176147034639</v>
       </c>
       <c r="W7" t="n">
-        <v>1.151534829448267</v>
+        <v>1.151534829448271</v>
       </c>
       <c r="X7" t="n">
-        <v>1.151534829448269</v>
+        <v>1.15153482944827</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.151534829448267</v>
+        <v>1.151534829448271</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.151534829448267</v>
+        <v>1.151534829448271</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.151534829448267</v>
+        <v>1.151534829448271</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.151534829448267</v>
+        <v>1.151534829448271</v>
       </c>
     </row>
     <row r="8">
@@ -4222,85 +4222,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.372873670028051</v>
+        <v>1.372873670028048</v>
       </c>
       <c r="C8" t="n">
-        <v>1.942799109620076</v>
+        <v>1.942799109620086</v>
       </c>
       <c r="D8" t="n">
-        <v>1.942799109620076</v>
+        <v>1.942799109620086</v>
       </c>
       <c r="E8" t="n">
-        <v>1.639330624851732</v>
+        <v>1.639330624851734</v>
       </c>
       <c r="F8" t="n">
-        <v>1.461661392617181</v>
+        <v>1.461661392617183</v>
       </c>
       <c r="G8" t="n">
-        <v>2.060976862213292</v>
+        <v>2.060976862213295</v>
       </c>
       <c r="H8" t="n">
-        <v>1.942799109620076</v>
+        <v>1.942799109620086</v>
       </c>
       <c r="I8" t="n">
-        <v>1.942799109620076</v>
+        <v>1.942799109620086</v>
       </c>
       <c r="J8" t="n">
-        <v>1.940612837015408</v>
+        <v>1.940612837015409</v>
       </c>
       <c r="K8" t="n">
-        <v>1.942799109620076</v>
+        <v>1.942799109620086</v>
       </c>
       <c r="L8" t="n">
-        <v>1.942799109620077</v>
+        <v>1.942799109620087</v>
       </c>
       <c r="M8" t="n">
-        <v>1.942799109621157</v>
+        <v>1.942799109621166</v>
       </c>
       <c r="N8" t="n">
-        <v>24.46190297069545</v>
+        <v>1.501011547399645</v>
       </c>
       <c r="O8" t="n">
-        <v>1.622418605303131</v>
+        <v>1.62241860530314</v>
       </c>
       <c r="P8" t="n">
-        <v>1.592658801822854</v>
+        <v>1.592658801822856</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.260870313322691</v>
+        <v>1.26087031332269</v>
       </c>
       <c r="R8" t="n">
-        <v>1.942799109620076</v>
+        <v>1.942799109620086</v>
       </c>
       <c r="S8" t="n">
-        <v>1.942799109620076</v>
+        <v>1.942799109620086</v>
       </c>
       <c r="T8" t="n">
-        <v>1.942799109620076</v>
+        <v>1.942799109620086</v>
       </c>
       <c r="U8" t="n">
-        <v>1.664276172561255</v>
+        <v>1.664276172561253</v>
       </c>
       <c r="V8" t="n">
-        <v>1.772285241210489</v>
+        <v>1.77228524121049</v>
       </c>
       <c r="W8" t="n">
-        <v>1.942911115965208</v>
+        <v>1.942911115965213</v>
       </c>
       <c r="X8" t="n">
-        <v>1.313105112116035</v>
+        <v>1.313105112116038</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.508864362230733</v>
+        <v>2.50886436223074</v>
       </c>
       <c r="Z8" t="n">
         <v>1.362287012414883</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.942799109620076</v>
+        <v>1.942799109620086</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.538133887357187</v>
+        <v>2.538133887357195</v>
       </c>
     </row>
     <row r="9">
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.392961591133727</v>
+        <v>2.392961591133731</v>
       </c>
       <c r="C9" t="n">
-        <v>2.923134056820696</v>
+        <v>2.923134056820698</v>
       </c>
       <c r="D9" t="n">
-        <v>2.923134056820696</v>
+        <v>2.923134056820698</v>
       </c>
       <c r="E9" t="n">
         <v>2.800772493140133</v>
       </c>
       <c r="F9" t="n">
-        <v>1.70094169178941</v>
+        <v>1.700941691789411</v>
       </c>
       <c r="G9" t="n">
-        <v>2.923134159349897</v>
+        <v>2.9231341593499</v>
       </c>
       <c r="H9" t="n">
-        <v>2.923134056820696</v>
+        <v>2.923134056820698</v>
       </c>
       <c r="I9" t="n">
-        <v>2.923134056820696</v>
+        <v>2.923134056820698</v>
       </c>
       <c r="J9" t="n">
-        <v>2.920947784216021</v>
+        <v>2.920947784216022</v>
       </c>
       <c r="K9" t="n">
-        <v>2.923134056820696</v>
+        <v>2.923134056820698</v>
       </c>
       <c r="L9" t="n">
-        <v>2.923134056820696</v>
+        <v>2.923134056820698</v>
       </c>
       <c r="M9" t="n">
-        <v>2.923134056820696</v>
+        <v>2.923134056820698</v>
       </c>
       <c r="N9" t="n">
-        <v>24.46190297069545</v>
+        <v>2.923134056820698</v>
       </c>
       <c r="O9" t="n">
-        <v>3.098832654255055</v>
+        <v>3.098832654255053</v>
       </c>
       <c r="P9" t="n">
-        <v>3.137044062418401</v>
+        <v>3.137044062418398</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.923134159349897</v>
+        <v>2.9231341593499</v>
       </c>
       <c r="R9" t="n">
-        <v>2.923134056820696</v>
+        <v>2.923134056820698</v>
       </c>
       <c r="S9" t="n">
-        <v>2.923134056820696</v>
+        <v>2.923134056820698</v>
       </c>
       <c r="T9" t="n">
-        <v>2.923134056820696</v>
+        <v>2.923134056820698</v>
       </c>
       <c r="U9" t="n">
-        <v>2.923134056820696</v>
+        <v>2.923134056820698</v>
       </c>
       <c r="V9" t="n">
         <v>3.520582377774622</v>
       </c>
       <c r="W9" t="n">
-        <v>2.923134056820696</v>
+        <v>2.923134056820698</v>
       </c>
       <c r="X9" t="n">
-        <v>2.923134056820696</v>
+        <v>2.923134056820698</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.923134056820696</v>
+        <v>2.923134056820698</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.603487245499784</v>
+        <v>2.603487245499786</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.923134056820696</v>
+        <v>2.923134056820698</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.923134056820696</v>
+        <v>2.923134056820698</v>
       </c>
     </row>
     <row r="10">
@@ -4404,10 +4404,10 @@
         <v>10.79678666299842</v>
       </c>
       <c r="D10" t="n">
-        <v>10.28482845436916</v>
+        <v>10.28482845436917</v>
       </c>
       <c r="E10" t="n">
-        <v>9.676786001670543</v>
+        <v>9.676786001670544</v>
       </c>
       <c r="F10" t="n">
         <v>10.74456710541665</v>
@@ -4428,7 +4428,7 @@
         <v>10.49156925823569</v>
       </c>
       <c r="L10" t="n">
-        <v>10.13007266072578</v>
+        <v>10.13007266072579</v>
       </c>
       <c r="M10" t="n">
         <v>9.957728131039156</v>
@@ -4437,7 +4437,7 @@
         <v>10.4876958504529</v>
       </c>
       <c r="O10" t="n">
-        <v>10.53372483357615</v>
+        <v>10.53372483357616</v>
       </c>
       <c r="P10" t="n">
         <v>10.25594063616187</v>
@@ -4446,7 +4446,7 @@
         <v>10.77538995419159</v>
       </c>
       <c r="R10" t="n">
-        <v>10.58720871308815</v>
+        <v>10.58720871308816</v>
       </c>
       <c r="S10" t="n">
         <v>10.21884508489462</v>
@@ -4458,7 +4458,7 @@
         <v>10.26745895209664</v>
       </c>
       <c r="V10" t="n">
-        <v>10.83222767749003</v>
+        <v>10.83222767749004</v>
       </c>
       <c r="W10" t="n">
         <v>10.14449265935266</v>
@@ -4476,7 +4476,7 @@
         <v>10.35350343559947</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.88659071060396</v>
+        <v>9.886590710603963</v>
       </c>
     </row>
     <row r="11">
@@ -4486,85 +4486,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.533706776061695</v>
+        <v>4.533706776061698</v>
       </c>
       <c r="C11" t="n">
-        <v>4.620959151747278</v>
+        <v>4.620959151747281</v>
       </c>
       <c r="D11" t="n">
-        <v>4.475690606401689</v>
+        <v>4.475690606401692</v>
       </c>
       <c r="E11" t="n">
         <v>3.5503771631105</v>
       </c>
       <c r="F11" t="n">
-        <v>4.606512124452194</v>
+        <v>4.6065121244522</v>
       </c>
       <c r="G11" t="n">
-        <v>4.396829032296827</v>
+        <v>4.39682903229683</v>
       </c>
       <c r="H11" t="n">
-        <v>4.53657903510386</v>
+        <v>4.536579035103863</v>
       </c>
       <c r="I11" t="n">
-        <v>4.580617782453966</v>
+        <v>4.580617782453969</v>
       </c>
       <c r="J11" t="n">
-        <v>4.46615103166139</v>
+        <v>4.466151031661391</v>
       </c>
       <c r="K11" t="n">
-        <v>4.534266228159493</v>
+        <v>4.534266228159495</v>
       </c>
       <c r="L11" t="n">
-        <v>4.430284251005459</v>
+        <v>4.43028425100546</v>
       </c>
       <c r="M11" t="n">
-        <v>4.383248530000014</v>
+        <v>4.383248530000018</v>
       </c>
       <c r="N11" t="n">
-        <v>4.532972012464651</v>
+        <v>4.532972012464652</v>
       </c>
       <c r="O11" t="n">
-        <v>4.544878176852682</v>
+        <v>4.544878176852686</v>
       </c>
       <c r="P11" t="n">
-        <v>4.465165152426528</v>
+        <v>4.465165152426533</v>
       </c>
       <c r="Q11" t="n">
         <v>4.615035570353199</v>
       </c>
       <c r="R11" t="n">
-        <v>4.562202796161169</v>
+        <v>4.562202796161171</v>
       </c>
       <c r="S11" t="n">
-        <v>4.455220948650551</v>
+        <v>4.455220948650553</v>
       </c>
       <c r="T11" t="n">
-        <v>4.550934061450525</v>
+        <v>4.550934061450526</v>
       </c>
       <c r="U11" t="n">
-        <v>4.469665103325972</v>
+        <v>4.469665103325974</v>
       </c>
       <c r="V11" t="n">
-        <v>4.760286607813141</v>
+        <v>4.760286607813144</v>
       </c>
       <c r="W11" t="n">
-        <v>4.434656659948576</v>
+        <v>4.434656659948579</v>
       </c>
       <c r="X11" t="n">
-        <v>4.430637046446604</v>
+        <v>4.430637046446605</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.456886747385155</v>
+        <v>4.456886747385162</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.532233335278127</v>
+        <v>4.532233335278132</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.494436833699058</v>
+        <v>4.494436833699062</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.364817566306529</v>
+        <v>4.364817566306531</v>
       </c>
     </row>
   </sheetData>
@@ -4730,85 +4730,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.754495199570993</v>
+        <v>4.754495199570985</v>
       </c>
       <c r="C2" t="n">
-        <v>4.721171002834285</v>
+        <v>4.72117100283429</v>
       </c>
       <c r="D2" t="n">
-        <v>4.764552530197375</v>
+        <v>4.764552530197372</v>
       </c>
       <c r="E2" t="n">
-        <v>3.648702273737698</v>
+        <v>3.648702273737694</v>
       </c>
       <c r="F2" t="n">
-        <v>4.731865191120468</v>
+        <v>4.731865191120471</v>
       </c>
       <c r="G2" t="n">
-        <v>4.820955688205821</v>
+        <v>4.820955688205819</v>
       </c>
       <c r="H2" t="n">
-        <v>4.756598288792793</v>
+        <v>4.756598288792794</v>
       </c>
       <c r="I2" t="n">
-        <v>4.740570862509086</v>
+        <v>4.740570862509087</v>
       </c>
       <c r="J2" t="n">
-        <v>4.791113459172938</v>
+        <v>4.791113459172939</v>
       </c>
       <c r="K2" t="n">
-        <v>4.78202541598032</v>
+        <v>4.782025415980317</v>
       </c>
       <c r="L2" t="n">
-        <v>4.803934097726867</v>
+        <v>4.803934097726865</v>
       </c>
       <c r="M2" t="n">
-        <v>4.831362747662276</v>
+        <v>4.831362747662278</v>
       </c>
       <c r="N2" t="n">
         <v>4.75492758305439</v>
       </c>
       <c r="O2" t="n">
-        <v>4.741028766417089</v>
+        <v>4.741028766417094</v>
       </c>
       <c r="P2" t="n">
-        <v>4.796238791127976</v>
+        <v>4.796238791127979</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.731234276046279</v>
+        <v>4.731234276046282</v>
       </c>
       <c r="R2" t="n">
-        <v>4.74346276844306</v>
+        <v>4.743462768443057</v>
       </c>
       <c r="S2" t="n">
-        <v>4.798034965263857</v>
+        <v>4.798034965263858</v>
       </c>
       <c r="T2" t="n">
-        <v>4.749373227521869</v>
+        <v>4.749373227521872</v>
       </c>
       <c r="U2" t="n">
         <v>4.813843962182109</v>
       </c>
       <c r="V2" t="n">
-        <v>4.983917543896826</v>
+        <v>4.983917543896828</v>
       </c>
       <c r="W2" t="n">
-        <v>4.824418053474933</v>
+        <v>4.824418053474929</v>
       </c>
       <c r="X2" t="n">
-        <v>4.837409733327227</v>
+        <v>4.83740973332723</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.86560310331662</v>
+        <v>4.865603103316623</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.755493679645507</v>
+        <v>4.755493679645509</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.795729081569946</v>
+        <v>4.795729081569943</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.855030166611975</v>
+        <v>4.855030166611976</v>
       </c>
     </row>
     <row r="3">
@@ -4827,7 +4827,7 @@
         <v>11.01673760801875</v>
       </c>
       <c r="E3" t="n">
-        <v>9.940536334534558</v>
+        <v>9.940536334534556</v>
       </c>
       <c r="F3" t="n">
         <v>11.01649848910185</v>
@@ -4842,7 +4842,7 @@
         <v>11.01673760801875</v>
       </c>
       <c r="J3" t="n">
-        <v>11.0156631934553</v>
+        <v>11.01566319345529</v>
       </c>
       <c r="K3" t="n">
         <v>11.01660109232173</v>
@@ -4878,7 +4878,7 @@
         <v>11.017813317002</v>
       </c>
       <c r="V3" t="n">
-        <v>11.22862837887557</v>
+        <v>11.22862837887556</v>
       </c>
       <c r="W3" t="n">
         <v>11.01673760801875</v>
@@ -4906,85 +4906,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.99928952450315</v>
+        <v>18.99928952450321</v>
       </c>
       <c r="C4" t="n">
-        <v>12.18656338118902</v>
+        <v>12.18656338118901</v>
       </c>
       <c r="D4" t="n">
-        <v>23.291771141501</v>
+        <v>23.29177114150097</v>
       </c>
       <c r="E4" t="n">
-        <v>8.654521849655282</v>
+        <v>8.654521849655277</v>
       </c>
       <c r="F4" t="n">
-        <v>15.51675637736527</v>
+        <v>15.51675637736519</v>
       </c>
       <c r="G4" t="n">
-        <v>33.90725904052989</v>
+        <v>33.90725904052985</v>
       </c>
       <c r="H4" t="n">
-        <v>23.37858777828318</v>
+        <v>23.37858777828315</v>
       </c>
       <c r="I4" t="n">
-        <v>17.94734525080739</v>
+        <v>17.94734525080738</v>
       </c>
       <c r="J4" t="n">
-        <v>28.71394286382977</v>
+        <v>28.71394286382971</v>
       </c>
       <c r="K4" t="n">
-        <v>25.83780966750613</v>
+        <v>25.83780966750616</v>
       </c>
       <c r="L4" t="n">
-        <v>31.73169380194152</v>
+        <v>31.73169380194154</v>
       </c>
       <c r="M4" t="n">
-        <v>40.80699926439485</v>
+        <v>40.80699926439482</v>
       </c>
       <c r="N4" t="n">
-        <v>21.45601633298416</v>
+        <v>21.45601633298413</v>
       </c>
       <c r="O4" t="n">
-        <v>15.70821451074266</v>
+        <v>15.70821451074262</v>
       </c>
       <c r="P4" t="n">
-        <v>28.41379478280739</v>
+        <v>28.4137947828073</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.60555381184755</v>
+        <v>14.60555381184751</v>
       </c>
       <c r="R4" t="n">
-        <v>19.14181560126161</v>
+        <v>19.14181560126162</v>
       </c>
       <c r="S4" t="n">
-        <v>29.52192042938808</v>
+        <v>29.52192042938805</v>
       </c>
       <c r="T4" t="n">
-        <v>20.61855201734124</v>
+        <v>20.61855201734127</v>
       </c>
       <c r="U4" t="n">
-        <v>33.02471853303042</v>
+        <v>33.02471853303044</v>
       </c>
       <c r="V4" t="n">
-        <v>23.0431289498845</v>
+        <v>23.04312894988444</v>
       </c>
       <c r="W4" t="n">
-        <v>38.71543286819615</v>
+        <v>38.71543286819607</v>
       </c>
       <c r="X4" t="n">
-        <v>41.19679334027103</v>
+        <v>41.19679334027089</v>
       </c>
       <c r="Y4" t="n">
-        <v>49.89716046662979</v>
+        <v>49.89716046662986</v>
       </c>
       <c r="Z4" t="n">
         <v>17.85183850856057</v>
       </c>
       <c r="AA4" t="n">
-        <v>31.5609125837645</v>
+        <v>31.56091258376447</v>
       </c>
       <c r="AB4" t="n">
-        <v>49.34536709621886</v>
+        <v>49.34536709621878</v>
       </c>
     </row>
     <row r="5">
@@ -4994,85 +4994,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6667142430191298</v>
+        <v>0.6667142430191088</v>
       </c>
       <c r="C5" t="n">
-        <v>0.66671424301913</v>
+        <v>0.6667142430191138</v>
       </c>
       <c r="D5" t="n">
-        <v>0.66671424301913</v>
+        <v>0.6667142430191138</v>
       </c>
       <c r="E5" t="n">
-        <v>0.66671424301913</v>
+        <v>0.6667142430191138</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6667142430191312</v>
+        <v>0.6667142430191297</v>
       </c>
       <c r="G5" t="n">
-        <v>0.66671424301913</v>
+        <v>0.6667142430191138</v>
       </c>
       <c r="H5" t="n">
-        <v>0.66671424301913</v>
+        <v>0.6667142430191138</v>
       </c>
       <c r="I5" t="n">
-        <v>0.66671424301913</v>
+        <v>0.6667142430191138</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6650153387935448</v>
+        <v>0.6650153387935421</v>
       </c>
       <c r="K5" t="n">
-        <v>0.66671424301913</v>
+        <v>0.6667142430191138</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6667142430191293</v>
+        <v>0.6667142430191119</v>
       </c>
       <c r="M5" t="n">
-        <v>0.66671424301913</v>
+        <v>0.6667142430191138</v>
       </c>
       <c r="N5" t="n">
-        <v>21.45601633298416</v>
+        <v>0.6667142430191297</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6667142430191312</v>
+        <v>0.6667142430191297</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6667142430191312</v>
+        <v>0.6667142430191297</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6667142430191312</v>
+        <v>0.6667142430191297</v>
       </c>
       <c r="R5" t="n">
-        <v>0.66671424301913</v>
+        <v>0.6667142430191138</v>
       </c>
       <c r="S5" t="n">
-        <v>0.66671424301913</v>
+        <v>0.6667142430191138</v>
       </c>
       <c r="T5" t="n">
-        <v>0.66671424301913</v>
+        <v>0.6667142430191138</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6509293193240268</v>
+        <v>0.650929319324004</v>
       </c>
       <c r="V5" t="n">
-        <v>0.655472742725017</v>
+        <v>0.6554727427250161</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6667142430191312</v>
+        <v>0.6667142430191297</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6667142430191301</v>
+        <v>0.6667142430191313</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6509293193240268</v>
+        <v>0.650929319324004</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.66671424301913</v>
+        <v>0.6667142430191138</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.66671424301913</v>
+        <v>0.6667142430191138</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6667142430191312</v>
+        <v>0.6667142430191297</v>
       </c>
     </row>
     <row r="6">
@@ -5082,85 +5082,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.798744059676518</v>
+        <v>0.7987440596765052</v>
       </c>
       <c r="C6" t="n">
-        <v>0.798744059676518</v>
+        <v>0.7987440596765052</v>
       </c>
       <c r="D6" t="n">
-        <v>1.194736367206513</v>
+        <v>1.194736367206511</v>
       </c>
       <c r="E6" t="n">
-        <v>1.194736367206513</v>
+        <v>1.194736367206511</v>
       </c>
       <c r="F6" t="n">
-        <v>0.798744059676518</v>
+        <v>0.7987440596765052</v>
       </c>
       <c r="G6" t="n">
-        <v>0.798744059676518</v>
+        <v>0.7987440596765052</v>
       </c>
       <c r="H6" t="n">
-        <v>1.194736367206513</v>
+        <v>1.194736367206511</v>
       </c>
       <c r="I6" t="n">
-        <v>0.798744059676518</v>
+        <v>0.7987440596765052</v>
       </c>
       <c r="J6" t="n">
-        <v>1.193037462980928</v>
+        <v>1.193037462980926</v>
       </c>
       <c r="K6" t="n">
-        <v>1.194736367206513</v>
+        <v>1.194736367206511</v>
       </c>
       <c r="L6" t="n">
-        <v>0.798744059676518</v>
+        <v>0.7987440596765052</v>
       </c>
       <c r="M6" t="n">
-        <v>0.798744059676518</v>
+        <v>0.7987440596765052</v>
       </c>
       <c r="N6" t="n">
-        <v>21.45601633298416</v>
+        <v>0.8046398633883597</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8052746359553522</v>
+        <v>0.8052746359553543</v>
       </c>
       <c r="P6" t="n">
-        <v>1.219342450582593</v>
+        <v>1.219342450582571</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.194736367206513</v>
+        <v>1.194736367206511</v>
       </c>
       <c r="R6" t="n">
-        <v>1.194736367206513</v>
+        <v>1.194736367206511</v>
       </c>
       <c r="S6" t="n">
-        <v>0.798744059676518</v>
+        <v>0.7987440596765052</v>
       </c>
       <c r="T6" t="n">
-        <v>1.194736367206513</v>
+        <v>1.194736367206511</v>
       </c>
       <c r="U6" t="n">
-        <v>1.194736367206513</v>
+        <v>1.194736367206511</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7875025593823992</v>
+        <v>0.7875025593824018</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8240614677389247</v>
+        <v>0.8240614677389193</v>
       </c>
       <c r="X6" t="n">
-        <v>0.798744059676518</v>
+        <v>0.7987440596765052</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.8178285206750641</v>
+        <v>0.8178285206750233</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.798744059676518</v>
+        <v>0.7987440596765052</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.194736367206513</v>
+        <v>1.194736367206511</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8112443000499682</v>
+        <v>0.811244300049952</v>
       </c>
     </row>
     <row r="7">
@@ -5170,85 +5170,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.150239869964611</v>
+        <v>1.150239869964592</v>
       </c>
       <c r="C7" t="n">
-        <v>1.150239869964612</v>
+        <v>1.150239869964594</v>
       </c>
       <c r="D7" t="n">
-        <v>1.150239869964612</v>
+        <v>1.150239869964594</v>
       </c>
       <c r="E7" t="n">
-        <v>1.150239869964612</v>
+        <v>1.150239869964594</v>
       </c>
       <c r="F7" t="n">
-        <v>1.150239869964612</v>
+        <v>1.150239869964594</v>
       </c>
       <c r="G7" t="n">
-        <v>1.150239869964612</v>
+        <v>1.150239869964594</v>
       </c>
       <c r="H7" t="n">
-        <v>1.150239869964612</v>
+        <v>1.150239869964594</v>
       </c>
       <c r="I7" t="n">
-        <v>1.150239869964612</v>
+        <v>1.150239869964594</v>
       </c>
       <c r="J7" t="n">
-        <v>1.148540965739027</v>
+        <v>1.148540965739024</v>
       </c>
       <c r="K7" t="n">
-        <v>1.150239869964612</v>
+        <v>1.150239869964594</v>
       </c>
       <c r="L7" t="n">
-        <v>1.150239869964611</v>
+        <v>1.150239869964592</v>
       </c>
       <c r="M7" t="n">
-        <v>1.150239869964612</v>
+        <v>1.150239869964594</v>
       </c>
       <c r="N7" t="n">
-        <v>21.45601633298416</v>
+        <v>1.150239869964594</v>
       </c>
       <c r="O7" t="n">
-        <v>1.148343523812732</v>
+        <v>1.148343523812716</v>
       </c>
       <c r="P7" t="n">
-        <v>1.148343523812732</v>
+        <v>1.148343523812716</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.150239869964612</v>
+        <v>1.150239869964594</v>
       </c>
       <c r="R7" t="n">
-        <v>1.150239869964612</v>
+        <v>1.150239869964594</v>
       </c>
       <c r="S7" t="n">
-        <v>1.150239869964612</v>
+        <v>1.150239869964594</v>
       </c>
       <c r="T7" t="n">
-        <v>1.150239869964612</v>
+        <v>1.150239869964594</v>
       </c>
       <c r="U7" t="n">
-        <v>1.146218925679954</v>
+        <v>1.146218925679945</v>
       </c>
       <c r="V7" t="n">
-        <v>1.138998369670499</v>
+        <v>1.138998369670495</v>
       </c>
       <c r="W7" t="n">
-        <v>1.150239869964612</v>
+        <v>1.150239869964594</v>
       </c>
       <c r="X7" t="n">
-        <v>1.150239869964611</v>
+        <v>1.150239869964592</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.150239869964612</v>
+        <v>1.150239869964594</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.150239869964612</v>
+        <v>1.150239869964594</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.150239869964612</v>
+        <v>1.150239869964594</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.150239869964612</v>
+        <v>1.150239869964594</v>
       </c>
     </row>
     <row r="8">
@@ -5258,85 +5258,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.353909380527313</v>
+        <v>1.353909380527298</v>
       </c>
       <c r="C8" t="n">
-        <v>1.898807229729456</v>
+        <v>1.898807229729431</v>
       </c>
       <c r="D8" t="n">
-        <v>1.898807229729456</v>
+        <v>1.898807229729431</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6086651985629</v>
+        <v>1.608665198562884</v>
       </c>
       <c r="F8" t="n">
-        <v>1.438798097044276</v>
+        <v>1.438798097044274</v>
       </c>
       <c r="G8" t="n">
-        <v>2.011795348420427</v>
+        <v>2.011795348420419</v>
       </c>
       <c r="H8" t="n">
-        <v>1.898807229729456</v>
+        <v>1.898807229729431</v>
       </c>
       <c r="I8" t="n">
-        <v>1.898807229729456</v>
+        <v>1.898807229729431</v>
       </c>
       <c r="J8" t="n">
-        <v>1.897108325503867</v>
+        <v>1.897108325503863</v>
       </c>
       <c r="K8" t="n">
-        <v>1.898807229729456</v>
+        <v>1.898807229729431</v>
       </c>
       <c r="L8" t="n">
-        <v>1.898807229729455</v>
+        <v>1.898807229729432</v>
       </c>
       <c r="M8" t="n">
-        <v>1.898807229730622</v>
+        <v>1.898807229730602</v>
       </c>
       <c r="N8" t="n">
-        <v>21.45601633298416</v>
+        <v>1.476420237101959</v>
       </c>
       <c r="O8" t="n">
-        <v>1.592495850061805</v>
+        <v>1.592495850061789</v>
       </c>
       <c r="P8" t="n">
-        <v>1.564042912559204</v>
+        <v>1.564042912559184</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.246824516542387</v>
+        <v>1.246824516542378</v>
       </c>
       <c r="R8" t="n">
-        <v>1.898807229729456</v>
+        <v>1.898807229729431</v>
       </c>
       <c r="S8" t="n">
-        <v>1.898807229729456</v>
+        <v>1.898807229729431</v>
       </c>
       <c r="T8" t="n">
-        <v>1.898807229729456</v>
+        <v>1.898807229729431</v>
       </c>
       <c r="U8" t="n">
-        <v>1.631203350643962</v>
+        <v>1.631203350643961</v>
       </c>
       <c r="V8" t="n">
-        <v>1.736820877138111</v>
+        <v>1.736820877138108</v>
       </c>
       <c r="W8" t="n">
-        <v>1.898914317499341</v>
+        <v>1.898914317499315</v>
       </c>
       <c r="X8" t="n">
-        <v>1.296765486985076</v>
+        <v>1.296765486985055</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.43777005648943</v>
+        <v>2.437770056489419</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.343787623248588</v>
+        <v>1.343787623248575</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.898807229729456</v>
+        <v>1.898807229729431</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.467998596591992</v>
+        <v>2.467998596591982</v>
       </c>
     </row>
     <row r="9">
@@ -5346,85 +5346,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.254294063757472</v>
+        <v>2.254294063757444</v>
       </c>
       <c r="C9" t="n">
-        <v>2.740468705605271</v>
+        <v>2.740468705605258</v>
       </c>
       <c r="D9" t="n">
-        <v>2.740468705605271</v>
+        <v>2.740468705605258</v>
       </c>
       <c r="E9" t="n">
-        <v>2.628261612484753</v>
+        <v>2.628261612484738</v>
       </c>
       <c r="F9" t="n">
-        <v>1.619703413642316</v>
+        <v>1.619703413642309</v>
       </c>
       <c r="G9" t="n">
-        <v>2.740468746098683</v>
+        <v>2.740468746098684</v>
       </c>
       <c r="H9" t="n">
-        <v>2.740468705605271</v>
+        <v>2.740468705605258</v>
       </c>
       <c r="I9" t="n">
-        <v>2.740468705605271</v>
+        <v>2.740468705605258</v>
       </c>
       <c r="J9" t="n">
-        <v>2.738769801379689</v>
+        <v>2.738769801379676</v>
       </c>
       <c r="K9" t="n">
-        <v>2.740468705605271</v>
+        <v>2.740468705605258</v>
       </c>
       <c r="L9" t="n">
-        <v>2.740468705605271</v>
+        <v>2.740468705605257</v>
       </c>
       <c r="M9" t="n">
-        <v>2.740468705605271</v>
+        <v>2.740468705605258</v>
       </c>
       <c r="N9" t="n">
-        <v>21.45601633298416</v>
+        <v>2.740468705605258</v>
       </c>
       <c r="O9" t="n">
-        <v>2.901586399235192</v>
+        <v>2.901586399235181</v>
       </c>
       <c r="P9" t="n">
-        <v>2.936626724478976</v>
+        <v>2.936626724478967</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.740468746098683</v>
+        <v>2.740468746098684</v>
       </c>
       <c r="R9" t="n">
-        <v>2.740468705605271</v>
+        <v>2.740468705605258</v>
       </c>
       <c r="S9" t="n">
-        <v>2.740468705605271</v>
+        <v>2.740468705605258</v>
       </c>
       <c r="T9" t="n">
-        <v>2.740468705605271</v>
+        <v>2.740468705605258</v>
       </c>
       <c r="U9" t="n">
-        <v>2.740468705605271</v>
+        <v>2.740468705605258</v>
       </c>
       <c r="V9" t="n">
-        <v>3.290261781803012</v>
+        <v>3.290261781803002</v>
       </c>
       <c r="W9" t="n">
-        <v>2.740468705605271</v>
+        <v>2.740468705605258</v>
       </c>
       <c r="X9" t="n">
-        <v>2.740468705605271</v>
+        <v>2.740468705605257</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.740468705605271</v>
+        <v>2.740468705605258</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.447348644986506</v>
+        <v>2.4473486449865</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.740468705605271</v>
+        <v>2.740468705605258</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.740468705605271</v>
+        <v>2.740468705605258</v>
       </c>
     </row>
     <row r="10">
@@ -5437,16 +5437,16 @@
         <v>10.54236140853054</v>
       </c>
       <c r="C10" t="n">
-        <v>10.74228687990802</v>
+        <v>10.74228687990801</v>
       </c>
       <c r="D10" t="n">
         <v>10.49077091154013</v>
       </c>
       <c r="E10" t="n">
-        <v>9.743226400163298</v>
+        <v>9.743226400163296</v>
       </c>
       <c r="F10" t="n">
-        <v>10.68236178322961</v>
+        <v>10.6823617832296</v>
       </c>
       <c r="G10" t="n">
         <v>10.14672693981739</v>
@@ -5464,16 +5464,16 @@
         <v>10.38666268627097</v>
       </c>
       <c r="L10" t="n">
-        <v>10.25306896555068</v>
+        <v>10.25306896555067</v>
       </c>
       <c r="M10" t="n">
         <v>10.09898822080568</v>
       </c>
       <c r="N10" t="n">
-        <v>10.54515905973336</v>
+        <v>10.54515905973335</v>
       </c>
       <c r="O10" t="n">
-        <v>10.62001724576711</v>
+        <v>10.6200172457671</v>
       </c>
       <c r="P10" t="n">
         <v>10.28876972399443</v>
@@ -5485,7 +5485,7 @@
         <v>10.6207624171806</v>
       </c>
       <c r="S10" t="n">
-        <v>10.28560279265342</v>
+        <v>10.28560279265341</v>
       </c>
       <c r="T10" t="n">
         <v>10.57708389924775</v>
@@ -5497,10 +5497,10 @@
         <v>10.6308849920415</v>
       </c>
       <c r="W10" t="n">
-        <v>10.13344874585029</v>
+        <v>10.13344874585028</v>
       </c>
       <c r="X10" t="n">
-        <v>10.07008379439997</v>
+        <v>10.07008379439996</v>
       </c>
       <c r="Y10" t="n">
         <v>9.884577898450713</v>
@@ -5509,10 +5509,10 @@
         <v>10.53675121366044</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.30335141534567</v>
+        <v>10.30335141534566</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.984184880668607</v>
+        <v>9.984184880668597</v>
       </c>
     </row>
     <row r="11">
@@ -5522,85 +5522,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.538652517056605</v>
+        <v>4.538652517056598</v>
       </c>
       <c r="C11" t="n">
-        <v>4.596457936683912</v>
+        <v>4.596457936683911</v>
       </c>
       <c r="D11" t="n">
-        <v>4.525236007143192</v>
+        <v>4.525236007143186</v>
       </c>
       <c r="E11" t="n">
-        <v>3.558925624809321</v>
+        <v>3.558925624809319</v>
       </c>
       <c r="F11" t="n">
-        <v>4.579831925118095</v>
+        <v>4.579831925118094</v>
       </c>
       <c r="G11" t="n">
-        <v>4.425149940685192</v>
+        <v>4.425149940685196</v>
       </c>
       <c r="H11" t="n">
-        <v>4.53995504504831</v>
+        <v>4.539955045048312</v>
       </c>
       <c r="I11" t="n">
-        <v>4.565499241321022</v>
+        <v>4.565499241321024</v>
       </c>
       <c r="J11" t="n">
-        <v>4.475509325197674</v>
+        <v>4.475509325197672</v>
       </c>
       <c r="K11" t="n">
-        <v>4.495401433732639</v>
+        <v>4.495401433732635</v>
       </c>
       <c r="L11" t="n">
-        <v>4.456462431736326</v>
+        <v>4.456462431736325</v>
       </c>
       <c r="M11" t="n">
         <v>4.414065810855361</v>
       </c>
       <c r="N11" t="n">
-        <v>4.540357840752868</v>
+        <v>4.540357840752869</v>
       </c>
       <c r="O11" t="n">
-        <v>4.560662967768838</v>
+        <v>4.560662967768844</v>
       </c>
       <c r="P11" t="n">
-        <v>4.465280703020345</v>
+        <v>4.465280703020344</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.580322984449889</v>
+        <v>4.580322984449891</v>
       </c>
       <c r="R11" t="n">
-        <v>4.562942941357666</v>
+        <v>4.562942941357665</v>
       </c>
       <c r="S11" t="n">
-        <v>4.465366294284217</v>
+        <v>4.46536629428422</v>
       </c>
       <c r="T11" t="n">
-        <v>4.549535652911755</v>
+        <v>4.549535652911753</v>
       </c>
       <c r="U11" t="n">
-        <v>4.441988653014011</v>
+        <v>4.441988653014008</v>
       </c>
       <c r="V11" t="n">
-        <v>4.711942397992177</v>
+        <v>4.711942397992178</v>
       </c>
       <c r="W11" t="n">
-        <v>4.422518806313692</v>
+        <v>4.422518806313688</v>
       </c>
       <c r="X11" t="n">
-        <v>4.406178719409721</v>
+        <v>4.406178719409716</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.35100972360768</v>
+        <v>4.351009723607675</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.537112713639259</v>
+        <v>4.537112713639252</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.471136090476788</v>
+        <v>4.47113609047678</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.383557104441064</v>
+        <v>4.383557104441056</v>
       </c>
     </row>
   </sheetData>
@@ -6066,7 +6066,7 @@
         <v>0.5453449314983445</v>
       </c>
       <c r="N5" t="n">
-        <v>7.34807092823842</v>
+        <v>0.5453449314983381</v>
       </c>
       <c r="O5" t="n">
         <v>0.5453449314983381</v>
@@ -6154,7 +6154,7 @@
         <v>0.8883441133899538</v>
       </c>
       <c r="N6" t="n">
-        <v>7.34807092823842</v>
+        <v>0.6071656898423654</v>
       </c>
       <c r="O6" t="n">
         <v>0.9191353406637838</v>
@@ -6242,7 +6242,7 @@
         <v>0.9612485229573943</v>
       </c>
       <c r="N7" t="n">
-        <v>7.34807092823842</v>
+        <v>0.9612485229573943</v>
       </c>
       <c r="O7" t="n">
         <v>0.9592184145395767</v>
@@ -6330,7 +6330,7 @@
         <v>1.540007248005954</v>
       </c>
       <c r="N8" t="n">
-        <v>7.34807092823842</v>
+        <v>1.195607571219351</v>
       </c>
       <c r="O8" t="n">
         <v>1.290251592683628</v>
@@ -6418,7 +6418,7 @@
         <v>2.296830679971506</v>
       </c>
       <c r="N9" t="n">
-        <v>7.34807092823842</v>
+        <v>2.296830679971506</v>
       </c>
       <c r="O9" t="n">
         <v>2.43326638472961</v>
@@ -6829,7 +6829,7 @@
         <v>4.496633061822275</v>
       </c>
       <c r="K2" t="n">
-        <v>4.477298860849168</v>
+        <v>4.477298860849169</v>
       </c>
       <c r="L2" t="n">
         <v>4.415196168860692</v>
@@ -6844,7 +6844,7 @@
         <v>4.48434145003039</v>
       </c>
       <c r="P2" t="n">
-        <v>4.448324523224332</v>
+        <v>4.448324523224333</v>
       </c>
       <c r="Q2" t="n">
         <v>4.489495392270479</v>
@@ -7038,7 +7038,7 @@
         <v>2.369263499106263</v>
       </c>
       <c r="V4" t="n">
-        <v>3.584697506349084</v>
+        <v>3.584697506349083</v>
       </c>
       <c r="W4" t="n">
         <v>17.40702983765546</v>
@@ -7053,7 +7053,7 @@
         <v>1.48804135400103</v>
       </c>
       <c r="AA4" t="n">
-        <v>28.80745206063597</v>
+        <v>28.80745206063598</v>
       </c>
       <c r="AB4" t="n">
         <v>0.6168045269620388</v>
@@ -7069,40 +7069,40 @@
         <v>0.4862690030925947</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4862690030925946</v>
+        <v>0.4862690030925947</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4862690030925946</v>
+        <v>0.4862690030925947</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4862690030925946</v>
+        <v>0.4862690030925947</v>
       </c>
       <c r="F5" t="n">
         <v>0.4862690030926027</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4862690030925946</v>
+        <v>0.4862690030925947</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4862690030925946</v>
+        <v>0.4862690030925947</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4862690030925946</v>
+        <v>0.4862690030925947</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4846999482977649</v>
+        <v>0.4846999482977651</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4862690030925946</v>
+        <v>0.4862690030925947</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4862690030925946</v>
+        <v>0.4862690030925947</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4862690030925946</v>
+        <v>0.4862690030925947</v>
       </c>
       <c r="N5" t="n">
-        <v>6.970149557687676</v>
+        <v>0.4862690030926028</v>
       </c>
       <c r="O5" t="n">
         <v>0.4862690030926027</v>
@@ -7114,13 +7114,13 @@
         <v>0.4862690030926027</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4862690030925946</v>
+        <v>0.4862690030925947</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4862690030925946</v>
+        <v>0.4862690030925947</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4862690030925946</v>
+        <v>0.4862690030925947</v>
       </c>
       <c r="U5" t="n">
         <v>0.4605734197552054</v>
@@ -7129,7 +7129,7 @@
         <v>0.4758289971372994</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4862690030926027</v>
+        <v>0.4862690030926028</v>
       </c>
       <c r="X5" t="n">
         <v>0.4862690030926027</v>
@@ -7138,10 +7138,10 @@
         <v>0.4605734197552054</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.4862690030925946</v>
+        <v>0.4862690030925947</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.4862690030925946</v>
+        <v>0.4862690030925947</v>
       </c>
       <c r="AB5" t="n">
         <v>0.4862690030926027</v>
@@ -7190,7 +7190,7 @@
         <v>0.7216999315837929</v>
       </c>
       <c r="N6" t="n">
-        <v>6.970149557687676</v>
+        <v>0.5071824737008064</v>
       </c>
       <c r="O6" t="n">
         <v>0.7480032003235375</v>
@@ -7266,7 +7266,7 @@
         <v>0.8289131149013869</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8273440601065589</v>
+        <v>0.827344060106559</v>
       </c>
       <c r="K7" t="n">
         <v>0.8289131149013869</v>
@@ -7278,7 +7278,7 @@
         <v>0.8289131149013869</v>
       </c>
       <c r="N7" t="n">
-        <v>6.970149557687676</v>
+        <v>0.8289131149013869</v>
       </c>
       <c r="O7" t="n">
         <v>0.8270220106406588</v>
@@ -7366,7 +7366,7 @@
         <v>1.236580823871079</v>
       </c>
       <c r="N8" t="n">
-        <v>6.970149557687676</v>
+        <v>0.9773408916433121</v>
       </c>
       <c r="O8" t="n">
         <v>1.048582276013304</v>
@@ -7375,7 +7375,7 @@
         <v>1.031119291265269</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8364265639072683</v>
+        <v>0.8364265639072682</v>
       </c>
       <c r="R8" t="n">
         <v>1.236580823871512</v>
@@ -7402,7 +7402,7 @@
         <v>1.561676764297097</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.8959376513134292</v>
+        <v>0.8959376513134291</v>
       </c>
       <c r="AA8" t="n">
         <v>1.236580823871512</v>
@@ -7454,7 +7454,7 @@
         <v>1.837086613530847</v>
       </c>
       <c r="N9" t="n">
-        <v>6.970149557687676</v>
+        <v>1.837086613530847</v>
       </c>
       <c r="O9" t="n">
         <v>1.941998779468213</v>
@@ -8050,7 +8050,7 @@
         <v>1.540851783207949</v>
       </c>
       <c r="N4" t="n">
-        <v>8.46511475785894</v>
+        <v>8.465114757858943</v>
       </c>
       <c r="O4" t="n">
         <v>-5.715586441676705</v>
@@ -8138,7 +8138,7 @@
         <v>0.4678127874097074</v>
       </c>
       <c r="N5" t="n">
-        <v>8.465114757858943</v>
+        <v>0.4678127874097043</v>
       </c>
       <c r="O5" t="n">
         <v>0.4678127874097043</v>
@@ -8226,7 +8226,7 @@
         <v>0.6730779340417989</v>
       </c>
       <c r="N6" t="n">
-        <v>8.46511475785894</v>
+        <v>0.4827162404965885</v>
       </c>
       <c r="O6" t="n">
         <v>0.483356310273286</v>
@@ -8314,7 +8314,7 @@
         <v>0.7944002183603719</v>
       </c>
       <c r="N7" t="n">
-        <v>8.46511475785894</v>
+        <v>0.7944002183603719</v>
       </c>
       <c r="O7" t="n">
         <v>0.7925100557761134</v>
@@ -8402,7 +8402,7 @@
         <v>1.155480222388914</v>
       </c>
       <c r="N8" t="n">
-        <v>8.46511475785894</v>
+        <v>0.9187813661527346</v>
       </c>
       <c r="O8" t="n">
         <v>0.9838282671933345</v>
@@ -8490,7 +8490,7 @@
         <v>1.678936870113226</v>
       </c>
       <c r="N9" t="n">
-        <v>8.46511475785894</v>
+        <v>1.678936870113226</v>
       </c>
       <c r="O9" t="n">
         <v>1.772943686671899</v>
@@ -9174,7 +9174,7 @@
         <v>0.6463288197093495</v>
       </c>
       <c r="N5" t="n">
-        <v>23.02229192515025</v>
+        <v>0.6463288197093485</v>
       </c>
       <c r="O5" t="n">
         <v>0.6463288197093485</v>
@@ -9262,7 +9262,7 @@
         <v>0.7416427901527879</v>
       </c>
       <c r="N6" t="n">
-        <v>23.02229192515025</v>
+        <v>0.7454478645239661</v>
       </c>
       <c r="O6" t="n">
         <v>1.206793312915399</v>
@@ -9350,7 +9350,7 @@
         <v>1.157216355788461</v>
       </c>
       <c r="N7" t="n">
-        <v>23.02229192515025</v>
+        <v>1.157216355788461</v>
       </c>
       <c r="O7" t="n">
         <v>1.155180421353243</v>
@@ -9438,7 +9438,7 @@
         <v>1.960421748038629</v>
       </c>
       <c r="N8" t="n">
-        <v>23.02229192515025</v>
+        <v>1.50737756182336</v>
       </c>
       <c r="O8" t="n">
         <v>1.631878037717287</v>
@@ -9526,7 +9526,7 @@
         <v>3.119081232470215</v>
       </c>
       <c r="N9" t="n">
-        <v>23.02229192515025</v>
+        <v>3.119081232470215</v>
       </c>
       <c r="O9" t="n">
         <v>3.310265811722907</v>
@@ -10210,7 +10210,7 @@
         <v>0.5611718248725824</v>
       </c>
       <c r="N5" t="n">
-        <v>2.225282937977763</v>
+        <v>0.5611718248725824</v>
       </c>
       <c r="O5" t="n">
         <v>0.5611718248725824</v>
@@ -10298,7 +10298,7 @@
         <v>0.6058940194213477</v>
       </c>
       <c r="N6" t="n">
-        <v>2.225282937977763</v>
+        <v>0.6086637044373258</v>
       </c>
       <c r="O6" t="n">
         <v>0.9660472637034678</v>
@@ -10386,7 +10386,7 @@
         <v>0.9610213322999008</v>
       </c>
       <c r="N7" t="n">
-        <v>2.225282937977763</v>
+        <v>0.9610213322999008</v>
       </c>
       <c r="O7" t="n">
         <v>0.9591267912875567</v>
@@ -10474,7 +10474,7 @@
         <v>1.523093925505093</v>
       </c>
       <c r="N8" t="n">
-        <v>2.225282937977763</v>
+        <v>1.189628156323629</v>
       </c>
       <c r="O8" t="n">
         <v>1.281267445060875</v>
@@ -10562,7 +10562,7 @@
         <v>2.381642301501532</v>
       </c>
       <c r="N9" t="n">
-        <v>2.225282937977763</v>
+        <v>2.381642301501532</v>
       </c>
       <c r="O9" t="n">
         <v>2.522775166804339</v>

--- a/Results/Phase 2/Hydrogen/hydrogen climate change results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen climate change results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20403"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\Phase 2\Hydrogen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E674B47-219B-4542-8F1A-F17A104A906B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE9EE409-9460-438A-899D-6961D2CE2006}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Results/Phase 2/Hydrogen/hydrogen climate change results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen climate change results.xlsx
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.881191330119987</v>
+        <v>4.881191330119985</v>
       </c>
       <c r="C2" t="n">
-        <v>4.780389762943906</v>
+        <v>4.780389762943904</v>
       </c>
       <c r="D2" t="n">
-        <v>4.841704359459894</v>
+        <v>4.841704359459891</v>
       </c>
       <c r="E2" t="n">
         <v>3.69957720265087</v>
@@ -601,70 +601,70 @@
         <v>4.820694723073959</v>
       </c>
       <c r="G2" t="n">
-        <v>4.927077042234933</v>
+        <v>4.927077042234931</v>
       </c>
       <c r="H2" t="n">
-        <v>4.876234084003245</v>
+        <v>4.876234084003252</v>
       </c>
       <c r="I2" t="n">
-        <v>4.824836275703204</v>
+        <v>4.824836275703205</v>
       </c>
       <c r="J2" t="n">
-        <v>4.878166690821575</v>
+        <v>4.878166690821574</v>
       </c>
       <c r="K2" t="n">
-        <v>4.872600530827083</v>
+        <v>4.87260053082708</v>
       </c>
       <c r="L2" t="n">
-        <v>4.936107096319013</v>
+        <v>4.936107096319009</v>
       </c>
       <c r="M2" t="n">
-        <v>4.964849111233649</v>
+        <v>4.964849111233647</v>
       </c>
       <c r="N2" t="n">
-        <v>4.884118011874994</v>
+        <v>4.884118011874991</v>
       </c>
       <c r="O2" t="n">
-        <v>4.864386171779026</v>
+        <v>4.864386171779023</v>
       </c>
       <c r="P2" t="n">
         <v>4.859183977400036</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.843474641762136</v>
+        <v>4.843474641762133</v>
       </c>
       <c r="R2" t="n">
-        <v>4.827029304480161</v>
+        <v>4.827029304480158</v>
       </c>
       <c r="S2" t="n">
         <v>4.897121331522501</v>
       </c>
       <c r="T2" t="n">
-        <v>4.859412759920294</v>
+        <v>4.859412759920289</v>
       </c>
       <c r="U2" t="n">
         <v>4.925360938377843</v>
       </c>
       <c r="V2" t="n">
-        <v>4.993399739692074</v>
+        <v>4.993399739692073</v>
       </c>
       <c r="W2" t="n">
-        <v>4.896615805502752</v>
+        <v>4.89661580550275</v>
       </c>
       <c r="X2" t="n">
-        <v>4.859928382074494</v>
+        <v>4.859928382074491</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.848273986650761</v>
+        <v>4.848273986650759</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.849142647759871</v>
+        <v>4.849142647759868</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.88994873164405</v>
+        <v>4.889948731644047</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.956833789132575</v>
+        <v>4.95683378913257</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="C3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="D3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="E3" t="n">
         <v>9.979520464623489</v>
       </c>
       <c r="F3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="G3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="H3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="I3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="J3" t="n">
         <v>11.07977878591611</v>
       </c>
       <c r="K3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="L3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="M3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="N3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="O3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="P3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="R3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="S3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="T3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="U3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="V3" t="n">
         <v>11.26953067715123</v>
       </c>
       <c r="W3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="X3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="Y3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.08367243963129</v>
+        <v>11.08367243963128</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.46781569787108</v>
+        <v>38.46781569787113</v>
       </c>
       <c r="C4" t="n">
-        <v>12.5554171966703</v>
+        <v>12.55541719667031</v>
       </c>
       <c r="D4" t="n">
-        <v>31.37167494124787</v>
+        <v>31.37167494124794</v>
       </c>
       <c r="E4" t="n">
-        <v>13.90032556613389</v>
+        <v>13.90032556613388</v>
       </c>
       <c r="F4" t="n">
-        <v>25.48977093699411</v>
+        <v>25.48977093699409</v>
       </c>
       <c r="G4" t="n">
-        <v>52.32018662060661</v>
+        <v>52.3201866206066</v>
       </c>
       <c r="H4" t="n">
-        <v>43.48790074098059</v>
+        <v>43.48790074098053</v>
       </c>
       <c r="I4" t="n">
-        <v>26.51757529272153</v>
+        <v>26.51757529272152</v>
       </c>
       <c r="J4" t="n">
-        <v>40.83587121540128</v>
+        <v>40.83587121540126</v>
       </c>
       <c r="K4" t="n">
-        <v>40.47120814478799</v>
+        <v>40.47120814478794</v>
       </c>
       <c r="L4" t="n">
-        <v>57.06010575485428</v>
+        <v>57.06010575485475</v>
       </c>
       <c r="M4" t="n">
-        <v>69.48568164437361</v>
+        <v>69.4856816443737</v>
       </c>
       <c r="N4" t="n">
-        <v>43.06464988705973</v>
+        <v>43.06464988705982</v>
       </c>
       <c r="O4" t="n">
-        <v>33.16224549332555</v>
+        <v>33.16224549332558</v>
       </c>
       <c r="P4" t="n">
-        <v>33.17665281027632</v>
+        <v>33.17665281027627</v>
       </c>
       <c r="Q4" t="n">
-        <v>31.26566144765292</v>
+        <v>31.26566144765288</v>
       </c>
       <c r="R4" t="n">
-        <v>27.51758864452954</v>
+        <v>27.51758864452949</v>
       </c>
       <c r="S4" t="n">
-        <v>44.056044730121</v>
+        <v>44.05604473012107</v>
       </c>
       <c r="T4" t="n">
-        <v>36.8934087302945</v>
+        <v>36.8934087302946</v>
       </c>
       <c r="U4" t="n">
-        <v>52.90485274409227</v>
+        <v>52.90485274409233</v>
       </c>
       <c r="V4" t="n">
-        <v>19.65868248425339</v>
+        <v>19.65868248425333</v>
       </c>
       <c r="W4" t="n">
-        <v>45.98913513932755</v>
+        <v>45.98913513932751</v>
       </c>
       <c r="X4" t="n">
-        <v>36.42743273439449</v>
+        <v>36.42743273439447</v>
       </c>
       <c r="Y4" t="n">
-        <v>31.90901600126482</v>
+        <v>31.90901600126492</v>
       </c>
       <c r="Z4" t="n">
-        <v>30.69854263719975</v>
+        <v>30.6985426371997</v>
       </c>
       <c r="AA4" t="n">
-        <v>44.34091143868642</v>
+        <v>44.34091143868634</v>
       </c>
       <c r="AB4" t="n">
-        <v>69.52381546312991</v>
+        <v>69.52381546312985</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.664172469175083</v>
+        <v>1.664172469175085</v>
       </c>
       <c r="C5" t="n">
-        <v>2.40135556618902</v>
+        <v>2.401355566189006</v>
       </c>
       <c r="D5" t="n">
-        <v>2.40135556618902</v>
+        <v>2.401355566189006</v>
       </c>
       <c r="E5" t="n">
-        <v>2.008827312682537</v>
+        <v>2.008827312682545</v>
       </c>
       <c r="F5" t="n">
-        <v>1.77901697998222</v>
+        <v>1.779016979982216</v>
       </c>
       <c r="G5" t="n">
-        <v>2.554215283616493</v>
+        <v>2.554215283616487</v>
       </c>
       <c r="H5" t="n">
-        <v>2.40135556618902</v>
+        <v>2.401355566189006</v>
       </c>
       <c r="I5" t="n">
-        <v>2.40135556618902</v>
+        <v>2.401355566189006</v>
       </c>
       <c r="J5" t="n">
-        <v>2.399075197032862</v>
+        <v>2.399075197032854</v>
       </c>
       <c r="K5" t="n">
-        <v>2.40135556618902</v>
+        <v>2.401355566189006</v>
       </c>
       <c r="L5" t="n">
-        <v>2.40135556618902</v>
+        <v>2.401355566189006</v>
       </c>
       <c r="M5" t="n">
-        <v>2.401355566189242</v>
+        <v>2.401355566189228</v>
       </c>
       <c r="N5" t="n">
-        <v>43.06464988705973</v>
+        <v>1.82991533781328</v>
       </c>
       <c r="O5" t="n">
-        <v>1.986952074014025</v>
+        <v>1.986952074014021</v>
       </c>
       <c r="P5" t="n">
-        <v>1.948458575462502</v>
+        <v>1.948458575462507</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.51929916537756</v>
+        <v>1.519299165377551</v>
       </c>
       <c r="R5" t="n">
-        <v>2.40135556618902</v>
+        <v>2.401355566189006</v>
       </c>
       <c r="S5" t="n">
-        <v>2.40135556618902</v>
+        <v>2.401355566189006</v>
       </c>
       <c r="T5" t="n">
-        <v>2.40135556618902</v>
+        <v>2.401355566189007</v>
       </c>
       <c r="U5" t="n">
-        <v>2.042456945019768</v>
+        <v>2.042456945019763</v>
       </c>
       <c r="V5" t="n">
-        <v>2.185927061677139</v>
+        <v>2.185927061677138</v>
       </c>
       <c r="W5" t="n">
-        <v>2.401500443230113</v>
+        <v>2.401500443230109</v>
       </c>
       <c r="X5" t="n">
-        <v>1.586863460680901</v>
+        <v>1.586863460680896</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.135877728362018</v>
+        <v>3.135877728362008</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.650478914724006</v>
+        <v>1.650478914724008</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.40135556618902</v>
+        <v>2.401355566189006</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.171404952749447</v>
+        <v>3.171404952749444</v>
       </c>
     </row>
     <row r="6">
@@ -941,82 +941,82 @@
         <v>3.294188205749118</v>
       </c>
       <c r="C6" t="n">
-        <v>4.065838789179352</v>
+        <v>4.065838789179353</v>
       </c>
       <c r="D6" t="n">
-        <v>4.065838789179352</v>
+        <v>4.065838789179353</v>
       </c>
       <c r="E6" t="n">
-        <v>3.887745065825718</v>
+        <v>3.887745065825704</v>
       </c>
       <c r="F6" t="n">
-        <v>2.286973448751603</v>
+        <v>2.286973448751596</v>
       </c>
       <c r="G6" t="n">
-        <v>4.065838898118771</v>
+        <v>4.065838898118764</v>
       </c>
       <c r="H6" t="n">
-        <v>4.065838789179352</v>
+        <v>4.065838789179353</v>
       </c>
       <c r="I6" t="n">
-        <v>4.065838789179352</v>
+        <v>4.065838789179353</v>
       </c>
       <c r="J6" t="n">
-        <v>4.063558420023194</v>
+        <v>4.063558420023184</v>
       </c>
       <c r="K6" t="n">
-        <v>4.065838789179352</v>
+        <v>4.065838789179353</v>
       </c>
       <c r="L6" t="n">
-        <v>4.065838789179352</v>
+        <v>4.065838789179353</v>
       </c>
       <c r="M6" t="n">
-        <v>4.065838789179352</v>
+        <v>4.065838789179353</v>
       </c>
       <c r="N6" t="n">
-        <v>43.06464988705973</v>
+        <v>4.065838789179353</v>
       </c>
       <c r="O6" t="n">
-        <v>4.321562927179751</v>
+        <v>4.321562927179741</v>
       </c>
       <c r="P6" t="n">
-        <v>4.377178516015062</v>
+        <v>4.377178516015048</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.065838898118771</v>
+        <v>4.065838898118764</v>
       </c>
       <c r="R6" t="n">
-        <v>4.065838789179352</v>
+        <v>4.065838789179353</v>
       </c>
       <c r="S6" t="n">
-        <v>4.065838789179352</v>
+        <v>4.065838789179353</v>
       </c>
       <c r="T6" t="n">
-        <v>4.065838789179352</v>
+        <v>4.065838789179353</v>
       </c>
       <c r="U6" t="n">
-        <v>4.065838789179352</v>
+        <v>4.065838789179353</v>
       </c>
       <c r="V6" t="n">
-        <v>4.94135646069668</v>
+        <v>4.941356460696675</v>
       </c>
       <c r="W6" t="n">
-        <v>4.065838789179352</v>
+        <v>4.065838789179353</v>
       </c>
       <c r="X6" t="n">
-        <v>4.065838789179352</v>
+        <v>4.065838789179353</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.065838789179352</v>
+        <v>4.065838789179353</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.600602148476722</v>
+        <v>3.600602148476714</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.065838789179352</v>
+        <v>4.065838789179353</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.065838789179352</v>
+        <v>4.065838789179353</v>
       </c>
     </row>
     <row r="7">
@@ -1053,22 +1053,22 @@
         <v>10.24507192971876</v>
       </c>
       <c r="K7" t="n">
-        <v>10.31181710477607</v>
+        <v>10.31181710477606</v>
       </c>
       <c r="L7" t="n">
-        <v>9.93031612753353</v>
+        <v>9.930316127533528</v>
       </c>
       <c r="M7" t="n">
-        <v>9.777541050956208</v>
+        <v>9.777541050956204</v>
       </c>
       <c r="N7" t="n">
-        <v>10.24189705043566</v>
+        <v>10.24189705043565</v>
       </c>
       <c r="O7" t="n">
-        <v>10.34890682866811</v>
+        <v>10.3489068286681</v>
       </c>
       <c r="P7" t="n">
-        <v>10.37926332694642</v>
+        <v>10.37926332694641</v>
       </c>
       <c r="Q7" t="n">
         <v>10.48197995446063</v>
@@ -1080,31 +1080,31 @@
         <v>10.15783002987967</v>
       </c>
       <c r="T7" t="n">
-        <v>10.39059975920144</v>
+        <v>10.39059975920143</v>
       </c>
       <c r="U7" t="n">
-        <v>9.992756799563763</v>
+        <v>9.992756799563759</v>
       </c>
       <c r="V7" t="n">
         <v>10.85597947223437</v>
       </c>
       <c r="W7" t="n">
-        <v>10.16531856681845</v>
+        <v>10.16531856681844</v>
       </c>
       <c r="X7" t="n">
         <v>10.38646745786046</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.45165447877909</v>
+        <v>10.45165447877908</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.44110705538654</v>
+        <v>10.44110705538653</v>
       </c>
       <c r="AA7" t="n">
         <v>10.2053826985783</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.819800773752208</v>
+        <v>9.819800773752206</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.501744982664254</v>
+        <v>4.501744982664253</v>
       </c>
       <c r="C8" t="n">
-        <v>4.67532846678762</v>
+        <v>4.675328466787616</v>
       </c>
       <c r="D8" t="n">
-        <v>4.573349812555792</v>
+        <v>4.573349812555786</v>
       </c>
       <c r="E8" t="n">
-        <v>3.577143932091937</v>
+        <v>3.577143932091931</v>
       </c>
       <c r="F8" t="n">
-        <v>4.609373251845873</v>
+        <v>4.609373251845868</v>
       </c>
       <c r="G8" t="n">
-        <v>4.423703224337516</v>
+        <v>4.423703224337515</v>
       </c>
       <c r="H8" t="n">
         <v>4.518284219970911</v>
       </c>
       <c r="I8" t="n">
-        <v>4.601857412069978</v>
+        <v>4.601857412069981</v>
       </c>
       <c r="J8" t="n">
-        <v>4.498372411198862</v>
+        <v>4.498372411198856</v>
       </c>
       <c r="K8" t="n">
-        <v>4.521403893710954</v>
+        <v>4.521403893710953</v>
       </c>
       <c r="L8" t="n">
-        <v>4.411326298786051</v>
+        <v>4.411326298786053</v>
       </c>
       <c r="M8" t="n">
-        <v>4.370555166992725</v>
+        <v>4.370555166992721</v>
       </c>
       <c r="N8" t="n">
-        <v>4.501107527211984</v>
+        <v>4.501107527211982</v>
       </c>
       <c r="O8" t="n">
-        <v>4.530065477231711</v>
+        <v>4.530065477231705</v>
       </c>
       <c r="P8" t="n">
-        <v>4.538675586309769</v>
+        <v>4.53867558630977</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.569702643529308</v>
+        <v>4.569702643529306</v>
       </c>
       <c r="R8" t="n">
-        <v>4.598691542692736</v>
+        <v>4.598691542692731</v>
       </c>
       <c r="S8" t="n">
-        <v>4.475860084600819</v>
+        <v>4.475860084600818</v>
       </c>
       <c r="T8" t="n">
-        <v>4.54406248163313</v>
+        <v>4.544062481633127</v>
       </c>
       <c r="U8" t="n">
-        <v>4.42899084560525</v>
+        <v>4.428990845605243</v>
       </c>
       <c r="V8" t="n">
         <v>4.805232623545407</v>
       </c>
       <c r="W8" t="n">
-        <v>4.478761866752764</v>
+        <v>4.478761866752762</v>
       </c>
       <c r="X8" t="n">
-        <v>4.542697893508321</v>
+        <v>4.542697893508322</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.560703800341274</v>
+        <v>4.560703800341269</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.556773350194129</v>
+        <v>4.556773350194123</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.490324100521608</v>
+        <v>4.490324100521605</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.381768153437576</v>
+        <v>4.381768153437572</v>
       </c>
     </row>
   </sheetData>
@@ -1358,73 +1358,73 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.510557403582763</v>
+        <v>4.510557403582764</v>
       </c>
       <c r="C2" t="n">
-        <v>4.507049449273199</v>
+        <v>4.507049449273197</v>
       </c>
       <c r="D2" t="n">
-        <v>4.525652260733384</v>
+        <v>4.525652260733389</v>
       </c>
       <c r="E2" t="n">
-        <v>3.522477920423184</v>
+        <v>3.522477920423183</v>
       </c>
       <c r="F2" t="n">
-        <v>4.467246497933532</v>
+        <v>4.467246497933533</v>
       </c>
       <c r="G2" t="n">
-        <v>4.542309020583772</v>
+        <v>4.542309020583771</v>
       </c>
       <c r="H2" t="n">
-        <v>4.538849418315904</v>
+        <v>4.5388494183159</v>
       </c>
       <c r="I2" t="n">
-        <v>4.517658377224364</v>
+        <v>4.517658377224363</v>
       </c>
       <c r="J2" t="n">
-        <v>4.529378728762964</v>
+        <v>4.529378728762972</v>
       </c>
       <c r="K2" t="n">
-        <v>4.516368041423244</v>
+        <v>4.516368041423243</v>
       </c>
       <c r="L2" t="n">
-        <v>4.421595085312702</v>
+        <v>4.4215950853127</v>
       </c>
       <c r="M2" t="n">
-        <v>4.51072686725642</v>
+        <v>4.510726867256419</v>
       </c>
       <c r="N2" t="n">
-        <v>4.515233868321425</v>
+        <v>4.515233868321426</v>
       </c>
       <c r="O2" t="n">
-        <v>4.484582186412617</v>
+        <v>4.484582186412618</v>
       </c>
       <c r="P2" t="n">
-        <v>4.510295573148001</v>
+        <v>4.510295573147998</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.523507891547391</v>
+        <v>4.523507891547393</v>
       </c>
       <c r="R2" t="n">
-        <v>4.37657163064188</v>
+        <v>4.376571630641876</v>
       </c>
       <c r="S2" t="n">
-        <v>4.475687575382033</v>
+        <v>4.475687575382032</v>
       </c>
       <c r="T2" t="n">
         <v>4.490983826548669</v>
       </c>
       <c r="U2" t="n">
-        <v>4.541942238415546</v>
+        <v>4.541942238415548</v>
       </c>
       <c r="V2" t="n">
-        <v>4.759919722845797</v>
+        <v>4.759919722845803</v>
       </c>
       <c r="W2" t="n">
-        <v>4.642386907382205</v>
+        <v>4.642386907382207</v>
       </c>
       <c r="X2" t="n">
-        <v>4.693850148542307</v>
+        <v>4.693850148542299</v>
       </c>
       <c r="Y2" t="n">
         <v>4.61820277763256</v>
@@ -1433,10 +1433,10 @@
         <v>4.547277948672636</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.656826518500128</v>
+        <v>4.656826518500131</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.530798514849674</v>
+        <v>4.530798514849675</v>
       </c>
     </row>
     <row r="3">
@@ -1455,13 +1455,13 @@
         <v>10.86147819482735</v>
       </c>
       <c r="E3" t="n">
-        <v>9.851940785578307</v>
+        <v>9.851940785578305</v>
       </c>
       <c r="F3" t="n">
         <v>10.86123907591045</v>
       </c>
       <c r="G3" t="n">
-        <v>10.8613641756908</v>
+        <v>10.86136417569081</v>
       </c>
       <c r="H3" t="n">
         <v>10.86147819482735</v>
@@ -1500,13 +1500,13 @@
         <v>10.86147819482735</v>
       </c>
       <c r="T3" t="n">
-        <v>10.86102487058719</v>
+        <v>10.8610248705872</v>
       </c>
       <c r="U3" t="n">
-        <v>10.86255390381059</v>
+        <v>10.8625539038106</v>
       </c>
       <c r="V3" t="n">
-        <v>11.06933648123704</v>
+        <v>11.06933648123705</v>
       </c>
       <c r="W3" t="n">
         <v>10.86147819482735</v>
@@ -1515,7 +1515,7 @@
         <v>10.86257821330802</v>
       </c>
       <c r="Y3" t="n">
-        <v>10.86028502489102</v>
+        <v>10.86028502489103</v>
       </c>
       <c r="Z3" t="n">
         <v>10.86144660592186</v>
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.782460705867441</v>
+        <v>-1.782460705867424</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.648048395931478</v>
+        <v>-2.64804839593148</v>
       </c>
       <c r="D4" t="n">
-        <v>1.801809304617796</v>
+        <v>1.801809304617812</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3997479453270065</v>
+        <v>-0.399747945326997</v>
       </c>
       <c r="F4" t="n">
-        <v>-12.98160136686501</v>
+        <v>-12.98160136686498</v>
       </c>
       <c r="G4" t="n">
-        <v>5.397891410940404</v>
+        <v>5.397891410940391</v>
       </c>
       <c r="H4" t="n">
-        <v>5.418467933747224</v>
+        <v>5.418467933747253</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2409488766220234</v>
+        <v>-0.2409488766220091</v>
       </c>
       <c r="J4" t="n">
-        <v>2.367416902071643</v>
+        <v>2.367416902071649</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3044938174415766</v>
+        <v>-0.3044938174415797</v>
       </c>
       <c r="L4" t="n">
-        <v>-21.87248841720222</v>
+        <v>-21.87248841720224</v>
       </c>
       <c r="M4" t="n">
         <v>-1.769821002288768</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9085121421246897</v>
+        <v>-0.9085121421246949</v>
       </c>
       <c r="O4" t="n">
-        <v>-7.382180613631013</v>
+        <v>-7.382180613631005</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.663568458915889</v>
+        <v>-1.663568458915883</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.232024146953717</v>
+        <v>1.232024146953715</v>
       </c>
       <c r="R4" t="n">
         <v>-38.14059996165504</v>
       </c>
       <c r="S4" t="n">
-        <v>-9.563770422750412</v>
+        <v>-9.563770422750403</v>
       </c>
       <c r="T4" t="n">
-        <v>-7.156431891986335</v>
+        <v>-7.156431891986331</v>
       </c>
       <c r="U4" t="n">
-        <v>5.113545591736808</v>
+        <v>5.113545591736809</v>
       </c>
       <c r="V4" t="n">
-        <v>8.327703566937217</v>
+        <v>8.327703566937238</v>
       </c>
       <c r="W4" t="n">
         <v>31.12678766876778</v>
       </c>
       <c r="X4" t="n">
-        <v>42.5289852913739</v>
+        <v>42.52898529137395</v>
       </c>
       <c r="Y4" t="n">
-        <v>25.79015235910689</v>
+        <v>25.79015235910688</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.296496898848474</v>
+        <v>6.296496898848482</v>
       </c>
       <c r="AA4" t="n">
-        <v>35.2618360525562</v>
+        <v>35.26183605255622</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.371797565575787</v>
+        <v>2.371797565575789</v>
       </c>
     </row>
     <row r="5">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9658972814196896</v>
+        <v>0.9658972814196904</v>
       </c>
       <c r="C5" t="n">
-        <v>1.323653176772051</v>
+        <v>1.323653176772066</v>
       </c>
       <c r="D5" t="n">
-        <v>1.323653176772051</v>
+        <v>1.323653176772066</v>
       </c>
       <c r="E5" t="n">
         <v>1.133158715630188</v>
       </c>
       <c r="F5" t="n">
-        <v>1.021631468730802</v>
+        <v>1.021631468730809</v>
       </c>
       <c r="G5" t="n">
-        <v>1.397836192234685</v>
+        <v>1.397836192234701</v>
       </c>
       <c r="H5" t="n">
-        <v>1.323653176772051</v>
+        <v>1.323653176772066</v>
       </c>
       <c r="I5" t="n">
-        <v>1.323653176772051</v>
+        <v>1.323653176772066</v>
       </c>
       <c r="J5" t="n">
-        <v>1.322298040883371</v>
+        <v>1.322298040883373</v>
       </c>
       <c r="K5" t="n">
-        <v>1.323653176772051</v>
+        <v>1.323653176772066</v>
       </c>
       <c r="L5" t="n">
-        <v>1.323653176772051</v>
+        <v>1.323653176772066</v>
       </c>
       <c r="M5" t="n">
-        <v>1.323653176773188</v>
+        <v>1.3236531767732</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9085121421246897</v>
+        <v>1.046332506612954</v>
       </c>
       <c r="O5" t="n">
-        <v>1.122542634711059</v>
+        <v>1.122542634711071</v>
       </c>
       <c r="P5" t="n">
-        <v>1.103861690817704</v>
+        <v>1.103861690817713</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8955900825957125</v>
+        <v>0.8955900825957039</v>
       </c>
       <c r="R5" t="n">
-        <v>1.323653176772051</v>
+        <v>1.323653176772066</v>
       </c>
       <c r="S5" t="n">
-        <v>1.323653176772051</v>
+        <v>1.323653176772066</v>
       </c>
       <c r="T5" t="n">
-        <v>1.323653176772051</v>
+        <v>1.323653176772066</v>
       </c>
       <c r="U5" t="n">
-        <v>1.14595929784363</v>
+        <v>1.145959297843629</v>
       </c>
       <c r="V5" t="n">
-        <v>1.213411365127434</v>
+        <v>1.213411365127448</v>
       </c>
       <c r="W5" t="n">
-        <v>1.323723486059443</v>
+        <v>1.323723486059442</v>
       </c>
       <c r="X5" t="n">
-        <v>0.9283791212802228</v>
+        <v>0.9283791212802178</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.674096155751</v>
+        <v>1.674096155751011</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.9592517819857661</v>
+        <v>0.9592517819857783</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.323653176772051</v>
+        <v>1.323653176772066</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.697359124543987</v>
+        <v>1.697359124543992</v>
       </c>
     </row>
     <row r="6">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.537808279051109</v>
+        <v>1.537808279051113</v>
       </c>
       <c r="C6" t="n">
-        <v>1.851687542116512</v>
+        <v>1.851687542116515</v>
       </c>
       <c r="D6" t="n">
-        <v>1.851687542116512</v>
+        <v>1.851687542116515</v>
       </c>
       <c r="E6" t="n">
-        <v>1.779245606067355</v>
+        <v>1.779245606067358</v>
       </c>
       <c r="F6" t="n">
-        <v>1.128109975455712</v>
+        <v>1.128109975455703</v>
       </c>
       <c r="G6" t="n">
-        <v>1.851687694970823</v>
+        <v>1.851687694970819</v>
       </c>
       <c r="H6" t="n">
-        <v>1.851687542116512</v>
+        <v>1.851687542116515</v>
       </c>
       <c r="I6" t="n">
-        <v>1.851687542116512</v>
+        <v>1.851687542116515</v>
       </c>
       <c r="J6" t="n">
-        <v>1.850332406227825</v>
+        <v>1.850332406227822</v>
       </c>
       <c r="K6" t="n">
-        <v>1.851687542116512</v>
+        <v>1.851687542116515</v>
       </c>
       <c r="L6" t="n">
-        <v>1.851687542116512</v>
+        <v>1.851687542116515</v>
       </c>
       <c r="M6" t="n">
-        <v>1.851687542116512</v>
+        <v>1.851687542116515</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9085121421246897</v>
+        <v>1.851687542116515</v>
       </c>
       <c r="O6" t="n">
-        <v>1.955706922416573</v>
+        <v>1.955706922416586</v>
       </c>
       <c r="P6" t="n">
-        <v>1.97832931971664</v>
+        <v>1.978329319716646</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.851687694970823</v>
+        <v>1.851687694970819</v>
       </c>
       <c r="R6" t="n">
-        <v>1.851687542116512</v>
+        <v>1.851687542116515</v>
       </c>
       <c r="S6" t="n">
-        <v>1.851687542116512</v>
+        <v>1.851687542116515</v>
       </c>
       <c r="T6" t="n">
-        <v>1.851687542116512</v>
+        <v>1.851687542116515</v>
       </c>
       <c r="U6" t="n">
-        <v>1.851687542116512</v>
+        <v>1.851687542116515</v>
       </c>
       <c r="V6" t="n">
-        <v>2.204830916053591</v>
+        <v>2.204830916053602</v>
       </c>
       <c r="W6" t="n">
-        <v>1.851687542116512</v>
+        <v>1.851687542116515</v>
       </c>
       <c r="X6" t="n">
-        <v>1.851687542116512</v>
+        <v>1.851687542116515</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.851687542116512</v>
+        <v>1.851687542116515</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.662446318417924</v>
+        <v>1.662446318417916</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.851687542116512</v>
+        <v>1.851687542116515</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.851687542116512</v>
+        <v>1.851687542116515</v>
       </c>
     </row>
     <row r="7">
@@ -1798,46 +1798,46 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.92258848616681</v>
+        <v>10.92258848616682</v>
       </c>
       <c r="C7" t="n">
-        <v>10.94002351630133</v>
+        <v>10.94002351630134</v>
       </c>
       <c r="D7" t="n">
-        <v>10.83324067172072</v>
+        <v>10.83324067172073</v>
       </c>
       <c r="E7" t="n">
-        <v>9.878917727360472</v>
+        <v>9.878917727360474</v>
       </c>
       <c r="F7" t="n">
-        <v>11.1723137636804</v>
+        <v>11.17231376368041</v>
       </c>
       <c r="G7" t="n">
         <v>10.73303060299517</v>
       </c>
       <c r="H7" t="n">
-        <v>10.7566552271639</v>
+        <v>10.75665522716391</v>
       </c>
       <c r="I7" t="n">
-        <v>10.88003177690452</v>
+        <v>10.88003177690453</v>
       </c>
       <c r="J7" t="n">
-        <v>10.81399469658047</v>
+        <v>10.81399469658048</v>
       </c>
       <c r="K7" t="n">
-        <v>10.88679099408088</v>
+        <v>10.88679099408089</v>
       </c>
       <c r="L7" t="n">
         <v>11.44814082442044</v>
       </c>
       <c r="M7" t="n">
-        <v>10.91652087267701</v>
+        <v>10.91652087267702</v>
       </c>
       <c r="N7" t="n">
-        <v>10.89440215930879</v>
+        <v>10.8944021593088</v>
       </c>
       <c r="O7" t="n">
-        <v>11.07532545563428</v>
+        <v>11.07532545563429</v>
       </c>
       <c r="P7" t="n">
         <v>10.92044816060032</v>
@@ -1846,7 +1846,7 @@
         <v>10.84573698338986</v>
       </c>
       <c r="R7" t="n">
-        <v>11.7080271741441</v>
+        <v>11.70802717414409</v>
       </c>
       <c r="S7" t="n">
         <v>11.12920841488351</v>
@@ -1858,25 +1858,25 @@
         <v>10.74343536503974</v>
       </c>
       <c r="V7" t="n">
-        <v>10.86464550667787</v>
+        <v>10.86464550667788</v>
       </c>
       <c r="W7" t="n">
-        <v>10.14405540876133</v>
+        <v>10.14405540876134</v>
       </c>
       <c r="X7" t="n">
-        <v>9.854034138202087</v>
+        <v>9.854034138202096</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.28010085067134</v>
+        <v>10.28010085067135</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.70410368119777</v>
+        <v>10.70410368119778</v>
       </c>
       <c r="AA7" t="n">
         <v>10.05948625193551</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.82625791174764</v>
+        <v>10.82625791174765</v>
       </c>
     </row>
     <row r="8">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.538362780889165</v>
+        <v>4.538362780889168</v>
       </c>
       <c r="C8" t="n">
         <v>4.542950710615536</v>
       </c>
       <c r="D8" t="n">
-        <v>4.512804097732224</v>
+        <v>4.512804097732225</v>
       </c>
       <c r="E8" t="n">
         <v>3.534752514904481</v>
       </c>
       <c r="F8" t="n">
-        <v>4.608786472205072</v>
+        <v>4.608786472205071</v>
       </c>
       <c r="G8" t="n">
-        <v>4.483916836032431</v>
+        <v>4.483916836032435</v>
       </c>
       <c r="H8" t="n">
-        <v>4.491154633978061</v>
+        <v>4.491154633978053</v>
       </c>
       <c r="I8" t="n">
-        <v>4.526100316196238</v>
+        <v>4.526100316196239</v>
       </c>
       <c r="J8" t="n">
-        <v>4.507538323009506</v>
+        <v>4.507538323009513</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5279475608279</v>
+        <v>4.527947560827904</v>
       </c>
       <c r="L8" t="n">
-        <v>4.688528451360435</v>
+        <v>4.688528451360429</v>
       </c>
       <c r="M8" t="n">
-        <v>4.536053420157416</v>
+        <v>4.536053420157415</v>
       </c>
       <c r="N8" t="n">
-        <v>4.530214377082928</v>
+        <v>4.530214377082936</v>
       </c>
       <c r="O8" t="n">
-        <v>4.582026602019592</v>
+        <v>4.582026602019591</v>
       </c>
       <c r="P8" t="n">
-        <v>4.53739671452027</v>
+        <v>4.537396714520268</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.516347181165283</v>
+        <v>4.516347181165284</v>
       </c>
       <c r="R8" t="n">
-        <v>4.761404260666557</v>
+        <v>4.761404260666541</v>
       </c>
       <c r="S8" t="n">
         <v>4.597505678713175</v>
       </c>
       <c r="T8" t="n">
-        <v>4.569380167954137</v>
+        <v>4.569380167954145</v>
       </c>
       <c r="U8" t="n">
-        <v>4.487742923666548</v>
+        <v>4.487742923666556</v>
       </c>
       <c r="V8" t="n">
-        <v>4.666784677109943</v>
+        <v>4.666784677109949</v>
       </c>
       <c r="W8" t="n">
-        <v>4.315957253431406</v>
+        <v>4.315957253431407</v>
       </c>
       <c r="X8" t="n">
-        <v>4.23495938032984</v>
+        <v>4.234959380329835</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.354217129425347</v>
+        <v>4.35421712942535</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.475686416501026</v>
+        <v>4.475686416501022</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.291917628687682</v>
+        <v>4.291917628687671</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.513114893131735</v>
+        <v>4.513114893131737</v>
       </c>
     </row>
   </sheetData>
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.822714581175867</v>
+        <v>4.822714581175868</v>
       </c>
       <c r="C2" t="n">
         <v>4.739955133706492</v>
@@ -2139,16 +2139,16 @@
         <v>4.822084176742925</v>
       </c>
       <c r="E2" t="n">
-        <v>3.685115608720088</v>
+        <v>3.685115608720086</v>
       </c>
       <c r="F2" t="n">
-        <v>4.77284825814582</v>
+        <v>4.772848258145821</v>
       </c>
       <c r="G2" t="n">
-        <v>4.889029545717205</v>
+        <v>4.889029545717204</v>
       </c>
       <c r="H2" t="n">
-        <v>4.815158044358525</v>
+        <v>4.815158044358524</v>
       </c>
       <c r="I2" t="n">
         <v>4.775411185812747</v>
@@ -2157,58 +2157,58 @@
         <v>4.840360513201337</v>
       </c>
       <c r="K2" t="n">
-        <v>4.824248703825575</v>
+        <v>4.824248703825573</v>
       </c>
       <c r="L2" t="n">
         <v>4.885370183604328</v>
       </c>
       <c r="M2" t="n">
-        <v>4.916668218938757</v>
+        <v>4.916668218938756</v>
       </c>
       <c r="N2" t="n">
         <v>4.830047393679307</v>
       </c>
       <c r="O2" t="n">
-        <v>4.812211824005145</v>
+        <v>4.812211824005144</v>
       </c>
       <c r="P2" t="n">
-        <v>4.840398676524116</v>
+        <v>4.840398676524114</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.79298081880492</v>
+        <v>4.792980818804922</v>
       </c>
       <c r="R2" t="n">
-        <v>4.796349952666329</v>
+        <v>4.79634995266633</v>
       </c>
       <c r="S2" t="n">
         <v>4.85724154846164</v>
       </c>
       <c r="T2" t="n">
-        <v>4.801499246541039</v>
+        <v>4.801499246541038</v>
       </c>
       <c r="U2" t="n">
-        <v>4.866814727101099</v>
+        <v>4.866814727101098</v>
       </c>
       <c r="V2" t="n">
-        <v>4.929311114573893</v>
+        <v>4.929311114573891</v>
       </c>
       <c r="W2" t="n">
-        <v>4.872206470384859</v>
+        <v>4.872206470384858</v>
       </c>
       <c r="X2" t="n">
-        <v>4.835316451735686</v>
+        <v>4.835316451735688</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.809803890790726</v>
+        <v>4.809803890790725</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.798311640364428</v>
+        <v>4.79831164036443</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.828340662395014</v>
+        <v>4.828340662395013</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.921590729808763</v>
+        <v>4.921590729808762</v>
       </c>
     </row>
     <row r="3">
@@ -2218,13 +2218,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.05131237462219</v>
+        <v>11.0513123746222</v>
       </c>
       <c r="C3" t="n">
         <v>11.05097015438426</v>
       </c>
       <c r="D3" t="n">
-        <v>11.05131237462219</v>
+        <v>11.0513123746222</v>
       </c>
       <c r="E3" t="n">
         <v>9.965590631112972</v>
@@ -2236,10 +2236,10 @@
         <v>11.05127313138218</v>
       </c>
       <c r="H3" t="n">
-        <v>11.05131237462219</v>
+        <v>11.0513123746222</v>
       </c>
       <c r="I3" t="n">
-        <v>11.05131237462219</v>
+        <v>11.0513123746222</v>
       </c>
       <c r="J3" t="n">
         <v>11.04685924082778</v>
@@ -2248,13 +2248,13 @@
         <v>11.05123729867644</v>
       </c>
       <c r="L3" t="n">
-        <v>11.05131237462219</v>
+        <v>11.0513123746222</v>
       </c>
       <c r="M3" t="n">
         <v>11.05122398468102</v>
       </c>
       <c r="N3" t="n">
-        <v>11.05131237462219</v>
+        <v>11.0513123746222</v>
       </c>
       <c r="O3" t="n">
         <v>11.05106596030613</v>
@@ -2269,7 +2269,7 @@
         <v>11.05129849575197</v>
       </c>
       <c r="S3" t="n">
-        <v>11.05131237462219</v>
+        <v>11.0513123746222</v>
       </c>
       <c r="T3" t="n">
         <v>11.05120518930387</v>
@@ -2281,7 +2281,7 @@
         <v>11.22792251404223</v>
       </c>
       <c r="W3" t="n">
-        <v>11.05131237462219</v>
+        <v>11.0513123746222</v>
       </c>
       <c r="X3" t="n">
         <v>11.05151339355469</v>
@@ -2293,7 +2293,7 @@
         <v>11.05129328135678</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.05131237462219</v>
+        <v>11.0513123746222</v>
       </c>
       <c r="AB3" t="n">
         <v>11.05495692201079</v>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.15250047409046</v>
+        <v>29.15250047409056</v>
       </c>
       <c r="C4" t="n">
-        <v>9.300587667402562</v>
+        <v>9.300587667402565</v>
       </c>
       <c r="D4" t="n">
-        <v>32.89303090620221</v>
+        <v>32.89303090620217</v>
       </c>
       <c r="E4" t="n">
-        <v>12.81837359405495</v>
+        <v>12.81837359405507</v>
       </c>
       <c r="F4" t="n">
-        <v>18.8864387147953</v>
+        <v>18.88643871479536</v>
       </c>
       <c r="G4" t="n">
-        <v>46.94251105152513</v>
+        <v>46.94251105152512</v>
       </c>
       <c r="H4" t="n">
         <v>31.97114051364062</v>
       </c>
       <c r="I4" t="n">
-        <v>19.81135974217364</v>
+        <v>19.81135974217363</v>
       </c>
       <c r="J4" t="n">
-        <v>36.67252123344734</v>
+        <v>36.67252123344728</v>
       </c>
       <c r="K4" t="n">
         <v>31.06507333600169</v>
       </c>
       <c r="L4" t="n">
-        <v>48.34253517504517</v>
+        <v>48.34253517504541</v>
       </c>
       <c r="M4" t="n">
-        <v>60.07285352080022</v>
+        <v>60.07285352079996</v>
       </c>
       <c r="N4" t="n">
-        <v>34.1913455747527</v>
+        <v>34.19134557475272</v>
       </c>
       <c r="O4" t="n">
-        <v>25.90594219928533</v>
+        <v>25.90594219928535</v>
       </c>
       <c r="P4" t="n">
-        <v>34.37086687976391</v>
+        <v>34.37086687976408</v>
       </c>
       <c r="Q4" t="n">
-        <v>23.9815043952284</v>
+        <v>23.98150439522847</v>
       </c>
       <c r="R4" t="n">
         <v>26.15059889833583</v>
       </c>
       <c r="S4" t="n">
-        <v>38.79840080943098</v>
+        <v>38.79840080943101</v>
       </c>
       <c r="T4" t="n">
-        <v>27.00983896226523</v>
+        <v>27.0098389622653</v>
       </c>
       <c r="U4" t="n">
-        <v>42.33027609138511</v>
+        <v>42.33027609138506</v>
       </c>
       <c r="V4" t="n">
-        <v>12.18835728444237</v>
+        <v>12.18835728444238</v>
       </c>
       <c r="W4" t="n">
-        <v>45.11465582524259</v>
+        <v>45.1146558252426</v>
       </c>
       <c r="X4" t="n">
-        <v>35.9367425005432</v>
+        <v>35.93674250054336</v>
       </c>
       <c r="Y4" t="n">
-        <v>27.94725303508018</v>
+        <v>27.94725303508017</v>
       </c>
       <c r="Z4" t="n">
-        <v>23.67882606135615</v>
+        <v>23.6788260613562</v>
       </c>
       <c r="AA4" t="n">
-        <v>33.10744761360566</v>
+        <v>33.10744761360576</v>
       </c>
       <c r="AB4" t="n">
-        <v>63.16112666974973</v>
+        <v>63.16112666975011</v>
       </c>
     </row>
     <row r="5">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.502127932109279</v>
+        <v>1.502127932109276</v>
       </c>
       <c r="C5" t="n">
-        <v>2.154318509494226</v>
+        <v>2.154318509494229</v>
       </c>
       <c r="D5" t="n">
-        <v>2.154318509494226</v>
+        <v>2.154318509494229</v>
       </c>
       <c r="E5" t="n">
-        <v>1.807046265546842</v>
+        <v>1.807046265546837</v>
       </c>
       <c r="F5" t="n">
-        <v>1.603731601697817</v>
+        <v>1.603731601697818</v>
       </c>
       <c r="G5" t="n">
-        <v>2.28955447430586</v>
+        <v>2.289554474305859</v>
       </c>
       <c r="H5" t="n">
-        <v>2.154318509494226</v>
+        <v>2.154318509494229</v>
       </c>
       <c r="I5" t="n">
-        <v>2.154318509494226</v>
+        <v>2.154318509494229</v>
       </c>
       <c r="J5" t="n">
-        <v>2.151921314539145</v>
+        <v>2.151921314539141</v>
       </c>
       <c r="K5" t="n">
-        <v>2.154318509494226</v>
+        <v>2.154318509494229</v>
       </c>
       <c r="L5" t="n">
-        <v>2.154318509494226</v>
+        <v>2.154318509494229</v>
       </c>
       <c r="M5" t="n">
-        <v>2.15431850949481</v>
+        <v>2.154318509494811</v>
       </c>
       <c r="N5" t="n">
-        <v>34.1913455747527</v>
+        <v>1.648761702792438</v>
       </c>
       <c r="O5" t="n">
-        <v>1.787693102711082</v>
+        <v>1.787693102711079</v>
       </c>
       <c r="P5" t="n">
-        <v>1.753637659562984</v>
+        <v>1.753637659562985</v>
       </c>
       <c r="Q5" t="n">
         <v>1.373957598252647</v>
       </c>
       <c r="R5" t="n">
-        <v>2.154318509494226</v>
+        <v>2.154318509494228</v>
       </c>
       <c r="S5" t="n">
-        <v>2.154318509494226</v>
+        <v>2.154318509494229</v>
       </c>
       <c r="T5" t="n">
-        <v>2.154318509494226</v>
+        <v>2.154318509494229</v>
       </c>
       <c r="U5" t="n">
-        <v>1.837004345111235</v>
+        <v>1.837004345111231</v>
       </c>
       <c r="V5" t="n">
         <v>1.961478229648371</v>
       </c>
       <c r="W5" t="n">
-        <v>2.154446683165091</v>
+        <v>2.154446683165086</v>
       </c>
       <c r="X5" t="n">
-        <v>1.433732160307305</v>
+        <v>1.433732160307303</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.804506884714728</v>
+        <v>2.804506884714723</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.490013157337214</v>
+        <v>1.490013157337211</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.154318509494226</v>
+        <v>2.154318509494229</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.835586102433148</v>
+        <v>2.835586102433152</v>
       </c>
     </row>
     <row r="6">
@@ -2485,82 +2485,82 @@
         <v>2.736967253776185</v>
       </c>
       <c r="C6" t="n">
-        <v>3.36233652198358</v>
+        <v>3.362336521983579</v>
       </c>
       <c r="D6" t="n">
-        <v>3.36233652198358</v>
+        <v>3.362336521983579</v>
       </c>
       <c r="E6" t="n">
         <v>3.218003910266592</v>
       </c>
       <c r="F6" t="n">
-        <v>1.920689569762288</v>
+        <v>1.920689569762285</v>
       </c>
       <c r="G6" t="n">
-        <v>3.362336605902118</v>
+        <v>3.362336605902116</v>
       </c>
       <c r="H6" t="n">
-        <v>3.36233652198358</v>
+        <v>3.362336521983579</v>
       </c>
       <c r="I6" t="n">
-        <v>3.36233652198358</v>
+        <v>3.362336521983579</v>
       </c>
       <c r="J6" t="n">
-        <v>3.359939327028498</v>
+        <v>3.359939327028495</v>
       </c>
       <c r="K6" t="n">
-        <v>3.36233652198358</v>
+        <v>3.362336521983579</v>
       </c>
       <c r="L6" t="n">
-        <v>3.36233652198358</v>
+        <v>3.362336521983579</v>
       </c>
       <c r="M6" t="n">
-        <v>3.36233652198358</v>
+        <v>3.362336521983579</v>
       </c>
       <c r="N6" t="n">
-        <v>34.1913455747527</v>
+        <v>3.362336521983579</v>
       </c>
       <c r="O6" t="n">
-        <v>3.569583190345405</v>
+        <v>3.569583190345402</v>
       </c>
       <c r="P6" t="n">
-        <v>3.614655766709242</v>
+        <v>3.614655766709239</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.362336605902118</v>
+        <v>3.362336605902116</v>
       </c>
       <c r="R6" t="n">
-        <v>3.36233652198358</v>
+        <v>3.362336521983579</v>
       </c>
       <c r="S6" t="n">
-        <v>3.36233652198358</v>
+        <v>3.362336521983579</v>
       </c>
       <c r="T6" t="n">
-        <v>3.36233652198358</v>
+        <v>3.362336521983579</v>
       </c>
       <c r="U6" t="n">
-        <v>3.36233652198358</v>
+        <v>3.362336521983579</v>
       </c>
       <c r="V6" t="n">
-        <v>4.0682961230166</v>
+        <v>4.068296123016599</v>
       </c>
       <c r="W6" t="n">
-        <v>3.36233652198358</v>
+        <v>3.362336521983579</v>
       </c>
       <c r="X6" t="n">
-        <v>3.36233652198358</v>
+        <v>3.362336521983579</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.36233652198358</v>
+        <v>3.362336521983579</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.985294496582733</v>
+        <v>2.985294496582727</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.36233652198358</v>
+        <v>3.362336521983579</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.36233652198358</v>
+        <v>3.362336521983579</v>
       </c>
     </row>
     <row r="7">
@@ -2570,25 +2570,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.37456216724134</v>
+        <v>10.37456216724135</v>
       </c>
       <c r="C7" t="n">
         <v>10.8673789280632</v>
       </c>
       <c r="D7" t="n">
-        <v>10.38869312727756</v>
+        <v>10.38869312727755</v>
       </c>
       <c r="E7" t="n">
-        <v>9.699775366806769</v>
+        <v>9.699775366806762</v>
       </c>
       <c r="F7" t="n">
         <v>10.67811699832811</v>
       </c>
       <c r="G7" t="n">
-        <v>9.980386546870536</v>
+        <v>9.980386546870538</v>
       </c>
       <c r="H7" t="n">
-        <v>10.43346425898556</v>
+        <v>10.43346425898555</v>
       </c>
       <c r="I7" t="n">
         <v>10.66281190005401</v>
@@ -2600,7 +2600,7 @@
         <v>10.3745782349804</v>
       </c>
       <c r="L7" t="n">
-        <v>10.00840483158364</v>
+        <v>10.00840483158365</v>
       </c>
       <c r="M7" t="n">
         <v>9.838724834369614</v>
@@ -2612,10 +2612,10 @@
         <v>10.43478750081429</v>
       </c>
       <c r="P7" t="n">
-        <v>10.26741012786017</v>
+        <v>10.26741012786018</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.55788399246888</v>
+        <v>10.55788399246887</v>
       </c>
       <c r="R7" t="n">
         <v>10.54136473575844</v>
@@ -2648,7 +2648,7 @@
         <v>10.34730662976105</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.829263249368646</v>
+        <v>9.829263249368648</v>
       </c>
     </row>
     <row r="8">
@@ -2661,37 +2661,37 @@
         <v>4.514791080142636</v>
       </c>
       <c r="C8" t="n">
-        <v>4.656420540659886</v>
+        <v>4.656420540659883</v>
       </c>
       <c r="D8" t="n">
-        <v>4.520590307558864</v>
+        <v>4.520590307558862</v>
       </c>
       <c r="E8" t="n">
-        <v>3.564168816357778</v>
+        <v>3.564168816357776</v>
       </c>
       <c r="F8" t="n">
         <v>4.6031012515901</v>
       </c>
       <c r="G8" t="n">
-        <v>4.401772737051351</v>
+        <v>4.401772737051349</v>
       </c>
       <c r="H8" t="n">
         <v>4.534035182778736</v>
       </c>
       <c r="I8" t="n">
-        <v>4.59864223180667</v>
+        <v>4.598642231806672</v>
       </c>
       <c r="J8" t="n">
         <v>4.474734471092455</v>
       </c>
       <c r="K8" t="n">
-        <v>4.516366673459389</v>
+        <v>4.516366673459388</v>
       </c>
       <c r="L8" t="n">
-        <v>4.410843927972642</v>
+        <v>4.410843927972637</v>
       </c>
       <c r="M8" t="n">
-        <v>4.364977241541541</v>
+        <v>4.36497724154154</v>
       </c>
       <c r="N8" t="n">
         <v>4.505963000385859</v>
@@ -2700,40 +2700,40 @@
         <v>4.531803160973435</v>
       </c>
       <c r="P8" t="n">
-        <v>4.483748720128511</v>
+        <v>4.48374872012851</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.568470923448424</v>
+        <v>4.568470923448425</v>
       </c>
       <c r="R8" t="n">
-        <v>4.564328466806799</v>
+        <v>4.5643284668068</v>
       </c>
       <c r="S8" t="n">
-        <v>4.457097738239484</v>
+        <v>4.457097738239483</v>
       </c>
       <c r="T8" t="n">
-        <v>4.554764210733602</v>
+        <v>4.5547642107336</v>
       </c>
       <c r="U8" t="n">
-        <v>4.442372089623143</v>
+        <v>4.442372089623142</v>
       </c>
       <c r="V8" t="n">
-        <v>4.803051331977757</v>
+        <v>4.803051331977756</v>
       </c>
       <c r="W8" t="n">
-        <v>4.433822678496677</v>
+        <v>4.433822678496678</v>
       </c>
       <c r="X8" t="n">
-        <v>4.498721602702865</v>
+        <v>4.498721602702864</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.538048820853059</v>
+        <v>4.538048820853061</v>
       </c>
       <c r="Z8" t="n">
         <v>4.556665500717902</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.508015804950004</v>
+        <v>4.508015804950003</v>
       </c>
       <c r="AB8" t="n">
         <v>4.363896202702612</v>
@@ -2914,10 +2914,10 @@
         <v>3.677151750319295</v>
       </c>
       <c r="F2" t="n">
-        <v>4.73608239212161</v>
+        <v>4.736082392121609</v>
       </c>
       <c r="G2" t="n">
-        <v>4.857661355673681</v>
+        <v>4.85766135567368</v>
       </c>
       <c r="H2" t="n">
         <v>4.778949962583519</v>
@@ -2926,16 +2926,16 @@
         <v>4.751706606650507</v>
       </c>
       <c r="J2" t="n">
-        <v>4.812882770376467</v>
+        <v>4.812882770376468</v>
       </c>
       <c r="K2" t="n">
-        <v>4.778984842009821</v>
+        <v>4.77898484200982</v>
       </c>
       <c r="L2" t="n">
         <v>4.839533421997777</v>
       </c>
       <c r="M2" t="n">
-        <v>4.870806226993526</v>
+        <v>4.870806226993524</v>
       </c>
       <c r="N2" t="n">
         <v>4.77950149245364</v>
@@ -2944,13 +2944,13 @@
         <v>4.77033912000696</v>
       </c>
       <c r="P2" t="n">
-        <v>4.81712983575564</v>
+        <v>4.817129835755638</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.730661725328164</v>
+        <v>4.730661725328165</v>
       </c>
       <c r="R2" t="n">
-        <v>4.763635095563829</v>
+        <v>4.763635095563826</v>
       </c>
       <c r="S2" t="n">
         <v>4.824078383745118</v>
@@ -2959,16 +2959,16 @@
         <v>4.768961095552166</v>
       </c>
       <c r="U2" t="n">
-        <v>4.816575228343513</v>
+        <v>4.816575228343512</v>
       </c>
       <c r="V2" t="n">
         <v>4.934584704089097</v>
       </c>
       <c r="W2" t="n">
-        <v>4.837344685611856</v>
+        <v>4.837344685611855</v>
       </c>
       <c r="X2" t="n">
-        <v>4.844851483368815</v>
+        <v>4.844851483368812</v>
       </c>
       <c r="Y2" t="n">
         <v>4.823517068557818</v>
@@ -2980,7 +2980,7 @@
         <v>4.802024290092214</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.886510081211504</v>
+        <v>4.886510081211505</v>
       </c>
     </row>
     <row r="3">
@@ -2999,7 +2999,7 @@
         <v>11.02951508850461</v>
       </c>
       <c r="E3" t="n">
-        <v>9.955409516589969</v>
+        <v>9.95540951658997</v>
       </c>
       <c r="F3" t="n">
         <v>11.02933492996215</v>
@@ -3050,7 +3050,7 @@
         <v>11.02989344722405</v>
       </c>
       <c r="V3" t="n">
-        <v>11.21529773354305</v>
+        <v>11.21529773354304</v>
       </c>
       <c r="W3" t="n">
         <v>11.02951508850461</v>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.03766546582385</v>
+        <v>22.03766546582388</v>
       </c>
       <c r="C4" t="n">
         <v>10.5193638544737</v>
@@ -3087,76 +3087,76 @@
         <v>34.05623627805078</v>
       </c>
       <c r="E4" t="n">
-        <v>12.5538459998978</v>
+        <v>12.55384599989778</v>
       </c>
       <c r="F4" t="n">
         <v>13.43103952136798</v>
       </c>
       <c r="G4" t="n">
-        <v>40.74268777083593</v>
+        <v>40.74268777083596</v>
       </c>
       <c r="H4" t="n">
         <v>25.97373766485647</v>
       </c>
       <c r="I4" t="n">
-        <v>17.84412835158932</v>
+        <v>17.84412835158928</v>
       </c>
       <c r="J4" t="n">
-        <v>32.17607648051514</v>
+        <v>32.17607648051515</v>
       </c>
       <c r="K4" t="n">
-        <v>22.15980292897401</v>
+        <v>22.15980292897399</v>
       </c>
       <c r="L4" t="n">
-        <v>38.75884452312436</v>
+        <v>38.75884452312434</v>
       </c>
       <c r="M4" t="n">
-        <v>49.66104221600438</v>
+        <v>49.66104221600437</v>
       </c>
       <c r="N4" t="n">
-        <v>24.46190297069542</v>
+        <v>24.46190297069544</v>
       </c>
       <c r="O4" t="n">
-        <v>19.38990354868091</v>
+        <v>19.38990354868095</v>
       </c>
       <c r="P4" t="n">
-        <v>31.24446064838011</v>
+        <v>31.24446064838019</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.62266485047809</v>
+        <v>11.62266485047811</v>
       </c>
       <c r="R4" t="n">
-        <v>21.26523126689966</v>
+        <v>21.26523126689965</v>
       </c>
       <c r="S4" t="n">
-        <v>33.10175339045627</v>
+        <v>33.1017533904563</v>
       </c>
       <c r="T4" t="n">
-        <v>22.39100553210472</v>
+        <v>22.39100553210477</v>
       </c>
       <c r="U4" t="n">
-        <v>31.99295706622206</v>
+        <v>31.99295706622203</v>
       </c>
       <c r="V4" t="n">
-        <v>15.19894445542933</v>
+        <v>15.1989444554294</v>
       </c>
       <c r="W4" t="n">
-        <v>38.70750313555602</v>
+        <v>38.70750313555597</v>
       </c>
       <c r="X4" t="n">
-        <v>40.87581830248151</v>
+        <v>40.87581830248155</v>
       </c>
       <c r="Y4" t="n">
-        <v>35.0188859950595</v>
+        <v>35.01888599505964</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.13883205707947</v>
+        <v>21.13883205707945</v>
       </c>
       <c r="AA4" t="n">
-        <v>29.75640163008458</v>
+        <v>29.7564016300846</v>
       </c>
       <c r="AB4" t="n">
-        <v>55.33011314621481</v>
+        <v>55.33011314621488</v>
       </c>
     </row>
     <row r="5">
@@ -3169,82 +3169,82 @@
         <v>1.372873670028049</v>
       </c>
       <c r="C5" t="n">
-        <v>1.942799109620081</v>
+        <v>1.942799109620079</v>
       </c>
       <c r="D5" t="n">
-        <v>1.942799109620081</v>
+        <v>1.942799109620079</v>
       </c>
       <c r="E5" t="n">
-        <v>1.639330624851733</v>
+        <v>1.639330624851734</v>
       </c>
       <c r="F5" t="n">
-        <v>1.461661392617179</v>
+        <v>1.46166139261718</v>
       </c>
       <c r="G5" t="n">
-        <v>2.06097686221329</v>
+        <v>2.060976862213291</v>
       </c>
       <c r="H5" t="n">
-        <v>1.942799109620081</v>
+        <v>1.942799109620079</v>
       </c>
       <c r="I5" t="n">
-        <v>1.942799109620081</v>
+        <v>1.942799109620079</v>
       </c>
       <c r="J5" t="n">
-        <v>1.940612837015407</v>
+        <v>1.940612837015408</v>
       </c>
       <c r="K5" t="n">
-        <v>1.942799109620081</v>
+        <v>1.942799109620079</v>
       </c>
       <c r="L5" t="n">
-        <v>1.942799109620082</v>
+        <v>1.94279910962008</v>
       </c>
       <c r="M5" t="n">
-        <v>1.94279910962116</v>
+        <v>1.942799109621159</v>
       </c>
       <c r="N5" t="n">
-        <v>24.46190297069542</v>
+        <v>1.501011547399644</v>
       </c>
       <c r="O5" t="n">
-        <v>1.622418605303135</v>
+        <v>1.622418605303133</v>
       </c>
       <c r="P5" t="n">
-        <v>1.592658801822852</v>
+        <v>1.592658801822855</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.260870313322696</v>
+        <v>1.260870313322692</v>
       </c>
       <c r="R5" t="n">
-        <v>1.942799109620081</v>
+        <v>1.942799109620079</v>
       </c>
       <c r="S5" t="n">
-        <v>1.942799109620081</v>
+        <v>1.942799109620079</v>
       </c>
       <c r="T5" t="n">
-        <v>1.942799109620081</v>
+        <v>1.942799109620079</v>
       </c>
       <c r="U5" t="n">
-        <v>1.664276172561255</v>
+        <v>1.664276172561254</v>
       </c>
       <c r="V5" t="n">
-        <v>1.772285241210499</v>
+        <v>1.772285241210489</v>
       </c>
       <c r="W5" t="n">
-        <v>1.942911115965208</v>
+        <v>1.94291111596521</v>
       </c>
       <c r="X5" t="n">
-        <v>1.313105112116031</v>
+        <v>1.313105112116034</v>
       </c>
       <c r="Y5" t="n">
         <v>2.508864362230736</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.362287012414884</v>
+        <v>1.362287012414882</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.942799109620081</v>
+        <v>1.942799109620079</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.538133887357185</v>
+        <v>2.538133887357191</v>
       </c>
     </row>
     <row r="6">
@@ -3257,82 +3257,82 @@
         <v>2.392961591133729</v>
       </c>
       <c r="C6" t="n">
-        <v>2.923134056820695</v>
+        <v>2.923134056820696</v>
       </c>
       <c r="D6" t="n">
-        <v>2.923134056820695</v>
+        <v>2.923134056820696</v>
       </c>
       <c r="E6" t="n">
-        <v>2.800772493140134</v>
+        <v>2.800772493140136</v>
       </c>
       <c r="F6" t="n">
-        <v>1.700941691789412</v>
+        <v>1.700941691789413</v>
       </c>
       <c r="G6" t="n">
-        <v>2.923134159349896</v>
+        <v>2.923134159349902</v>
       </c>
       <c r="H6" t="n">
-        <v>2.923134056820695</v>
+        <v>2.923134056820696</v>
       </c>
       <c r="I6" t="n">
-        <v>2.923134056820695</v>
+        <v>2.923134056820696</v>
       </c>
       <c r="J6" t="n">
-        <v>2.920947784216022</v>
+        <v>2.920947784216021</v>
       </c>
       <c r="K6" t="n">
-        <v>2.923134056820695</v>
+        <v>2.923134056820696</v>
       </c>
       <c r="L6" t="n">
         <v>2.923134056820698</v>
       </c>
       <c r="M6" t="n">
-        <v>2.923134056820695</v>
+        <v>2.923134056820696</v>
       </c>
       <c r="N6" t="n">
-        <v>24.46190297069542</v>
+        <v>2.923134056820696</v>
       </c>
       <c r="O6" t="n">
-        <v>3.098832654255056</v>
+        <v>3.098832654255057</v>
       </c>
       <c r="P6" t="n">
-        <v>3.137044062418402</v>
+        <v>3.1370440624184</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.923134159349896</v>
+        <v>2.923134159349902</v>
       </c>
       <c r="R6" t="n">
-        <v>2.923134056820695</v>
+        <v>2.923134056820696</v>
       </c>
       <c r="S6" t="n">
-        <v>2.923134056820695</v>
+        <v>2.923134056820696</v>
       </c>
       <c r="T6" t="n">
-        <v>2.923134056820695</v>
+        <v>2.923134056820696</v>
       </c>
       <c r="U6" t="n">
-        <v>2.923134056820695</v>
+        <v>2.923134056820696</v>
       </c>
       <c r="V6" t="n">
-        <v>3.520582377774633</v>
+        <v>3.520582377774625</v>
       </c>
       <c r="W6" t="n">
-        <v>2.923134056820695</v>
+        <v>2.923134056820696</v>
       </c>
       <c r="X6" t="n">
         <v>2.923134056820698</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.923134056820695</v>
+        <v>2.923134056820696</v>
       </c>
       <c r="Z6" t="n">
         <v>2.603487245499785</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.923134056820695</v>
+        <v>2.923134056820696</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.923134056820695</v>
+        <v>2.923134056820696</v>
       </c>
     </row>
     <row r="7">
@@ -3351,7 +3351,7 @@
         <v>10.28482845436917</v>
       </c>
       <c r="E7" t="n">
-        <v>9.676786001670543</v>
+        <v>9.676786001670544</v>
       </c>
       <c r="F7" t="n">
         <v>10.74456710541665</v>
@@ -3372,7 +3372,7 @@
         <v>10.49156925823569</v>
       </c>
       <c r="L7" t="n">
-        <v>10.13007266072579</v>
+        <v>10.13007266072578</v>
       </c>
       <c r="M7" t="n">
         <v>9.957728131039152</v>
@@ -3402,7 +3402,7 @@
         <v>10.26745895209664</v>
       </c>
       <c r="V7" t="n">
-        <v>10.83222767749004</v>
+        <v>10.83222767749003</v>
       </c>
       <c r="W7" t="n">
         <v>10.14449265935265</v>
@@ -3414,13 +3414,13 @@
         <v>10.22305974734567</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.4884531787497</v>
+        <v>10.48845317874971</v>
       </c>
       <c r="AA7" t="n">
         <v>10.35350343559947</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.886590710603956</v>
+        <v>9.886590710603958</v>
       </c>
     </row>
     <row r="8">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.533706776061699</v>
+        <v>4.533706776061698</v>
       </c>
       <c r="C8" t="n">
-        <v>4.620959151747279</v>
+        <v>4.620959151747278</v>
       </c>
       <c r="D8" t="n">
-        <v>4.475690606401689</v>
+        <v>4.475690606401687</v>
       </c>
       <c r="E8" t="n">
-        <v>3.550377163110498</v>
+        <v>3.550377163110499</v>
       </c>
       <c r="F8" t="n">
         <v>4.606512124452196</v>
       </c>
       <c r="G8" t="n">
-        <v>4.396829032296829</v>
+        <v>4.396829032296827</v>
       </c>
       <c r="H8" t="n">
-        <v>4.536579035103861</v>
+        <v>4.536579035103863</v>
       </c>
       <c r="I8" t="n">
-        <v>4.580617782453966</v>
+        <v>4.580617782453967</v>
       </c>
       <c r="J8" t="n">
         <v>4.46615103166139</v>
       </c>
       <c r="K8" t="n">
-        <v>4.534266228159492</v>
+        <v>4.534266228159493</v>
       </c>
       <c r="L8" t="n">
         <v>4.430284251005459</v>
       </c>
       <c r="M8" t="n">
-        <v>4.383248530000015</v>
+        <v>4.383248530000016</v>
       </c>
       <c r="N8" t="n">
         <v>4.532972012464652</v>
       </c>
       <c r="O8" t="n">
-        <v>4.544878176852684</v>
+        <v>4.544878176852683</v>
       </c>
       <c r="P8" t="n">
         <v>4.465165152426531</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.615035570353201</v>
+        <v>4.615035570353199</v>
       </c>
       <c r="R8" t="n">
-        <v>4.562202796161169</v>
+        <v>4.562202796161168</v>
       </c>
       <c r="S8" t="n">
-        <v>4.455220948650552</v>
+        <v>4.455220948650551</v>
       </c>
       <c r="T8" t="n">
         <v>4.550934061450524</v>
       </c>
       <c r="U8" t="n">
-        <v>4.469665103325969</v>
+        <v>4.46966510332597</v>
       </c>
       <c r="V8" t="n">
-        <v>4.760286607813144</v>
+        <v>4.760286607813141</v>
       </c>
       <c r="W8" t="n">
-        <v>4.434656659948577</v>
+        <v>4.434656659948575</v>
       </c>
       <c r="X8" t="n">
-        <v>4.430637046446606</v>
+        <v>4.430637046446603</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.456886747385159</v>
+        <v>4.456886747385157</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.53223333527813</v>
+        <v>4.532233335278129</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.494436833699059</v>
+        <v>4.49443683369906</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.364817566306531</v>
+        <v>4.364817566306529</v>
       </c>
     </row>
   </sheetData>
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.754495199570997</v>
+        <v>4.754495199570993</v>
       </c>
       <c r="C2" t="n">
-        <v>4.721171002834285</v>
+        <v>4.721171002834284</v>
       </c>
       <c r="D2" t="n">
-        <v>4.764552530197373</v>
+        <v>4.764552530197371</v>
       </c>
       <c r="E2" t="n">
-        <v>3.648702273737696</v>
+        <v>3.648702273737697</v>
       </c>
       <c r="F2" t="n">
-        <v>4.731865191120467</v>
+        <v>4.731865191120468</v>
       </c>
       <c r="G2" t="n">
-        <v>4.820955688205818</v>
+        <v>4.820955688205816</v>
       </c>
       <c r="H2" t="n">
-        <v>4.756598288792794</v>
+        <v>4.75659828879279</v>
       </c>
       <c r="I2" t="n">
-        <v>4.740570862509096</v>
+        <v>4.740570862509086</v>
       </c>
       <c r="J2" t="n">
-        <v>4.791113459172941</v>
+        <v>4.791113459172938</v>
       </c>
       <c r="K2" t="n">
-        <v>4.782025415980321</v>
+        <v>4.782025415980319</v>
       </c>
       <c r="L2" t="n">
-        <v>4.803934097726872</v>
+        <v>4.803934097726867</v>
       </c>
       <c r="M2" t="n">
-        <v>4.831362747662279</v>
+        <v>4.831362747662274</v>
       </c>
       <c r="N2" t="n">
         <v>4.754927583054387</v>
       </c>
       <c r="O2" t="n">
-        <v>4.741028766417079</v>
+        <v>4.741028766417093</v>
       </c>
       <c r="P2" t="n">
-        <v>4.796238791127965</v>
+        <v>4.796238791127975</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.731234276046283</v>
+        <v>4.73123427604628</v>
       </c>
       <c r="R2" t="n">
-        <v>4.743462768443059</v>
+        <v>4.743462768443061</v>
       </c>
       <c r="S2" t="n">
-        <v>4.798034965263844</v>
+        <v>4.798034965263853</v>
       </c>
       <c r="T2" t="n">
-        <v>4.749373227521868</v>
+        <v>4.749373227521869</v>
       </c>
       <c r="U2" t="n">
-        <v>4.813843962182106</v>
+        <v>4.813843962182107</v>
       </c>
       <c r="V2" t="n">
-        <v>4.983917543896827</v>
+        <v>4.983917543896831</v>
       </c>
       <c r="W2" t="n">
-        <v>4.824418053474933</v>
+        <v>4.824418053474932</v>
       </c>
       <c r="X2" t="n">
-        <v>4.837409733327224</v>
+        <v>4.837409733327228</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.865603103316624</v>
+        <v>4.865603103316621</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.755493679645512</v>
+        <v>4.755493679645507</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.79572908156994</v>
+        <v>4.795729081569945</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.855030166611973</v>
+        <v>4.855030166611972</v>
       </c>
     </row>
     <row r="3">
@@ -3822,7 +3822,7 @@
         <v>11.017813317002</v>
       </c>
       <c r="V3" t="n">
-        <v>11.22862837887556</v>
+        <v>11.22862837887557</v>
       </c>
       <c r="W3" t="n">
         <v>11.01673760801875</v>
@@ -3834,7 +3834,7 @@
         <v>11.01554443808243</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.01670601911327</v>
+        <v>11.01670601911326</v>
       </c>
       <c r="AA3" t="n">
         <v>11.01673760801875</v>
@@ -3850,25 +3850,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.99928952450322</v>
+        <v>18.9992895245032</v>
       </c>
       <c r="C4" t="n">
-        <v>12.18656338118902</v>
+        <v>12.18656338118901</v>
       </c>
       <c r="D4" t="n">
-        <v>23.29177114150086</v>
+        <v>23.2917711415009</v>
       </c>
       <c r="E4" t="n">
-        <v>8.65452184965528</v>
+        <v>8.654521849655275</v>
       </c>
       <c r="F4" t="n">
-        <v>15.51675637736526</v>
+        <v>15.51675637736528</v>
       </c>
       <c r="G4" t="n">
-        <v>33.90725904052989</v>
+        <v>33.90725904052987</v>
       </c>
       <c r="H4" t="n">
-        <v>23.37858777828316</v>
+        <v>23.37858777828319</v>
       </c>
       <c r="I4" t="n">
         <v>17.94734525080738</v>
@@ -3877,22 +3877,22 @@
         <v>28.71394286382972</v>
       </c>
       <c r="K4" t="n">
-        <v>25.83780966750615</v>
+        <v>25.8378096675062</v>
       </c>
       <c r="L4" t="n">
-        <v>31.73169380194159</v>
+        <v>31.73169380194165</v>
       </c>
       <c r="M4" t="n">
-        <v>40.80699926439481</v>
+        <v>40.80699926439484</v>
       </c>
       <c r="N4" t="n">
-        <v>21.45601633298419</v>
+        <v>21.45601633298416</v>
       </c>
       <c r="O4" t="n">
-        <v>15.7082145107426</v>
+        <v>15.70821451074262</v>
       </c>
       <c r="P4" t="n">
-        <v>28.41379478280744</v>
+        <v>28.41379478280741</v>
       </c>
       <c r="Q4" t="n">
         <v>14.60555381184755</v>
@@ -3901,34 +3901,34 @@
         <v>19.14181560126165</v>
       </c>
       <c r="S4" t="n">
-        <v>29.52192042938803</v>
+        <v>29.52192042938807</v>
       </c>
       <c r="T4" t="n">
-        <v>20.61855201734125</v>
+        <v>20.61855201734126</v>
       </c>
       <c r="U4" t="n">
-        <v>33.02471853303039</v>
+        <v>33.02471853303036</v>
       </c>
       <c r="V4" t="n">
-        <v>23.04312894988448</v>
+        <v>23.04312894988452</v>
       </c>
       <c r="W4" t="n">
-        <v>38.71543286819609</v>
+        <v>38.7154328681961</v>
       </c>
       <c r="X4" t="n">
-        <v>41.19679334027099</v>
+        <v>41.19679334027096</v>
       </c>
       <c r="Y4" t="n">
-        <v>49.89716046662993</v>
+        <v>49.89716046662991</v>
       </c>
       <c r="Z4" t="n">
-        <v>17.85183850856059</v>
+        <v>17.8518385085606</v>
       </c>
       <c r="AA4" t="n">
-        <v>31.56091258376448</v>
+        <v>31.56091258376453</v>
       </c>
       <c r="AB4" t="n">
-        <v>49.34536709621889</v>
+        <v>49.34536709621887</v>
       </c>
     </row>
     <row r="5">
@@ -3938,85 +3938,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.353909380527321</v>
+        <v>1.353909380527307</v>
       </c>
       <c r="C5" t="n">
-        <v>1.898807229729447</v>
+        <v>1.898807229729446</v>
       </c>
       <c r="D5" t="n">
-        <v>1.898807229729447</v>
+        <v>1.898807229729446</v>
       </c>
       <c r="E5" t="n">
-        <v>1.608665198562884</v>
+        <v>1.608665198562893</v>
       </c>
       <c r="F5" t="n">
-        <v>1.438798097044264</v>
+        <v>1.438798097044273</v>
       </c>
       <c r="G5" t="n">
-        <v>2.011795348420408</v>
+        <v>2.011795348420421</v>
       </c>
       <c r="H5" t="n">
-        <v>1.898807229729447</v>
+        <v>1.898807229729446</v>
       </c>
       <c r="I5" t="n">
-        <v>1.898807229729447</v>
+        <v>1.898807229729446</v>
       </c>
       <c r="J5" t="n">
-        <v>1.897108325503849</v>
+        <v>1.897108325503864</v>
       </c>
       <c r="K5" t="n">
-        <v>1.898807229729447</v>
+        <v>1.898807229729446</v>
       </c>
       <c r="L5" t="n">
-        <v>1.898807229729445</v>
+        <v>1.898807229729446</v>
       </c>
       <c r="M5" t="n">
-        <v>1.898807229730617</v>
+        <v>1.898807229730616</v>
       </c>
       <c r="N5" t="n">
-        <v>21.45601633298419</v>
+        <v>1.476420237101956</v>
       </c>
       <c r="O5" t="n">
-        <v>1.592495850061787</v>
+        <v>1.592495850061794</v>
       </c>
       <c r="P5" t="n">
-        <v>1.564042912559195</v>
+        <v>1.564042912559197</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.246824516542379</v>
+        <v>1.246824516542382</v>
       </c>
       <c r="R5" t="n">
-        <v>1.898807229729447</v>
+        <v>1.898807229729446</v>
       </c>
       <c r="S5" t="n">
-        <v>1.898807229729447</v>
+        <v>1.898807229729446</v>
       </c>
       <c r="T5" t="n">
-        <v>1.898807229729447</v>
+        <v>1.898807229729446</v>
       </c>
       <c r="U5" t="n">
-        <v>1.631203350643951</v>
+        <v>1.631203350643958</v>
       </c>
       <c r="V5" t="n">
-        <v>1.736820877138113</v>
+        <v>1.736820877138121</v>
       </c>
       <c r="W5" t="n">
-        <v>1.898914317499323</v>
+        <v>1.898914317499334</v>
       </c>
       <c r="X5" t="n">
-        <v>1.296765486985063</v>
+        <v>1.296765486985066</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.437770056489427</v>
+        <v>2.437770056489424</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.343787623248592</v>
+        <v>1.343787623248581</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.898807229729447</v>
+        <v>1.898807229729446</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.467998596592003</v>
+        <v>2.467998596591988</v>
       </c>
     </row>
     <row r="6">
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.254294063757468</v>
+        <v>2.254294063757466</v>
       </c>
       <c r="C6" t="n">
-        <v>2.740468705605264</v>
+        <v>2.740468705605274</v>
       </c>
       <c r="D6" t="n">
-        <v>2.740468705605264</v>
+        <v>2.740468705605274</v>
       </c>
       <c r="E6" t="n">
         <v>2.628261612484745</v>
       </c>
       <c r="F6" t="n">
-        <v>1.619703413642302</v>
+        <v>1.619703413642312</v>
       </c>
       <c r="G6" t="n">
         <v>2.740468746098684</v>
       </c>
       <c r="H6" t="n">
-        <v>2.740468705605264</v>
+        <v>2.740468705605274</v>
       </c>
       <c r="I6" t="n">
-        <v>2.740468705605264</v>
+        <v>2.740468705605274</v>
       </c>
       <c r="J6" t="n">
-        <v>2.738769801379684</v>
+        <v>2.738769801379692</v>
       </c>
       <c r="K6" t="n">
-        <v>2.740468705605264</v>
+        <v>2.740468705605274</v>
       </c>
       <c r="L6" t="n">
-        <v>2.740468705605262</v>
+        <v>2.740468705605274</v>
       </c>
       <c r="M6" t="n">
-        <v>2.740468705605264</v>
+        <v>2.740468705605274</v>
       </c>
       <c r="N6" t="n">
-        <v>21.45601633298419</v>
+        <v>2.740468705605274</v>
       </c>
       <c r="O6" t="n">
-        <v>2.901586399235185</v>
+        <v>2.901586399235188</v>
       </c>
       <c r="P6" t="n">
-        <v>2.936626724478971</v>
+        <v>2.936626724478976</v>
       </c>
       <c r="Q6" t="n">
         <v>2.740468746098684</v>
       </c>
       <c r="R6" t="n">
-        <v>2.740468705605264</v>
+        <v>2.740468705605274</v>
       </c>
       <c r="S6" t="n">
-        <v>2.740468705605264</v>
+        <v>2.740468705605274</v>
       </c>
       <c r="T6" t="n">
-        <v>2.740468705605264</v>
+        <v>2.740468705605274</v>
       </c>
       <c r="U6" t="n">
-        <v>2.740468705605264</v>
+        <v>2.740468705605274</v>
       </c>
       <c r="V6" t="n">
-        <v>3.290261781803005</v>
+        <v>3.290261781803014</v>
       </c>
       <c r="W6" t="n">
-        <v>2.740468705605264</v>
+        <v>2.740468705605274</v>
       </c>
       <c r="X6" t="n">
-        <v>2.740468705605262</v>
+        <v>2.740468705605274</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.740468705605264</v>
+        <v>2.740468705605274</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.447348644986509</v>
+        <v>2.447348644986499</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.740468705605264</v>
+        <v>2.740468705605274</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.740468705605264</v>
+        <v>2.740468705605275</v>
       </c>
     </row>
     <row r="7">
@@ -4114,46 +4114,46 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.54236140853052</v>
+        <v>10.54236140853053</v>
       </c>
       <c r="C7" t="n">
         <v>10.74228687990802</v>
       </c>
       <c r="D7" t="n">
-        <v>10.49077091154014</v>
+        <v>10.49077091154013</v>
       </c>
       <c r="E7" t="n">
-        <v>9.743226400163289</v>
+        <v>9.743226400163294</v>
       </c>
       <c r="F7" t="n">
         <v>10.6823617832296</v>
       </c>
       <c r="G7" t="n">
-        <v>10.1467269398174</v>
+        <v>10.14672693981739</v>
       </c>
       <c r="H7" t="n">
         <v>10.5406019456228</v>
       </c>
       <c r="I7" t="n">
-        <v>10.63196750912091</v>
+        <v>10.63196750912092</v>
       </c>
       <c r="J7" t="n">
         <v>10.32203259234388</v>
       </c>
       <c r="K7" t="n">
-        <v>10.38666268627098</v>
+        <v>10.38666268627097</v>
       </c>
       <c r="L7" t="n">
         <v>10.25306896555067</v>
       </c>
       <c r="M7" t="n">
-        <v>10.09898822080569</v>
+        <v>10.09898822080568</v>
       </c>
       <c r="N7" t="n">
         <v>10.54515905973336</v>
       </c>
       <c r="O7" t="n">
-        <v>10.6200172457671</v>
+        <v>10.62001724576711</v>
       </c>
       <c r="P7" t="n">
         <v>10.28876972399443</v>
@@ -4168,19 +4168,19 @@
         <v>10.28560279265342</v>
       </c>
       <c r="T7" t="n">
-        <v>10.57708389924776</v>
+        <v>10.57708389924775</v>
       </c>
       <c r="U7" t="n">
-        <v>10.20055462531151</v>
+        <v>10.2005546253115</v>
       </c>
       <c r="V7" t="n">
         <v>10.6308849920415</v>
       </c>
       <c r="W7" t="n">
-        <v>10.13344874585029</v>
+        <v>10.13344874585028</v>
       </c>
       <c r="X7" t="n">
-        <v>10.07008379439996</v>
+        <v>10.07008379439997</v>
       </c>
       <c r="Y7" t="n">
         <v>9.884577898450713</v>
@@ -4189,10 +4189,10 @@
         <v>10.53675121366044</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.30335141534567</v>
+        <v>10.30335141534566</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.984184880668607</v>
+        <v>9.984184880668602</v>
       </c>
     </row>
     <row r="8">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.538652517056592</v>
+        <v>4.538652517056604</v>
       </c>
       <c r="C8" t="n">
-        <v>4.596457936683912</v>
+        <v>4.596457936683911</v>
       </c>
       <c r="D8" t="n">
-        <v>4.525236007143193</v>
+        <v>4.525236007143191</v>
       </c>
       <c r="E8" t="n">
-        <v>3.558925624809322</v>
+        <v>3.558925624809319</v>
       </c>
       <c r="F8" t="n">
-        <v>4.579831925118088</v>
+        <v>4.579831925118093</v>
       </c>
       <c r="G8" t="n">
-        <v>4.425149940685194</v>
+        <v>4.425149940685192</v>
       </c>
       <c r="H8" t="n">
-        <v>4.539955045048315</v>
+        <v>4.539955045048308</v>
       </c>
       <c r="I8" t="n">
         <v>4.565499241321022</v>
       </c>
       <c r="J8" t="n">
-        <v>4.475509325197677</v>
+        <v>4.475509325197671</v>
       </c>
       <c r="K8" t="n">
-        <v>4.495401433732639</v>
+        <v>4.495401433732638</v>
       </c>
       <c r="L8" t="n">
-        <v>4.456462431736329</v>
+        <v>4.456462431736325</v>
       </c>
       <c r="M8" t="n">
-        <v>4.414065810855361</v>
+        <v>4.414065810855359</v>
       </c>
       <c r="N8" t="n">
-        <v>4.540357840752872</v>
+        <v>4.540357840752868</v>
       </c>
       <c r="O8" t="n">
-        <v>4.56066296776884</v>
+        <v>4.560662967768841</v>
       </c>
       <c r="P8" t="n">
-        <v>4.465280703020347</v>
+        <v>4.465280703020346</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.580322984449895</v>
+        <v>4.580322984449889</v>
       </c>
       <c r="R8" t="n">
-        <v>4.562942941357666</v>
+        <v>4.562942941357664</v>
       </c>
       <c r="S8" t="n">
-        <v>4.465366294284218</v>
+        <v>4.465366294284217</v>
       </c>
       <c r="T8" t="n">
-        <v>4.549535652911754</v>
+        <v>4.549535652911755</v>
       </c>
       <c r="U8" t="n">
-        <v>4.441988653014011</v>
+        <v>4.441988653014009</v>
       </c>
       <c r="V8" t="n">
-        <v>4.711942397992178</v>
+        <v>4.711942397992181</v>
       </c>
       <c r="W8" t="n">
-        <v>4.422518806313695</v>
+        <v>4.422518806313697</v>
       </c>
       <c r="X8" t="n">
-        <v>4.40617871940972</v>
+        <v>4.406178719409716</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.351009723607681</v>
+        <v>4.35100972360768</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.537112713639264</v>
+        <v>4.537112713639257</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.471136090476788</v>
+        <v>4.471136090476787</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.383557104441058</v>
+        <v>4.38355710444106</v>
       </c>
     </row>
   </sheetData>
@@ -4449,31 +4449,31 @@
         <v>4.569128357756633</v>
       </c>
       <c r="C2" t="n">
-        <v>4.562098469278329</v>
+        <v>4.562098469278328</v>
       </c>
       <c r="D2" t="n">
-        <v>4.59253498094147</v>
+        <v>4.592534980941472</v>
       </c>
       <c r="E2" t="n">
-        <v>3.547009971874688</v>
+        <v>3.54700997187469</v>
       </c>
       <c r="F2" t="n">
-        <v>4.553617591668726</v>
+        <v>4.553617591668728</v>
       </c>
       <c r="G2" t="n">
-        <v>4.605848542344074</v>
+        <v>4.605848542344073</v>
       </c>
       <c r="H2" t="n">
-        <v>4.572606106574671</v>
+        <v>4.57260610657467</v>
       </c>
       <c r="I2" t="n">
-        <v>4.572137420425493</v>
+        <v>4.572137420425492</v>
       </c>
       <c r="J2" t="n">
-        <v>4.589337468162595</v>
+        <v>4.589337468162596</v>
       </c>
       <c r="K2" t="n">
-        <v>4.593476433796644</v>
+        <v>4.593476433796642</v>
       </c>
       <c r="L2" t="n">
         <v>4.561524277336847</v>
@@ -4482,16 +4482,16 @@
         <v>4.61372564805107</v>
       </c>
       <c r="N2" t="n">
-        <v>4.578691193709364</v>
+        <v>4.578691193709365</v>
       </c>
       <c r="O2" t="n">
-        <v>4.562977946348997</v>
+        <v>4.562977946348998</v>
       </c>
       <c r="P2" t="n">
         <v>4.569492042125932</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.567605610016972</v>
+        <v>4.567605610016971</v>
       </c>
       <c r="R2" t="n">
         <v>4.50667837426163</v>
@@ -4503,28 +4503,28 @@
         <v>4.565144526656297</v>
       </c>
       <c r="U2" t="n">
-        <v>4.62974230140558</v>
+        <v>4.629742301405581</v>
       </c>
       <c r="V2" t="n">
-        <v>4.755869461041476</v>
+        <v>4.755869461041475</v>
       </c>
       <c r="W2" t="n">
-        <v>4.690606984676988</v>
+        <v>4.69060698467699</v>
       </c>
       <c r="X2" t="n">
         <v>4.619182201423749</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.582116152507325</v>
+        <v>4.582116152507323</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.570105165088596</v>
+        <v>4.570105165088594</v>
       </c>
       <c r="AA2" t="n">
         <v>4.625651337456048</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.611117270147186</v>
+        <v>4.611117270147187</v>
       </c>
     </row>
     <row r="3">
@@ -4543,7 +4543,7 @@
         <v>10.89439356646197</v>
       </c>
       <c r="E3" t="n">
-        <v>9.872570669421322</v>
+        <v>9.872570669421325</v>
       </c>
       <c r="F3" t="n">
         <v>10.89426592128746</v>
@@ -4558,7 +4558,7 @@
         <v>10.89439356646197</v>
       </c>
       <c r="J3" t="n">
-        <v>10.89305201968298</v>
+        <v>10.89305201968297</v>
       </c>
       <c r="K3" t="n">
         <v>10.89431849051622</v>
@@ -4588,7 +4588,7 @@
         <v>10.89439356646197</v>
       </c>
       <c r="T3" t="n">
-        <v>10.89428638114365</v>
+        <v>10.89428638114364</v>
       </c>
       <c r="U3" t="n">
         <v>10.89463558074041</v>
@@ -4600,7 +4600,7 @@
         <v>10.89439356646197</v>
       </c>
       <c r="X3" t="n">
-        <v>10.89459458539447</v>
+        <v>10.89459458539446</v>
       </c>
       <c r="Y3" t="n">
         <v>10.89382777438205</v>
@@ -4612,7 +4612,7 @@
         <v>10.89439356646197</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.89803811385057</v>
+        <v>10.89803811385056</v>
       </c>
     </row>
     <row r="4">
@@ -4625,82 +4625,82 @@
         <v>4.485908206947439</v>
       </c>
       <c r="C4" t="n">
-        <v>3.058676493813997</v>
+        <v>3.058676493813988</v>
       </c>
       <c r="D4" t="n">
-        <v>11.53282649474371</v>
+        <v>11.53282649474368</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4699483357343266</v>
+        <v>0.4699483357343244</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7058781408401629</v>
+        <v>0.7058781408401495</v>
       </c>
       <c r="G4" t="n">
-        <v>12.80446841669337</v>
+        <v>12.80446841669336</v>
       </c>
       <c r="H4" t="n">
-        <v>6.217330728810214</v>
+        <v>6.21733072881024</v>
       </c>
       <c r="I4" t="n">
-        <v>5.900228927150561</v>
+        <v>5.900228927150547</v>
       </c>
       <c r="J4" t="n">
-        <v>9.828589873144391</v>
+        <v>9.828589873144386</v>
       </c>
       <c r="K4" t="n">
         <v>10.83293453275802</v>
       </c>
       <c r="L4" t="n">
-        <v>2.642449134051182</v>
+        <v>2.642449134051177</v>
       </c>
       <c r="M4" t="n">
-        <v>16.14293258023554</v>
+        <v>16.14293258023553</v>
       </c>
       <c r="N4" t="n">
-        <v>7.348070928238499</v>
+        <v>7.348070928238455</v>
       </c>
       <c r="O4" t="n">
-        <v>2.990875491887804</v>
+        <v>2.990875491887846</v>
       </c>
       <c r="P4" t="n">
-        <v>4.660525911532007</v>
+        <v>4.660525911531885</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.344789080023995</v>
+        <v>4.344789080024018</v>
       </c>
       <c r="R4" t="n">
-        <v>-13.04237134076031</v>
+        <v>-13.04237134076034</v>
       </c>
       <c r="S4" t="n">
-        <v>6.298986141841659</v>
+        <v>6.298986141841657</v>
       </c>
       <c r="T4" t="n">
-        <v>3.820339641350994</v>
+        <v>3.820339641350972</v>
       </c>
       <c r="U4" t="n">
-        <v>20.10470266106018</v>
+        <v>20.1047026610601</v>
       </c>
       <c r="V4" t="n">
-        <v>4.144810773599025</v>
+        <v>4.144810773599009</v>
       </c>
       <c r="W4" t="n">
-        <v>37.88499794717981</v>
+        <v>37.88499794717985</v>
       </c>
       <c r="X4" t="n">
-        <v>18.68930061258866</v>
+        <v>18.68930061258863</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.419780729244465</v>
+        <v>8.419780729244247</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.638930083875389</v>
+        <v>4.63893008387539</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.15605583335104</v>
+        <v>20.156055833351</v>
       </c>
       <c r="AB4" t="n">
-        <v>16.15416157750406</v>
+        <v>16.15416157750403</v>
       </c>
     </row>
     <row r="5">
@@ -4710,85 +4710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.095716475740715</v>
+        <v>1.09571647574072</v>
       </c>
       <c r="C5" t="n">
-        <v>1.540007248004895</v>
+        <v>1.540007248004902</v>
       </c>
       <c r="D5" t="n">
-        <v>1.540007248004895</v>
+        <v>1.540007248004902</v>
       </c>
       <c r="E5" t="n">
-        <v>1.303435517559648</v>
+        <v>1.303435517559645</v>
       </c>
       <c r="F5" t="n">
-        <v>1.16493178549794</v>
+        <v>1.164931785497944</v>
       </c>
       <c r="G5" t="n">
-        <v>1.632133833902292</v>
+        <v>1.632133833902291</v>
       </c>
       <c r="H5" t="n">
-        <v>1.540007248004895</v>
+        <v>1.540007248004902</v>
       </c>
       <c r="I5" t="n">
-        <v>1.540007248004895</v>
+        <v>1.540007248004902</v>
       </c>
       <c r="J5" t="n">
-        <v>1.538271021178348</v>
+        <v>1.538271021178349</v>
       </c>
       <c r="K5" t="n">
-        <v>1.540007248004895</v>
+        <v>1.540007248004902</v>
       </c>
       <c r="L5" t="n">
-        <v>1.540007248004895</v>
+        <v>1.540007248004902</v>
       </c>
       <c r="M5" t="n">
-        <v>1.540007248005942</v>
+        <v>1.540007248005949</v>
       </c>
       <c r="N5" t="n">
-        <v>7.348070928238499</v>
+        <v>1.195607571219333</v>
       </c>
       <c r="O5" t="n">
-        <v>1.290251592683619</v>
+        <v>1.290251592683622</v>
       </c>
       <c r="P5" t="n">
-        <v>1.267052056111566</v>
+        <v>1.267052056111571</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.008403198588036</v>
+        <v>1.008403198588039</v>
       </c>
       <c r="R5" t="n">
-        <v>1.540007248004895</v>
+        <v>1.540007248004902</v>
       </c>
       <c r="S5" t="n">
-        <v>1.540007248004895</v>
+        <v>1.540007248004902</v>
       </c>
       <c r="T5" t="n">
-        <v>1.540007248004895</v>
+        <v>1.540007248004902</v>
       </c>
       <c r="U5" t="n">
-        <v>1.319831878010673</v>
+        <v>1.319831878010677</v>
       </c>
       <c r="V5" t="n">
-        <v>1.403425065875518</v>
+        <v>1.403425065875517</v>
       </c>
       <c r="W5" t="n">
-        <v>1.540094563692954</v>
+        <v>1.540094563692961</v>
       </c>
       <c r="X5" t="n">
         <v>1.049123330576557</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.97607080870715</v>
+        <v>1.976070808707155</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.087463546554829</v>
+        <v>1.087463546554826</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.540007248004895</v>
+        <v>1.540007248004902</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.004106110472681</v>
+        <v>2.004106110472677</v>
       </c>
     </row>
     <row r="6">
@@ -4798,85 +4798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.885134087511321</v>
+        <v>1.88513408751132</v>
       </c>
       <c r="C6" t="n">
-        <v>2.296830679971503</v>
+        <v>2.296830679971502</v>
       </c>
       <c r="D6" t="n">
-        <v>2.296830679971503</v>
+        <v>2.296830679971502</v>
       </c>
       <c r="E6" t="n">
-        <v>2.20181278171784</v>
+        <v>2.201812781717841</v>
       </c>
       <c r="F6" t="n">
-        <v>1.347757678467117</v>
+        <v>1.347757678467118</v>
       </c>
       <c r="G6" t="n">
-        <v>2.29683067477957</v>
+        <v>2.296830674779572</v>
       </c>
       <c r="H6" t="n">
-        <v>2.296830679971503</v>
+        <v>2.296830679971502</v>
       </c>
       <c r="I6" t="n">
-        <v>2.296830679971503</v>
+        <v>2.296830679971502</v>
       </c>
       <c r="J6" t="n">
-        <v>2.295094453144944</v>
+        <v>2.295094453144946</v>
       </c>
       <c r="K6" t="n">
-        <v>2.296830679971503</v>
+        <v>2.296830679971502</v>
       </c>
       <c r="L6" t="n">
-        <v>2.296830679971503</v>
+        <v>2.296830679971502</v>
       </c>
       <c r="M6" t="n">
-        <v>2.296830679971503</v>
+        <v>2.296830679971502</v>
       </c>
       <c r="N6" t="n">
-        <v>7.348070928238499</v>
+        <v>2.296830679971502</v>
       </c>
       <c r="O6" t="n">
-        <v>2.433266384729584</v>
+        <v>2.433266384729591</v>
       </c>
       <c r="P6" t="n">
-        <v>2.462938810801149</v>
+        <v>2.462938810801152</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.29683067477957</v>
+        <v>2.296830674779572</v>
       </c>
       <c r="R6" t="n">
-        <v>2.296830679971503</v>
+        <v>2.296830679971502</v>
       </c>
       <c r="S6" t="n">
-        <v>2.296830679971503</v>
+        <v>2.296830679971502</v>
       </c>
       <c r="T6" t="n">
-        <v>2.296830679971503</v>
+        <v>2.296830679971502</v>
       </c>
       <c r="U6" t="n">
-        <v>2.296830679971503</v>
+        <v>2.296830679971502</v>
       </c>
       <c r="V6" t="n">
-        <v>2.760433724154766</v>
+        <v>2.760433724154765</v>
       </c>
       <c r="W6" t="n">
-        <v>2.296830679971503</v>
+        <v>2.296830679971502</v>
       </c>
       <c r="X6" t="n">
-        <v>2.296830679971503</v>
+        <v>2.296830679971502</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.296830679971503</v>
+        <v>2.296830679971502</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.048614242145743</v>
+        <v>2.048614242145749</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.296830679971503</v>
+        <v>2.296830679971502</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.296830679971503</v>
+        <v>2.296830679971502</v>
       </c>
     </row>
     <row r="7">
@@ -4895,7 +4895,7 @@
         <v>10.66515727180935</v>
       </c>
       <c r="E7" t="n">
-        <v>9.875513120659512</v>
+        <v>9.875513120659516</v>
       </c>
       <c r="F7" t="n">
         <v>10.89231982883081</v>
@@ -4916,7 +4916,7 @@
         <v>10.65883125777129</v>
       </c>
       <c r="L7" t="n">
-        <v>10.84635467900611</v>
+        <v>10.84635467900612</v>
       </c>
       <c r="M7" t="n">
         <v>10.54181660183034</v>
@@ -4925,7 +4925,7 @@
         <v>10.74561754150356</v>
       </c>
       <c r="O7" t="n">
-        <v>10.83574756774545</v>
+        <v>10.83574756774546</v>
       </c>
       <c r="P7" t="n">
         <v>10.79805590774414</v>
@@ -4934,7 +4934,7 @@
         <v>10.8109447009454</v>
       </c>
       <c r="R7" t="n">
-        <v>11.16690206092679</v>
+        <v>11.1669020609268</v>
       </c>
       <c r="S7" t="n">
         <v>10.74421661807293</v>
@@ -4955,10 +4955,10 @@
         <v>10.50997679942088</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.72156602416106</v>
+        <v>10.72156602416107</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.79498527352721</v>
+        <v>10.7949852735272</v>
       </c>
       <c r="AA7" t="n">
         <v>10.46830717444212</v>
@@ -4974,64 +4974,64 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.526546717644122</v>
+        <v>4.526546717644123</v>
       </c>
       <c r="C8" t="n">
-        <v>4.538052744496917</v>
+        <v>4.538052744496916</v>
       </c>
       <c r="D8" t="n">
         <v>4.488231736341803</v>
       </c>
       <c r="E8" t="n">
-        <v>3.548348796565098</v>
+        <v>3.548348796565101</v>
       </c>
       <c r="F8" t="n">
-        <v>4.552732113399122</v>
+        <v>4.552732113399123</v>
       </c>
       <c r="G8" t="n">
         <v>4.463851436488667</v>
       </c>
       <c r="H8" t="n">
-        <v>4.52176503046285</v>
+        <v>4.521765030462851</v>
       </c>
       <c r="I8" t="n">
-        <v>4.522291836133912</v>
+        <v>4.522291836133913</v>
       </c>
       <c r="J8" t="n">
         <v>4.488995850941781</v>
       </c>
       <c r="K8" t="n">
-        <v>4.486328992444416</v>
+        <v>4.486328992444417</v>
       </c>
       <c r="L8" t="n">
-        <v>4.539666430453582</v>
+        <v>4.539666430453583</v>
       </c>
       <c r="M8" t="n">
-        <v>4.45334222325247</v>
+        <v>4.453342223252469</v>
       </c>
       <c r="N8" t="n">
-        <v>4.510997628232229</v>
+        <v>4.510997628232227</v>
       </c>
       <c r="O8" t="n">
-        <v>4.536405949338357</v>
+        <v>4.536405949338358</v>
       </c>
       <c r="P8" t="n">
-        <v>4.52568616442877</v>
+        <v>4.525686164428771</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.529637701257388</v>
+        <v>4.529637701257391</v>
       </c>
       <c r="R8" t="n">
-        <v>4.63067692260635</v>
+        <v>4.630676922606348</v>
       </c>
       <c r="S8" t="n">
-        <v>4.510388480464008</v>
+        <v>4.510388480464007</v>
       </c>
       <c r="T8" t="n">
-        <v>4.533601430683055</v>
+        <v>4.53360143068305</v>
       </c>
       <c r="U8" t="n">
-        <v>4.424774523584443</v>
+        <v>4.424774523584444</v>
       </c>
       <c r="V8" t="n">
         <v>4.716798598345925</v>
@@ -5040,19 +5040,19 @@
         <v>4.322145245003072</v>
       </c>
       <c r="X8" t="n">
-        <v>4.444179883101609</v>
+        <v>4.444179883101607</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.503736507191152</v>
+        <v>4.503736507191153</v>
       </c>
       <c r="Z8" t="n">
         <v>4.524882762504452</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.431780671230253</v>
+        <v>4.431780671230251</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.466197992070454</v>
+        <v>4.466197992070453</v>
       </c>
     </row>
   </sheetData>
@@ -5218,85 +5218,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.448893773410729</v>
+        <v>4.448893773410727</v>
       </c>
       <c r="C2" t="n">
-        <v>4.485856713866299</v>
+        <v>4.485856713866296</v>
       </c>
       <c r="D2" t="n">
-        <v>4.49794698320152</v>
+        <v>4.497946983201518</v>
       </c>
       <c r="E2" t="n">
         <v>3.415562886142028</v>
       </c>
       <c r="F2" t="n">
-        <v>4.429050087143546</v>
+        <v>4.429050087143542</v>
       </c>
       <c r="G2" t="n">
-        <v>4.523443226360321</v>
+        <v>4.523443226360317</v>
       </c>
       <c r="H2" t="n">
-        <v>4.489735880033822</v>
+        <v>4.489735880033821</v>
       </c>
       <c r="I2" t="n">
-        <v>4.477364240646868</v>
+        <v>4.477364240646864</v>
       </c>
       <c r="J2" t="n">
-        <v>4.496633061822279</v>
+        <v>4.496633061822275</v>
       </c>
       <c r="K2" t="n">
-        <v>4.477298860849171</v>
+        <v>4.477298860849169</v>
       </c>
       <c r="L2" t="n">
-        <v>4.415196168860697</v>
+        <v>4.415196168860694</v>
       </c>
       <c r="M2" t="n">
-        <v>4.482922842536408</v>
+        <v>4.482922842536404</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5123420159483</v>
+        <v>4.512342015948297</v>
       </c>
       <c r="O2" t="n">
-        <v>4.484341450030394</v>
+        <v>4.484341450030391</v>
       </c>
       <c r="P2" t="n">
-        <v>4.448324523224338</v>
+        <v>4.448324523224336</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.489495392270483</v>
+        <v>4.489495392270481</v>
       </c>
       <c r="R2" t="n">
-        <v>4.348376850915242</v>
+        <v>4.348376850915241</v>
       </c>
       <c r="S2" t="n">
-        <v>4.468588375756934</v>
+        <v>4.468588375756927</v>
       </c>
       <c r="T2" t="n">
-        <v>4.463825477215343</v>
+        <v>4.463825477215337</v>
       </c>
       <c r="U2" t="n">
         <v>4.494433884341715</v>
       </c>
       <c r="V2" t="n">
-        <v>4.693045501486588</v>
+        <v>4.693045501486584</v>
       </c>
       <c r="W2" t="n">
         <v>4.556996252038837</v>
       </c>
       <c r="X2" t="n">
-        <v>4.641319513141118</v>
+        <v>4.641319513141113</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.533734144316065</v>
+        <v>4.533734144316062</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.490076830504267</v>
+        <v>4.490076830504263</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.598019393406676</v>
+        <v>4.598019393406673</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.489406676087859</v>
+        <v>4.489406676087857</v>
       </c>
     </row>
     <row r="3">
@@ -5315,7 +5315,7 @@
         <v>10.82624769287415</v>
       </c>
       <c r="E3" t="n">
-        <v>9.807934111927523</v>
+        <v>9.807934111927519</v>
       </c>
       <c r="F3" t="n">
         <v>10.82606753433168</v>
@@ -5348,7 +5348,7 @@
         <v>10.82597252375094</v>
       </c>
       <c r="P3" t="n">
-        <v>10.82621657721879</v>
+        <v>10.82621657721878</v>
       </c>
       <c r="Q3" t="n">
         <v>10.82624419622564</v>
@@ -5360,7 +5360,7 @@
         <v>10.82624769287415</v>
       </c>
       <c r="T3" t="n">
-        <v>10.82593203309708</v>
+        <v>10.82593203309707</v>
       </c>
       <c r="U3" t="n">
         <v>10.82662605159358</v>
@@ -5372,7 +5372,7 @@
         <v>10.82624769287415</v>
       </c>
       <c r="X3" t="n">
-        <v>10.82864712394257</v>
+        <v>10.82864712394256</v>
       </c>
       <c r="Y3" t="n">
         <v>10.82556763373542</v>
@@ -5394,85 +5394,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-8.135355247104568</v>
+        <v>-8.135355247104584</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6481675488939267</v>
+        <v>0.6481675488939258</v>
       </c>
       <c r="D4" t="n">
-        <v>3.51263866242355</v>
+        <v>3.512638662423546</v>
       </c>
       <c r="E4" t="n">
-        <v>-16.37693292504724</v>
+        <v>-16.37693292504726</v>
       </c>
       <c r="F4" t="n">
-        <v>-13.65188703255935</v>
+        <v>-13.65188703255936</v>
       </c>
       <c r="G4" t="n">
-        <v>8.441092830905477</v>
+        <v>8.441092830905486</v>
       </c>
       <c r="H4" t="n">
-        <v>1.568216044916147</v>
+        <v>1.568216044916144</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.635486764764999</v>
+        <v>-1.635486764765005</v>
       </c>
       <c r="J4" t="n">
-        <v>2.990367831139486</v>
+        <v>2.990367831139494</v>
       </c>
       <c r="K4" t="n">
         <v>-1.30301311903539</v>
       </c>
       <c r="L4" t="n">
-        <v>-13.14199185218319</v>
+        <v>-13.14199185218317</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09102395217595882</v>
+        <v>0.09102395217595616</v>
       </c>
       <c r="N4" t="n">
-        <v>6.970149557687731</v>
+        <v>6.970149557687677</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2877206425466763</v>
+        <v>0.287720642546706</v>
       </c>
       <c r="P4" t="n">
-        <v>-8.169342237999651</v>
+        <v>-8.169342237999604</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.390216452423051</v>
+        <v>1.390216452423034</v>
       </c>
       <c r="R4" t="n">
-        <v>-35.59302333797734</v>
+        <v>-35.59302333797731</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.00345376366896</v>
+        <v>-3.003453763668961</v>
       </c>
       <c r="T4" t="n">
-        <v>-4.682273587362458</v>
+        <v>-4.682273587362463</v>
       </c>
       <c r="U4" t="n">
-        <v>2.369263499106273</v>
+        <v>2.369263499106268</v>
       </c>
       <c r="V4" t="n">
-        <v>3.584697506349093</v>
+        <v>3.584697506349094</v>
       </c>
       <c r="W4" t="n">
-        <v>17.40702983765546</v>
+        <v>17.40702983765545</v>
       </c>
       <c r="X4" t="n">
-        <v>37.49953135509825</v>
+        <v>37.49953135509829</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.76004469027501</v>
+        <v>12.76004469027503</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.488041354001038</v>
+        <v>1.488041354001032</v>
       </c>
       <c r="AA4" t="n">
-        <v>28.80745206063593</v>
+        <v>28.807452060636</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.616804526962048</v>
+        <v>0.6168045269620428</v>
       </c>
     </row>
     <row r="5">
@@ -5482,85 +5482,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9021498778476978</v>
+        <v>0.9021498778476924</v>
       </c>
       <c r="C5" t="n">
-        <v>1.236580823871519</v>
+        <v>1.236580823871517</v>
       </c>
       <c r="D5" t="n">
-        <v>1.236580823871519</v>
+        <v>1.236580823871517</v>
       </c>
       <c r="E5" t="n">
-        <v>1.058506210184729</v>
+        <v>1.058506210184721</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9542503106678327</v>
+        <v>0.954250310667822</v>
       </c>
       <c r="G5" t="n">
-        <v>1.305927259148814</v>
+        <v>1.305927259148808</v>
       </c>
       <c r="H5" t="n">
-        <v>1.236580823871519</v>
+        <v>1.236580823871517</v>
       </c>
       <c r="I5" t="n">
-        <v>1.236580823871519</v>
+        <v>1.236580823871517</v>
       </c>
       <c r="J5" t="n">
-        <v>1.23501176907669</v>
+        <v>1.235011769076686</v>
       </c>
       <c r="K5" t="n">
-        <v>1.236580823871519</v>
+        <v>1.236580823871517</v>
       </c>
       <c r="L5" t="n">
-        <v>1.236580823871519</v>
+        <v>1.236580823871517</v>
       </c>
       <c r="M5" t="n">
-        <v>1.236580823871081</v>
+        <v>1.23658082387108</v>
       </c>
       <c r="N5" t="n">
-        <v>6.970149557687731</v>
+        <v>0.9773408916433132</v>
       </c>
       <c r="O5" t="n">
-        <v>1.04858227601331</v>
+        <v>1.048582276013309</v>
       </c>
       <c r="P5" t="n">
-        <v>1.031119291265274</v>
+        <v>1.031119291265269</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8364265639072853</v>
+        <v>0.8364265639072724</v>
       </c>
       <c r="R5" t="n">
-        <v>1.236580823871519</v>
+        <v>1.236580823871517</v>
       </c>
       <c r="S5" t="n">
-        <v>1.236580823871519</v>
+        <v>1.236580823871517</v>
       </c>
       <c r="T5" t="n">
-        <v>1.236580823871519</v>
+        <v>1.236580823871517</v>
       </c>
       <c r="U5" t="n">
-        <v>1.069011495290821</v>
+        <v>1.069011495290812</v>
       </c>
       <c r="V5" t="n">
-        <v>1.129951058397351</v>
+        <v>1.129951058397345</v>
       </c>
       <c r="W5" t="n">
-        <v>1.236646549228744</v>
+        <v>1.236646549228741</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8670778246937986</v>
+        <v>0.8670778246937988</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.561676764297113</v>
+        <v>1.561676764297105</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.8959376513134331</v>
+        <v>0.8959376513134272</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.236580823871519</v>
+        <v>1.236580823871517</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.585921911756568</v>
+        <v>1.585921911756561</v>
       </c>
     </row>
     <row r="6">
@@ -5570,85 +5570,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.520512958838096</v>
+        <v>1.520512958838097</v>
       </c>
       <c r="C6" t="n">
-        <v>1.837086613530848</v>
+        <v>1.837086613530842</v>
       </c>
       <c r="D6" t="n">
-        <v>1.837086613530848</v>
+        <v>1.837086613530842</v>
       </c>
       <c r="E6" t="n">
-        <v>1.764022746495364</v>
+        <v>1.76402274649536</v>
       </c>
       <c r="F6" t="n">
-        <v>1.10729786842524</v>
+        <v>1.107297868425231</v>
       </c>
       <c r="G6" t="n">
-        <v>1.837086667076071</v>
+        <v>1.837086667076066</v>
       </c>
       <c r="H6" t="n">
-        <v>1.837086613530848</v>
+        <v>1.837086613530842</v>
       </c>
       <c r="I6" t="n">
-        <v>1.837086613530848</v>
+        <v>1.837086613530842</v>
       </c>
       <c r="J6" t="n">
-        <v>1.835517558736011</v>
+        <v>1.835517558736007</v>
       </c>
       <c r="K6" t="n">
-        <v>1.837086613530848</v>
+        <v>1.837086613530842</v>
       </c>
       <c r="L6" t="n">
-        <v>1.837086613530848</v>
+        <v>1.837086613530842</v>
       </c>
       <c r="M6" t="n">
-        <v>1.837086613530848</v>
+        <v>1.837086613530842</v>
       </c>
       <c r="N6" t="n">
-        <v>6.970149557687731</v>
+        <v>1.837086613530842</v>
       </c>
       <c r="O6" t="n">
-        <v>1.94199877946822</v>
+        <v>1.941998779468215</v>
       </c>
       <c r="P6" t="n">
-        <v>1.964815363924798</v>
+        <v>1.96481536392479</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.837086667076071</v>
+        <v>1.837086667076066</v>
       </c>
       <c r="R6" t="n">
-        <v>1.837086613530848</v>
+        <v>1.837086613530842</v>
       </c>
       <c r="S6" t="n">
-        <v>1.837086613530848</v>
+        <v>1.837086613530842</v>
       </c>
       <c r="T6" t="n">
-        <v>1.837086613530848</v>
+        <v>1.837086613530842</v>
       </c>
       <c r="U6" t="n">
-        <v>1.837086613530848</v>
+        <v>1.837086613530842</v>
       </c>
       <c r="V6" t="n">
-        <v>2.19196587145943</v>
+        <v>2.191965871459423</v>
       </c>
       <c r="W6" t="n">
-        <v>1.837086613530848</v>
+        <v>1.837086613530842</v>
       </c>
       <c r="X6" t="n">
-        <v>1.837086613530848</v>
+        <v>1.837086613530842</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.837086613530848</v>
+        <v>1.837086613530842</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.646220871841064</v>
+        <v>1.646220871841062</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.837086613530848</v>
+        <v>1.837086613530842</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.837086613530848</v>
+        <v>1.837086613530842</v>
       </c>
     </row>
     <row r="7">
@@ -5658,7 +5658,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.0466970728184</v>
+        <v>11.04669707281839</v>
       </c>
       <c r="C7" t="n">
         <v>10.82451609955228</v>
@@ -5685,10 +5685,10 @@
         <v>10.75895864233426</v>
       </c>
       <c r="K7" t="n">
-        <v>10.87632310186929</v>
+        <v>10.87632310186928</v>
       </c>
       <c r="L7" t="n">
-        <v>11.24453335245585</v>
+        <v>11.24453335245584</v>
       </c>
       <c r="M7" t="n">
         <v>10.84240862629478</v>
@@ -5697,25 +5697,25 @@
         <v>10.67100596157612</v>
       </c>
       <c r="O7" t="n">
-        <v>10.83404946364941</v>
+        <v>10.8340494636494</v>
       </c>
       <c r="P7" t="n">
         <v>11.05032428783218</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.80541066804154</v>
+        <v>10.80541066804155</v>
       </c>
       <c r="R7" t="n">
         <v>11.63144775359861</v>
       </c>
       <c r="S7" t="n">
-        <v>10.92921400745597</v>
+        <v>10.92921400745596</v>
       </c>
       <c r="T7" t="n">
-        <v>10.95376438396045</v>
+        <v>10.95376438396044</v>
       </c>
       <c r="U7" t="n">
-        <v>10.77846633845797</v>
+        <v>10.77846633845796</v>
       </c>
       <c r="V7" t="n">
         <v>10.9418366802909</v>
@@ -5724,7 +5724,7 @@
         <v>10.40693614380612</v>
       </c>
       <c r="X7" t="n">
-        <v>9.930552400961012</v>
+        <v>9.930552400961009</v>
       </c>
       <c r="Y7" t="n">
         <v>10.54034325643008</v>
@@ -5733,7 +5733,7 @@
         <v>10.8015135917712</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.16535688349294</v>
+        <v>10.16535688349293</v>
       </c>
       <c r="AB7" t="n">
         <v>10.8291605786979</v>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.54919894381585</v>
+        <v>4.549198943815847</v>
       </c>
       <c r="C8" t="n">
-        <v>4.485232362749034</v>
+        <v>4.485232362749031</v>
       </c>
       <c r="D8" t="n">
-        <v>4.465976138338497</v>
+        <v>4.465976138338493</v>
       </c>
       <c r="E8" t="n">
-        <v>3.59833624378829</v>
+        <v>3.598336243788289</v>
       </c>
       <c r="F8" t="n">
-        <v>4.579528061627951</v>
+        <v>4.579528061627948</v>
       </c>
       <c r="G8" t="n">
-        <v>4.421825393082438</v>
+        <v>4.421825393082435</v>
       </c>
       <c r="H8" t="n">
-        <v>4.479719787301956</v>
+        <v>4.479719787301954</v>
       </c>
       <c r="I8" t="n">
         <v>4.500208254531286</v>
       </c>
       <c r="J8" t="n">
-        <v>4.466257644770509</v>
+        <v>4.466257644770503</v>
       </c>
       <c r="K8" t="n">
-        <v>4.500131784776496</v>
+        <v>4.500131784776492</v>
       </c>
       <c r="L8" t="n">
-        <v>4.605517476967671</v>
+        <v>4.60551747696767</v>
       </c>
       <c r="M8" t="n">
-        <v>4.49038490298028</v>
+        <v>4.490384902980277</v>
       </c>
       <c r="N8" t="n">
-        <v>4.441706533481653</v>
+        <v>4.441706533481652</v>
       </c>
       <c r="O8" t="n">
-        <v>4.488016483423872</v>
+        <v>4.488016483423871</v>
       </c>
       <c r="P8" t="n">
-        <v>4.550294245742336</v>
+        <v>4.550294245742332</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.480016070554207</v>
+        <v>4.480016070554206</v>
       </c>
       <c r="R8" t="n">
-        <v>4.714563955523831</v>
+        <v>4.714563955523829</v>
       </c>
       <c r="S8" t="n">
-        <v>4.515438377025831</v>
+        <v>4.515438377025829</v>
       </c>
       <c r="T8" t="n">
-        <v>4.521989604235707</v>
+        <v>4.521989604235703</v>
       </c>
       <c r="U8" t="n">
-        <v>4.472521061389111</v>
+        <v>4.472521061389109</v>
       </c>
       <c r="V8" t="n">
-        <v>4.656195853186802</v>
+        <v>4.656195853186799</v>
       </c>
       <c r="W8" t="n">
-        <v>4.366208160946265</v>
+        <v>4.366208160946262</v>
       </c>
       <c r="X8" t="n">
-        <v>4.232683552126447</v>
+        <v>4.232683552126442</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.403956143685977</v>
+        <v>4.403956143685974</v>
       </c>
       <c r="Z8" t="n">
         <v>4.478837343334067</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.297311969004178</v>
+        <v>4.297311969004175</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.489073767744187</v>
+        <v>4.489073767744186</v>
       </c>
     </row>
   </sheetData>
@@ -5990,34 +5990,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.385583146869775</v>
+        <v>4.385583146869773</v>
       </c>
       <c r="C2" t="n">
-        <v>4.431788720621863</v>
+        <v>4.43178872062186</v>
       </c>
       <c r="D2" t="n">
-        <v>4.445433060982485</v>
+        <v>4.445433060982483</v>
       </c>
       <c r="E2" t="n">
         <v>3.387597926805638</v>
       </c>
       <c r="F2" t="n">
-        <v>4.407205423122831</v>
+        <v>4.407205423122829</v>
       </c>
       <c r="G2" t="n">
-        <v>4.484443612229197</v>
+        <v>4.484443612229195</v>
       </c>
       <c r="H2" t="n">
-        <v>4.465505834845572</v>
+        <v>4.465505834845569</v>
       </c>
       <c r="I2" t="n">
-        <v>4.457051729669831</v>
+        <v>4.457051729669828</v>
       </c>
       <c r="J2" t="n">
-        <v>4.459584068577476</v>
+        <v>4.459584068577477</v>
       </c>
       <c r="K2" t="n">
-        <v>4.451238198257915</v>
+        <v>4.451238198257912</v>
       </c>
       <c r="L2" t="n">
         <v>4.368284600550829</v>
@@ -6026,49 +6026,49 @@
         <v>4.458423885437734</v>
       </c>
       <c r="N2" t="n">
-        <v>4.486940360355457</v>
+        <v>4.486940360355455</v>
       </c>
       <c r="O2" t="n">
-        <v>4.426585642006599</v>
+        <v>4.426585642006597</v>
       </c>
       <c r="P2" t="n">
-        <v>4.4059527916334</v>
+        <v>4.405952791633398</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.460332511042448</v>
+        <v>4.460332511042446</v>
       </c>
       <c r="R2" t="n">
-        <v>4.321775303977258</v>
+        <v>4.321775303977256</v>
       </c>
       <c r="S2" t="n">
-        <v>4.422214851186102</v>
+        <v>4.422214851186101</v>
       </c>
       <c r="T2" t="n">
-        <v>4.440128543463515</v>
+        <v>4.440128543463512</v>
       </c>
       <c r="U2" t="n">
-        <v>4.464684258556828</v>
+        <v>4.464684258556827</v>
       </c>
       <c r="V2" t="n">
         <v>4.676833568439092</v>
       </c>
       <c r="W2" t="n">
-        <v>4.517261408596089</v>
+        <v>4.517261408596087</v>
       </c>
       <c r="X2" t="n">
-        <v>4.657247386808339</v>
+        <v>4.657247386808337</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.488376005754754</v>
+        <v>4.488376005754751</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.434884734690521</v>
+        <v>4.434884734690517</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.584306224379393</v>
+        <v>4.58430622437939</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.463735051859974</v>
+        <v>4.463735051859971</v>
       </c>
     </row>
     <row r="3">
@@ -6087,7 +6087,7 @@
         <v>10.79510220231279</v>
       </c>
       <c r="E3" t="n">
-        <v>9.790231705084981</v>
+        <v>9.790231705084983</v>
       </c>
       <c r="F3" t="n">
         <v>10.79486308339589</v>
@@ -6105,7 +6105,7 @@
         <v>10.79532945823042</v>
       </c>
       <c r="K3" t="n">
-        <v>10.79496568661576</v>
+        <v>10.79496568661577</v>
       </c>
       <c r="L3" t="n">
         <v>10.79510220231279</v>
@@ -6156,7 +6156,7 @@
         <v>10.79510220231279</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.79874674970138</v>
+        <v>10.79874674970139</v>
       </c>
     </row>
     <row r="4">
@@ -6166,79 +6166,79 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-15.5594067187298</v>
+        <v>-15.55940671872979</v>
       </c>
       <c r="C4" t="n">
-        <v>-5.106181376237997</v>
+        <v>-5.106181376238006</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.853085304626239</v>
+        <v>-1.853085304626236</v>
       </c>
       <c r="E4" t="n">
-        <v>-17.64326438302734</v>
+        <v>-17.64326438302731</v>
       </c>
       <c r="F4" t="n">
-        <v>-11.76300250862553</v>
+        <v>-11.76300250862556</v>
       </c>
       <c r="G4" t="n">
-        <v>7.06009699203818</v>
+        <v>7.060096992038186</v>
       </c>
       <c r="H4" t="n">
-        <v>3.309119822005159</v>
+        <v>3.309119822005163</v>
       </c>
       <c r="I4" t="n">
-        <v>1.035645259669014</v>
+        <v>1.035645259669013</v>
       </c>
       <c r="J4" t="n">
         <v>1.559268097571073</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3156982028468291</v>
+        <v>-0.3156982028468254</v>
       </c>
       <c r="L4" t="n">
         <v>-17.80236270884266</v>
       </c>
       <c r="M4" t="n">
-        <v>1.540851783207946</v>
+        <v>1.540851783207948</v>
       </c>
       <c r="N4" t="n">
-        <v>8.465114757858943</v>
+        <v>8.465114757858935</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.715586441676718</v>
+        <v>-5.715586441676711</v>
       </c>
       <c r="P4" t="n">
-        <v>-10.37703298820857</v>
+        <v>-10.37703298820855</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.789215299952105</v>
+        <v>1.789215299952106</v>
       </c>
       <c r="R4" t="n">
         <v>-35.07472389441547</v>
       </c>
       <c r="S4" t="n">
-        <v>-6.801126810234729</v>
+        <v>-6.801126810234731</v>
       </c>
       <c r="T4" t="n">
-        <v>-3.137558014162486</v>
+        <v>-3.137558014162482</v>
       </c>
       <c r="U4" t="n">
-        <v>2.482706562205359</v>
+        <v>2.482706562205356</v>
       </c>
       <c r="V4" t="n">
-        <v>4.908735685569283</v>
+        <v>4.908735685569289</v>
       </c>
       <c r="W4" t="n">
-        <v>15.5808409846788</v>
+        <v>15.58084098467883</v>
       </c>
       <c r="X4" t="n">
-        <v>48.2712229964975</v>
+        <v>48.27122299649749</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.30860088199471</v>
+        <v>9.308600881994726</v>
       </c>
       <c r="Z4" t="n">
-        <v>-3.771058870018995</v>
+        <v>-3.771058870018999</v>
       </c>
       <c r="AA4" t="n">
         <v>33.25427987863914</v>
@@ -6254,85 +6254,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.850128258490319</v>
+        <v>0.8501282584903185</v>
       </c>
       <c r="C5" t="n">
-        <v>1.155480222390177</v>
+        <v>1.155480222390178</v>
       </c>
       <c r="D5" t="n">
-        <v>1.155480222390177</v>
+        <v>1.155480222390178</v>
       </c>
       <c r="E5" t="n">
-        <v>0.992889308878786</v>
+        <v>0.9928893088787867</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8976985257649318</v>
+        <v>0.8976985257649287</v>
       </c>
       <c r="G5" t="n">
-        <v>1.218796941303018</v>
+        <v>1.218796941303017</v>
       </c>
       <c r="H5" t="n">
-        <v>1.155480222390177</v>
+        <v>1.155480222390178</v>
       </c>
       <c r="I5" t="n">
-        <v>1.155480222390177</v>
+        <v>1.155480222390178</v>
       </c>
       <c r="J5" t="n">
-        <v>1.15406131373262</v>
+        <v>1.154061313732617</v>
       </c>
       <c r="K5" t="n">
-        <v>1.155480222390177</v>
+        <v>1.155480222390178</v>
       </c>
       <c r="L5" t="n">
-        <v>1.155480222390177</v>
+        <v>1.155480222390178</v>
       </c>
       <c r="M5" t="n">
-        <v>1.155480222388918</v>
+        <v>1.15548022238892</v>
       </c>
       <c r="N5" t="n">
-        <v>8.465114757858947</v>
+        <v>0.9187813661527305</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9838282671933348</v>
+        <v>0.9838282671933345</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9678836999812291</v>
+        <v>0.9678836999812337</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7901196281937075</v>
+        <v>0.7901196281937053</v>
       </c>
       <c r="R5" t="n">
-        <v>1.155480222390177</v>
+        <v>1.155480222390178</v>
       </c>
       <c r="S5" t="n">
-        <v>1.155480222390177</v>
+        <v>1.155480222390178</v>
       </c>
       <c r="T5" t="n">
-        <v>1.155480222390177</v>
+        <v>1.155480222390178</v>
       </c>
       <c r="U5" t="n">
-        <v>1.00081318781118</v>
+        <v>1.000813187811181</v>
       </c>
       <c r="V5" t="n">
         <v>1.056329153975639</v>
       </c>
       <c r="W5" t="n">
-        <v>1.155540233037352</v>
+        <v>1.155540233037349</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8181057425756456</v>
+        <v>0.8181057425756463</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.449455462347857</v>
+        <v>1.449455462347851</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.8444561889655486</v>
+        <v>0.8444561889655483</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.155480222390177</v>
+        <v>1.155480222390178</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.474445882037213</v>
+        <v>1.474445882037217</v>
       </c>
     </row>
     <row r="6">
@@ -6342,85 +6342,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.395269626175403</v>
+        <v>1.395269626175396</v>
       </c>
       <c r="C6" t="n">
-        <v>1.678936870113224</v>
+        <v>1.678936870113227</v>
       </c>
       <c r="D6" t="n">
-        <v>1.678936870113224</v>
+        <v>1.678936870113227</v>
       </c>
       <c r="E6" t="n">
         <v>1.613467548320608</v>
       </c>
       <c r="F6" t="n">
-        <v>1.025006586670676</v>
+        <v>1.025006586670677</v>
       </c>
       <c r="G6" t="n">
-        <v>1.678936767475498</v>
+        <v>1.678936767475499</v>
       </c>
       <c r="H6" t="n">
-        <v>1.678936870113224</v>
+        <v>1.678936870113227</v>
       </c>
       <c r="I6" t="n">
-        <v>1.678936870113224</v>
+        <v>1.678936870113227</v>
       </c>
       <c r="J6" t="n">
-        <v>1.677517961455669</v>
+        <v>1.67751796145567</v>
       </c>
       <c r="K6" t="n">
-        <v>1.678936870113224</v>
+        <v>1.678936870113227</v>
       </c>
       <c r="L6" t="n">
-        <v>1.678936870113224</v>
+        <v>1.678936870113227</v>
       </c>
       <c r="M6" t="n">
-        <v>1.678936870113224</v>
+        <v>1.678936870113227</v>
       </c>
       <c r="N6" t="n">
-        <v>8.465114757858943</v>
+        <v>1.678936870113227</v>
       </c>
       <c r="O6" t="n">
         <v>1.7729436866719</v>
       </c>
       <c r="P6" t="n">
-        <v>1.793388578710006</v>
+        <v>1.793388578710007</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.678936767475498</v>
+        <v>1.678936767475499</v>
       </c>
       <c r="R6" t="n">
-        <v>1.678936870113224</v>
+        <v>1.678936870113227</v>
       </c>
       <c r="S6" t="n">
-        <v>1.678936870113224</v>
+        <v>1.678936870113227</v>
       </c>
       <c r="T6" t="n">
-        <v>1.678936870113224</v>
+        <v>1.678936870113227</v>
       </c>
       <c r="U6" t="n">
-        <v>1.678936870113224</v>
+        <v>1.678936870113227</v>
       </c>
       <c r="V6" t="n">
-        <v>1.996797338173247</v>
+        <v>1.996797338173246</v>
       </c>
       <c r="W6" t="n">
-        <v>1.678936870113224</v>
+        <v>1.678936870113227</v>
       </c>
       <c r="X6" t="n">
-        <v>1.678936870113224</v>
+        <v>1.678936870113227</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.678936870113224</v>
+        <v>1.678936870113227</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.507910705937924</v>
+        <v>1.507910705937923</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.678936870113224</v>
+        <v>1.678936870113227</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.678936870113224</v>
+        <v>1.678936870113227</v>
       </c>
     </row>
     <row r="7">
@@ -6439,7 +6439,7 @@
         <v>10.85179975115777</v>
       </c>
       <c r="E7" t="n">
-        <v>10.25317586557951</v>
+        <v>10.25317586557952</v>
       </c>
       <c r="F7" t="n">
         <v>11.07284106848223</v>
@@ -6448,7 +6448,7 @@
         <v>10.6199580944232</v>
       </c>
       <c r="H7" t="n">
-        <v>10.73463890083882</v>
+        <v>10.73463890083881</v>
       </c>
       <c r="I7" t="n">
         <v>10.78376574585003</v>
@@ -6518,10 +6518,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.573786107052699</v>
+        <v>4.573786107052697</v>
       </c>
       <c r="C8" t="n">
-        <v>4.493149914391078</v>
+        <v>4.493149914391076</v>
       </c>
       <c r="D8" t="n">
         <v>4.471230626391322</v>
@@ -6533,46 +6533,46 @@
         <v>4.53368629220039</v>
       </c>
       <c r="G8" t="n">
-        <v>4.404804364058761</v>
+        <v>4.404804364058759</v>
       </c>
       <c r="H8" t="n">
-        <v>4.437994839989805</v>
+        <v>4.437994839989804</v>
       </c>
       <c r="I8" t="n">
-        <v>4.451893605852129</v>
+        <v>4.451893605852128</v>
       </c>
       <c r="J8" t="n">
         <v>4.448086169331721</v>
       </c>
       <c r="K8" t="n">
-        <v>4.461245142581406</v>
+        <v>4.461245142581403</v>
       </c>
       <c r="L8" t="n">
-        <v>4.601840147852891</v>
+        <v>4.601840147852888</v>
       </c>
       <c r="M8" t="n">
         <v>4.448129658848753</v>
       </c>
       <c r="N8" t="n">
-        <v>4.401752506973691</v>
+        <v>4.40175250697369</v>
       </c>
       <c r="O8" t="n">
-        <v>4.503103395919197</v>
+        <v>4.503103395919193</v>
       </c>
       <c r="P8" t="n">
-        <v>4.537811160939732</v>
+        <v>4.537811160939731</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.446375099600158</v>
+        <v>4.44637509960016</v>
       </c>
       <c r="R8" t="n">
-        <v>4.677611417581262</v>
+        <v>4.677611417581259</v>
       </c>
       <c r="S8" t="n">
-        <v>4.510985880053467</v>
+        <v>4.510985880053468</v>
       </c>
       <c r="T8" t="n">
-        <v>4.478935182833407</v>
+        <v>4.478935182833408</v>
       </c>
       <c r="U8" t="n">
         <v>4.441554619245745</v>
@@ -6581,22 +6581,22 @@
         <v>4.624585697272739</v>
       </c>
       <c r="W8" t="n">
-        <v>4.350362911099711</v>
+        <v>4.35036291109971</v>
       </c>
       <c r="X8" t="n">
-        <v>4.120681357123178</v>
+        <v>4.120681357123182</v>
       </c>
       <c r="Y8" t="n">
         <v>4.39626838182086</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.489495289715896</v>
+        <v>4.489495289715893</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.23764670593031</v>
+        <v>4.237646705930308</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.449633730987556</v>
+        <v>4.449633730987558</v>
       </c>
     </row>
   </sheetData>
@@ -6762,85 +6762,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.725322890426214</v>
+        <v>4.725322890426217</v>
       </c>
       <c r="C2" t="n">
-        <v>4.673513662263693</v>
+        <v>4.673513662263696</v>
       </c>
       <c r="D2" t="n">
-        <v>4.736088740641626</v>
+        <v>4.736088740641621</v>
       </c>
       <c r="E2" t="n">
-        <v>3.628552158082476</v>
+        <v>3.628552158082479</v>
       </c>
       <c r="F2" t="n">
-        <v>4.681117347520552</v>
+        <v>4.681117347520556</v>
       </c>
       <c r="G2" t="n">
-        <v>4.828446923413098</v>
+        <v>4.828446923413096</v>
       </c>
       <c r="H2" t="n">
-        <v>4.747020451408719</v>
+        <v>4.747020451408722</v>
       </c>
       <c r="I2" t="n">
-        <v>4.689600022907632</v>
+        <v>4.689600022907634</v>
       </c>
       <c r="J2" t="n">
-        <v>4.764945411235419</v>
+        <v>4.764945411235418</v>
       </c>
       <c r="K2" t="n">
-        <v>4.722255882696651</v>
+        <v>4.722255882696649</v>
       </c>
       <c r="L2" t="n">
-        <v>4.797629098768276</v>
+        <v>4.797629098768277</v>
       </c>
       <c r="M2" t="n">
-        <v>4.849042949079813</v>
+        <v>4.849042949079817</v>
       </c>
       <c r="N2" t="n">
-        <v>4.739558325787447</v>
+        <v>4.739558325787442</v>
       </c>
       <c r="O2" t="n">
-        <v>4.719229804467079</v>
+        <v>4.719229804467083</v>
       </c>
       <c r="P2" t="n">
         <v>4.742063172169278</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.701583515997825</v>
+        <v>4.701583515997823</v>
       </c>
       <c r="R2" t="n">
-        <v>4.668604227252602</v>
+        <v>4.668604227252608</v>
       </c>
       <c r="S2" t="n">
         <v>4.743936742700845</v>
       </c>
       <c r="T2" t="n">
-        <v>4.697741437159282</v>
+        <v>4.697741437159284</v>
       </c>
       <c r="U2" t="n">
-        <v>4.785879389642021</v>
+        <v>4.78587938964202</v>
       </c>
       <c r="V2" t="n">
-        <v>4.877004249287314</v>
+        <v>4.877004249287315</v>
       </c>
       <c r="W2" t="n">
-        <v>4.798062835911708</v>
+        <v>4.798062835911711</v>
       </c>
       <c r="X2" t="n">
         <v>4.770487792250404</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.755520265886162</v>
+        <v>4.755520265886164</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.715436251023564</v>
+        <v>4.715436251023567</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.766575308777877</v>
+        <v>4.766575308777879</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.844327673227621</v>
+        <v>4.844327673227625</v>
       </c>
     </row>
     <row r="3">
@@ -6850,49 +6850,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.00046262528668</v>
+        <v>11.00046262528667</v>
       </c>
       <c r="C3" t="n">
-        <v>11.00012040504875</v>
+        <v>11.00012040504874</v>
       </c>
       <c r="D3" t="n">
-        <v>11.00046262528668</v>
+        <v>11.00046262528667</v>
       </c>
       <c r="E3" t="n">
         <v>9.932272077021059</v>
       </c>
       <c r="F3" t="n">
-        <v>11.00033498011217</v>
+        <v>11.00033498011216</v>
       </c>
       <c r="G3" t="n">
         <v>11.00042338204666</v>
       </c>
       <c r="H3" t="n">
-        <v>11.00046262528668</v>
+        <v>11.00046262528667</v>
       </c>
       <c r="I3" t="n">
-        <v>11.00046262528668</v>
+        <v>11.00046262528667</v>
       </c>
       <c r="J3" t="n">
-        <v>10.9965874932952</v>
+        <v>10.99658749329519</v>
       </c>
       <c r="K3" t="n">
-        <v>11.00038754934093</v>
+        <v>11.00038754934092</v>
       </c>
       <c r="L3" t="n">
-        <v>11.00046262528668</v>
+        <v>11.00046262528667</v>
       </c>
       <c r="M3" t="n">
-        <v>11.00037423534551</v>
+        <v>11.0003742353455</v>
       </c>
       <c r="N3" t="n">
-        <v>11.00046262528668</v>
+        <v>11.00046262528667</v>
       </c>
       <c r="O3" t="n">
-        <v>11.00021621097062</v>
+        <v>11.00021621097061</v>
       </c>
       <c r="P3" t="n">
-        <v>11.00040094653329</v>
+        <v>11.00040094653328</v>
       </c>
       <c r="Q3" t="n">
         <v>11.00045912863816</v>
@@ -6901,7 +6901,7 @@
         <v>11.00044874641645</v>
       </c>
       <c r="S3" t="n">
-        <v>11.00046262528668</v>
+        <v>11.00046262528667</v>
       </c>
       <c r="T3" t="n">
         <v>11.00035543996835</v>
@@ -6913,7 +6913,7 @@
         <v>11.18215260838753</v>
       </c>
       <c r="W3" t="n">
-        <v>11.00046262528668</v>
+        <v>11.00046262528667</v>
       </c>
       <c r="X3" t="n">
         <v>11.00066364421917</v>
@@ -6925,7 +6925,7 @@
         <v>11.00044353202126</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.00046262528668</v>
+        <v>11.00046262528667</v>
       </c>
       <c r="AB3" t="n">
         <v>11.00410717267527</v>
@@ -6938,64 +6938,64 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.25089436256067</v>
+        <v>17.25089436256076</v>
       </c>
       <c r="C4" t="n">
-        <v>4.863665638021176</v>
+        <v>4.863665638021181</v>
       </c>
       <c r="D4" t="n">
         <v>22.70510287470778</v>
       </c>
       <c r="E4" t="n">
-        <v>6.461552805431934</v>
+        <v>6.461552805431958</v>
       </c>
       <c r="F4" t="n">
-        <v>7.040451180821548</v>
+        <v>7.040451180821542</v>
       </c>
       <c r="G4" t="n">
         <v>42.27575845720376</v>
       </c>
       <c r="H4" t="n">
-        <v>26.65156844132099</v>
+        <v>26.65156844132098</v>
       </c>
       <c r="I4" t="n">
-        <v>9.477514411986201</v>
+        <v>9.477514411986187</v>
       </c>
       <c r="J4" t="n">
-        <v>28.62844634220727</v>
+        <v>28.62844634220731</v>
       </c>
       <c r="K4" t="n">
         <v>16.89726376859747</v>
       </c>
       <c r="L4" t="n">
-        <v>36.80182361259698</v>
+        <v>36.8018236125972</v>
       </c>
       <c r="M4" t="n">
-        <v>50.62032966467729</v>
+        <v>50.6203296646774</v>
       </c>
       <c r="N4" t="n">
         <v>23.02229192515029</v>
       </c>
       <c r="O4" t="n">
-        <v>15.40719551957031</v>
+        <v>15.4071955195703</v>
       </c>
       <c r="P4" t="n">
-        <v>22.01349127875337</v>
+        <v>22.01349127875338</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.28342270215721</v>
+        <v>12.28342270215723</v>
       </c>
       <c r="R4" t="n">
-        <v>3.564470587330807</v>
+        <v>3.564470587330792</v>
       </c>
       <c r="S4" t="n">
-        <v>21.17013969691472</v>
+        <v>21.17013969691473</v>
       </c>
       <c r="T4" t="n">
         <v>11.79083144439496</v>
       </c>
       <c r="U4" t="n">
-        <v>33.97491629437664</v>
+        <v>33.97491629437658</v>
       </c>
       <c r="V4" t="n">
         <v>10.40380701310833</v>
@@ -7004,19 +7004,19 @@
         <v>38.58513839244661</v>
       </c>
       <c r="X4" t="n">
-        <v>31.82228477090514</v>
+        <v>31.82228477090531</v>
       </c>
       <c r="Y4" t="n">
-        <v>26.76183782206302</v>
+        <v>26.76183782206304</v>
       </c>
       <c r="Z4" t="n">
         <v>14.92135359346627</v>
       </c>
       <c r="AA4" t="n">
-        <v>29.92639838562693</v>
+        <v>29.92639838562694</v>
       </c>
       <c r="AB4" t="n">
-        <v>54.86721223866682</v>
+        <v>54.86721223866683</v>
       </c>
     </row>
     <row r="5">
@@ -7029,82 +7029,82 @@
         <v>1.375974767052177</v>
       </c>
       <c r="C5" t="n">
-        <v>1.960421748038043</v>
+        <v>1.960421748038047</v>
       </c>
       <c r="D5" t="n">
-        <v>1.960421748038043</v>
+        <v>1.960421748038047</v>
       </c>
       <c r="E5" t="n">
-        <v>1.649220970840789</v>
+        <v>1.649220970840791</v>
       </c>
       <c r="F5" t="n">
-        <v>1.467024776066943</v>
+        <v>1.467024776066948</v>
       </c>
       <c r="G5" t="n">
-        <v>2.081610636831526</v>
+        <v>2.081610636831531</v>
       </c>
       <c r="H5" t="n">
-        <v>1.960421748038043</v>
+        <v>1.960421748038047</v>
       </c>
       <c r="I5" t="n">
-        <v>1.960421748038043</v>
+        <v>1.960421748038047</v>
       </c>
       <c r="J5" t="n">
-        <v>1.958154102761805</v>
+        <v>1.95815410276181</v>
       </c>
       <c r="K5" t="n">
-        <v>1.960421748038043</v>
+        <v>1.960421748038047</v>
       </c>
       <c r="L5" t="n">
-        <v>1.960421748038043</v>
+        <v>1.960421748038047</v>
       </c>
       <c r="M5" t="n">
-        <v>1.960421748038635</v>
+        <v>1.960421748038639</v>
       </c>
       <c r="N5" t="n">
-        <v>23.02229192515029</v>
+        <v>1.507377561823357</v>
       </c>
       <c r="O5" t="n">
-        <v>1.631878037717287</v>
+        <v>1.631878037717289</v>
       </c>
       <c r="P5" t="n">
-        <v>1.601359962742073</v>
+        <v>1.601359962742076</v>
       </c>
       <c r="Q5" t="n">
         <v>1.261117596035342</v>
       </c>
       <c r="R5" t="n">
-        <v>1.960421748038043</v>
+        <v>1.960421748038047</v>
       </c>
       <c r="S5" t="n">
-        <v>1.960421748038043</v>
+        <v>1.960421748038047</v>
       </c>
       <c r="T5" t="n">
-        <v>1.960421748038043</v>
+        <v>1.960421748038047</v>
       </c>
       <c r="U5" t="n">
-        <v>1.67515816302118</v>
+        <v>1.675158163021184</v>
       </c>
       <c r="V5" t="n">
-        <v>1.785799902115098</v>
+        <v>1.785799902115097</v>
       </c>
       <c r="W5" t="n">
-        <v>1.960536608236852</v>
+        <v>1.960536608236855</v>
       </c>
       <c r="X5" t="n">
-        <v>1.314683322923857</v>
+        <v>1.314683322923861</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.541519264501346</v>
+        <v>2.541519264501353</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.365118364353911</v>
+        <v>1.365118364353914</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.960421748038043</v>
+        <v>1.960421748038047</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.570925489993822</v>
+        <v>2.570925489993824</v>
       </c>
     </row>
     <row r="6">
@@ -7114,85 +7114,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.542178858809471</v>
+        <v>2.542178858809482</v>
       </c>
       <c r="C6" t="n">
-        <v>3.119081232470219</v>
+        <v>3.119081232470221</v>
       </c>
       <c r="D6" t="n">
-        <v>3.119081232470219</v>
+        <v>3.119081232470221</v>
       </c>
       <c r="E6" t="n">
-        <v>2.985934453070391</v>
+        <v>2.985934453070395</v>
       </c>
       <c r="F6" t="n">
         <v>1.789163919377879</v>
       </c>
       <c r="G6" t="n">
-        <v>3.119081148356199</v>
+        <v>3.119081148356193</v>
       </c>
       <c r="H6" t="n">
-        <v>3.119081232470219</v>
+        <v>3.119081232470221</v>
       </c>
       <c r="I6" t="n">
-        <v>3.119081232470219</v>
+        <v>3.119081232470221</v>
       </c>
       <c r="J6" t="n">
-        <v>3.116813587193979</v>
+        <v>3.116813587193978</v>
       </c>
       <c r="K6" t="n">
-        <v>3.119081232470219</v>
+        <v>3.119081232470221</v>
       </c>
       <c r="L6" t="n">
-        <v>3.119081232470219</v>
+        <v>3.119081232470221</v>
       </c>
       <c r="M6" t="n">
-        <v>3.119081232470219</v>
+        <v>3.119081232470221</v>
       </c>
       <c r="N6" t="n">
-        <v>23.02229192515029</v>
+        <v>3.119081232470221</v>
       </c>
       <c r="O6" t="n">
-        <v>3.310265811722905</v>
+        <v>3.310265811722904</v>
       </c>
       <c r="P6" t="n">
-        <v>3.351845195828751</v>
+        <v>3.351845195828754</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.119081148356199</v>
+        <v>3.119081148356193</v>
       </c>
       <c r="R6" t="n">
-        <v>3.119081232470219</v>
+        <v>3.119081232470221</v>
       </c>
       <c r="S6" t="n">
-        <v>3.119081232470219</v>
+        <v>3.119081232470221</v>
       </c>
       <c r="T6" t="n">
-        <v>3.119081232470219</v>
+        <v>3.119081232470221</v>
       </c>
       <c r="U6" t="n">
-        <v>3.119081232470219</v>
+        <v>3.119081232470221</v>
       </c>
       <c r="V6" t="n">
-        <v>3.769932690989372</v>
+        <v>3.769932690989376</v>
       </c>
       <c r="W6" t="n">
-        <v>3.119081232470219</v>
+        <v>3.119081232470221</v>
       </c>
       <c r="X6" t="n">
-        <v>3.119081232470219</v>
+        <v>3.119081232470221</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.119081232470219</v>
+        <v>3.119081232470221</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.771260367912705</v>
+        <v>2.771260367912708</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.119081232470219</v>
+        <v>3.119081232470221</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.119081232470219</v>
+        <v>3.119081232470221</v>
       </c>
     </row>
     <row r="7">
@@ -7235,7 +7235,7 @@
         <v>10.17871320905291</v>
       </c>
       <c r="M7" t="n">
-        <v>9.888787884082314</v>
+        <v>9.888787884082316</v>
       </c>
       <c r="N7" t="n">
         <v>10.52441218046748</v>
@@ -7253,7 +7253,7 @@
         <v>10.94218292494599</v>
       </c>
       <c r="S7" t="n">
-        <v>10.49451302115344</v>
+        <v>10.49451302115343</v>
       </c>
       <c r="T7" t="n">
         <v>10.77083051188874</v>
@@ -7268,7 +7268,7 @@
         <v>10.17752578666749</v>
       </c>
       <c r="X7" t="n">
-        <v>10.34589771403564</v>
+        <v>10.34589771403563</v>
       </c>
       <c r="Y7" t="n">
         <v>10.42592341973852</v>
@@ -7277,10 +7277,10 @@
         <v>10.66275039166858</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.36388298708333</v>
+        <v>10.36388298708332</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.936128386175286</v>
+        <v>9.936128386175284</v>
       </c>
     </row>
     <row r="8">
@@ -7290,85 +7290,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.544785741121116</v>
+        <v>4.544785741121111</v>
       </c>
       <c r="C8" t="n">
-        <v>4.632964412218826</v>
+        <v>4.632964412218822</v>
       </c>
       <c r="D8" t="n">
-        <v>4.529645548894469</v>
+        <v>4.529645548894466</v>
       </c>
       <c r="E8" t="n">
-        <v>3.570797220971191</v>
+        <v>3.570797220971193</v>
       </c>
       <c r="F8" t="n">
-        <v>4.621168718187224</v>
+        <v>4.621168718187227</v>
       </c>
       <c r="G8" t="n">
-        <v>4.368922831735073</v>
+        <v>4.368922831735071</v>
       </c>
       <c r="H8" t="n">
-        <v>4.513033532486846</v>
+        <v>4.513033532486848</v>
       </c>
       <c r="I8" t="n">
-        <v>4.607213596306474</v>
+        <v>4.607213596306472</v>
       </c>
       <c r="J8" t="n">
-        <v>4.468268125441163</v>
+        <v>4.468268125441164</v>
       </c>
       <c r="K8" t="n">
-        <v>4.55225590738801</v>
+        <v>4.552255907388011</v>
       </c>
       <c r="L8" t="n">
-        <v>4.423730495621902</v>
+        <v>4.423730495621904</v>
       </c>
       <c r="M8" t="n">
-        <v>4.343267616839553</v>
+        <v>4.343267616839552</v>
       </c>
       <c r="N8" t="n">
-        <v>4.522953856311953</v>
+        <v>4.522953856311958</v>
       </c>
       <c r="O8" t="n">
-        <v>4.554396710204379</v>
+        <v>4.554396710204384</v>
       </c>
       <c r="P8" t="n">
-        <v>4.515611443618977</v>
+        <v>4.515611443618976</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.586801211255843</v>
+        <v>4.586801211255842</v>
       </c>
       <c r="R8" t="n">
-        <v>4.642093092801391</v>
+        <v>4.64209309280139</v>
       </c>
       <c r="S8" t="n">
-        <v>4.5137280604545</v>
+        <v>4.513728060454499</v>
       </c>
       <c r="T8" t="n">
-        <v>4.593306863430519</v>
+        <v>4.593306863430517</v>
       </c>
       <c r="U8" t="n">
-        <v>4.443839780100464</v>
+        <v>4.443839780100462</v>
       </c>
       <c r="V8" t="n">
-        <v>4.769670657614611</v>
+        <v>4.769670657614613</v>
       </c>
       <c r="W8" t="n">
-        <v>4.423623951795884</v>
+        <v>4.423623951795885</v>
       </c>
       <c r="X8" t="n">
-        <v>4.47256720740169</v>
+        <v>4.472567207401688</v>
       </c>
       <c r="Y8" t="n">
         <v>4.494360533613378</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.561784795998919</v>
+        <v>4.561784795998918</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.476929544736422</v>
+        <v>4.476929544736415</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.358393921923677</v>
+        <v>4.358393921923681</v>
       </c>
     </row>
   </sheetData>
@@ -7534,85 +7534,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.560360724860653</v>
+        <v>4.560360724860652</v>
       </c>
       <c r="C2" t="n">
         <v>4.56076964476954</v>
       </c>
       <c r="D2" t="n">
-        <v>4.583914259333805</v>
+        <v>4.583914259333803</v>
       </c>
       <c r="E2" t="n">
-        <v>3.539516640832808</v>
+        <v>3.53951664083281</v>
       </c>
       <c r="F2" t="n">
-        <v>4.513274502131999</v>
+        <v>4.513274502131997</v>
       </c>
       <c r="G2" t="n">
-        <v>4.711779588777489</v>
+        <v>4.711779588777488</v>
       </c>
       <c r="H2" t="n">
-        <v>4.628383683353747</v>
+        <v>4.628383683353744</v>
       </c>
       <c r="I2" t="n">
-        <v>4.55731529823479</v>
+        <v>4.557315298234788</v>
       </c>
       <c r="J2" t="n">
-        <v>4.614166857046908</v>
+        <v>4.614166857046909</v>
       </c>
       <c r="K2" t="n">
-        <v>4.571235452668144</v>
+        <v>4.571235452668142</v>
       </c>
       <c r="L2" t="n">
-        <v>4.494039295089248</v>
+        <v>4.494039295089247</v>
       </c>
       <c r="M2" t="n">
-        <v>4.570561394162491</v>
+        <v>4.57056139416249</v>
       </c>
       <c r="N2" t="n">
-        <v>4.576569100432541</v>
+        <v>4.576569100432538</v>
       </c>
       <c r="O2" t="n">
-        <v>4.550916869313075</v>
+        <v>4.550916869313074</v>
       </c>
       <c r="P2" t="n">
-        <v>4.601009958738974</v>
+        <v>4.601009958738971</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.569361072425777</v>
+        <v>4.569361072425778</v>
       </c>
       <c r="R2" t="n">
-        <v>4.452134261079435</v>
+        <v>4.452134261079433</v>
       </c>
       <c r="S2" t="n">
-        <v>4.525171695648688</v>
+        <v>4.525171695648686</v>
       </c>
       <c r="T2" t="n">
-        <v>4.533190011983684</v>
+        <v>4.533190011983685</v>
       </c>
       <c r="U2" t="n">
         <v>4.593641725839337</v>
       </c>
       <c r="V2" t="n">
-        <v>4.783838591736031</v>
+        <v>4.78383859173603</v>
       </c>
       <c r="W2" t="n">
-        <v>4.663010074958847</v>
+        <v>4.663010074958845</v>
       </c>
       <c r="X2" t="n">
-        <v>4.707110752353376</v>
+        <v>4.707110752353375</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.743842533182681</v>
+        <v>4.74384253318268</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.590658527428237</v>
+        <v>4.590658527428236</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.625623312586418</v>
+        <v>4.625623312586417</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.682115796783903</v>
+        <v>4.682115796783902</v>
       </c>
     </row>
     <row r="3">
@@ -7655,7 +7655,7 @@
         <v>10.91114772901754</v>
       </c>
       <c r="M3" t="n">
-        <v>10.91090864445989</v>
+        <v>10.9109086444599</v>
       </c>
       <c r="N3" t="n">
         <v>10.91114772901754</v>
@@ -7670,37 +7670,37 @@
         <v>10.91114423236903</v>
       </c>
       <c r="R3" t="n">
-        <v>10.91154660323786</v>
+        <v>10.91154660323787</v>
       </c>
       <c r="S3" t="n">
         <v>10.91114772901754</v>
       </c>
       <c r="T3" t="n">
-        <v>10.91083206924046</v>
+        <v>10.91083206924047</v>
       </c>
       <c r="U3" t="n">
-        <v>10.91152608773697</v>
+        <v>10.91152608773698</v>
       </c>
       <c r="V3" t="n">
-        <v>11.10226853876664</v>
+        <v>11.10226853876663</v>
       </c>
       <c r="W3" t="n">
         <v>10.91114772901754</v>
       </c>
       <c r="X3" t="n">
-        <v>10.91354716008595</v>
+        <v>10.91354716008596</v>
       </c>
       <c r="Y3" t="n">
         <v>10.91046766987881</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.91111562450712</v>
+        <v>10.91111562450713</v>
       </c>
       <c r="AA3" t="n">
         <v>10.91114772901754</v>
       </c>
       <c r="AB3" t="n">
-        <v>10.91479227640613</v>
+        <v>10.91479227640614</v>
       </c>
     </row>
     <row r="4">
@@ -7710,85 +7710,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-1.691442577305239</v>
+        <v>-1.691442577305242</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.517645832491917</v>
+        <v>-1.517645832491932</v>
       </c>
       <c r="D4" t="n">
-        <v>4.136681371350637</v>
+        <v>4.136681371350635</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.437874110401831</v>
+        <v>-2.437874110401828</v>
       </c>
       <c r="F4" t="n">
-        <v>-13.76649914865523</v>
+        <v>-13.76649914865524</v>
       </c>
       <c r="G4" t="n">
-        <v>31.52745858267715</v>
+        <v>31.52745858267713</v>
       </c>
       <c r="H4" t="n">
         <v>16.65570503405852</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.821171417848253</v>
+        <v>-2.82117141784827</v>
       </c>
       <c r="J4" t="n">
         <v>11.04479079694516</v>
       </c>
       <c r="K4" t="n">
-        <v>1.047507758459143</v>
+        <v>1.047507758459155</v>
       </c>
       <c r="L4" t="n">
-        <v>-16.48101306114234</v>
+        <v>-16.48101306114232</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9127518700709041</v>
+        <v>0.9127518700709056</v>
       </c>
       <c r="N4" t="n">
         <v>2.225282937977767</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.52630229047569</v>
+        <v>-3.526302290475657</v>
       </c>
       <c r="P4" t="n">
-        <v>7.761701659550703</v>
+        <v>7.761701659550686</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4874271146727498</v>
+        <v>0.487427114672748</v>
       </c>
       <c r="R4" t="n">
-        <v>-31.37570771835192</v>
+        <v>-31.37570771835198</v>
       </c>
       <c r="S4" t="n">
-        <v>-9.244543007205607</v>
+        <v>-9.244543007205612</v>
       </c>
       <c r="T4" t="n">
-        <v>-8.956361367995401</v>
+        <v>-8.956361367995365</v>
       </c>
       <c r="U4" t="n">
-        <v>5.98594121480883</v>
+        <v>5.985941214808821</v>
       </c>
       <c r="V4" t="n">
-        <v>6.383418130825627</v>
+        <v>6.383418130825631</v>
       </c>
       <c r="W4" t="n">
-        <v>24.12135788770673</v>
+        <v>24.12135788770672</v>
       </c>
       <c r="X4" t="n">
-        <v>34.41518040605119</v>
+        <v>34.41518040605117</v>
       </c>
       <c r="Y4" t="n">
-        <v>44.17343487053862</v>
+        <v>44.17343487053849</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.195418260782508</v>
+        <v>5.195418260782496</v>
       </c>
       <c r="AA4" t="n">
-        <v>14.63213017103669</v>
+        <v>14.63213017103668</v>
       </c>
       <c r="AB4" t="n">
-        <v>29.9442856272918</v>
+        <v>29.94428562729182</v>
       </c>
     </row>
     <row r="5">
@@ -7798,46 +7798,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.092908376255932</v>
+        <v>1.09290837625593</v>
       </c>
       <c r="C5" t="n">
-        <v>1.523093925504184</v>
+        <v>1.523093925504181</v>
       </c>
       <c r="D5" t="n">
-        <v>1.523093925504184</v>
+        <v>1.523093925504181</v>
       </c>
       <c r="E5" t="n">
-        <v>1.294032810232047</v>
+        <v>1.294032810232046</v>
       </c>
       <c r="F5" t="n">
-        <v>1.15992625712612</v>
+        <v>1.159926257126122</v>
       </c>
       <c r="G5" t="n">
-        <v>1.612295701527473</v>
+        <v>1.612295701527475</v>
       </c>
       <c r="H5" t="n">
-        <v>1.523093925504184</v>
+        <v>1.523093925504181</v>
       </c>
       <c r="I5" t="n">
-        <v>1.523093925504184</v>
+        <v>1.523093925504181</v>
       </c>
       <c r="J5" t="n">
         <v>1.521041108487123</v>
       </c>
       <c r="K5" t="n">
-        <v>1.523093925504184</v>
+        <v>1.523093925504181</v>
       </c>
       <c r="L5" t="n">
-        <v>1.523093925504185</v>
+        <v>1.523093925504182</v>
       </c>
       <c r="M5" t="n">
-        <v>1.523093925505095</v>
+        <v>1.523093925505092</v>
       </c>
       <c r="N5" t="n">
-        <v>2.225282937977767</v>
+        <v>1.189628156323627</v>
       </c>
       <c r="O5" t="n">
-        <v>1.281267445060871</v>
+        <v>1.281267445060874</v>
       </c>
       <c r="P5" t="n">
         <v>1.258804441082009</v>
@@ -7846,34 +7846,34 @@
         <v>1.008367097353849</v>
       </c>
       <c r="R5" t="n">
-        <v>1.523093925504184</v>
+        <v>1.523093925504181</v>
       </c>
       <c r="S5" t="n">
-        <v>1.523093925504184</v>
+        <v>1.523093925504181</v>
       </c>
       <c r="T5" t="n">
-        <v>1.523093925504184</v>
+        <v>1.523093925504181</v>
       </c>
       <c r="U5" t="n">
-        <v>1.311345496377022</v>
+        <v>1.31134549637702</v>
       </c>
       <c r="V5" t="n">
         <v>1.390029597364736</v>
       </c>
       <c r="W5" t="n">
-        <v>1.523178469155636</v>
+        <v>1.523178469155632</v>
       </c>
       <c r="X5" t="n">
-        <v>1.047794457652687</v>
+        <v>1.047794457652688</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.947771529915617</v>
+        <v>1.947771529915621</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.084917458828992</v>
+        <v>1.084917458828988</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.523093925504184</v>
+        <v>1.523093925504181</v>
       </c>
       <c r="AB5" t="n">
         <v>1.972458703108075</v>
@@ -7889,82 +7889,82 @@
         <v>1.955773166760568</v>
       </c>
       <c r="C6" t="n">
-        <v>2.381642301501532</v>
+        <v>2.381642301501529</v>
       </c>
       <c r="D6" t="n">
-        <v>2.381642301501532</v>
+        <v>2.381642301501529</v>
       </c>
       <c r="E6" t="n">
-        <v>2.283353668580265</v>
+        <v>2.28335366858027</v>
       </c>
       <c r="F6" t="n">
         <v>1.399897331217405</v>
       </c>
       <c r="G6" t="n">
-        <v>2.381642595686665</v>
+        <v>2.381642595686659</v>
       </c>
       <c r="H6" t="n">
-        <v>2.381642301501532</v>
+        <v>2.381642301501529</v>
       </c>
       <c r="I6" t="n">
-        <v>2.381642301501532</v>
+        <v>2.381642301501529</v>
       </c>
       <c r="J6" t="n">
-        <v>2.37958948448447</v>
+        <v>2.379589484484471</v>
       </c>
       <c r="K6" t="n">
-        <v>2.381642301501532</v>
+        <v>2.381642301501529</v>
       </c>
       <c r="L6" t="n">
-        <v>2.381642301501532</v>
+        <v>2.381642301501531</v>
       </c>
       <c r="M6" t="n">
-        <v>2.381642301501532</v>
+        <v>2.381642301501529</v>
       </c>
       <c r="N6" t="n">
-        <v>2.225282937977767</v>
+        <v>2.381642301501529</v>
       </c>
       <c r="O6" t="n">
-        <v>2.522775166804339</v>
+        <v>2.522775166804335</v>
       </c>
       <c r="P6" t="n">
-        <v>2.553469079595291</v>
+        <v>2.553469079595293</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.381642595686665</v>
+        <v>2.381642595686659</v>
       </c>
       <c r="R6" t="n">
-        <v>2.381642301501532</v>
+        <v>2.381642301501529</v>
       </c>
       <c r="S6" t="n">
-        <v>2.381642301501532</v>
+        <v>2.381642301501529</v>
       </c>
       <c r="T6" t="n">
-        <v>2.381642301501532</v>
+        <v>2.381642301501529</v>
       </c>
       <c r="U6" t="n">
-        <v>2.381642301501532</v>
+        <v>2.381642301501529</v>
       </c>
       <c r="V6" t="n">
-        <v>2.859562269668334</v>
+        <v>2.859562269668332</v>
       </c>
       <c r="W6" t="n">
-        <v>2.381642301501532</v>
+        <v>2.381642301501529</v>
       </c>
       <c r="X6" t="n">
-        <v>2.381642301501532</v>
+        <v>2.381642301501529</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.381642301501532</v>
+        <v>2.381642301501529</v>
       </c>
       <c r="Z6" t="n">
         <v>2.124881199831416</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.381642301501532</v>
+        <v>2.381642301501529</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.381642301501532</v>
+        <v>2.381642301501529</v>
       </c>
     </row>
     <row r="7">
@@ -7977,16 +7977,16 @@
         <v>10.96946407692004</v>
       </c>
       <c r="C7" t="n">
-        <v>10.96396057991086</v>
+        <v>10.96396057991085</v>
       </c>
       <c r="D7" t="n">
-        <v>10.83061274668717</v>
+        <v>10.83061274668718</v>
       </c>
       <c r="E7" t="n">
-        <v>9.948243122337709</v>
+        <v>9.948243122337708</v>
       </c>
       <c r="F7" t="n">
-        <v>11.24162551370925</v>
+        <v>11.24162551370926</v>
       </c>
       <c r="G7" t="n">
         <v>10.06864155375113</v>
@@ -8043,13 +8043,13 @@
         <v>10.12346811965426</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.883417407996015</v>
+        <v>9.883417407996017</v>
       </c>
       <c r="Z7" t="n">
         <v>10.78914676424787</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.5840964552185</v>
+        <v>10.58409645521851</v>
       </c>
       <c r="AB7" t="n">
         <v>10.27869226585961</v>
@@ -8065,55 +8065,55 @@
         <v>4.586894848999461</v>
       </c>
       <c r="C8" t="n">
-        <v>4.584963189593017</v>
+        <v>4.584963189593015</v>
       </c>
       <c r="D8" t="n">
-        <v>4.547270585723727</v>
+        <v>4.547270585723725</v>
       </c>
       <c r="E8" t="n">
-        <v>3.572157477640924</v>
+        <v>3.572157477640925</v>
       </c>
       <c r="F8" t="n">
         <v>4.663724920047894</v>
       </c>
       <c r="G8" t="n">
-        <v>4.328470139292492</v>
+        <v>4.328470139292491</v>
       </c>
       <c r="H8" t="n">
         <v>4.474269289351692</v>
       </c>
       <c r="I8" t="n">
-        <v>4.591499640621593</v>
+        <v>4.591499640621595</v>
       </c>
       <c r="J8" t="n">
-        <v>4.487410812502764</v>
+        <v>4.487410812502762</v>
       </c>
       <c r="K8" t="n">
         <v>4.568119006706765</v>
       </c>
       <c r="L8" t="n">
-        <v>4.698807609600512</v>
+        <v>4.69880760960051</v>
       </c>
       <c r="M8" t="n">
-        <v>4.56893104043379</v>
+        <v>4.568931040433789</v>
       </c>
       <c r="N8" t="n">
-        <v>4.559427955363152</v>
+        <v>4.559427955363151</v>
       </c>
       <c r="O8" t="n">
-        <v>4.602389396785052</v>
+        <v>4.602389396785049</v>
       </c>
       <c r="P8" t="n">
         <v>4.517267931502236</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.57150046436833</v>
+        <v>4.571500464368325</v>
       </c>
       <c r="R8" t="n">
         <v>4.766439645233748</v>
       </c>
       <c r="S8" t="n">
-        <v>4.646583883780985</v>
+        <v>4.646583883780986</v>
       </c>
       <c r="T8" t="n">
         <v>4.630905743365011</v>
@@ -8125,22 +8125,22 @@
         <v>4.714395103984756</v>
       </c>
       <c r="W8" t="n">
-        <v>4.41368024447769</v>
+        <v>4.413680244477685</v>
       </c>
       <c r="X8" t="n">
-        <v>4.347622271124441</v>
+        <v>4.347622271124442</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.276531391011022</v>
+        <v>4.276531391011025</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.535162307318577</v>
+        <v>4.535162307318578</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.476813940757291</v>
+        <v>4.47681394075729</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.39268826485478</v>
+        <v>4.392688264854779</v>
       </c>
     </row>
   </sheetData>
